--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_PAKH\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1A6299-79C6-4F63-A066-8AA70540CC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678A3BDE-1EE7-4046-A2A4-6611298513A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{15FDD92A-6CAD-44EB-866F-DB764FC19082}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{15FDD92A-6CAD-44EB-866F-DB764FC19082}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$216</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="523">
   <si>
     <t>Thời gian update</t>
   </si>
@@ -1634,6 +1637,55 @@
   </si>
   <si>
     <t>25/08/2026 08:02</t>
+  </si>
+  <si>
+    <t>25/08/2026 08:44</t>
+  </si>
+  <si>
+    <t>- Đã gửi hóa đơn vat và giải thích CB đóng ngắt DC khi bật tắt không có hiện tượng cho khách hiểu và đóng Ticket
+- GĐKD đã trao đổi lại với KH, Hợp đồng đã gửi lại KH, Hóa đơn sẽ hẹn lại gửi cho khách. Vấn đề KT đã cho ae kiểm tra giải thích cho KH là hệ HĐ bình thường không lỗi gì, Dự kiến đóng Ticket trc 9h ngyaf 25/8</t>
+  </si>
+  <si>
+    <t>25/08/2026 08:46</t>
+  </si>
+  <si>
+    <t>25/08/2026 08:49</t>
+  </si>
+  <si>
+    <t>25/08/2026 08:51</t>
+  </si>
+  <si>
+    <t>25/08/2026 08:52</t>
+  </si>
+  <si>
+    <t>25/08/2026 08:53</t>
+  </si>
+  <si>
+    <t>25/08/2026 08:54</t>
+  </si>
+  <si>
+    <t>25/08/2026 08:55</t>
+  </si>
+  <si>
+    <t>NGUYỄN NGỌC HUY</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thu Hương</t>
+  </si>
+  <si>
+    <t>Lê Điền</t>
+  </si>
+  <si>
+    <t>25/08/2026 08:56</t>
+  </si>
+  <si>
+    <t>25/08/2026 08:57</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Quý</t>
+  </si>
+  <si>
+    <t>Đang xử lý cho KH, dự kiến hoàn thành trước 17h</t>
   </si>
 </sst>
 </file>
@@ -8649,759 +8701,1717 @@
       </c>
       <c r="K216" s="5"/>
     </row>
-    <row r="217" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="2"/>
-      <c r="B217" s="2"/>
-      <c r="C217" s="2"/>
-      <c r="D217" s="2"/>
-      <c r="E217" s="2"/>
-      <c r="F217" s="2"/>
-      <c r="G217" s="2"/>
-      <c r="H217" s="2"/>
-      <c r="I217" s="2"/>
-      <c r="J217" s="2"/>
-      <c r="K217" s="2"/>
-    </row>
-    <row r="218" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="2"/>
-      <c r="B218" s="2"/>
-      <c r="C218" s="2"/>
-      <c r="D218" s="2"/>
-      <c r="E218" s="2"/>
-      <c r="F218" s="2"/>
-      <c r="G218" s="2"/>
-      <c r="H218" s="2"/>
-      <c r="I218" s="2"/>
-      <c r="J218" s="2"/>
-      <c r="K218" s="2"/>
-    </row>
-    <row r="219" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="2"/>
-      <c r="B219" s="2"/>
-      <c r="C219" s="2"/>
-      <c r="D219" s="2"/>
-      <c r="E219" s="2"/>
-      <c r="F219" s="2"/>
-      <c r="G219" s="2"/>
-      <c r="H219" s="2"/>
-      <c r="I219" s="2"/>
-      <c r="J219" s="2"/>
-      <c r="K219" s="2"/>
+    <row r="217" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B217" s="5"/>
+      <c r="C217" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D217" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E217" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F217" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G217" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="H217" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I217" s="3">
+        <v>63</v>
+      </c>
+      <c r="J217" s="5"/>
+      <c r="K217" s="5"/>
+    </row>
+    <row r="218" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B218" s="5"/>
+      <c r="C218" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D218" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E218" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F218" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G218" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="H218" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I218" s="3">
+        <v>34</v>
+      </c>
+      <c r="J218" s="5"/>
+      <c r="K218" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B219" s="5"/>
+      <c r="C219" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D219" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E219" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F219" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G219" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="H219" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I219" s="3">
+        <v>34</v>
+      </c>
+      <c r="J219" s="5"/>
+      <c r="K219" s="4" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="220" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="2"/>
-      <c r="B220" s="2"/>
-      <c r="C220" s="2"/>
-      <c r="D220" s="2"/>
-      <c r="E220" s="2"/>
-      <c r="F220" s="2"/>
-      <c r="G220" s="2"/>
-      <c r="H220" s="2"/>
-      <c r="I220" s="2"/>
-      <c r="J220" s="2"/>
-      <c r="K220" s="2"/>
+      <c r="A220" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B220" s="5"/>
+      <c r="C220" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D220" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E220" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F220" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G220" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="H220" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I220" s="3">
+        <v>29</v>
+      </c>
+      <c r="J220" s="5"/>
+      <c r="K220" s="4" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="221" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="2"/>
-      <c r="B221" s="2"/>
-      <c r="C221" s="2"/>
-      <c r="D221" s="2"/>
-      <c r="E221" s="2"/>
-      <c r="F221" s="2"/>
-      <c r="G221" s="2"/>
-      <c r="H221" s="2"/>
-      <c r="I221" s="2"/>
-      <c r="J221" s="2"/>
-      <c r="K221" s="2"/>
-    </row>
-    <row r="222" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="2"/>
-      <c r="B222" s="2"/>
-      <c r="C222" s="2"/>
-      <c r="D222" s="2"/>
-      <c r="E222" s="2"/>
-      <c r="F222" s="2"/>
-      <c r="G222" s="2"/>
-      <c r="H222" s="2"/>
-      <c r="I222" s="2"/>
-      <c r="J222" s="2"/>
-      <c r="K222" s="2"/>
+      <c r="A221" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B221" s="5"/>
+      <c r="C221" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E221" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F221" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G221" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="H221" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I221" s="3">
+        <v>53</v>
+      </c>
+      <c r="J221" s="5"/>
+      <c r="K221" s="5"/>
+    </row>
+    <row r="222" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B222" s="5"/>
+      <c r="C222" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D222" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E222" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F222" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G222" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="H222" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I222" s="3">
+        <v>7</v>
+      </c>
+      <c r="J222" s="5"/>
+      <c r="K222" s="5"/>
     </row>
     <row r="223" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="2"/>
-      <c r="B223" s="2"/>
-      <c r="C223" s="2"/>
-      <c r="D223" s="2"/>
-      <c r="E223" s="2"/>
-      <c r="F223" s="2"/>
-      <c r="G223" s="2"/>
-      <c r="H223" s="2"/>
-      <c r="I223" s="2"/>
-      <c r="J223" s="2"/>
-      <c r="K223" s="2"/>
+      <c r="A223" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B223" s="5"/>
+      <c r="C223" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="D223" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E223" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F223" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G223" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="H223" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I223" s="3">
+        <v>8</v>
+      </c>
+      <c r="J223" s="5"/>
+      <c r="K223" s="5"/>
     </row>
     <row r="224" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="2"/>
-      <c r="B224" s="2"/>
-      <c r="C224" s="2"/>
-      <c r="D224" s="2"/>
-      <c r="E224" s="2"/>
-      <c r="F224" s="2"/>
-      <c r="G224" s="2"/>
-      <c r="H224" s="2"/>
-      <c r="I224" s="2"/>
-      <c r="J224" s="2"/>
-      <c r="K224" s="2"/>
-    </row>
-    <row r="225" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="2"/>
-      <c r="B225" s="2"/>
-      <c r="C225" s="2"/>
-      <c r="D225" s="2"/>
-      <c r="E225" s="2"/>
-      <c r="F225" s="2"/>
-      <c r="G225" s="2"/>
-      <c r="H225" s="2"/>
-      <c r="I225" s="2"/>
-      <c r="J225" s="2"/>
-      <c r="K225" s="2"/>
-    </row>
-    <row r="226" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="2"/>
-      <c r="B226" s="2"/>
-      <c r="C226" s="2"/>
-      <c r="D226" s="2"/>
-      <c r="E226" s="2"/>
-      <c r="F226" s="2"/>
-      <c r="G226" s="2"/>
-      <c r="H226" s="2"/>
-      <c r="I226" s="2"/>
-      <c r="J226" s="2"/>
-      <c r="K226" s="2"/>
-    </row>
-    <row r="227" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="2"/>
-      <c r="B227" s="2"/>
-      <c r="C227" s="2"/>
-      <c r="D227" s="2"/>
-      <c r="E227" s="2"/>
-      <c r="F227" s="2"/>
-      <c r="G227" s="2"/>
-      <c r="H227" s="2"/>
-      <c r="I227" s="2"/>
-      <c r="J227" s="2"/>
-      <c r="K227" s="2"/>
-    </row>
-    <row r="228" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="2"/>
-      <c r="B228" s="2"/>
-      <c r="C228" s="2"/>
-      <c r="D228" s="2"/>
-      <c r="E228" s="2"/>
-      <c r="F228" s="2"/>
-      <c r="G228" s="2"/>
-      <c r="H228" s="2"/>
-      <c r="I228" s="2"/>
-      <c r="J228" s="2"/>
-      <c r="K228" s="2"/>
-    </row>
-    <row r="229" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="2"/>
-      <c r="B229" s="2"/>
-      <c r="C229" s="2"/>
-      <c r="D229" s="2"/>
-      <c r="E229" s="2"/>
-      <c r="F229" s="2"/>
-      <c r="G229" s="2"/>
-      <c r="H229" s="2"/>
-      <c r="I229" s="2"/>
-      <c r="J229" s="2"/>
-      <c r="K229" s="2"/>
+      <c r="A224" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B224" s="5"/>
+      <c r="C224" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D224" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E224" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F224" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G224" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="H224" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I224" s="3">
+        <v>12</v>
+      </c>
+      <c r="J224" s="5"/>
+      <c r="K224" s="5"/>
+    </row>
+    <row r="225" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B225" s="5"/>
+      <c r="C225" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D225" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E225" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F225" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G225" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="H225" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I225" s="3">
+        <v>15</v>
+      </c>
+      <c r="J225" s="5"/>
+      <c r="K225" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B226" s="5"/>
+      <c r="C226" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D226" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E226" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F226" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G226" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="H226" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I226" s="3">
+        <v>15</v>
+      </c>
+      <c r="J226" s="5"/>
+      <c r="K226" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B227" s="5"/>
+      <c r="C227" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D227" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E227" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G227" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="H227" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I227" s="3">
+        <v>18</v>
+      </c>
+      <c r="J227" s="5"/>
+      <c r="K227" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B228" s="5"/>
+      <c r="C228" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D228" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E228" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F228" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G228" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H228" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I228" s="3">
+        <v>22</v>
+      </c>
+      <c r="J228" s="5"/>
+      <c r="K228" s="5"/>
+    </row>
+    <row r="229" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B229" s="5"/>
+      <c r="C229" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D229" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E229" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F229" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G229" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="H229" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I229" s="3">
+        <v>23</v>
+      </c>
+      <c r="J229" s="5"/>
+      <c r="K229" s="5"/>
     </row>
     <row r="230" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="2"/>
-      <c r="B230" s="2"/>
-      <c r="C230" s="2"/>
-      <c r="D230" s="2"/>
-      <c r="E230" s="2"/>
-      <c r="F230" s="2"/>
-      <c r="G230" s="2"/>
-      <c r="H230" s="2"/>
-      <c r="I230" s="2"/>
-      <c r="J230" s="2"/>
-      <c r="K230" s="2"/>
-    </row>
-    <row r="231" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="2"/>
-      <c r="B231" s="2"/>
-      <c r="C231" s="2"/>
-      <c r="D231" s="2"/>
-      <c r="E231" s="2"/>
-      <c r="F231" s="2"/>
-      <c r="G231" s="2"/>
-      <c r="H231" s="2"/>
-      <c r="I231" s="2"/>
-      <c r="J231" s="2"/>
-      <c r="K231" s="2"/>
-    </row>
-    <row r="232" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="2"/>
-      <c r="B232" s="2"/>
-      <c r="C232" s="2"/>
-      <c r="D232" s="2"/>
-      <c r="E232" s="2"/>
-      <c r="F232" s="2"/>
-      <c r="G232" s="2"/>
-      <c r="H232" s="2"/>
-      <c r="I232" s="2"/>
-      <c r="J232" s="2"/>
-      <c r="K232" s="2"/>
-    </row>
-    <row r="233" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="2"/>
-      <c r="B233" s="2"/>
-      <c r="C233" s="2"/>
-      <c r="D233" s="2"/>
-      <c r="E233" s="2"/>
-      <c r="F233" s="2"/>
-      <c r="G233" s="2"/>
-      <c r="H233" s="2"/>
-      <c r="I233" s="2"/>
-      <c r="J233" s="2"/>
-      <c r="K233" s="2"/>
-    </row>
-    <row r="234" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="2"/>
-      <c r="B234" s="2"/>
-      <c r="C234" s="2"/>
-      <c r="D234" s="2"/>
-      <c r="E234" s="2"/>
-      <c r="F234" s="2"/>
-      <c r="G234" s="2"/>
-      <c r="H234" s="2"/>
-      <c r="I234" s="2"/>
-      <c r="J234" s="2"/>
-      <c r="K234" s="2"/>
-    </row>
-    <row r="235" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="2"/>
-      <c r="B235" s="2"/>
-      <c r="C235" s="2"/>
-      <c r="D235" s="2"/>
-      <c r="E235" s="2"/>
-      <c r="F235" s="2"/>
-      <c r="G235" s="2"/>
-      <c r="H235" s="2"/>
-      <c r="I235" s="2"/>
-      <c r="J235" s="2"/>
-      <c r="K235" s="2"/>
-    </row>
-    <row r="236" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="2"/>
-      <c r="B236" s="2"/>
-      <c r="C236" s="2"/>
-      <c r="D236" s="2"/>
-      <c r="E236" s="2"/>
-      <c r="F236" s="2"/>
-      <c r="G236" s="2"/>
-      <c r="H236" s="2"/>
-      <c r="I236" s="2"/>
-      <c r="J236" s="2"/>
-      <c r="K236" s="2"/>
+      <c r="A230" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B230" s="5"/>
+      <c r="C230" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D230" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E230" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F230" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G230" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="H230" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I230" s="3">
+        <v>29</v>
+      </c>
+      <c r="J230" s="5"/>
+      <c r="K230" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B231" s="5"/>
+      <c r="C231" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E231" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F231" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G231" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="H231" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I231" s="3">
+        <v>31</v>
+      </c>
+      <c r="J231" s="5"/>
+      <c r="K231" s="5"/>
+    </row>
+    <row r="232" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B232" s="5"/>
+      <c r="C232" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D232" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E232" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F232" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G232" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="H232" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I232" s="3">
+        <v>33</v>
+      </c>
+      <c r="J232" s="5"/>
+      <c r="K232" s="5"/>
+    </row>
+    <row r="233" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B233" s="5"/>
+      <c r="C233" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D233" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E233" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F233" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G233" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="H233" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I233" s="3">
+        <v>35</v>
+      </c>
+      <c r="J233" s="5"/>
+      <c r="K233" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B234" s="5"/>
+      <c r="C234" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D234" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E234" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F234" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G234" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="H234" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I234" s="3">
+        <v>36</v>
+      </c>
+      <c r="J234" s="5"/>
+      <c r="K234" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B235" s="5"/>
+      <c r="C235" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D235" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E235" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F235" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G235" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="H235" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I235" s="3">
+        <v>37</v>
+      </c>
+      <c r="J235" s="5"/>
+      <c r="K235" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B236" s="5"/>
+      <c r="C236" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D236" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E236" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F236" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G236" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="H236" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I236" s="3">
+        <v>38</v>
+      </c>
+      <c r="J236" s="5"/>
+      <c r="K236" s="4" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="237" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="2"/>
-      <c r="B237" s="2"/>
-      <c r="C237" s="2"/>
-      <c r="D237" s="2"/>
-      <c r="E237" s="2"/>
-      <c r="F237" s="2"/>
-      <c r="G237" s="2"/>
-      <c r="H237" s="2"/>
-      <c r="I237" s="2"/>
-      <c r="J237" s="2"/>
-      <c r="K237" s="2"/>
-    </row>
-    <row r="238" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="2"/>
-      <c r="B238" s="2"/>
-      <c r="C238" s="2"/>
-      <c r="D238" s="2"/>
-      <c r="E238" s="2"/>
-      <c r="F238" s="2"/>
-      <c r="G238" s="2"/>
-      <c r="H238" s="2"/>
-      <c r="I238" s="2"/>
-      <c r="J238" s="2"/>
-      <c r="K238" s="2"/>
-    </row>
-    <row r="239" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="2"/>
-      <c r="B239" s="2"/>
-      <c r="C239" s="2"/>
-      <c r="D239" s="2"/>
-      <c r="E239" s="2"/>
-      <c r="F239" s="2"/>
-      <c r="G239" s="2"/>
-      <c r="H239" s="2"/>
-      <c r="I239" s="2"/>
-      <c r="J239" s="2"/>
-      <c r="K239" s="2"/>
-    </row>
-    <row r="240" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="2"/>
-      <c r="B240" s="2"/>
-      <c r="C240" s="2"/>
-      <c r="D240" s="2"/>
-      <c r="E240" s="2"/>
-      <c r="F240" s="2"/>
-      <c r="G240" s="2"/>
-      <c r="H240" s="2"/>
-      <c r="I240" s="2"/>
-      <c r="J240" s="2"/>
-      <c r="K240" s="2"/>
-    </row>
-    <row r="241" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="2"/>
-      <c r="B241" s="2"/>
-      <c r="C241" s="2"/>
-      <c r="D241" s="2"/>
-      <c r="E241" s="2"/>
-      <c r="F241" s="2"/>
-      <c r="G241" s="2"/>
-      <c r="H241" s="2"/>
-      <c r="I241" s="2"/>
-      <c r="J241" s="2"/>
-      <c r="K241" s="2"/>
+      <c r="A237" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B237" s="5"/>
+      <c r="C237" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D237" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E237" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G237" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="H237" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I237" s="3">
+        <v>40</v>
+      </c>
+      <c r="J237" s="5"/>
+      <c r="K237" s="5"/>
+    </row>
+    <row r="238" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A238" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B238" s="5"/>
+      <c r="C238" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D238" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E238" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G238" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="H238" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I238" s="3">
+        <v>41</v>
+      </c>
+      <c r="J238" s="5"/>
+      <c r="K238" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B239" s="5"/>
+      <c r="C239" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D239" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E239" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F239" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G239" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="H239" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I239" s="3">
+        <v>41</v>
+      </c>
+      <c r="J239" s="5"/>
+      <c r="K239" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B240" s="5"/>
+      <c r="C240" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="D240" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E240" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F240" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G240" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="H240" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I240" s="3">
+        <v>42</v>
+      </c>
+      <c r="J240" s="5"/>
+      <c r="K240" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B241" s="5"/>
+      <c r="C241" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="D241" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E241" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G241" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="H241" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I241" s="3">
+        <v>43</v>
+      </c>
+      <c r="J241" s="5"/>
+      <c r="K241" s="4" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="242" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="2"/>
-      <c r="B242" s="2"/>
-      <c r="C242" s="2"/>
-      <c r="D242" s="2"/>
-      <c r="E242" s="2"/>
-      <c r="F242" s="2"/>
-      <c r="G242" s="2"/>
-      <c r="H242" s="2"/>
-      <c r="I242" s="2"/>
-      <c r="J242" s="2"/>
-      <c r="K242" s="2"/>
-    </row>
-    <row r="243" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="2"/>
-      <c r="B243" s="2"/>
-      <c r="C243" s="2"/>
-      <c r="D243" s="2"/>
-      <c r="E243" s="2"/>
-      <c r="F243" s="2"/>
-      <c r="G243" s="2"/>
-      <c r="H243" s="2"/>
-      <c r="I243" s="2"/>
-      <c r="J243" s="2"/>
-      <c r="K243" s="2"/>
-    </row>
-    <row r="244" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="2"/>
-      <c r="B244" s="2"/>
-      <c r="C244" s="2"/>
-      <c r="D244" s="2"/>
-      <c r="E244" s="2"/>
-      <c r="F244" s="2"/>
-      <c r="G244" s="2"/>
-      <c r="H244" s="2"/>
-      <c r="I244" s="2"/>
-      <c r="J244" s="2"/>
-      <c r="K244" s="2"/>
-    </row>
-    <row r="245" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="2"/>
-      <c r="B245" s="2"/>
-      <c r="C245" s="2"/>
-      <c r="D245" s="2"/>
-      <c r="E245" s="2"/>
-      <c r="F245" s="2"/>
-      <c r="G245" s="2"/>
-      <c r="H245" s="2"/>
-      <c r="I245" s="2"/>
-      <c r="J245" s="2"/>
-      <c r="K245" s="2"/>
+      <c r="A242" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B242" s="5"/>
+      <c r="C242" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D242" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E242" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G242" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="H242" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I242" s="3">
+        <v>44</v>
+      </c>
+      <c r="J242" s="5"/>
+      <c r="K242" s="5"/>
+    </row>
+    <row r="243" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B243" s="5"/>
+      <c r="C243" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D243" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E243" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F243" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G243" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="H243" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I243" s="3">
+        <v>48</v>
+      </c>
+      <c r="J243" s="5"/>
+      <c r="K243" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B244" s="5"/>
+      <c r="C244" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D244" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E244" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F244" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G244" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="H244" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I244" s="3">
+        <v>56</v>
+      </c>
+      <c r="J244" s="5"/>
+      <c r="K244" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B245" s="5"/>
+      <c r="C245" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D245" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E245" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G245" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="H245" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I245" s="3">
+        <v>63</v>
+      </c>
+      <c r="J245" s="5"/>
+      <c r="K245" s="5"/>
     </row>
     <row r="246" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="2"/>
-      <c r="B246" s="2"/>
-      <c r="C246" s="2"/>
-      <c r="D246" s="2"/>
-      <c r="E246" s="2"/>
-      <c r="F246" s="2"/>
-      <c r="G246" s="2"/>
-      <c r="H246" s="2"/>
-      <c r="I246" s="2"/>
-      <c r="J246" s="2"/>
-      <c r="K246" s="2"/>
+      <c r="A246" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B246" s="5"/>
+      <c r="C246" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="D246" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="E246" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F246" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G246" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="H246" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I246" s="3">
+        <v>64</v>
+      </c>
+      <c r="J246" s="5"/>
+      <c r="K246" s="5"/>
     </row>
     <row r="247" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="2"/>
-      <c r="B247" s="2"/>
-      <c r="C247" s="2"/>
-      <c r="D247" s="2"/>
-      <c r="E247" s="2"/>
-      <c r="F247" s="2"/>
-      <c r="G247" s="2"/>
-      <c r="H247" s="2"/>
-      <c r="I247" s="2"/>
-      <c r="J247" s="2"/>
-      <c r="K247" s="2"/>
+      <c r="A247" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B247" s="5"/>
+      <c r="C247" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="D247" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E247" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G247" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="H247" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I247" s="3">
+        <v>71</v>
+      </c>
+      <c r="J247" s="5"/>
+      <c r="K247" s="5"/>
     </row>
     <row r="248" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="2"/>
-      <c r="B248" s="2"/>
-      <c r="C248" s="2"/>
-      <c r="D248" s="2"/>
-      <c r="E248" s="2"/>
-      <c r="F248" s="2"/>
-      <c r="G248" s="2"/>
-      <c r="H248" s="2"/>
-      <c r="I248" s="2"/>
-      <c r="J248" s="2"/>
-      <c r="K248" s="2"/>
+      <c r="A248" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B248" s="5"/>
+      <c r="C248" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D248" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E248" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F248" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G248" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="H248" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I248" s="3">
+        <v>73</v>
+      </c>
+      <c r="J248" s="5"/>
+      <c r="K248" s="5"/>
     </row>
     <row r="249" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="2"/>
-      <c r="B249" s="2"/>
-      <c r="C249" s="2"/>
-      <c r="D249" s="2"/>
-      <c r="E249" s="2"/>
-      <c r="F249" s="2"/>
-      <c r="G249" s="2"/>
-      <c r="H249" s="2"/>
-      <c r="I249" s="2"/>
-      <c r="J249" s="2"/>
-      <c r="K249" s="2"/>
+      <c r="A249" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B249" s="5"/>
+      <c r="C249" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D249" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E249" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G249" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="H249" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I249" s="3">
+        <v>75</v>
+      </c>
+      <c r="J249" s="5"/>
+      <c r="K249" s="5"/>
     </row>
     <row r="250" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="2"/>
-      <c r="B250" s="2"/>
-      <c r="C250" s="2"/>
-      <c r="D250" s="2"/>
-      <c r="E250" s="2"/>
-      <c r="F250" s="2"/>
-      <c r="G250" s="2"/>
-      <c r="H250" s="2"/>
-      <c r="I250" s="2"/>
-      <c r="J250" s="2"/>
-      <c r="K250" s="2"/>
+      <c r="A250" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B250" s="5"/>
+      <c r="C250" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D250" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E250" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F250" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G250" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="H250" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I250" s="3">
+        <v>76</v>
+      </c>
+      <c r="J250" s="5"/>
+      <c r="K250" s="5"/>
     </row>
     <row r="251" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="2"/>
-      <c r="B251" s="2"/>
-      <c r="C251" s="2"/>
-      <c r="D251" s="2"/>
-      <c r="E251" s="2"/>
-      <c r="F251" s="2"/>
-      <c r="G251" s="2"/>
-      <c r="H251" s="2"/>
-      <c r="I251" s="2"/>
-      <c r="J251" s="2"/>
-      <c r="K251" s="2"/>
+      <c r="A251" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B251" s="5"/>
+      <c r="C251" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E251" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G251" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="H251" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I251" s="3">
+        <v>79</v>
+      </c>
+      <c r="J251" s="5"/>
+      <c r="K251" s="5"/>
     </row>
     <row r="252" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="2"/>
-      <c r="B252" s="2"/>
-      <c r="C252" s="2"/>
-      <c r="D252" s="2"/>
-      <c r="E252" s="2"/>
-      <c r="F252" s="2"/>
-      <c r="G252" s="2"/>
-      <c r="H252" s="2"/>
-      <c r="I252" s="2"/>
-      <c r="J252" s="2"/>
-      <c r="K252" s="2"/>
-    </row>
-    <row r="253" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="2"/>
-      <c r="B253" s="2"/>
-      <c r="C253" s="2"/>
-      <c r="D253" s="2"/>
-      <c r="E253" s="2"/>
-      <c r="F253" s="2"/>
-      <c r="G253" s="2"/>
-      <c r="H253" s="2"/>
-      <c r="I253" s="2"/>
-      <c r="J253" s="2"/>
-      <c r="K253" s="2"/>
+      <c r="A252" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B252" s="5"/>
+      <c r="C252" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="D252" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E252" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F252" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G252" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="H252" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I252" s="3">
+        <v>85</v>
+      </c>
+      <c r="J252" s="5"/>
+      <c r="K252" s="5"/>
+    </row>
+    <row r="253" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B253" s="5"/>
+      <c r="C253" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D253" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E253" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F253" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G253" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="H253" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I253" s="3">
+        <v>101</v>
+      </c>
+      <c r="J253" s="5"/>
+      <c r="K253" s="5"/>
     </row>
     <row r="254" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="2"/>
-      <c r="B254" s="2"/>
-      <c r="C254" s="2"/>
-      <c r="D254" s="2"/>
-      <c r="E254" s="2"/>
-      <c r="F254" s="2"/>
-      <c r="G254" s="2"/>
-      <c r="H254" s="2"/>
-      <c r="I254" s="2"/>
-      <c r="J254" s="2"/>
-      <c r="K254" s="2"/>
+      <c r="A254" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B254" s="5"/>
+      <c r="C254" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="D254" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E254" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G254" s="5"/>
+      <c r="H254" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I254" s="3">
+        <v>108</v>
+      </c>
+      <c r="J254" s="5"/>
+      <c r="K254" s="5"/>
     </row>
     <row r="255" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="2"/>
-      <c r="B255" s="2"/>
-      <c r="C255" s="2"/>
-      <c r="D255" s="2"/>
-      <c r="E255" s="2"/>
-      <c r="F255" s="2"/>
-      <c r="G255" s="2"/>
-      <c r="H255" s="2"/>
-      <c r="I255" s="2"/>
-      <c r="J255" s="2"/>
-      <c r="K255" s="2"/>
+      <c r="A255" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B255" s="5"/>
+      <c r="C255" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="D255" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E255" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F255" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G255" s="5"/>
+      <c r="H255" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I255" s="3">
+        <v>109</v>
+      </c>
+      <c r="J255" s="5"/>
+      <c r="K255" s="5"/>
     </row>
     <row r="256" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="2"/>
-      <c r="B256" s="2"/>
-      <c r="C256" s="2"/>
-      <c r="D256" s="2"/>
-      <c r="E256" s="2"/>
-      <c r="F256" s="2"/>
-      <c r="G256" s="2"/>
-      <c r="H256" s="2"/>
-      <c r="I256" s="2"/>
-      <c r="J256" s="2"/>
-      <c r="K256" s="2"/>
-    </row>
-    <row r="257" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="2"/>
-      <c r="B257" s="2"/>
-      <c r="C257" s="2"/>
-      <c r="D257" s="2"/>
-      <c r="E257" s="2"/>
-      <c r="F257" s="2"/>
-      <c r="G257" s="2"/>
-      <c r="H257" s="2"/>
-      <c r="I257" s="2"/>
-      <c r="J257" s="2"/>
-      <c r="K257" s="2"/>
+      <c r="A256" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B256" s="5"/>
+      <c r="C256" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="D256" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E256" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F256" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G256" s="5"/>
+      <c r="H256" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I256" s="3">
+        <v>111</v>
+      </c>
+      <c r="J256" s="5"/>
+      <c r="K256" s="5"/>
+    </row>
+    <row r="257" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D257" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E257" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F257" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G257" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="H257" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I257" s="3">
+        <v>59</v>
+      </c>
+      <c r="J257" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K257" s="5"/>
     </row>
     <row r="258" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="2"/>
-      <c r="B258" s="2"/>
-      <c r="C258" s="2"/>
-      <c r="D258" s="2"/>
-      <c r="E258" s="2"/>
-      <c r="F258" s="2"/>
-      <c r="G258" s="2"/>
-      <c r="H258" s="2"/>
-      <c r="I258" s="2"/>
-      <c r="J258" s="2"/>
-      <c r="K258" s="2"/>
+      <c r="A258" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B258" s="5"/>
+      <c r="C258" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D258" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E258" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F258" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G258" s="5"/>
+      <c r="H258" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I258" s="3">
+        <v>2</v>
+      </c>
+      <c r="J258" s="5"/>
+      <c r="K258" s="5"/>
     </row>
     <row r="259" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="2"/>
-      <c r="B259" s="2"/>
-      <c r="C259" s="2"/>
-      <c r="D259" s="2"/>
-      <c r="E259" s="2"/>
-      <c r="F259" s="2"/>
-      <c r="G259" s="2"/>
-      <c r="H259" s="2"/>
-      <c r="I259" s="2"/>
-      <c r="J259" s="2"/>
-      <c r="K259" s="2"/>
-    </row>
-    <row r="260" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="2"/>
-      <c r="B260" s="2"/>
-      <c r="C260" s="2"/>
-      <c r="D260" s="2"/>
-      <c r="E260" s="2"/>
-      <c r="F260" s="2"/>
-      <c r="G260" s="2"/>
-      <c r="H260" s="2"/>
-      <c r="I260" s="2"/>
-      <c r="J260" s="2"/>
-      <c r="K260" s="2"/>
-    </row>
-    <row r="261" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="2"/>
-      <c r="B261" s="2"/>
-      <c r="C261" s="2"/>
-      <c r="D261" s="2"/>
-      <c r="E261" s="2"/>
-      <c r="F261" s="2"/>
-      <c r="G261" s="2"/>
-      <c r="H261" s="2"/>
-      <c r="I261" s="2"/>
-      <c r="J261" s="2"/>
-      <c r="K261" s="2"/>
+      <c r="A259" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B259" s="5"/>
+      <c r="C259" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D259" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E259" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F259" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G259" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="H259" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I259" s="3">
+        <v>21</v>
+      </c>
+      <c r="J259" s="5"/>
+      <c r="K259" s="5"/>
+    </row>
+    <row r="260" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B260" s="5"/>
+      <c r="C260" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D260" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E260" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F260" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G260" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="H260" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I260" s="3">
+        <v>25</v>
+      </c>
+      <c r="J260" s="5"/>
+      <c r="K260" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B261" s="5"/>
+      <c r="C261" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D261" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E261" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F261" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G261" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="H261" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I261" s="3">
+        <v>28</v>
+      </c>
+      <c r="J261" s="5"/>
+      <c r="K261" s="5"/>
     </row>
     <row r="262" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="2"/>
-      <c r="B262" s="2"/>
-      <c r="C262" s="2"/>
-      <c r="D262" s="2"/>
-      <c r="E262" s="2"/>
-      <c r="F262" s="2"/>
-      <c r="G262" s="2"/>
-      <c r="H262" s="2"/>
-      <c r="I262" s="2"/>
-      <c r="J262" s="2"/>
-      <c r="K262" s="2"/>
-    </row>
-    <row r="263" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="2"/>
-      <c r="B263" s="2"/>
-      <c r="C263" s="2"/>
-      <c r="D263" s="2"/>
-      <c r="E263" s="2"/>
-      <c r="F263" s="2"/>
-      <c r="G263" s="2"/>
-      <c r="H263" s="2"/>
-      <c r="I263" s="2"/>
-      <c r="J263" s="2"/>
-      <c r="K263" s="2"/>
+      <c r="A262" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B262" s="5"/>
+      <c r="C262" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D262" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E262" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F262" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G262" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="H262" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I262" s="3">
+        <v>47</v>
+      </c>
+      <c r="J262" s="5"/>
+      <c r="K262" s="5"/>
+    </row>
+    <row r="263" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A263" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B263" s="5"/>
+      <c r="C263" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D263" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E263" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F263" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G263" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="H263" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I263" s="3">
+        <v>61</v>
+      </c>
+      <c r="J263" s="5"/>
+      <c r="K263" s="5"/>
     </row>
     <row r="264" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A264" s="2"/>
-      <c r="B264" s="2"/>
-      <c r="C264" s="2"/>
-      <c r="D264" s="2"/>
-      <c r="E264" s="2"/>
-      <c r="F264" s="2"/>
-      <c r="G264" s="2"/>
-      <c r="H264" s="2"/>
-      <c r="I264" s="2"/>
-      <c r="J264" s="2"/>
-      <c r="K264" s="2"/>
-    </row>
-    <row r="265" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="2"/>
-      <c r="B265" s="2"/>
-      <c r="C265" s="2"/>
-      <c r="D265" s="2"/>
-      <c r="E265" s="2"/>
-      <c r="F265" s="2"/>
-      <c r="G265" s="2"/>
-      <c r="H265" s="2"/>
-      <c r="I265" s="2"/>
-      <c r="J265" s="2"/>
-      <c r="K265" s="2"/>
+      <c r="A264" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B264" s="5"/>
+      <c r="C264" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D264" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E264" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F264" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G264" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="H264" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I264" s="3">
+        <v>68</v>
+      </c>
+      <c r="J264" s="5"/>
+      <c r="K264" s="5"/>
+    </row>
+    <row r="265" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A265" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B265" s="5"/>
+      <c r="C265" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="D265" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E265" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F265" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G265" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="H265" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I265" s="3">
+        <v>69</v>
+      </c>
+      <c r="J265" s="5"/>
+      <c r="K265" s="5"/>
     </row>
     <row r="266" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="2"/>
-      <c r="B266" s="2"/>
-      <c r="C266" s="2"/>
-      <c r="D266" s="2"/>
-      <c r="E266" s="2"/>
-      <c r="F266" s="2"/>
-      <c r="G266" s="2"/>
-      <c r="H266" s="2"/>
-      <c r="I266" s="2"/>
-      <c r="J266" s="2"/>
-      <c r="K266" s="2"/>
+      <c r="A266" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B266" s="5"/>
+      <c r="C266" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D266" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E266" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F266" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G266" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="H266" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I266" s="3">
+        <v>83</v>
+      </c>
+      <c r="J266" s="5"/>
+      <c r="K266" s="5"/>
     </row>
     <row r="267" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="2"/>
-      <c r="B267" s="2"/>
-      <c r="C267" s="2"/>
-      <c r="D267" s="2"/>
-      <c r="E267" s="2"/>
-      <c r="F267" s="2"/>
-      <c r="G267" s="2"/>
-      <c r="H267" s="2"/>
-      <c r="I267" s="2"/>
-      <c r="J267" s="2"/>
-      <c r="K267" s="2"/>
+      <c r="A267" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B267" s="5"/>
+      <c r="C267" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="D267" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E267" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F267" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G267" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="H267" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I267" s="3">
+        <v>83</v>
+      </c>
+      <c r="J267" s="5"/>
+      <c r="K267" s="5"/>
     </row>
     <row r="268" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="2"/>
-      <c r="B268" s="2"/>
-      <c r="C268" s="2"/>
-      <c r="D268" s="2"/>
-      <c r="E268" s="2"/>
-      <c r="F268" s="2"/>
-      <c r="G268" s="2"/>
-      <c r="H268" s="2"/>
-      <c r="I268" s="2"/>
-      <c r="J268" s="2"/>
-      <c r="K268" s="2"/>
+      <c r="A268" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B268" s="5"/>
+      <c r="C268" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="D268" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E268" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F268" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G268" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="H268" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I268" s="3">
+        <v>86</v>
+      </c>
+      <c r="J268" s="5"/>
+      <c r="K268" s="5"/>
     </row>
     <row r="269" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="2"/>
-      <c r="B269" s="2"/>
-      <c r="C269" s="2"/>
-      <c r="D269" s="2"/>
-      <c r="E269" s="2"/>
-      <c r="F269" s="2"/>
-      <c r="G269" s="2"/>
-      <c r="H269" s="2"/>
-      <c r="I269" s="2"/>
-      <c r="J269" s="2"/>
-      <c r="K269" s="2"/>
+      <c r="A269" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B269" s="5"/>
+      <c r="C269" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="D269" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E269" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F269" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G269" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="H269" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I269" s="3">
+        <v>87</v>
+      </c>
+      <c r="J269" s="5"/>
+      <c r="K269" s="5"/>
     </row>
     <row r="270" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A270" s="2"/>
-      <c r="B270" s="2"/>
-      <c r="C270" s="2"/>
-      <c r="D270" s="2"/>
-      <c r="E270" s="2"/>
-      <c r="F270" s="2"/>
-      <c r="G270" s="2"/>
-      <c r="H270" s="2"/>
-      <c r="I270" s="2"/>
-      <c r="J270" s="2"/>
-      <c r="K270" s="2"/>
-    </row>
-    <row r="271" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="2"/>
-      <c r="B271" s="2"/>
-      <c r="C271" s="2"/>
-      <c r="D271" s="2"/>
-      <c r="E271" s="2"/>
-      <c r="F271" s="2"/>
-      <c r="G271" s="2"/>
-      <c r="H271" s="2"/>
-      <c r="I271" s="2"/>
-      <c r="J271" s="2"/>
-      <c r="K271" s="2"/>
+      <c r="A270" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B270" s="5"/>
+      <c r="C270" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D270" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E270" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F270" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G270" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="H270" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I270" s="3">
+        <v>88</v>
+      </c>
+      <c r="J270" s="5"/>
+      <c r="K270" s="5"/>
+    </row>
+    <row r="271" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A271" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B271" s="5"/>
+      <c r="C271" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="D271" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E271" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F271" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G271" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="H271" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I271" s="3">
+        <v>93</v>
+      </c>
+      <c r="J271" s="5"/>
+      <c r="K271" s="5"/>
     </row>
     <row r="272" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="2"/>
-      <c r="B272" s="2"/>
-      <c r="C272" s="2"/>
-      <c r="D272" s="2"/>
-      <c r="E272" s="2"/>
-      <c r="F272" s="2"/>
-      <c r="G272" s="2"/>
-      <c r="H272" s="2"/>
-      <c r="I272" s="2"/>
-      <c r="J272" s="2"/>
-      <c r="K272" s="2"/>
+      <c r="A272" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B272" s="5"/>
+      <c r="C272" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D272" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E272" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F272" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G272" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="H272" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I272" s="3">
+        <v>96</v>
+      </c>
+      <c r="J272" s="5"/>
+      <c r="K272" s="5"/>
     </row>
     <row r="273" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="2"/>
-      <c r="B273" s="2"/>
-      <c r="C273" s="2"/>
-      <c r="D273" s="2"/>
-      <c r="E273" s="2"/>
-      <c r="F273" s="2"/>
-      <c r="G273" s="2"/>
-      <c r="H273" s="2"/>
-      <c r="I273" s="2"/>
-      <c r="J273" s="2"/>
-      <c r="K273" s="2"/>
+      <c r="A273" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B273" s="5"/>
+      <c r="C273" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="D273" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E273" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F273" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G273" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="H273" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I273" s="3">
+        <v>112</v>
+      </c>
+      <c r="J273" s="5"/>
+      <c r="K273" s="5"/>
     </row>
     <row r="274" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="2"/>
-      <c r="B274" s="2"/>
-      <c r="C274" s="2"/>
-      <c r="D274" s="2"/>
-      <c r="E274" s="2"/>
-      <c r="F274" s="2"/>
-      <c r="G274" s="2"/>
-      <c r="H274" s="2"/>
-      <c r="I274" s="2"/>
-      <c r="J274" s="2"/>
-      <c r="K274" s="2"/>
+      <c r="A274" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B274" s="5"/>
+      <c r="C274" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="D274" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E274" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="F274" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G274" s="5"/>
+      <c r="H274" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="I274" s="3">
+        <v>112</v>
+      </c>
+      <c r="J274" s="5"/>
+      <c r="K274" s="5"/>
     </row>
     <row r="275" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="2"/>
@@ -18829,6 +19839,8 @@
       <c r="K999" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K216" xr:uid="{271A8CFB-3293-473B-894F-86B249B2B19B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_PAKH\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678A3BDE-1EE7-4046-A2A4-6611298513A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBADA33-15A7-4844-A07D-81EDEC064845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{15FDD92A-6CAD-44EB-866F-DB764FC19082}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$274</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2097,6 +2097,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{271A8CFB-3293-473B-894F-86B249B2B19B}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K999"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2148,7 +2149,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -2181,7 +2182,7 @@
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
@@ -2214,7 +2215,7 @@
       </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
@@ -2247,7 +2248,7 @@
       </c>
       <c r="K4" s="5"/>
     </row>
-    <row r="5" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
@@ -2278,7 +2279,7 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
@@ -2307,7 +2308,7 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
@@ -2336,7 +2337,7 @@
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
@@ -2367,7 +2368,7 @@
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>36</v>
       </c>
@@ -2398,7 +2399,7 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
@@ -2429,7 +2430,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
@@ -2460,7 +2461,7 @@
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>47</v>
       </c>
@@ -2491,7 +2492,7 @@
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>52</v>
       </c>
@@ -2522,7 +2523,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>56</v>
       </c>
@@ -2553,7 +2554,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>59</v>
       </c>
@@ -2584,7 +2585,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>63</v>
       </c>
@@ -2615,7 +2616,7 @@
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>66</v>
       </c>
@@ -2646,7 +2647,7 @@
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>71</v>
       </c>
@@ -2677,7 +2678,7 @@
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>75</v>
       </c>
@@ -2708,7 +2709,7 @@
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>79</v>
       </c>
@@ -2739,7 +2740,7 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>82</v>
       </c>
@@ -2770,7 +2771,7 @@
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
     </row>
-    <row r="22" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>85</v>
       </c>
@@ -2801,7 +2802,7 @@
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
     </row>
-    <row r="23" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>88</v>
       </c>
@@ -2832,7 +2833,7 @@
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
     </row>
-    <row r="24" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>92</v>
       </c>
@@ -2863,7 +2864,7 @@
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
     </row>
-    <row r="25" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>92</v>
       </c>
@@ -2894,7 +2895,7 @@
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
     </row>
-    <row r="26" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>96</v>
       </c>
@@ -2923,7 +2924,7 @@
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
     </row>
-    <row r="27" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>98</v>
       </c>
@@ -2954,7 +2955,7 @@
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
     </row>
-    <row r="28" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>102</v>
       </c>
@@ -2985,7 +2986,7 @@
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>106</v>
       </c>
@@ -3014,7 +3015,7 @@
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
     </row>
-    <row r="30" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>108</v>
       </c>
@@ -3043,7 +3044,7 @@
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
     </row>
-    <row r="31" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>110</v>
       </c>
@@ -3074,7 +3075,7 @@
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
     </row>
-    <row r="32" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>113</v>
       </c>
@@ -3105,7 +3106,7 @@
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
     </row>
-    <row r="33" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>113</v>
       </c>
@@ -3134,7 +3135,7 @@
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
     </row>
-    <row r="34" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>116</v>
       </c>
@@ -3165,7 +3166,7 @@
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
     </row>
-    <row r="35" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>119</v>
       </c>
@@ -3196,7 +3197,7 @@
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
     </row>
-    <row r="36" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>122</v>
       </c>
@@ -3227,7 +3228,7 @@
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
     </row>
-    <row r="37" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>125</v>
       </c>
@@ -3258,7 +3259,7 @@
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
     </row>
-    <row r="38" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>128</v>
       </c>
@@ -3289,7 +3290,7 @@
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
     </row>
-    <row r="39" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>131</v>
       </c>
@@ -3318,7 +3319,7 @@
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
     </row>
-    <row r="40" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>133</v>
       </c>
@@ -3347,7 +3348,7 @@
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
     </row>
-    <row r="41" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>133</v>
       </c>
@@ -3376,7 +3377,7 @@
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
     </row>
-    <row r="42" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>137</v>
       </c>
@@ -3407,7 +3408,7 @@
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
     </row>
-    <row r="43" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>140</v>
       </c>
@@ -3438,7 +3439,7 @@
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
     </row>
-    <row r="44" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>143</v>
       </c>
@@ -3469,7 +3470,7 @@
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
     </row>
-    <row r="45" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>146</v>
       </c>
@@ -3500,7 +3501,7 @@
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
     </row>
-    <row r="46" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>149</v>
       </c>
@@ -3531,7 +3532,7 @@
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
     </row>
-    <row r="47" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>149</v>
       </c>
@@ -3560,7 +3561,7 @@
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
     </row>
-    <row r="48" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>151</v>
       </c>
@@ -3593,7 +3594,7 @@
       </c>
       <c r="K48" s="5"/>
     </row>
-    <row r="49" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>154</v>
       </c>
@@ -3626,7 +3627,7 @@
       </c>
       <c r="K49" s="5"/>
     </row>
-    <row r="50" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>157</v>
       </c>
@@ -3657,7 +3658,7 @@
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
     </row>
-    <row r="51" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>160</v>
       </c>
@@ -3690,7 +3691,7 @@
       </c>
       <c r="K51" s="5"/>
     </row>
-    <row r="52" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>163</v>
       </c>
@@ -3723,7 +3724,7 @@
       </c>
       <c r="K52" s="5"/>
     </row>
-    <row r="53" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>167</v>
       </c>
@@ -3752,7 +3753,7 @@
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
     </row>
-    <row r="54" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>170</v>
       </c>
@@ -3783,7 +3784,7 @@
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
     </row>
-    <row r="55" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>173</v>
       </c>
@@ -3814,7 +3815,7 @@
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
     </row>
-    <row r="56" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>175</v>
       </c>
@@ -3845,7 +3846,7 @@
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
     </row>
-    <row r="57" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>179</v>
       </c>
@@ -3874,7 +3875,7 @@
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
     </row>
-    <row r="58" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>180</v>
       </c>
@@ -3903,7 +3904,7 @@
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
     </row>
-    <row r="59" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>182</v>
       </c>
@@ -3936,7 +3937,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>185</v>
       </c>
@@ -3967,7 +3968,7 @@
       </c>
       <c r="K60" s="5"/>
     </row>
-    <row r="61" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>185</v>
       </c>
@@ -3996,7 +3997,7 @@
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
     </row>
-    <row r="62" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>186</v>
       </c>
@@ -4029,7 +4030,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>191</v>
       </c>
@@ -4062,7 +4063,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>193</v>
       </c>
@@ -4093,7 +4094,7 @@
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
     </row>
-    <row r="65" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>195</v>
       </c>
@@ -4124,7 +4125,7 @@
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
     </row>
-    <row r="66" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>195</v>
       </c>
@@ -4155,7 +4156,7 @@
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
     </row>
-    <row r="67" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>198</v>
       </c>
@@ -4188,7 +4189,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>202</v>
       </c>
@@ -4221,7 +4222,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>206</v>
       </c>
@@ -4254,7 +4255,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>209</v>
       </c>
@@ -4287,7 +4288,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>213</v>
       </c>
@@ -4318,7 +4319,7 @@
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
     </row>
-    <row r="72" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>216</v>
       </c>
@@ -4351,7 +4352,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>219</v>
       </c>
@@ -4384,7 +4385,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>222</v>
       </c>
@@ -4415,7 +4416,7 @@
       <c r="J74" s="5"/>
       <c r="K74" s="5"/>
     </row>
-    <row r="75" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>225</v>
       </c>
@@ -4448,7 +4449,7 @@
       </c>
       <c r="K75" s="5"/>
     </row>
-    <row r="76" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>227</v>
       </c>
@@ -4479,7 +4480,7 @@
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
     </row>
-    <row r="77" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>231</v>
       </c>
@@ -4510,7 +4511,7 @@
       <c r="J77" s="5"/>
       <c r="K77" s="5"/>
     </row>
-    <row r="78" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>233</v>
       </c>
@@ -4543,7 +4544,7 @@
       </c>
       <c r="K78" s="5"/>
     </row>
-    <row r="79" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>234</v>
       </c>
@@ -4574,7 +4575,7 @@
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
     </row>
-    <row r="80" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>236</v>
       </c>
@@ -4605,7 +4606,7 @@
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
     </row>
-    <row r="81" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>237</v>
       </c>
@@ -4636,7 +4637,7 @@
       <c r="J81" s="5"/>
       <c r="K81" s="5"/>
     </row>
-    <row r="82" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>237</v>
       </c>
@@ -4698,7 +4699,7 @@
       <c r="J83" s="5"/>
       <c r="K83" s="5"/>
     </row>
-    <row r="84" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>238</v>
       </c>
@@ -4729,7 +4730,7 @@
       <c r="J84" s="5"/>
       <c r="K84" s="5"/>
     </row>
-    <row r="85" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>238</v>
       </c>
@@ -4760,7 +4761,7 @@
       <c r="J85" s="5"/>
       <c r="K85" s="5"/>
     </row>
-    <row r="86" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>242</v>
       </c>
@@ -4791,7 +4792,7 @@
       <c r="J86" s="5"/>
       <c r="K86" s="5"/>
     </row>
-    <row r="87" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>242</v>
       </c>
@@ -4822,7 +4823,7 @@
       <c r="J87" s="5"/>
       <c r="K87" s="5"/>
     </row>
-    <row r="88" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>243</v>
       </c>
@@ -4855,7 +4856,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>245</v>
       </c>
@@ -4884,7 +4885,7 @@
       <c r="J89" s="5"/>
       <c r="K89" s="5"/>
     </row>
-    <row r="90" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" ht="90.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>247</v>
       </c>
@@ -4915,7 +4916,7 @@
       <c r="J90" s="5"/>
       <c r="K90" s="5"/>
     </row>
-    <row r="91" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" ht="90.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>247</v>
       </c>
@@ -4946,7 +4947,7 @@
       <c r="J91" s="5"/>
       <c r="K91" s="5"/>
     </row>
-    <row r="92" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>249</v>
       </c>
@@ -4977,7 +4978,7 @@
       <c r="J92" s="5"/>
       <c r="K92" s="5"/>
     </row>
-    <row r="93" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>252</v>
       </c>
@@ -5008,7 +5009,7 @@
       <c r="J93" s="5"/>
       <c r="K93" s="5"/>
     </row>
-    <row r="94" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>255</v>
       </c>
@@ -5037,7 +5038,7 @@
       <c r="J94" s="5"/>
       <c r="K94" s="5"/>
     </row>
-    <row r="95" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>258</v>
       </c>
@@ -5068,7 +5069,7 @@
       <c r="J95" s="5"/>
       <c r="K95" s="5"/>
     </row>
-    <row r="96" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>261</v>
       </c>
@@ -5103,7 +5104,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>262</v>
       </c>
@@ -5134,7 +5135,7 @@
       <c r="J97" s="5"/>
       <c r="K97" s="5"/>
     </row>
-    <row r="98" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>265</v>
       </c>
@@ -5165,7 +5166,7 @@
       <c r="J98" s="5"/>
       <c r="K98" s="5"/>
     </row>
-    <row r="99" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>268</v>
       </c>
@@ -5196,7 +5197,7 @@
       <c r="J99" s="5"/>
       <c r="K99" s="5"/>
     </row>
-    <row r="100" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>269</v>
       </c>
@@ -5227,7 +5228,7 @@
       <c r="J100" s="5"/>
       <c r="K100" s="5"/>
     </row>
-    <row r="101" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>272</v>
       </c>
@@ -5256,7 +5257,7 @@
       <c r="J101" s="5"/>
       <c r="K101" s="5"/>
     </row>
-    <row r="102" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>274</v>
       </c>
@@ -5287,7 +5288,7 @@
       <c r="J102" s="5"/>
       <c r="K102" s="5"/>
     </row>
-    <row r="103" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>274</v>
       </c>
@@ -5318,7 +5319,7 @@
       <c r="J103" s="5"/>
       <c r="K103" s="5"/>
     </row>
-    <row r="104" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>280</v>
       </c>
@@ -5349,7 +5350,7 @@
       <c r="J104" s="5"/>
       <c r="K104" s="5"/>
     </row>
-    <row r="105" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>283</v>
       </c>
@@ -5380,7 +5381,7 @@
       <c r="J105" s="5"/>
       <c r="K105" s="5"/>
     </row>
-    <row r="106" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>286</v>
       </c>
@@ -5411,7 +5412,7 @@
       <c r="J106" s="5"/>
       <c r="K106" s="5"/>
     </row>
-    <row r="107" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>290</v>
       </c>
@@ -5442,7 +5443,7 @@
       <c r="J107" s="5"/>
       <c r="K107" s="5"/>
     </row>
-    <row r="108" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>293</v>
       </c>
@@ -5473,7 +5474,7 @@
       <c r="J108" s="5"/>
       <c r="K108" s="5"/>
     </row>
-    <row r="109" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>296</v>
       </c>
@@ -5504,7 +5505,7 @@
       <c r="J109" s="5"/>
       <c r="K109" s="5"/>
     </row>
-    <row r="110" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>299</v>
       </c>
@@ -5566,7 +5567,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>302</v>
       </c>
@@ -5597,7 +5598,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
         <v>303</v>
       </c>
@@ -5626,7 +5627,7 @@
       <c r="J113" s="5"/>
       <c r="K113" s="5"/>
     </row>
-    <row r="114" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
         <v>306</v>
       </c>
@@ -5655,7 +5656,7 @@
       <c r="J114" s="5"/>
       <c r="K114" s="5"/>
     </row>
-    <row r="115" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>309</v>
       </c>
@@ -5684,7 +5685,7 @@
       <c r="J115" s="5"/>
       <c r="K115" s="5"/>
     </row>
-    <row r="116" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>312</v>
       </c>
@@ -5717,7 +5718,7 @@
       </c>
       <c r="K116" s="5"/>
     </row>
-    <row r="117" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>314</v>
       </c>
@@ -5746,7 +5747,7 @@
       <c r="J117" s="5"/>
       <c r="K117" s="5"/>
     </row>
-    <row r="118" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>315</v>
       </c>
@@ -5775,7 +5776,7 @@
       <c r="J118" s="5"/>
       <c r="K118" s="5"/>
     </row>
-    <row r="119" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
         <v>316</v>
       </c>
@@ -5804,7 +5805,7 @@
       <c r="J119" s="5"/>
       <c r="K119" s="5"/>
     </row>
-    <row r="120" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
         <v>318</v>
       </c>
@@ -5833,7 +5834,7 @@
       <c r="J120" s="5"/>
       <c r="K120" s="5"/>
     </row>
-    <row r="121" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
         <v>320</v>
       </c>
@@ -5862,7 +5863,7 @@
       <c r="J121" s="5"/>
       <c r="K121" s="5"/>
     </row>
-    <row r="122" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>322</v>
       </c>
@@ -5893,7 +5894,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>324</v>
       </c>
@@ -5924,7 +5925,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>325</v>
       </c>
@@ -5953,7 +5954,7 @@
       <c r="J124" s="5"/>
       <c r="K124" s="5"/>
     </row>
-    <row r="125" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>328</v>
       </c>
@@ -5982,7 +5983,7 @@
       <c r="J125" s="5"/>
       <c r="K125" s="5"/>
     </row>
-    <row r="126" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>332</v>
       </c>
@@ -6011,7 +6012,7 @@
       <c r="J126" s="5"/>
       <c r="K126" s="5"/>
     </row>
-    <row r="127" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>335</v>
       </c>
@@ -6040,7 +6041,7 @@
       <c r="J127" s="5"/>
       <c r="K127" s="5"/>
     </row>
-    <row r="128" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>335</v>
       </c>
@@ -6069,7 +6070,7 @@
       <c r="J128" s="5"/>
       <c r="K128" s="5"/>
     </row>
-    <row r="129" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>339</v>
       </c>
@@ -6098,7 +6099,7 @@
       <c r="J129" s="5"/>
       <c r="K129" s="5"/>
     </row>
-    <row r="130" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>342</v>
       </c>
@@ -6127,7 +6128,7 @@
       <c r="J130" s="5"/>
       <c r="K130" s="5"/>
     </row>
-    <row r="131" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>344</v>
       </c>
@@ -6156,7 +6157,7 @@
       <c r="J131" s="5"/>
       <c r="K131" s="5"/>
     </row>
-    <row r="132" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>346</v>
       </c>
@@ -6185,7 +6186,7 @@
       <c r="J132" s="5"/>
       <c r="K132" s="5"/>
     </row>
-    <row r="133" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>349</v>
       </c>
@@ -6214,7 +6215,7 @@
       <c r="J133" s="5"/>
       <c r="K133" s="5"/>
     </row>
-    <row r="134" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>349</v>
       </c>
@@ -6243,7 +6244,7 @@
       <c r="J134" s="5"/>
       <c r="K134" s="5"/>
     </row>
-    <row r="135" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>353</v>
       </c>
@@ -6272,7 +6273,7 @@
       <c r="J135" s="5"/>
       <c r="K135" s="5"/>
     </row>
-    <row r="136" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>356</v>
       </c>
@@ -6301,7 +6302,7 @@
       <c r="J136" s="5"/>
       <c r="K136" s="5"/>
     </row>
-    <row r="137" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>358</v>
       </c>
@@ -6330,7 +6331,7 @@
       <c r="J137" s="5"/>
       <c r="K137" s="5"/>
     </row>
-    <row r="138" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>358</v>
       </c>
@@ -6359,7 +6360,7 @@
       <c r="J138" s="5"/>
       <c r="K138" s="5"/>
     </row>
-    <row r="139" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>360</v>
       </c>
@@ -6388,7 +6389,7 @@
       <c r="J139" s="5"/>
       <c r="K139" s="5"/>
     </row>
-    <row r="140" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>360</v>
       </c>
@@ -6417,7 +6418,7 @@
       <c r="J140" s="5"/>
       <c r="K140" s="5"/>
     </row>
-    <row r="141" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>362</v>
       </c>
@@ -6446,7 +6447,7 @@
       <c r="J141" s="5"/>
       <c r="K141" s="5"/>
     </row>
-    <row r="142" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>363</v>
       </c>
@@ -6475,7 +6476,7 @@
       <c r="J142" s="5"/>
       <c r="K142" s="5"/>
     </row>
-    <row r="143" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>365</v>
       </c>
@@ -6504,7 +6505,7 @@
       <c r="J143" s="5"/>
       <c r="K143" s="5"/>
     </row>
-    <row r="144" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>367</v>
       </c>
@@ -6533,7 +6534,7 @@
       <c r="J144" s="5"/>
       <c r="K144" s="5"/>
     </row>
-    <row r="145" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>369</v>
       </c>
@@ -6562,7 +6563,7 @@
       <c r="J145" s="5"/>
       <c r="K145" s="5"/>
     </row>
-    <row r="146" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>372</v>
       </c>
@@ -6593,7 +6594,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>374</v>
       </c>
@@ -6622,7 +6623,7 @@
       <c r="J147" s="5"/>
       <c r="K147" s="5"/>
     </row>
-    <row r="148" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>374</v>
       </c>
@@ -6653,7 +6654,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>378</v>
       </c>
@@ -6682,7 +6683,7 @@
       <c r="J149" s="5"/>
       <c r="K149" s="5"/>
     </row>
-    <row r="150" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>381</v>
       </c>
@@ -6711,7 +6712,7 @@
       <c r="J150" s="5"/>
       <c r="K150" s="5"/>
     </row>
-    <row r="151" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>383</v>
       </c>
@@ -6740,7 +6741,7 @@
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
     </row>
-    <row r="152" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>386</v>
       </c>
@@ -6769,7 +6770,7 @@
       <c r="J152" s="5"/>
       <c r="K152" s="5"/>
     </row>
-    <row r="153" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>386</v>
       </c>
@@ -6798,7 +6799,7 @@
       <c r="J153" s="5"/>
       <c r="K153" s="5"/>
     </row>
-    <row r="154" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>391</v>
       </c>
@@ -6827,7 +6828,7 @@
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
     </row>
-    <row r="155" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>395</v>
       </c>
@@ -6856,7 +6857,7 @@
       <c r="J155" s="5"/>
       <c r="K155" s="5"/>
     </row>
-    <row r="156" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>398</v>
       </c>
@@ -6887,7 +6888,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>400</v>
       </c>
@@ -6916,7 +6917,7 @@
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
     </row>
-    <row r="158" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>402</v>
       </c>
@@ -6949,7 +6950,7 @@
       </c>
       <c r="K158" s="5"/>
     </row>
-    <row r="159" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>404</v>
       </c>
@@ -6978,7 +6979,7 @@
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
     </row>
-    <row r="160" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
         <v>406</v>
       </c>
@@ -7009,7 +7010,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>406</v>
       </c>
@@ -7038,7 +7039,7 @@
       <c r="J161" s="5"/>
       <c r="K161" s="5"/>
     </row>
-    <row r="162" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>408</v>
       </c>
@@ -7067,7 +7068,7 @@
       <c r="J162" s="5"/>
       <c r="K162" s="5"/>
     </row>
-    <row r="163" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>410</v>
       </c>
@@ -7098,7 +7099,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>412</v>
       </c>
@@ -7129,7 +7130,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>414</v>
       </c>
@@ -7160,7 +7161,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>416</v>
       </c>
@@ -7189,7 +7190,7 @@
       <c r="J166" s="5"/>
       <c r="K166" s="5"/>
     </row>
-    <row r="167" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>418</v>
       </c>
@@ -7220,7 +7221,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>419</v>
       </c>
@@ -7253,7 +7254,7 @@
       </c>
       <c r="K168" s="5"/>
     </row>
-    <row r="169" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>421</v>
       </c>
@@ -7286,7 +7287,7 @@
       </c>
       <c r="K169" s="5"/>
     </row>
-    <row r="170" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>422</v>
       </c>
@@ -7317,7 +7318,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>424</v>
       </c>
@@ -7346,7 +7347,7 @@
       <c r="J171" s="5"/>
       <c r="K171" s="5"/>
     </row>
-    <row r="172" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>426</v>
       </c>
@@ -7375,7 +7376,7 @@
       <c r="J172" s="5"/>
       <c r="K172" s="5"/>
     </row>
-    <row r="173" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>429</v>
       </c>
@@ -7406,7 +7407,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>431</v>
       </c>
@@ -7435,7 +7436,7 @@
       <c r="J174" s="5"/>
       <c r="K174" s="5"/>
     </row>
-    <row r="175" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>432</v>
       </c>
@@ -7464,7 +7465,7 @@
       <c r="J175" s="5"/>
       <c r="K175" s="5"/>
     </row>
-    <row r="176" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
         <v>432</v>
       </c>
@@ -7493,7 +7494,7 @@
       <c r="J176" s="5"/>
       <c r="K176" s="5"/>
     </row>
-    <row r="177" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
         <v>435</v>
       </c>
@@ -7522,7 +7523,7 @@
       <c r="J177" s="5"/>
       <c r="K177" s="5"/>
     </row>
-    <row r="178" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
         <v>437</v>
       </c>
@@ -7555,7 +7556,7 @@
       </c>
       <c r="K178" s="5"/>
     </row>
-    <row r="179" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
         <v>438</v>
       </c>
@@ -7584,7 +7585,7 @@
       <c r="J179" s="5"/>
       <c r="K179" s="5"/>
     </row>
-    <row r="180" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
         <v>439</v>
       </c>
@@ -7619,7 +7620,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
         <v>439</v>
       </c>
@@ -7648,7 +7649,7 @@
       <c r="J181" s="5"/>
       <c r="K181" s="5"/>
     </row>
-    <row r="182" spans="1:11" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" ht="116.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
         <v>442</v>
       </c>
@@ -7710,7 +7711,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
         <v>446</v>
       </c>
@@ -7739,7 +7740,7 @@
       <c r="J184" s="5"/>
       <c r="K184" s="5"/>
     </row>
-    <row r="185" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" ht="90.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
         <v>448</v>
       </c>
@@ -7768,7 +7769,7 @@
       <c r="J185" s="5"/>
       <c r="K185" s="5"/>
     </row>
-    <row r="186" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
         <v>450</v>
       </c>
@@ -7797,7 +7798,7 @@
       <c r="J186" s="5"/>
       <c r="K186" s="5"/>
     </row>
-    <row r="187" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
         <v>452</v>
       </c>
@@ -7828,7 +7829,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
         <v>452</v>
       </c>
@@ -7859,7 +7860,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
         <v>455</v>
       </c>
@@ -7890,7 +7891,7 @@
       <c r="J189" s="5"/>
       <c r="K189" s="5"/>
     </row>
-    <row r="190" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
         <v>455</v>
       </c>
@@ -7921,7 +7922,7 @@
       <c r="J190" s="5"/>
       <c r="K190" s="5"/>
     </row>
-    <row r="191" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
         <v>456</v>
       </c>
@@ -7981,7 +7982,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
         <v>459</v>
       </c>
@@ -8041,7 +8042,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
         <v>464</v>
       </c>
@@ -8070,7 +8071,7 @@
       <c r="J195" s="5"/>
       <c r="K195" s="5"/>
     </row>
-    <row r="196" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
         <v>467</v>
       </c>
@@ -8099,7 +8100,7 @@
       <c r="J196" s="5"/>
       <c r="K196" s="5"/>
     </row>
-    <row r="197" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
         <v>470</v>
       </c>
@@ -8134,7 +8135,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="198" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
         <v>472</v>
       </c>
@@ -8163,7 +8164,7 @@
       <c r="J198" s="5"/>
       <c r="K198" s="5"/>
     </row>
-    <row r="199" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
         <v>475</v>
       </c>
@@ -8192,7 +8193,7 @@
       <c r="J199" s="5"/>
       <c r="K199" s="5"/>
     </row>
-    <row r="200" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
         <v>478</v>
       </c>
@@ -8221,7 +8222,7 @@
       <c r="J200" s="5"/>
       <c r="K200" s="5"/>
     </row>
-    <row r="201" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
         <v>481</v>
       </c>
@@ -8250,7 +8251,7 @@
       <c r="J201" s="5"/>
       <c r="K201" s="5"/>
     </row>
-    <row r="202" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
         <v>482</v>
       </c>
@@ -8279,7 +8280,7 @@
       <c r="J202" s="5"/>
       <c r="K202" s="5"/>
     </row>
-    <row r="203" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
         <v>484</v>
       </c>
@@ -8310,7 +8311,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="204" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
         <v>486</v>
       </c>
@@ -8343,7 +8344,7 @@
       </c>
       <c r="K204" s="5"/>
     </row>
-    <row r="205" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
         <v>488</v>
       </c>
@@ -8372,7 +8373,7 @@
       <c r="J205" s="5"/>
       <c r="K205" s="5"/>
     </row>
-    <row r="206" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
         <v>490</v>
       </c>
@@ -8401,7 +8402,7 @@
       <c r="J206" s="5"/>
       <c r="K206" s="5"/>
     </row>
-    <row r="207" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
         <v>492</v>
       </c>
@@ -8430,7 +8431,7 @@
       <c r="J207" s="5"/>
       <c r="K207" s="5"/>
     </row>
-    <row r="208" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
         <v>492</v>
       </c>
@@ -8459,7 +8460,7 @@
       <c r="J208" s="5"/>
       <c r="K208" s="5"/>
     </row>
-    <row r="209" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
         <v>495</v>
       </c>
@@ -8488,7 +8489,7 @@
       <c r="J209" s="5"/>
       <c r="K209" s="5"/>
     </row>
-    <row r="210" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
         <v>497</v>
       </c>
@@ -8517,7 +8518,7 @@
       <c r="J210" s="5"/>
       <c r="K210" s="5"/>
     </row>
-    <row r="211" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
         <v>499</v>
       </c>
@@ -8548,7 +8549,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
         <v>501</v>
       </c>
@@ -8577,7 +8578,7 @@
       <c r="J212" s="5"/>
       <c r="K212" s="5"/>
     </row>
-    <row r="213" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
         <v>503</v>
       </c>
@@ -8606,7 +8607,7 @@
       <c r="J213" s="5"/>
       <c r="K213" s="5"/>
     </row>
-    <row r="214" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
         <v>505</v>
       </c>
@@ -8639,7 +8640,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="215" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
         <v>506</v>
       </c>
@@ -8670,7 +8671,7 @@
       </c>
       <c r="K215" s="5"/>
     </row>
-    <row r="216" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
         <v>506</v>
       </c>
@@ -8701,7 +8702,7 @@
       </c>
       <c r="K216" s="5"/>
     </row>
-    <row r="217" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" ht="90.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
         <v>507</v>
       </c>
@@ -8792,7 +8793,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
         <v>510</v>
       </c>
@@ -8823,7 +8824,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="221" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>510</v>
       </c>
@@ -8852,7 +8853,7 @@
       <c r="J221" s="5"/>
       <c r="K221" s="5"/>
     </row>
-    <row r="222" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
         <v>511</v>
       </c>
@@ -8881,7 +8882,7 @@
       <c r="J222" s="5"/>
       <c r="K222" s="5"/>
     </row>
-    <row r="223" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
         <v>511</v>
       </c>
@@ -8910,7 +8911,7 @@
       <c r="J223" s="5"/>
       <c r="K223" s="5"/>
     </row>
-    <row r="224" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
         <v>511</v>
       </c>
@@ -8939,7 +8940,7 @@
       <c r="J224" s="5"/>
       <c r="K224" s="5"/>
     </row>
-    <row r="225" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
         <v>512</v>
       </c>
@@ -8970,7 +8971,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="226" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
         <v>512</v>
       </c>
@@ -9001,7 +9002,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="227" spans="1:11" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:11" ht="116.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
         <v>512</v>
       </c>
@@ -9032,7 +9033,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="228" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>512</v>
       </c>
@@ -9061,7 +9062,7 @@
       <c r="J228" s="5"/>
       <c r="K228" s="5"/>
     </row>
-    <row r="229" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
         <v>512</v>
       </c>
@@ -9090,7 +9091,7 @@
       <c r="J229" s="5"/>
       <c r="K229" s="5"/>
     </row>
-    <row r="230" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
         <v>513</v>
       </c>
@@ -9121,7 +9122,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="231" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
         <v>513</v>
       </c>
@@ -9150,7 +9151,7 @@
       <c r="J231" s="5"/>
       <c r="K231" s="5"/>
     </row>
-    <row r="232" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
         <v>513</v>
       </c>
@@ -9179,7 +9180,7 @@
       <c r="J232" s="5"/>
       <c r="K232" s="5"/>
     </row>
-    <row r="233" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
         <v>513</v>
       </c>
@@ -9210,7 +9211,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="234" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
         <v>513</v>
       </c>
@@ -9241,7 +9242,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="235" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
         <v>513</v>
       </c>
@@ -9272,7 +9273,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="236" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
         <v>513</v>
       </c>
@@ -9303,7 +9304,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
         <v>513</v>
       </c>
@@ -9332,7 +9333,7 @@
       <c r="J237" s="5"/>
       <c r="K237" s="5"/>
     </row>
-    <row r="238" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
         <v>513</v>
       </c>
@@ -9363,7 +9364,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
         <v>514</v>
       </c>
@@ -9394,7 +9395,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
         <v>514</v>
       </c>
@@ -9425,7 +9426,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="241" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
         <v>514</v>
       </c>
@@ -9456,7 +9457,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
         <v>514</v>
       </c>
@@ -9485,7 +9486,7 @@
       <c r="J242" s="5"/>
       <c r="K242" s="5"/>
     </row>
-    <row r="243" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
         <v>514</v>
       </c>
@@ -9516,7 +9517,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="244" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
         <v>514</v>
       </c>
@@ -9547,7 +9548,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
         <v>514</v>
       </c>
@@ -9576,7 +9577,7 @@
       <c r="J245" s="5"/>
       <c r="K245" s="5"/>
     </row>
-    <row r="246" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
         <v>514</v>
       </c>
@@ -9605,7 +9606,7 @@
       <c r="J246" s="5"/>
       <c r="K246" s="5"/>
     </row>
-    <row r="247" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
         <v>514</v>
       </c>
@@ -9634,7 +9635,7 @@
       <c r="J247" s="5"/>
       <c r="K247" s="5"/>
     </row>
-    <row r="248" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
         <v>514</v>
       </c>
@@ -9663,7 +9664,7 @@
       <c r="J248" s="5"/>
       <c r="K248" s="5"/>
     </row>
-    <row r="249" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
         <v>515</v>
       </c>
@@ -9692,7 +9693,7 @@
       <c r="J249" s="5"/>
       <c r="K249" s="5"/>
     </row>
-    <row r="250" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
         <v>515</v>
       </c>
@@ -9721,7 +9722,7 @@
       <c r="J250" s="5"/>
       <c r="K250" s="5"/>
     </row>
-    <row r="251" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
         <v>515</v>
       </c>
@@ -9750,7 +9751,7 @@
       <c r="J251" s="5"/>
       <c r="K251" s="5"/>
     </row>
-    <row r="252" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
         <v>515</v>
       </c>
@@ -9779,7 +9780,7 @@
       <c r="J252" s="5"/>
       <c r="K252" s="5"/>
     </row>
-    <row r="253" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
         <v>515</v>
       </c>
@@ -9808,7 +9809,7 @@
       <c r="J253" s="5"/>
       <c r="K253" s="5"/>
     </row>
-    <row r="254" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
         <v>515</v>
       </c>
@@ -9835,7 +9836,7 @@
       <c r="J254" s="5"/>
       <c r="K254" s="5"/>
     </row>
-    <row r="255" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
         <v>515</v>
       </c>
@@ -9862,7 +9863,7 @@
       <c r="J255" s="5"/>
       <c r="K255" s="5"/>
     </row>
-    <row r="256" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
         <v>515</v>
       </c>
@@ -9889,7 +9890,7 @@
       <c r="J256" s="5"/>
       <c r="K256" s="5"/>
     </row>
-    <row r="257" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
         <v>515</v>
       </c>
@@ -9922,7 +9923,7 @@
       </c>
       <c r="K257" s="5"/>
     </row>
-    <row r="258" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
         <v>515</v>
       </c>
@@ -9949,7 +9950,7 @@
       <c r="J258" s="5"/>
       <c r="K258" s="5"/>
     </row>
-    <row r="259" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
         <v>519</v>
       </c>
@@ -9978,7 +9979,7 @@
       <c r="J259" s="5"/>
       <c r="K259" s="5"/>
     </row>
-    <row r="260" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="3" t="s">
         <v>519</v>
       </c>
@@ -10009,7 +10010,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="261" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
         <v>519</v>
       </c>
@@ -10038,7 +10039,7 @@
       <c r="J261" s="5"/>
       <c r="K261" s="5"/>
     </row>
-    <row r="262" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
         <v>519</v>
       </c>
@@ -10067,7 +10068,7 @@
       <c r="J262" s="5"/>
       <c r="K262" s="5"/>
     </row>
-    <row r="263" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
         <v>519</v>
       </c>
@@ -10096,7 +10097,7 @@
       <c r="J263" s="5"/>
       <c r="K263" s="5"/>
     </row>
-    <row r="264" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
         <v>519</v>
       </c>
@@ -10125,7 +10126,7 @@
       <c r="J264" s="5"/>
       <c r="K264" s="5"/>
     </row>
-    <row r="265" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
         <v>519</v>
       </c>
@@ -10154,7 +10155,7 @@
       <c r="J265" s="5"/>
       <c r="K265" s="5"/>
     </row>
-    <row r="266" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
         <v>519</v>
       </c>
@@ -10183,7 +10184,7 @@
       <c r="J266" s="5"/>
       <c r="K266" s="5"/>
     </row>
-    <row r="267" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
         <v>519</v>
       </c>
@@ -10212,7 +10213,7 @@
       <c r="J267" s="5"/>
       <c r="K267" s="5"/>
     </row>
-    <row r="268" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="3" t="s">
         <v>519</v>
       </c>
@@ -10241,7 +10242,7 @@
       <c r="J268" s="5"/>
       <c r="K268" s="5"/>
     </row>
-    <row r="269" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
         <v>520</v>
       </c>
@@ -10270,7 +10271,7 @@
       <c r="J269" s="5"/>
       <c r="K269" s="5"/>
     </row>
-    <row r="270" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="3" t="s">
         <v>520</v>
       </c>
@@ -10299,7 +10300,7 @@
       <c r="J270" s="5"/>
       <c r="K270" s="5"/>
     </row>
-    <row r="271" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
         <v>520</v>
       </c>
@@ -10328,7 +10329,7 @@
       <c r="J271" s="5"/>
       <c r="K271" s="5"/>
     </row>
-    <row r="272" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
         <v>520</v>
       </c>
@@ -10357,7 +10358,7 @@
       <c r="J272" s="5"/>
       <c r="K272" s="5"/>
     </row>
-    <row r="273" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
         <v>520</v>
       </c>
@@ -10386,7 +10387,7 @@
       <c r="J273" s="5"/>
       <c r="K273" s="5"/>
     </row>
-    <row r="274" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
         <v>520</v>
       </c>
@@ -19839,7 +19840,13 @@
       <c r="K999" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K216" xr:uid="{271A8CFB-3293-473B-894F-86B249B2B19B}"/>
+  <autoFilter ref="A1:K274" xr:uid="{271A8CFB-3293-473B-894F-86B249B2B19B}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Huỳnh Chí Băng"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_PAKH\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBADA33-15A7-4844-A07D-81EDEC064845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C636266F-0223-44AD-89EC-B23C54E52B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{15FDD92A-6CAD-44EB-866F-DB764FC19082}"/>
+    <workbookView xWindow="2130" yWindow="1890" windowWidth="21600" windowHeight="11295" xr2:uid="{15FDD92A-6CAD-44EB-866F-DB764FC19082}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$274</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$226</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="431">
   <si>
     <t>Thời gian update</t>
   </si>
@@ -963,34 +963,13 @@
     <t>22/08/2026 18:20</t>
   </si>
   <si>
-    <t>24/08/2026 08:09</t>
-  </si>
-  <si>
-    <t>24/08/2026</t>
-  </si>
-  <si>
-    <t>24/08/2026 08:12</t>
-  </si>
-  <si>
-    <t>24/08/2026 08:41</t>
-  </si>
-  <si>
     <t>Đạt</t>
   </si>
   <si>
     <t>- Đã Điều phối cho GĐKD liên hệ tư vấn cho KH xong</t>
   </si>
   <si>
-    <t>24/08/2026 08:53</t>
-  </si>
-  <si>
     <t>Đăng</t>
-  </si>
-  <si>
-    <t>Đã xử lý xong cho khách hàng. Dự kiến trước 12h trưa hoàn thành</t>
-  </si>
-  <si>
-    <t>24/08/2026 08:56</t>
   </si>
   <si>
     <t>Hiếu</t>
@@ -998,9 +977,6 @@
   <si>
     <t>Nhà thầu phụ và Đ/c Tân HNI qua nhà KH lúc 16h ngày 21/08 để kiểm tra. sẽ cập nhật khi có kết quả
 đã thay 01 biến tần, 01 bo điều khiển nóc cabin, 01 bo nút gọi cabib, 01 bo hiện thị cabin. kiểm tra điện áp đầu vào đầu ra 380V +_5% đạt. cho thang máy hoạt động và tiếp tục theo dõi</t>
-  </si>
-  <si>
-    <t>24/08/2026 09:09</t>
   </si>
   <si>
     <t>Đã kiểm tra, HT NLMT ký HĐ với KH hoạt động bình thường. Lỗi tại thiết bị ATS của Khách, thiết bị ATS này do GĐKD lắp riêng cho khách, không thuộc HĐ.
@@ -1008,54 +984,19 @@
 -24/8 GĐKD đang qua kiểm tra và Phối hợp nhà cc kết nối lại cho khách</t>
   </si>
   <si>
-    <t>24/08/2026 09:11</t>
-  </si>
-  <si>
-    <t>24/08/2026 09:22</t>
-  </si>
-  <si>
-    <t>24/08/2026 09:26</t>
-  </si>
-  <si>
-    <t>Tủ điện bị hỏng timer, hiện Đ/c Minh FT3 đang đặt cái mới vè để thay cho KH (KH dùng 2 công tơ)
-Ngày 25/8 hàng về rồi qua thay cho KH</t>
-  </si>
-  <si>
-    <t>24/08/2026 09:27</t>
-  </si>
-  <si>
-    <t>Tủ điện bị hỏng timer, hiện Đ/c Minh FT3 đang đặt cái mới vè để thay cho KH (KH dùng 2 công tơ)
-Ngày 26/8 hàng về rồi qua thay cho KH</t>
-  </si>
-  <si>
-    <t>24/08/2026 09:28</t>
-  </si>
-  <si>
     <t>Tủ điện bị hỏng timer, hiện Đ/c Minh FT3 đang đặt cái mới vè để thay cho KH (KH dùng 2 công tơ)
 Ngày 27/8 hàng về rồi qua thay cho KH</t>
   </si>
   <si>
-    <t>24/08/2026 09:32</t>
-  </si>
-  <si>
     <t>Lỗi Pin lưu trữ.</t>
   </si>
   <si>
-    <t>24/08/2026 09:34</t>
-  </si>
-  <si>
-    <t>24/08/2026 09:36</t>
-  </si>
-  <si>
     <t>Nguyễn Thị Thu Hiền</t>
   </si>
   <si>
     <t>Đã hoàn thành cho KH</t>
   </si>
   <si>
-    <t>24/08/2026 09:40</t>
-  </si>
-  <si>
     <t>Hàng Quốc Điện</t>
   </si>
   <si>
@@ -1065,16 +1006,7 @@
     <t>- Lỗi phần mềm, cập nhật lại phần mềm cho khách</t>
   </si>
   <si>
-    <t>24/08/2026 09:41</t>
-  </si>
-  <si>
     <t>Nguyễn Việt Tuấn</t>
-  </si>
-  <si>
-    <t>- KH chưa nghe máy =&gt; Liên hệ lại với KH</t>
-  </si>
-  <si>
-    <t>24/08/2026 09:42</t>
   </si>
   <si>
     <t>Lê Ngọc Tuấn</t>
@@ -1088,116 +1020,55 @@
 Ngày 24/8 KT qua lắp lại biến tần mới</t>
   </si>
   <si>
-    <t>24/08/2026 09:58</t>
-  </si>
-  <si>
     <t>Anh Hoàng</t>
   </si>
   <si>
-    <t>KH đang bận sẽ gọi lại sau. KH phản hồi sai địa chỉ, sai khu vực.</t>
-  </si>
-  <si>
-    <t>24/08/2026 10:00</t>
-  </si>
-  <si>
-    <t>meter hết hạn bảo hành, dự kiến ngày 24/8 hỗ trợ thay cho khách và đóng Ticket
-Đã đến nhà KH để kiểm tra và thông báo cho KH</t>
-  </si>
-  <si>
-    <t>24/08/2026 10:05</t>
-  </si>
-  <si>
     <t>cài lại Logger cho KH</t>
   </si>
   <si>
-    <t>24/08/2026 10:07</t>
-  </si>
-  <si>
     <t>Nguyễn Hữu Năm</t>
   </si>
   <si>
     <t>Bị mất giám sát, đã xủ lý xong</t>
   </si>
   <si>
-    <t>24/08/2026 10:08</t>
-  </si>
-  <si>
     <t>Trịnh Hữu Hùng</t>
   </si>
   <si>
     <t>Đã hẹn KH</t>
   </si>
   <si>
-    <t>KH đang bận hẹn gọi lại sau</t>
-  </si>
-  <si>
-    <t>24/08/2026 10:09</t>
-  </si>
-  <si>
     <t>PHẠM THÁI HƯNG</t>
   </si>
   <si>
     <t>Trời mưa nên chưa thực hiện đc.</t>
   </si>
   <si>
-    <t>24/08/2026 10:10</t>
-  </si>
-  <si>
     <t>KH đã tải app và sử dụng được bt</t>
-  </si>
-  <si>
-    <t>24/08/2026 10:11</t>
   </si>
   <si>
     <t>- Liên hệ KH nhiều lần chưa nghe máy, vấn đề dốt đã xử lý cho KH, dự kiến mai qua nhà KH trao đổi xem còn vấn đề gì không
 Đã bắn lại keo</t>
   </si>
   <si>
-    <t>24/08/2026 10:13</t>
-  </si>
-  <si>
     <t>Đã đóng Ticket
 NCC đã phối hợp up phần mềm xong ngày 17/08/2026, đang theo dõi dự kiến ngày 21/08/2026 đóng tickit</t>
   </si>
   <si>
-    <t>24/08/2026 10:14</t>
-  </si>
-  <si>
-    <t>24/08/2026 10:16</t>
-  </si>
-  <si>
     <t>KT đang xin user để vào check hệ thống</t>
   </si>
   <si>
-    <t>24/08/2026 10:17</t>
-  </si>
-  <si>
     <t>Đã xử lý</t>
-  </si>
-  <si>
-    <t>24/08/2026 10:18</t>
   </si>
   <si>
     <t>Đã qua kiểm tra cho khách và đóng Ticket
 Ngày 22/08/2026 đến để kiểm tra cho KH,</t>
   </si>
   <si>
-    <t>24/08/2026 10:21</t>
-  </si>
-  <si>
     <t>Ngô Thuỵ Miên</t>
   </si>
   <si>
     <t>Đã trao đổi với KH</t>
-  </si>
-  <si>
-    <t>24/08/2026 10:23</t>
-  </si>
-  <si>
-    <t>hỏng metter, hiện đã chuyển về bảo hành cho hãng powrtech từ 18/08. đang chờ hàng bảo hành về để lắp cho KH, dự kiến 29/8</t>
-  </si>
-  <si>
-    <t>24/08/2026 10:24</t>
   </si>
   <si>
     <t>Hoàng Thị Tuyết Nga</t>
@@ -1211,33 +1082,18 @@
 Tạo mới YCBH YCBH_AGG_1786617217200 từ B2C lúc 17:33 13/08/2026 Hạn hoàn thành 23:59 28/08/2026</t>
   </si>
   <si>
-    <t>24/08/2026 10:28</t>
-  </si>
-  <si>
     <t>A Quân Quyên</t>
   </si>
   <si>
     <t>Không phải sự cố NLMT</t>
   </si>
   <si>
-    <t>24/08/2026 10:29</t>
-  </si>
-  <si>
     <t>Đã giải thích cho Kh và đóng Ticket</t>
   </si>
   <si>
-    <t>24/08/2026 10:31</t>
-  </si>
-  <si>
     <t>Hồ Thị Mỹ Hạnh</t>
   </si>
   <si>
-    <t>Điều phối lại cho FT</t>
-  </si>
-  <si>
-    <t>24/08/2026 10:34</t>
-  </si>
-  <si>
     <t>Tô Phước</t>
   </si>
   <si>
@@ -1250,9 +1106,6 @@
     <t>KH đã tìm thấy HĐ</t>
   </si>
   <si>
-    <t>24/08/2026 10:37</t>
-  </si>
-  <si>
     <t>Lê Quốc Kỳ</t>
   </si>
   <si>
@@ -1262,158 +1115,55 @@
     <t>PAKH liên quan đến YCTX bên phòng KD</t>
   </si>
   <si>
-    <t>24/08/2026 10:38</t>
-  </si>
-  <si>
     <t>Tạ Văn Sơn Long</t>
-  </si>
-  <si>
-    <t>Đang cập nhật thông tin</t>
-  </si>
-  <si>
-    <t>24/08/2026 10:40</t>
   </si>
   <si>
     <t>Lỗi IVT đã gửi thiết bị đi bảo hành và tạo mới YCBH YCBH_CTO_1786867140558 từ B2C lúc 14:59 16/08/2026
 Hạn hoàn thành 09:00 03/09/2026</t>
   </si>
   <si>
-    <t>24/08/2026 10:46</t>
-  </si>
-  <si>
     <t>Lê Thị Cúc</t>
-  </si>
-  <si>
-    <t>24/08/2026 10:47</t>
   </si>
   <si>
     <t>Khách hàng đang đi công tác, Thứ 7 khách về sẽ trao đổi với khách và ký biên bản xác nhận bảo hành hoặc thay thế khách tự bỏ chi phí. Pin Canadian 450 do chi nhánh cung cấp, hiện pin đang vỡ do ngoại lực.
 Đã làm việc thống nhất với KH. BH 1 tấm pin. Chờ thủ tục xuất hàng ra thay cho KH</t>
   </si>
   <si>
-    <t>24/08/2026 10:55</t>
-  </si>
-  <si>
     <t>Thay thế thiết bị mới</t>
   </si>
   <si>
-    <t>24/08/2026 11:04</t>
-  </si>
-  <si>
-    <t>Tạo mới YCBH YCBH_QNI_1786934328026 từ B2C lúc 09:38 17/08/2026 Hạn hoàn thành 09:00 03/09/2026</t>
-  </si>
-  <si>
-    <t>24/08/2026 11:05</t>
-  </si>
-  <si>
-    <t>Đã gửi email xác nhận chính sách bảo hành với hãng
-Sáng T2 hãng phản hồi
-Tạo mới YCBH YCBH_DLK_1787016249475 từ B2C lúc 08:24 18/08/2026 Hạn hoàn thành 09:00 03/09/2026</t>
-  </si>
-  <si>
-    <t>24/08/2026 11:06</t>
-  </si>
-  <si>
     <t>hỏng metter, hiện đã chuyển về bảo hành cho hãng powrtech từ 18/08, thiết bị metter không tạo được bảo hành. Đang chờ hàng bảo hành về để lắp cho KH, dự kiến 29/8</t>
-  </si>
-  <si>
-    <t>24/08/2026 11:07</t>
   </si>
   <si>
     <t>- Gửi thiết bị đi bảo hành, dự kiến 27/08 về thay cho khách
 Tạo mới YCBH YCBH_CMU_1787372431973 từ B2C lúc 11:20 22/08/2026</t>
   </si>
   <si>
-    <t>24/08/2026 11:09</t>
-  </si>
-  <si>
     <t>Bảo hành IVT và đã tạo bảo hành, dự kiến 29/8 xong
 Tạo mới YCBH YCBH_DTP_1786585633759 từ B2C lúc 08:47 13/08/2026 Hạn hoàn thành 23:59 28/08/2026</t>
   </si>
   <si>
-    <t>24/08/2026 11:11</t>
-  </si>
-  <si>
-    <t>Điều phối lại cho FT kienpv6</t>
-  </si>
-  <si>
-    <t>24/08/2026 11:13</t>
-  </si>
-  <si>
-    <t>24/08/2026 11:31</t>
-  </si>
-  <si>
-    <t>Hệ thống đang dùng bình thường. Ban đầu lắp xong 30kw, giờ hiệu suất chỉ còn 26kw. KH muốn hiệu suất lên lại như ban đầu. CNCT đã kiểm tra xử lý nhưng không chịu cho đóng nên phải tìm phương án. CNCT đã đo nhiệt, cân tải cho KH
-Ngày 24 khách hàng đi công tác về chi nhánh sẽ qua trao đổi lại để đóng tickit</t>
-  </si>
-  <si>
-    <t>24/08/2026 11:34</t>
-  </si>
-  <si>
-    <t>24/08/2026 11:42</t>
-  </si>
-  <si>
     <t>- Đã gửi IVT đi bảo hành dự kiến 03/09 về thay cho khách
 - Tạo mới YCBH YCBH_CMU_1786682703995 từ B2C lúc 11:45 14/08/2026</t>
   </si>
   <si>
-    <t>24/08/2026 11:49</t>
-  </si>
-  <si>
-    <t>- GĐKD đã trao đổi lại với KH, Hợp đồng đã gửi lại KH, Hóa đơn sẽ hẹn lại gửi cho khách. Vấn đề KT đã cho ae kiểm tra giải thích cho KH là hệ HĐ bình thường không lỗi gì, Dự kiến đóng Ticket trc 9h ngyaf 25/8</t>
-  </si>
-  <si>
-    <t>24/08/2026 11:50</t>
-  </si>
-  <si>
     <t>Bùi Thị Tuyết Lan</t>
   </si>
   <si>
     <t>-Đã hẹn lại KH ngày 26/8 xử lý xong cho khách</t>
-  </si>
-  <si>
-    <t>24/08/2026 12:13</t>
   </si>
   <si>
     <t>- Đã gửi thiết bị bảo hành ngày 10/08, dự kiến ngày 28/08 có thiết bị bảo hành. (Tạo mới YCBH YCBH_DNI_1786939964679 từ B2C lúc 11:12 17/08/2026)
 - Ngày 01/09 hoàn thành công tác lắp đặt và chạy thử cho khách hàng</t>
   </si>
   <si>
-    <t>24/08/2026 13:03</t>
-  </si>
-  <si>
-    <t>24/08/2026 13:31</t>
-  </si>
-  <si>
     <t>kt đã nhận đơn và liên hệ khách</t>
   </si>
   <si>
     <t>Đã xử lý xong cho khách hàng</t>
   </si>
   <si>
-    <t>24/08/2026 13:32</t>
-  </si>
-  <si>
     <t>Đã gọi điện cho KH hẹn tư vấn</t>
-  </si>
-  <si>
-    <t>24/08/2026 13:36</t>
-  </si>
-  <si>
-    <t>24/08/2026 13:42</t>
-  </si>
-  <si>
-    <t>24/08/2026 13:48</t>
-  </si>
-  <si>
-    <t>- Tạo mới YCBH YCBH_CMU_1785983741402 từ B2C lúc 09:35 06/08/2026, dự kiến 28/8 thiết bị gửi về
-- Đã gửi pin lưu trữ đi bảo hành và tạo bảo hành, dự kiến 28/8 xong. Chi nhánh CMU phải lấy xe từ chi nhánh lên HCM để gửi thiết bị (không có đơn vị vận chuyển bộ lưu trữ từ CMU=&gt;HCM)</t>
-  </si>
-  <si>
-    <t>Liên hệ KH để xử lý</t>
-  </si>
-  <si>
-    <t>24/08/2026 13:52</t>
   </si>
   <si>
     <t>- Hệ thống NLMT bị sét đánh trúng, hỏng 2 SPD DC + 1 ATS.
@@ -1423,62 +1173,18 @@
 - Dự kiến 28/8 có hàng thay cho khách</t>
   </si>
   <si>
-    <t>24/08/2026 13:56</t>
-  </si>
-  <si>
-    <t>Tủ điện bị cháy, không rõ nguyên nhân. Tâm-TPGP đặt hàng nhưng chưa có thông tin hàng về.
-Dự kiến ngày 24/08 có tủ điện mới thay thế cho khách hàng, chưa thấy thông tin gì.
-Dự kiến ngày 28/08 hoàn thành công tác lắp đặt và chạy thử cho khách hàng.
-Đang yêu cầu gia hạn đến 15/09/2026.</t>
-  </si>
-  <si>
-    <t>24/08/2026 14:08</t>
-  </si>
-  <si>
-    <t>Biến tần Solax hỏng chân MC4
-YCBH YCBH_DNG_1787381571244 từ B2C lúc 13:52 22/08/2026 
-Hạn hoàn thành 09:00 07/09/2026</t>
-  </si>
-  <si>
-    <t>24/08/2026 14:15</t>
-  </si>
-  <si>
-    <t>Đã gửi email xác nhận chính sách bảo hành với hãng
-Hãng đang yêu cầu ảnh chụp nhưng nhà KH cách xa khoảng 60km, hiện tại chỉ có video quay lại, đã gửi để hãng kiểm tra.
-Tạo mới YCBH YCBH_DLK_1787016249475 từ B2C lúc 08:24 18/08/2026 
-Hạn hoàn thành 09:00 03/09/2026</t>
-  </si>
-  <si>
-    <t>24/08/2026 14:18</t>
-  </si>
-  <si>
     <t>Đã hoàn thành xử lý cho KH
 Tạo mới YCBH YCBH_QNI_1786934328026 từ B2C lúc 09:38 17/08/2026 
 Hạn hoàn thành 09:00 03/09/2026</t>
   </si>
   <si>
-    <t>24/08/2026 14:22</t>
-  </si>
-  <si>
-    <t>Tạo mới YCBH YCBH_CTO_1787219323253 từ B2C lúc 16:48 20/08/2026, dự kiến 4/9 xong</t>
-  </si>
-  <si>
     <t>Đã gửi thiết bị đi bảo hành và Tạo mới YCBH YCBH_CTO_1787219323253 từ B2C lúc 16:48 20/08/2026, dự kiến 4/9 xong</t>
   </si>
   <si>
-    <t>24/08/2026 14:48</t>
-  </si>
-  <si>
-    <t>24/08/2026 14:53</t>
-  </si>
-  <si>
     <t>Nguyễn Minh Phúc</t>
   </si>
   <si>
     <t>Hệ bị mất giám sát, ngày 25/8 KT qua cài lại Wifi</t>
-  </si>
-  <si>
-    <t>24/08/2026 14:57</t>
   </si>
   <si>
     <t>Tủ điện bị cháy, không rõ nguyên nhân. Tâm-TPGP đặt hàng, dự kiến thứ 3-thứ 4 hàng sẽ về, nhưng sẽ thiếu CT do chưa đủ kinh phí.
@@ -1495,25 +1201,16 @@
     <t>26/08/2026</t>
   </si>
   <si>
-    <t>24/08/2026 14:58</t>
-  </si>
-  <si>
     <t>Bùi Quang Vũ</t>
   </si>
   <si>
     <t>Trời mưa nên chưa qua kiểm tra được, đã hẹn lịch KH bjo tạnh thì qua kiểm tra và xử lý</t>
   </si>
   <si>
-    <t>24/08/2026 15:04</t>
-  </si>
-  <si>
     <t>Trần Văn Túy</t>
   </si>
   <si>
     <t>Nghi ngờ bị hỏng ATS. Đang liên hệ KH</t>
-  </si>
-  <si>
-    <t>24/08/2026 15:12</t>
   </si>
   <si>
     <t>- Ticket bảo hành trên 15 ngày, CSKH đã yêu cầu giải trình
@@ -1521,37 +1218,22 @@
 - Đã gửi pin lưu trữ đi bảo hành và tạo bảo hành, dự kiến 28/8 xong. Chi nhánh CMU phải lấy xe từ chi nhánh lên HCM để gửi thiết bị (không có đơn vị vận chuyển bộ lưu trữ từ CMU=&gt;HCM)</t>
   </si>
   <si>
-    <t>24/08/2026 15:14</t>
-  </si>
-  <si>
     <t>Ngô Bá Tuấn</t>
   </si>
   <si>
     <t>Mất kết nối giám sát</t>
   </si>
   <si>
-    <t>24/08/2026 15:15</t>
-  </si>
-  <si>
     <t>Nguyễn Anh Tuấn</t>
   </si>
   <si>
     <t>Cập nhật lại phần mềm app</t>
   </si>
   <si>
-    <t>24/08/2026 15:16</t>
-  </si>
-  <si>
     <t>Phan Cao Cường</t>
   </si>
   <si>
     <t>Lỗi ATS</t>
-  </si>
-  <si>
-    <t>24/08/2026 15:23</t>
-  </si>
-  <si>
-    <t>24/08/2026 15:26</t>
   </si>
   <si>
     <t>- đang đặng hàng mua ngoài nhưng chưa có, dự kiến 1/9 có hàng xử lý cho khách
@@ -1559,37 +1241,22 @@
 CN đã mua lại để thay cho KH và KH đã đồng ý</t>
   </si>
   <si>
-    <t>24/08/2026 15:41</t>
-  </si>
-  <si>
     <t>Tạo mới YCBH YCBH_TNH_1786501745031 từ B2C lúc 09:29 12/08/2026
 Hỏng logger, (hãng Deye) đã gửi bảo hành cho Powetech từ 12/08. 21/08 Hãng yêu cầu gửi thêm bo Wifi, hiện chi nhánh đã gửi, FT 3 Tiến 0868285199 đang xử lý
 - 24/08, hôm nay hãng gửi hỏa tốc thiết bị về, dự kiến xong trc 28/8</t>
   </si>
   <si>
-    <t>24/08/2026 15:43</t>
-  </si>
-  <si>
     <t>Hệ thống đang dùng bình thường. Ban đầu lắp xong 30kw, giờ hiệu suất chỉ còn 26kw. KH muốn hiệu suất lên lại như ban đầu. CNCT đã cho người đo nhiệt, cân tải nhưng chưa tìm được phương án giải quyết cho KH nên KH không đồng ý cho đóng ticket. Đã tạo nhóm điều hành để trao đổi phương án xử lý.</t>
-  </si>
-  <si>
-    <t>24/08/2026 15:46</t>
   </si>
   <si>
     <t>- KH chưa nghe máy =&gt; Liên hệ lại với KH
 - Đã qua kiểm tra xử lý cho khách, IVT lỗi phần mềm phối hợp vs hãng cập nhật cho khách và hoàn thành Ticket</t>
   </si>
   <si>
-    <t>24/08/2026 16:19</t>
-  </si>
-  <si>
     <t>Hỏng biến tần, hàng từ chối bảo hành, Đã tạo nhóm để điều hành ticket này,.
 Ngày 26/8 sẽ qua nhà KH trao đổi</t>
   </si>
   <si>
-    <t>24/08/2026 16:20</t>
-  </si>
-  <si>
     <t>honbgr biến tần huawei, hàng giải tồn của TCT, hiện đang gửi vào HCM để sửa. dự kiến 25-28/08 mới sửa xong.
 CN HNI đang làm tờ trình xin kinh phí sửa chữa. Dự kiến ngày 26/8 trình ký</t>
   </si>
@@ -1598,34 +1265,15 @@
 Hãng đang yêu cầu ảnh chụp nhưng nhà KH cách xa khoảng 60km, hiện tại chỉ có video quay lại, đã gửi để hãng kiểm tra.</t>
   </si>
   <si>
-    <t>24/08/2026 16:21</t>
-  </si>
-  <si>
     <t>Đã tạo nhóm whatsapp, đang triển khai cho khách hàng
 Hãng đã BH xong, chờ KH trả tiền là gửi lại tb. Dự kiến ngày 28/8 KH đóng tiền</t>
   </si>
   <si>
-    <t>24/08/2026 16:24</t>
-  </si>
-  <si>
     <t>Lỗi sạc xả acquy đã cài lại cho khách</t>
-  </si>
-  <si>
-    <t>24/08/2026 16:26</t>
   </si>
   <si>
     <t>Biến tần Solax hỏng chân MC4
 Thiết bị đã gửi bảo hành, mai sẽ lắp đặt cho KH</t>
-  </si>
-  <si>
-    <t>24/08/2026 16:34</t>
-  </si>
-  <si>
-    <t>Điều phối lại cho FT kienpv6
-Đang tiếp nhận và xử lý</t>
-  </si>
-  <si>
-    <t>24/08/2026 16:43</t>
   </si>
   <si>
     <t>Metter hết hạn bảo hành đã báo KH và đóng đóng Ticket
@@ -1633,59 +1281,131 @@
 Đã đến nhà KH để kiểm tra và thông báo cho KH</t>
   </si>
   <si>
-    <t>24/08/2026 17:37</t>
-  </si>
-  <si>
-    <t>25/08/2026 08:02</t>
-  </si>
-  <si>
-    <t>25/08/2026 08:44</t>
-  </si>
-  <si>
-    <t>- Đã gửi hóa đơn vat và giải thích CB đóng ngắt DC khi bật tắt không có hiện tượng cho khách hiểu và đóng Ticket
+    <t>NGUYỄN NGỌC HUY</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thu Hương</t>
+  </si>
+  <si>
+    <t>Lê Điền</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn Quý</t>
+  </si>
+  <si>
+    <t>25/08/2026 09:46</t>
+  </si>
+  <si>
+    <t>25/08/2026 09:47</t>
+  </si>
+  <si>
+    <t>25/08/2026 09:48</t>
+  </si>
+  <si>
+    <t>Điều phối lại cho FT kienpv6
+Đang ở nhà KH xử lý sự cố, đã xin gia hạn đến 12:25:00 25/08/2026</t>
+  </si>
+  <si>
+    <t>Phạm Đình Văn</t>
+  </si>
+  <si>
+    <t>Hẹn khách chiều 14h qua thực hiện</t>
+  </si>
+  <si>
+    <t>25/08/2026 09:49</t>
+  </si>
+  <si>
+    <t>25/08/2026 09:50</t>
+  </si>
+  <si>
+    <t>25/08/2026 09:51</t>
+  </si>
+  <si>
+    <t>- GĐKD đã gửi hóa đơn vat và giải thích CB đóng ngắt DC khi bật tắt không có hiện tượng và đóng Ticket
 - GĐKD đã trao đổi lại với KH, Hợp đồng đã gửi lại KH, Hóa đơn sẽ hẹn lại gửi cho khách. Vấn đề KT đã cho ae kiểm tra giải thích cho KH là hệ HĐ bình thường không lỗi gì, Dự kiến đóng Ticket trc 9h ngyaf 25/8</t>
   </si>
   <si>
-    <t>25/08/2026 08:46</t>
-  </si>
-  <si>
-    <t>25/08/2026 08:49</t>
-  </si>
-  <si>
-    <t>25/08/2026 08:51</t>
-  </si>
-  <si>
-    <t>25/08/2026 08:52</t>
-  </si>
-  <si>
-    <t>25/08/2026 08:53</t>
-  </si>
-  <si>
-    <t>25/08/2026 08:54</t>
-  </si>
-  <si>
-    <t>25/08/2026 08:55</t>
-  </si>
-  <si>
-    <t>NGUYỄN NGỌC HUY</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Thu Hương</t>
-  </si>
-  <si>
-    <t>Lê Điền</t>
-  </si>
-  <si>
-    <t>25/08/2026 08:56</t>
-  </si>
-  <si>
-    <t>25/08/2026 08:57</t>
-  </si>
-  <si>
-    <t>Nguyễn Văn Quý</t>
-  </si>
-  <si>
-    <t>Đang xử lý cho KH, dự kiến hoàn thành trước 17h</t>
+    <t>25/08/2026 09:52</t>
+  </si>
+  <si>
+    <t>- Đ/c Khánh báo đang xử lý cho khách, dự kiến đóng Ticket trước 15h ngày 25/8</t>
+  </si>
+  <si>
+    <t>- KT đã liên hệ với KH và hôm nay hỗ trợ KH phần cài kết nối App trc và kiểm tra thêm cho khách</t>
+  </si>
+  <si>
+    <t>- GĐKD Tùng đang hỗ trợ làm thủ tục cho KH dự kiến xong trước 28/8</t>
+  </si>
+  <si>
+    <t>25/08/2026 09:53</t>
+  </si>
+  <si>
+    <t>25/08/2026 09:54</t>
+  </si>
+  <si>
+    <t>25/08/2026 09:55</t>
+  </si>
+  <si>
+    <t>- Dự kiến ngày mai về hàng rồi thay cho khách, xử lý xong trước 28/8
+- Hệ thống NLMT bị sét đánh trúng, hỏng 2 SPD DC + 1 ATS.
+- Đã lắp đặt hệ thống để thiết bị hoạt động không bị mất sản lượng.
+- Thiết bị nhập khẩu Trung Quốc, hiện tại không sẵn hàng.
+- Khách hàng không đồng ý đổi sang mã hàng tương đương.
+- Dự kiến 28/8 có hàng thay cho khách</t>
+  </si>
+  <si>
+    <t>25/08/2026 09:56</t>
+  </si>
+  <si>
+    <t>25/08/2026 09:57</t>
+  </si>
+  <si>
+    <t>25/08/2026 09:58</t>
+  </si>
+  <si>
+    <t>Phạm Văn Trọng</t>
+  </si>
+  <si>
+    <t>Phạm Văn Hương</t>
+  </si>
+  <si>
+    <t>Nhuyễn Văn Hùng</t>
+  </si>
+  <si>
+    <t>Phạm Đình Phương</t>
+  </si>
+  <si>
+    <t>25/08/2026 10:03</t>
+  </si>
+  <si>
+    <t>Hệ thống lỗi, Đã khắc phục cho KH</t>
+  </si>
+  <si>
+    <t>25/08/2026 10:04</t>
+  </si>
+  <si>
+    <t>Hỏng biến tần Ehuatech, hệ lắp từ 2022, hiện đang tìm lại dữ liệu hãng để liên hệ bảo hành.
+Ngày 25/8 tháo IVT để gửi hãng BH</t>
+  </si>
+  <si>
+    <t>Biến tần Solax hỏng chân MC4
+Đã xử lý xong cho KH</t>
+  </si>
+  <si>
+    <t>- Đã bảo hành và lắp xong cho khách 
+Lỗi IVT đã gửi thiết bị đi bảo hành và tạo mới YCBH YCBH_CTO_1786867140558 từ B2C lúc 14:59 16/08/2026
+Hạn hoàn thành 09:00 03/09/2026</t>
+  </si>
+  <si>
+    <t>25/08/2026 10:19</t>
+  </si>
+  <si>
+    <t>25/08/2026 10:21</t>
+  </si>
+  <si>
+    <t>Điều phối lại cho FT kienpv6
+Đang ở nhà KH xử lý sự cố, đã xin gia hạn đến 12:25:00 25/08/2026
+test</t>
   </si>
 </sst>
 </file>
@@ -2097,8 +1817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{271A8CFB-3293-473B-894F-86B249B2B19B}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:K999"/>
+  <dimension ref="A1:K951"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.625" bestFit="1" customWidth="1"/>
@@ -2149,7 +1868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -2182,7 +1901,7 @@
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
@@ -2215,7 +1934,7 @@
       </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>21</v>
       </c>
@@ -2248,7 +1967,7 @@
       </c>
       <c r="K4" s="5"/>
     </row>
-    <row r="5" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
@@ -2279,7 +1998,7 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
@@ -2308,7 +2027,7 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>29</v>
       </c>
@@ -2337,7 +2056,7 @@
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
@@ -2368,7 +2087,7 @@
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>36</v>
       </c>
@@ -2399,7 +2118,7 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
@@ -2430,7 +2149,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
@@ -2461,7 +2180,7 @@
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>47</v>
       </c>
@@ -2492,7 +2211,7 @@
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
     </row>
-    <row r="13" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>52</v>
       </c>
@@ -2523,7 +2242,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>56</v>
       </c>
@@ -2554,7 +2273,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>59</v>
       </c>
@@ -2585,7 +2304,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>63</v>
       </c>
@@ -2616,7 +2335,7 @@
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>66</v>
       </c>
@@ -2647,7 +2366,7 @@
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>71</v>
       </c>
@@ -2678,7 +2397,7 @@
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>75</v>
       </c>
@@ -2709,7 +2428,7 @@
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>79</v>
       </c>
@@ -2740,7 +2459,7 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>82</v>
       </c>
@@ -2771,7 +2490,7 @@
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
     </row>
-    <row r="22" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>85</v>
       </c>
@@ -2802,7 +2521,7 @@
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
     </row>
-    <row r="23" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>88</v>
       </c>
@@ -2833,7 +2552,7 @@
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
     </row>
-    <row r="24" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>92</v>
       </c>
@@ -2864,7 +2583,7 @@
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
     </row>
-    <row r="25" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>92</v>
       </c>
@@ -2895,7 +2614,7 @@
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
     </row>
-    <row r="26" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>96</v>
       </c>
@@ -2924,7 +2643,7 @@
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
     </row>
-    <row r="27" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>98</v>
       </c>
@@ -2955,7 +2674,7 @@
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
     </row>
-    <row r="28" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>102</v>
       </c>
@@ -2986,7 +2705,7 @@
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>106</v>
       </c>
@@ -3015,7 +2734,7 @@
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
     </row>
-    <row r="30" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>108</v>
       </c>
@@ -3044,7 +2763,7 @@
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
     </row>
-    <row r="31" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>110</v>
       </c>
@@ -3075,7 +2794,7 @@
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
     </row>
-    <row r="32" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>113</v>
       </c>
@@ -3106,7 +2825,7 @@
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
     </row>
-    <row r="33" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>113</v>
       </c>
@@ -3135,7 +2854,7 @@
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
     </row>
-    <row r="34" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>116</v>
       </c>
@@ -3166,7 +2885,7 @@
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
     </row>
-    <row r="35" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>119</v>
       </c>
@@ -3197,7 +2916,7 @@
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
     </row>
-    <row r="36" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>122</v>
       </c>
@@ -3228,7 +2947,7 @@
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
     </row>
-    <row r="37" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>125</v>
       </c>
@@ -3259,7 +2978,7 @@
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
     </row>
-    <row r="38" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>128</v>
       </c>
@@ -3290,7 +3009,7 @@
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
     </row>
-    <row r="39" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>131</v>
       </c>
@@ -3319,7 +3038,7 @@
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
     </row>
-    <row r="40" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>133</v>
       </c>
@@ -3348,7 +3067,7 @@
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
     </row>
-    <row r="41" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>133</v>
       </c>
@@ -3377,7 +3096,7 @@
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
     </row>
-    <row r="42" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>137</v>
       </c>
@@ -3408,7 +3127,7 @@
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
     </row>
-    <row r="43" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>140</v>
       </c>
@@ -3439,7 +3158,7 @@
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
     </row>
-    <row r="44" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>143</v>
       </c>
@@ -3470,7 +3189,7 @@
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
     </row>
-    <row r="45" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>146</v>
       </c>
@@ -3501,7 +3220,7 @@
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
     </row>
-    <row r="46" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>149</v>
       </c>
@@ -3532,7 +3251,7 @@
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
     </row>
-    <row r="47" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>149</v>
       </c>
@@ -3561,7 +3280,7 @@
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
     </row>
-    <row r="48" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>151</v>
       </c>
@@ -3594,7 +3313,7 @@
       </c>
       <c r="K48" s="5"/>
     </row>
-    <row r="49" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>154</v>
       </c>
@@ -3627,7 +3346,7 @@
       </c>
       <c r="K49" s="5"/>
     </row>
-    <row r="50" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>157</v>
       </c>
@@ -3658,7 +3377,7 @@
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
     </row>
-    <row r="51" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>160</v>
       </c>
@@ -3691,7 +3410,7 @@
       </c>
       <c r="K51" s="5"/>
     </row>
-    <row r="52" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>163</v>
       </c>
@@ -3724,7 +3443,7 @@
       </c>
       <c r="K52" s="5"/>
     </row>
-    <row r="53" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>167</v>
       </c>
@@ -3753,7 +3472,7 @@
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
     </row>
-    <row r="54" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>170</v>
       </c>
@@ -3784,7 +3503,7 @@
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
     </row>
-    <row r="55" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>173</v>
       </c>
@@ -3815,7 +3534,7 @@
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
     </row>
-    <row r="56" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>175</v>
       </c>
@@ -3846,7 +3565,7 @@
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
     </row>
-    <row r="57" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>179</v>
       </c>
@@ -3875,7 +3594,7 @@
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
     </row>
-    <row r="58" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>180</v>
       </c>
@@ -3904,7 +3623,7 @@
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
     </row>
-    <row r="59" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>182</v>
       </c>
@@ -3937,7 +3656,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>185</v>
       </c>
@@ -3968,7 +3687,7 @@
       </c>
       <c r="K60" s="5"/>
     </row>
-    <row r="61" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>185</v>
       </c>
@@ -3997,7 +3716,7 @@
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
     </row>
-    <row r="62" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>186</v>
       </c>
@@ -4030,7 +3749,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>191</v>
       </c>
@@ -4063,7 +3782,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>193</v>
       </c>
@@ -4094,7 +3813,7 @@
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
     </row>
-    <row r="65" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>195</v>
       </c>
@@ -4125,7 +3844,7 @@
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
     </row>
-    <row r="66" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>195</v>
       </c>
@@ -4156,7 +3875,7 @@
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
     </row>
-    <row r="67" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>198</v>
       </c>
@@ -4189,7 +3908,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>202</v>
       </c>
@@ -4222,7 +3941,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>206</v>
       </c>
@@ -4255,7 +3974,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>209</v>
       </c>
@@ -4288,7 +4007,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>213</v>
       </c>
@@ -4319,7 +4038,7 @@
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
     </row>
-    <row r="72" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>216</v>
       </c>
@@ -4352,7 +4071,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>219</v>
       </c>
@@ -4385,7 +4104,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>222</v>
       </c>
@@ -4416,7 +4135,7 @@
       <c r="J74" s="5"/>
       <c r="K74" s="5"/>
     </row>
-    <row r="75" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>225</v>
       </c>
@@ -4449,7 +4168,7 @@
       </c>
       <c r="K75" s="5"/>
     </row>
-    <row r="76" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>227</v>
       </c>
@@ -4480,7 +4199,7 @@
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
     </row>
-    <row r="77" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>231</v>
       </c>
@@ -4511,7 +4230,7 @@
       <c r="J77" s="5"/>
       <c r="K77" s="5"/>
     </row>
-    <row r="78" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>233</v>
       </c>
@@ -4544,7 +4263,7 @@
       </c>
       <c r="K78" s="5"/>
     </row>
-    <row r="79" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>234</v>
       </c>
@@ -4575,7 +4294,7 @@
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
     </row>
-    <row r="80" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>236</v>
       </c>
@@ -4606,7 +4325,7 @@
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
     </row>
-    <row r="81" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>237</v>
       </c>
@@ -4637,7 +4356,7 @@
       <c r="J81" s="5"/>
       <c r="K81" s="5"/>
     </row>
-    <row r="82" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>237</v>
       </c>
@@ -4699,7 +4418,7 @@
       <c r="J83" s="5"/>
       <c r="K83" s="5"/>
     </row>
-    <row r="84" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>238</v>
       </c>
@@ -4730,7 +4449,7 @@
       <c r="J84" s="5"/>
       <c r="K84" s="5"/>
     </row>
-    <row r="85" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>238</v>
       </c>
@@ -4761,7 +4480,7 @@
       <c r="J85" s="5"/>
       <c r="K85" s="5"/>
     </row>
-    <row r="86" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>242</v>
       </c>
@@ -4792,7 +4511,7 @@
       <c r="J86" s="5"/>
       <c r="K86" s="5"/>
     </row>
-    <row r="87" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>242</v>
       </c>
@@ -4823,7 +4542,7 @@
       <c r="J87" s="5"/>
       <c r="K87" s="5"/>
     </row>
-    <row r="88" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>243</v>
       </c>
@@ -4856,7 +4575,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>245</v>
       </c>
@@ -4885,7 +4604,7 @@
       <c r="J89" s="5"/>
       <c r="K89" s="5"/>
     </row>
-    <row r="90" spans="1:11" ht="90.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>247</v>
       </c>
@@ -4916,7 +4635,7 @@
       <c r="J90" s="5"/>
       <c r="K90" s="5"/>
     </row>
-    <row r="91" spans="1:11" ht="90.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>247</v>
       </c>
@@ -4947,7 +4666,7 @@
       <c r="J91" s="5"/>
       <c r="K91" s="5"/>
     </row>
-    <row r="92" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>249</v>
       </c>
@@ -4978,7 +4697,7 @@
       <c r="J92" s="5"/>
       <c r="K92" s="5"/>
     </row>
-    <row r="93" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>252</v>
       </c>
@@ -5009,7 +4728,7 @@
       <c r="J93" s="5"/>
       <c r="K93" s="5"/>
     </row>
-    <row r="94" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>255</v>
       </c>
@@ -5038,7 +4757,7 @@
       <c r="J94" s="5"/>
       <c r="K94" s="5"/>
     </row>
-    <row r="95" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>258</v>
       </c>
@@ -5069,7 +4788,7 @@
       <c r="J95" s="5"/>
       <c r="K95" s="5"/>
     </row>
-    <row r="96" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>261</v>
       </c>
@@ -5104,7 +4823,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>262</v>
       </c>
@@ -5135,7 +4854,7 @@
       <c r="J97" s="5"/>
       <c r="K97" s="5"/>
     </row>
-    <row r="98" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>265</v>
       </c>
@@ -5166,7 +4885,7 @@
       <c r="J98" s="5"/>
       <c r="K98" s="5"/>
     </row>
-    <row r="99" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>268</v>
       </c>
@@ -5197,7 +4916,7 @@
       <c r="J99" s="5"/>
       <c r="K99" s="5"/>
     </row>
-    <row r="100" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>269</v>
       </c>
@@ -5228,7 +4947,7 @@
       <c r="J100" s="5"/>
       <c r="K100" s="5"/>
     </row>
-    <row r="101" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>272</v>
       </c>
@@ -5257,7 +4976,7 @@
       <c r="J101" s="5"/>
       <c r="K101" s="5"/>
     </row>
-    <row r="102" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>274</v>
       </c>
@@ -5288,7 +5007,7 @@
       <c r="J102" s="5"/>
       <c r="K102" s="5"/>
     </row>
-    <row r="103" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>274</v>
       </c>
@@ -5319,7 +5038,7 @@
       <c r="J103" s="5"/>
       <c r="K103" s="5"/>
     </row>
-    <row r="104" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>280</v>
       </c>
@@ -5350,7 +5069,7 @@
       <c r="J104" s="5"/>
       <c r="K104" s="5"/>
     </row>
-    <row r="105" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>283</v>
       </c>
@@ -5381,7 +5100,7 @@
       <c r="J105" s="5"/>
       <c r="K105" s="5"/>
     </row>
-    <row r="106" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>286</v>
       </c>
@@ -5412,7 +5131,7 @@
       <c r="J106" s="5"/>
       <c r="K106" s="5"/>
     </row>
-    <row r="107" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>290</v>
       </c>
@@ -5443,7 +5162,7 @@
       <c r="J107" s="5"/>
       <c r="K107" s="5"/>
     </row>
-    <row r="108" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>293</v>
       </c>
@@ -5474,7 +5193,7 @@
       <c r="J108" s="5"/>
       <c r="K108" s="5"/>
     </row>
-    <row r="109" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>296</v>
       </c>
@@ -5505,7 +5224,7 @@
       <c r="J109" s="5"/>
       <c r="K109" s="5"/>
     </row>
-    <row r="110" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>299</v>
       </c>
@@ -5536,102 +5255,106 @@
       <c r="J110" s="5"/>
       <c r="K110" s="5"/>
     </row>
-    <row r="111" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="B111" s="5"/>
+        <v>397</v>
+      </c>
+      <c r="B111" s="4">
+        <v>4612987</v>
+      </c>
       <c r="C111" s="5" t="s">
-        <v>239</v>
+        <v>164</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>69</v>
+        <v>302</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>240</v>
+        <v>384</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>14</v>
+        <v>302</v>
       </c>
       <c r="I111" s="3">
-        <v>34</v>
-      </c>
-      <c r="J111" s="5"/>
-      <c r="K111" s="4" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+      <c r="J111" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K111" s="5"/>
+    </row>
+    <row r="112" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B112" s="4">
+        <v>4615732</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="B112" s="5"/>
-      <c r="C112" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="F112" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>51</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G112" s="5"/>
       <c r="H112" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I112" s="3">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="J112" s="5"/>
-      <c r="K112" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K112" s="5"/>
+    </row>
+    <row r="113" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B113" s="5"/>
+        <v>398</v>
+      </c>
+      <c r="B113" s="4">
+        <v>4615652</v>
+      </c>
       <c r="C113" s="5" t="s">
-        <v>270</v>
+        <v>45</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>229</v>
+        <v>13</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>305</v>
+        <v>360</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>69</v>
+        <v>302</v>
       </c>
       <c r="I113" s="3">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="J113" s="5"/>
       <c r="K113" s="5"/>
     </row>
-    <row r="114" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B114" s="5"/>
+        <v>398</v>
+      </c>
+      <c r="B114" s="4">
+        <v>4615652</v>
+      </c>
       <c r="C114" s="5" t="s">
         <v>45</v>
       </c>
@@ -5639,16 +5362,16 @@
         <v>13</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>308</v>
+        <v>360</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="I114" s="3">
         <v>21</v>
@@ -5656,442 +5379,468 @@
       <c r="J114" s="5"/>
       <c r="K114" s="5"/>
     </row>
-    <row r="115" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B115" s="5"/>
+        <v>398</v>
+      </c>
+      <c r="B115" s="4">
+        <v>4615642</v>
+      </c>
       <c r="C115" s="5" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F115" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="H115" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I115" s="3">
+        <v>25</v>
+      </c>
+      <c r="J115" s="5"/>
+      <c r="K115" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B116" s="4">
+        <v>4615612</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="H116" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I116" s="3">
+        <v>28</v>
+      </c>
+      <c r="J116" s="5"/>
+      <c r="K116" s="5"/>
+    </row>
+    <row r="117" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B117" s="4">
+        <v>4615579</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="H117" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I117" s="3">
         <v>34</v>
       </c>
-      <c r="G115" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H115" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I115" s="3">
-        <v>6</v>
-      </c>
-      <c r="J115" s="5"/>
-      <c r="K115" s="5"/>
-    </row>
-    <row r="116" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G116" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="H116" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I116" s="3">
-        <v>39</v>
-      </c>
-      <c r="J116" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K116" s="5"/>
-    </row>
-    <row r="117" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="F117" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H117" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I117" s="3">
-        <v>11</v>
-      </c>
       <c r="J117" s="5"/>
-      <c r="K117" s="5"/>
-    </row>
-    <row r="118" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K117" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B118" s="5"/>
+        <v>398</v>
+      </c>
+      <c r="B118" s="4">
+        <v>4615275</v>
+      </c>
       <c r="C118" s="5" t="s">
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="I118" s="3">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="J118" s="5"/>
       <c r="K118" s="5"/>
     </row>
-    <row r="119" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B119" s="5"/>
+        <v>399</v>
+      </c>
+      <c r="B119" s="4">
+        <v>4614881</v>
+      </c>
       <c r="C119" s="5" t="s">
-        <v>111</v>
+        <v>168</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>33</v>
+        <v>302</v>
       </c>
       <c r="I119" s="3">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="J119" s="5"/>
       <c r="K119" s="5"/>
     </row>
-    <row r="120" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="B120" s="5"/>
+        <v>399</v>
+      </c>
+      <c r="B120" s="4">
+        <v>4612186</v>
+      </c>
       <c r="C120" s="5" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>319</v>
+        <v>388</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>33</v>
+        <v>302</v>
       </c>
       <c r="I120" s="3">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="J120" s="5"/>
       <c r="K120" s="5"/>
     </row>
-    <row r="121" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B121" s="5"/>
+        <v>399</v>
+      </c>
+      <c r="B121" s="4">
+        <v>4615761</v>
+      </c>
       <c r="C121" s="5" t="s">
-        <v>111</v>
+        <v>273</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>33</v>
+        <v>302</v>
       </c>
       <c r="I121" s="3">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="J121" s="5"/>
       <c r="K121" s="5"/>
     </row>
-    <row r="122" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B122" s="5"/>
+        <v>399</v>
+      </c>
+      <c r="B122" s="4">
+        <v>4615758</v>
+      </c>
       <c r="C122" s="5" t="s">
-        <v>48</v>
+        <v>339</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>49</v>
+        <v>165</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>323</v>
+        <v>400</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>14</v>
+        <v>302</v>
       </c>
       <c r="I122" s="3">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="J122" s="5"/>
-      <c r="K122" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K122" s="5"/>
+    </row>
+    <row r="123" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B123" s="5"/>
+        <v>399</v>
+      </c>
+      <c r="B123" s="4">
+        <v>4615727</v>
+      </c>
       <c r="C123" s="5" t="s">
-        <v>48</v>
+        <v>287</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>49</v>
+        <v>288</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="H123" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I123" s="3">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="J123" s="5"/>
-      <c r="K123" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K123" s="5"/>
+    </row>
+    <row r="124" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B124" s="5"/>
+        <v>399</v>
+      </c>
+      <c r="B124" s="4">
+        <v>4615727</v>
+      </c>
       <c r="C124" s="5" t="s">
-        <v>326</v>
+        <v>287</v>
       </c>
       <c r="D124" s="5" t="s">
         <v>288</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>327</v>
+        <v>289</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>307</v>
+        <v>14</v>
       </c>
       <c r="I124" s="3">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="J124" s="5"/>
       <c r="K124" s="5"/>
     </row>
-    <row r="125" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B125" s="5"/>
+        <v>399</v>
+      </c>
+      <c r="B125" s="4">
+        <v>4615789</v>
+      </c>
       <c r="C125" s="5" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>330</v>
+        <v>288</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>331</v>
+        <v>390</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>17</v>
+        <v>302</v>
       </c>
       <c r="I125" s="3">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="J125" s="5"/>
       <c r="K125" s="5"/>
     </row>
-    <row r="126" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B126" s="5"/>
+        <v>399</v>
+      </c>
+      <c r="B126" s="4">
+        <v>4615784</v>
+      </c>
       <c r="C126" s="5" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>229</v>
+        <v>13</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>17</v>
+        <v>302</v>
       </c>
       <c r="I126" s="3">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="J126" s="5"/>
       <c r="K126" s="5"/>
     </row>
-    <row r="127" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B127" s="5"/>
+        <v>399</v>
+      </c>
+      <c r="B127" s="4">
+        <v>4615783</v>
+      </c>
       <c r="C127" s="5" t="s">
-        <v>336</v>
+        <v>308</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>288</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>337</v>
+        <v>309</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="I127" s="3">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="J127" s="5"/>
       <c r="K127" s="5"/>
     </row>
-    <row r="128" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B128" s="5"/>
+        <v>399</v>
+      </c>
+      <c r="B128" s="4">
+        <v>4615775</v>
+      </c>
       <c r="C128" s="5" t="s">
-        <v>126</v>
+        <v>314</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>73</v>
+        <v>288</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>338</v>
+        <v>315</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>33</v>
+        <v>302</v>
       </c>
       <c r="I128" s="3">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="J128" s="5"/>
       <c r="K128" s="5"/>
     </row>
-    <row r="129" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B129" s="5"/>
+        <v>399</v>
+      </c>
+      <c r="B129" s="4">
+        <v>4615766</v>
+      </c>
       <c r="C129" s="5" t="s">
-        <v>340</v>
+        <v>317</v>
       </c>
       <c r="D129" s="5" t="s">
         <v>61</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="I129" s="3">
         <v>96</v>
@@ -6099,301 +5848,327 @@
       <c r="J129" s="5"/>
       <c r="K129" s="5"/>
     </row>
-    <row r="130" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="B130" s="5"/>
+        <v>399</v>
+      </c>
+      <c r="B130" s="4">
+        <v>4615834</v>
+      </c>
       <c r="C130" s="5" t="s">
-        <v>176</v>
+        <v>401</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>177</v>
+        <v>288</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>343</v>
+        <v>402</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>69</v>
+        <v>302</v>
       </c>
       <c r="I130" s="3">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="J130" s="5"/>
       <c r="K130" s="5"/>
     </row>
-    <row r="131" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B131" s="5"/>
+        <v>403</v>
+      </c>
+      <c r="B131" s="4">
+        <v>4615801</v>
+      </c>
       <c r="C131" s="5" t="s">
-        <v>294</v>
+        <v>396</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G131" s="5" t="s">
-        <v>345</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G131" s="5"/>
       <c r="H131" s="5" t="s">
-        <v>33</v>
+        <v>302</v>
       </c>
       <c r="I131" s="3">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="J131" s="5"/>
       <c r="K131" s="5"/>
     </row>
-    <row r="132" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B132" s="5"/>
+        <v>403</v>
+      </c>
+      <c r="B132" s="4">
+        <v>4615716</v>
+      </c>
       <c r="C132" s="5" t="s">
-        <v>347</v>
+        <v>176</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>257</v>
+        <v>177</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>348</v>
+        <v>392</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="I132" s="3">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="J132" s="5"/>
       <c r="K132" s="5"/>
     </row>
-    <row r="133" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="B133" s="5"/>
+        <v>403</v>
+      </c>
+      <c r="B133" s="4">
+        <v>4615713</v>
+      </c>
       <c r="C133" s="5" t="s">
-        <v>350</v>
+        <v>228</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>351</v>
+        <v>230</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="I133" s="3">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="J133" s="5"/>
       <c r="K133" s="5"/>
     </row>
-    <row r="134" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="B134" s="5"/>
+        <v>403</v>
+      </c>
+      <c r="B134" s="4">
+        <v>4615700</v>
+      </c>
       <c r="C134" s="5" t="s">
-        <v>340</v>
+        <v>223</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>61</v>
+        <v>177</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>352</v>
+        <v>224</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>307</v>
+        <v>69</v>
       </c>
       <c r="I134" s="3">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="J134" s="5"/>
       <c r="K134" s="5"/>
     </row>
-    <row r="135" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="B135" s="5"/>
+        <v>403</v>
+      </c>
+      <c r="B135" s="4">
+        <v>4615690</v>
+      </c>
       <c r="C135" s="5" t="s">
-        <v>354</v>
+        <v>41</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="I135" s="3">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="J135" s="5"/>
-      <c r="K135" s="5"/>
-    </row>
-    <row r="136" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K135" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B136" s="5"/>
+        <v>403</v>
+      </c>
+      <c r="B136" s="4">
+        <v>4615669</v>
+      </c>
       <c r="C136" s="5" t="s">
-        <v>275</v>
+        <v>220</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>276</v>
+        <v>177</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="H136" s="5" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="I136" s="3">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="J136" s="5"/>
-      <c r="K136" s="5"/>
-    </row>
-    <row r="137" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K136" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B137" s="5"/>
+        <v>403</v>
+      </c>
+      <c r="B137" s="4">
+        <v>4615648</v>
+      </c>
       <c r="C137" s="5" t="s">
-        <v>263</v>
+        <v>93</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>359</v>
+        <v>94</v>
       </c>
       <c r="H137" s="5" t="s">
         <v>69</v>
       </c>
       <c r="I137" s="3">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="J137" s="5"/>
       <c r="K137" s="5"/>
     </row>
-    <row r="138" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="B138" s="5"/>
+        <v>403</v>
+      </c>
+      <c r="B138" s="4">
+        <v>4615646</v>
+      </c>
       <c r="C138" s="5" t="s">
-        <v>266</v>
+        <v>76</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>267</v>
+        <v>382</v>
       </c>
       <c r="H138" s="5" t="s">
         <v>69</v>
       </c>
       <c r="I138" s="3">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="J138" s="5"/>
       <c r="K138" s="5"/>
     </row>
-    <row r="139" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B139" s="5"/>
+        <v>403</v>
+      </c>
+      <c r="B139" s="4">
+        <v>4615610</v>
+      </c>
       <c r="C139" s="5" t="s">
-        <v>259</v>
+        <v>181</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="H139" s="5" t="s">
         <v>69</v>
       </c>
       <c r="I139" s="3">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="J139" s="5"/>
-      <c r="K139" s="5"/>
-    </row>
-    <row r="140" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K139" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="B140" s="5"/>
+        <v>403</v>
+      </c>
+      <c r="B140" s="4">
+        <v>4615589</v>
+      </c>
       <c r="C140" s="5" t="s">
         <v>67</v>
       </c>
@@ -6401,13 +6176,13 @@
         <v>68</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>361</v>
+        <v>327</v>
       </c>
       <c r="H140" s="5" t="s">
         <v>69</v>
@@ -6418,4001 +6193,3373 @@
       <c r="J140" s="5"/>
       <c r="K140" s="5"/>
     </row>
-    <row r="141" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B141" s="5"/>
+        <v>404</v>
+      </c>
+      <c r="B141" s="4">
+        <v>4615580</v>
+      </c>
       <c r="C141" s="5" t="s">
-        <v>253</v>
+        <v>80</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>254</v>
+        <v>330</v>
       </c>
       <c r="H141" s="5" t="s">
         <v>69</v>
       </c>
       <c r="I141" s="3">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="J141" s="5"/>
       <c r="K141" s="5"/>
     </row>
-    <row r="142" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B142" s="5"/>
+        <v>404</v>
+      </c>
+      <c r="B142" s="4">
+        <v>4615553</v>
+      </c>
       <c r="C142" s="5" t="s">
-        <v>297</v>
+        <v>99</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="H142" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I142" s="3">
+        <v>35</v>
+      </c>
+      <c r="J142" s="5"/>
+      <c r="K142" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B143" s="4">
+        <v>4615536</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="H143" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="I142" s="3">
-        <v>82</v>
-      </c>
-      <c r="J142" s="5"/>
-      <c r="K142" s="5"/>
-    </row>
-    <row r="143" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="B143" s="5"/>
-      <c r="C143" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="D143" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E143" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="F143" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G143" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="H143" s="5" t="s">
+      <c r="I143" s="3">
+        <v>36</v>
+      </c>
+      <c r="J143" s="5"/>
+      <c r="K143" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B144" s="4">
+        <v>4615525</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="H144" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I143" s="3">
-        <v>84</v>
-      </c>
-      <c r="J143" s="5"/>
-      <c r="K143" s="5"/>
-    </row>
-    <row r="144" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B144" s="5"/>
-      <c r="C144" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G144" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="H144" s="5" t="s">
+      <c r="I144" s="3">
+        <v>37</v>
+      </c>
+      <c r="J144" s="5"/>
+      <c r="K144" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B145" s="4">
+        <v>4615522</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="H145" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="I144" s="3">
-        <v>33</v>
-      </c>
-      <c r="J144" s="5"/>
-      <c r="K144" s="5"/>
-    </row>
-    <row r="145" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B145" s="5"/>
-      <c r="C145" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G145" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="H145" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="I145" s="3">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="J145" s="5"/>
-      <c r="K145" s="5"/>
-    </row>
-    <row r="146" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K145" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="B146" s="5"/>
+        <v>404</v>
+      </c>
+      <c r="B146" s="4">
+        <v>4615494</v>
+      </c>
       <c r="C146" s="5" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>100</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>373</v>
+        <v>338</v>
       </c>
       <c r="H146" s="5" t="s">
         <v>33</v>
       </c>
       <c r="I146" s="3">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J146" s="5"/>
-      <c r="K146" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K146" s="5"/>
+    </row>
+    <row r="147" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B147" s="5"/>
+        <v>404</v>
+      </c>
+      <c r="B147" s="4">
+        <v>4615476</v>
+      </c>
       <c r="C147" s="5" t="s">
-        <v>375</v>
+        <v>53</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="H147" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I147" s="3">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="J147" s="5"/>
-      <c r="K147" s="5"/>
-    </row>
-    <row r="148" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K147" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="B148" s="5"/>
+        <v>404</v>
+      </c>
+      <c r="B148" s="4">
+        <v>4615461</v>
+      </c>
       <c r="C148" s="5" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>43</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="H148" s="5" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="I148" s="3">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J148" s="5"/>
       <c r="K148" s="4" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="B149" s="5"/>
+        <v>404</v>
+      </c>
+      <c r="B149" s="4">
+        <v>4615434</v>
+      </c>
       <c r="C149" s="5" t="s">
-        <v>379</v>
+        <v>207</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>380</v>
+        <v>355</v>
       </c>
       <c r="H149" s="5" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="I149" s="3">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="J149" s="5"/>
-      <c r="K149" s="5"/>
-    </row>
-    <row r="150" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K149" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="B150" s="5"/>
+        <v>404</v>
+      </c>
+      <c r="B150" s="4">
+        <v>4615329</v>
+      </c>
       <c r="C150" s="5" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>382</v>
+        <v>87</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="I150" s="3">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J150" s="5"/>
       <c r="K150" s="5"/>
     </row>
-    <row r="151" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="B151" s="5"/>
+        <v>404</v>
+      </c>
+      <c r="B151" s="4">
+        <v>4615274</v>
+      </c>
       <c r="C151" s="5" t="s">
-        <v>384</v>
+        <v>187</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="H151" s="5" t="s">
-        <v>307</v>
+        <v>69</v>
       </c>
       <c r="I151" s="3">
+        <v>48</v>
+      </c>
+      <c r="J151" s="5"/>
+      <c r="K151" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B152" s="4">
+        <v>4614161</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H152" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J151" s="5"/>
-      <c r="K151" s="5"/>
-    </row>
-    <row r="152" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B152" s="5"/>
-      <c r="C152" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="D152" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E152" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F152" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G152" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="H152" s="5" t="s">
-        <v>307</v>
-      </c>
       <c r="I152" s="3">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="J152" s="5"/>
-      <c r="K152" s="5"/>
-    </row>
-    <row r="153" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K152" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B153" s="5"/>
+        <v>405</v>
+      </c>
+      <c r="B153" s="4">
+        <v>4615773</v>
+      </c>
       <c r="C153" s="5" t="s">
-        <v>389</v>
+        <v>246</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="H153" s="5" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="I153" s="3">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="J153" s="5"/>
       <c r="K153" s="5"/>
     </row>
-    <row r="154" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="B154" s="5"/>
+        <v>405</v>
+      </c>
+      <c r="B154" s="4">
+        <v>4615772</v>
+      </c>
       <c r="C154" s="5" t="s">
-        <v>392</v>
+        <v>310</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>393</v>
+        <v>311</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>394</v>
+        <v>312</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I154" s="3">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="J154" s="5"/>
       <c r="K154" s="5"/>
     </row>
-    <row r="155" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="B155" s="5"/>
+        <v>405</v>
+      </c>
+      <c r="B155" s="4">
+        <v>4615756</v>
+      </c>
       <c r="C155" s="5" t="s">
-        <v>396</v>
+        <v>250</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>288</v>
+        <v>229</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>397</v>
+        <v>251</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>307</v>
+        <v>69</v>
       </c>
       <c r="I155" s="3">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="J155" s="5"/>
       <c r="K155" s="5"/>
     </row>
-    <row r="156" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="B156" s="5"/>
+        <v>405</v>
+      </c>
+      <c r="B156" s="4">
+        <v>4615752</v>
+      </c>
       <c r="C156" s="5" t="s">
-        <v>57</v>
+        <v>278</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>399</v>
+        <v>279</v>
       </c>
       <c r="H156" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I156" s="3">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="J156" s="5"/>
-      <c r="K156" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K156" s="5"/>
+    </row>
+    <row r="157" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="B157" s="5"/>
+        <v>405</v>
+      </c>
+      <c r="B157" s="4">
+        <v>4615747</v>
+      </c>
       <c r="C157" s="5" t="s">
-        <v>401</v>
+        <v>281</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>366</v>
+        <v>282</v>
       </c>
       <c r="H157" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I157" s="3">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J157" s="5"/>
       <c r="K157" s="5"/>
     </row>
-    <row r="158" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="B158" s="5" t="s">
-        <v>18</v>
+        <v>405</v>
+      </c>
+      <c r="B158" s="4">
+        <v>4615746</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>155</v>
+        <v>284</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>403</v>
+        <v>285</v>
       </c>
       <c r="H158" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I158" s="3">
-        <v>60</v>
-      </c>
-      <c r="J158" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="J158" s="5"/>
       <c r="K158" s="5"/>
     </row>
-    <row r="159" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="B159" s="5"/>
+        <v>405</v>
+      </c>
+      <c r="B159" s="4">
+        <v>4615739</v>
+      </c>
       <c r="C159" s="5" t="s">
-        <v>168</v>
+        <v>270</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>169</v>
+        <v>229</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>405</v>
+        <v>301</v>
       </c>
       <c r="H159" s="5" t="s">
-        <v>307</v>
+        <v>69</v>
       </c>
       <c r="I159" s="3">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="J159" s="5"/>
       <c r="K159" s="5"/>
     </row>
-    <row r="160" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="B160" s="5"/>
+        <v>405</v>
+      </c>
+      <c r="B160" s="4">
+        <v>4615790</v>
+      </c>
       <c r="C160" s="5" t="s">
-        <v>60</v>
+        <v>356</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>61</v>
+        <v>177</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>407</v>
+        <v>357</v>
       </c>
       <c r="H160" s="5" t="s">
-        <v>307</v>
+        <v>69</v>
       </c>
       <c r="I160" s="3">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="J160" s="5"/>
-      <c r="K160" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K160" s="5"/>
+    </row>
+    <row r="161" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="B161" s="5"/>
+        <v>405</v>
+      </c>
+      <c r="B161" s="4">
+        <v>4615788</v>
+      </c>
       <c r="C161" s="5" t="s">
-        <v>60</v>
+        <v>313</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>61</v>
+        <v>229</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>407</v>
+        <v>385</v>
       </c>
       <c r="H161" s="5" t="s">
-        <v>307</v>
+        <v>17</v>
       </c>
       <c r="I161" s="3">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="J161" s="5"/>
       <c r="K161" s="5"/>
     </row>
-    <row r="162" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B162" s="4">
+        <v>4615817</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G162" s="5" t="s">
         <v>408</v>
       </c>
-      <c r="B162" s="5"/>
-      <c r="C162" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D162" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E162" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F162" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G162" s="5" t="s">
-        <v>409</v>
-      </c>
       <c r="H162" s="5" t="s">
-        <v>307</v>
+        <v>69</v>
       </c>
       <c r="I162" s="3">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="J162" s="5"/>
       <c r="K162" s="5"/>
     </row>
-    <row r="163" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B163" s="4">
+        <v>4615816</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="H163" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I163" s="3">
+        <v>109</v>
+      </c>
+      <c r="J163" s="5"/>
+      <c r="K163" s="5"/>
+    </row>
+    <row r="164" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B164" s="4">
+        <v>4615806</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E164" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G164" s="5" t="s">
         <v>410</v>
-      </c>
-      <c r="B163" s="5"/>
-      <c r="C163" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D163" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E163" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G163" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="H163" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I163" s="3">
-        <v>35</v>
-      </c>
-      <c r="J163" s="5"/>
-      <c r="K163" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="B164" s="5"/>
-      <c r="C164" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="D164" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="E164" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G164" s="5" t="s">
-        <v>413</v>
       </c>
       <c r="H164" s="5" t="s">
         <v>69</v>
       </c>
       <c r="I164" s="3">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="J164" s="5"/>
-      <c r="K164" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K164" s="5"/>
+    </row>
+    <row r="165" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="B165" s="5"/>
+        <v>407</v>
+      </c>
+      <c r="B165" s="4">
+        <v>4614075</v>
+      </c>
       <c r="C165" s="5" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>43</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>415</v>
+        <v>389</v>
       </c>
       <c r="H165" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I165" s="3">
+        <v>57</v>
+      </c>
+      <c r="J165" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K165" s="5"/>
+    </row>
+    <row r="166" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B166" s="4">
+        <v>4612554</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="H166" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I165" s="3">
-        <v>41</v>
-      </c>
-      <c r="J165" s="5"/>
-      <c r="K165" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="B166" s="5"/>
-      <c r="C166" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="D166" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E166" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G166" s="5" t="s">
-        <v>417</v>
-      </c>
-      <c r="H166" s="5" t="s">
-        <v>307</v>
-      </c>
       <c r="I166" s="3">
-        <v>69</v>
-      </c>
-      <c r="J166" s="5"/>
+        <v>60</v>
+      </c>
+      <c r="J166" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="K166" s="5"/>
     </row>
-    <row r="167" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="B167" s="5"/>
+        <v>407</v>
+      </c>
+      <c r="B167" s="4">
+        <v>4615731</v>
+      </c>
       <c r="C167" s="5" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G167" s="5" t="s">
-        <v>118</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G167" s="5"/>
       <c r="H167" s="5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="I167" s="3">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="J167" s="5"/>
-      <c r="K167" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K167" s="5"/>
+    </row>
+    <row r="168" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="B168" s="5" t="s">
-        <v>18</v>
+        <v>407</v>
+      </c>
+      <c r="B168" s="4">
+        <v>4615730</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>165</v>
+        <v>25</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G168" s="5" t="s">
-        <v>420</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G168" s="5"/>
       <c r="H168" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I168" s="3">
-        <v>59</v>
-      </c>
-      <c r="J168" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J168" s="5"/>
       <c r="K168" s="5"/>
     </row>
-    <row r="169" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="B169" s="5" t="s">
-        <v>18</v>
+        <v>407</v>
+      </c>
+      <c r="B169" s="4">
+        <v>4615725</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>420</v>
+        <v>232</v>
       </c>
       <c r="H169" s="5" t="s">
-        <v>307</v>
+        <v>17</v>
       </c>
       <c r="I169" s="3">
-        <v>59</v>
-      </c>
-      <c r="J169" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J169" s="5"/>
       <c r="K169" s="5"/>
     </row>
-    <row r="170" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="B170" s="5"/>
+        <v>407</v>
+      </c>
+      <c r="B170" s="4">
+        <v>4615724</v>
+      </c>
       <c r="C170" s="5" t="s">
-        <v>207</v>
+        <v>144</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
       <c r="E170" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G170" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="F170" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G170" s="5" t="s">
-        <v>423</v>
-      </c>
       <c r="H170" s="5" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="I170" s="3">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="J170" s="5"/>
-      <c r="K170" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K170" s="5"/>
+    </row>
+    <row r="171" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="B171" s="5"/>
+        <v>411</v>
+      </c>
+      <c r="B171" s="4">
+        <v>4615711</v>
+      </c>
       <c r="C171" s="5" t="s">
-        <v>246</v>
+        <v>31</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>425</v>
+        <v>35</v>
       </c>
       <c r="H171" s="5" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="I171" s="3">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="J171" s="5"/>
       <c r="K171" s="5"/>
     </row>
-    <row r="172" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="B172" s="5"/>
+        <v>411</v>
+      </c>
+      <c r="B172" s="4">
+        <v>4615710</v>
+      </c>
       <c r="C172" s="5" t="s">
-        <v>427</v>
+        <v>103</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>34</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>428</v>
+        <v>235</v>
       </c>
       <c r="H172" s="5" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="I172" s="3">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="J172" s="5"/>
       <c r="K172" s="5"/>
     </row>
-    <row r="173" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="B173" s="5"/>
+        <v>411</v>
+      </c>
+      <c r="B173" s="4">
+        <v>4615704</v>
+      </c>
       <c r="C173" s="5" t="s">
-        <v>217</v>
+        <v>37</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>177</v>
+        <v>38</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>430</v>
+        <v>39</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="I173" s="3">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="J173" s="5"/>
-      <c r="K173" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="174" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K173" s="5"/>
+    </row>
+    <row r="174" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="B174" s="5"/>
+        <v>411</v>
+      </c>
+      <c r="B174" s="4">
+        <v>4615698</v>
+      </c>
       <c r="C174" s="5" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G174" s="5" t="s">
-        <v>26</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G174" s="5"/>
       <c r="H174" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I174" s="3">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="J174" s="5"/>
       <c r="K174" s="5"/>
     </row>
-    <row r="175" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="B175" s="5"/>
+        <v>411</v>
+      </c>
+      <c r="B175" s="4">
+        <v>4615692</v>
+      </c>
       <c r="C175" s="5" t="s">
-        <v>273</v>
+        <v>138</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>433</v>
+        <v>139</v>
       </c>
       <c r="H175" s="5" t="s">
-        <v>307</v>
+        <v>33</v>
       </c>
       <c r="I175" s="3">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="J175" s="5"/>
       <c r="K175" s="5"/>
     </row>
-    <row r="176" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="B176" s="5"/>
+        <v>411</v>
+      </c>
+      <c r="B176" s="4">
+        <v>4615676</v>
+      </c>
       <c r="C176" s="5" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G176" s="5" t="s">
-        <v>434</v>
-      </c>
+      <c r="G176" s="5"/>
       <c r="H176" s="5" t="s">
-        <v>307</v>
+        <v>33</v>
       </c>
       <c r="I176" s="3">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J176" s="5"/>
       <c r="K176" s="5"/>
     </row>
-    <row r="177" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="B177" s="5"/>
+        <v>411</v>
+      </c>
+      <c r="B177" s="4">
+        <v>4615672</v>
+      </c>
       <c r="C177" s="5" t="s">
-        <v>340</v>
+        <v>109</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G177" s="5" t="s">
-        <v>436</v>
-      </c>
+      <c r="G177" s="5"/>
       <c r="H177" s="5" t="s">
-        <v>307</v>
+        <v>33</v>
       </c>
       <c r="I177" s="3">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="J177" s="5"/>
       <c r="K177" s="5"/>
     </row>
-    <row r="178" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>18</v>
+        <v>411</v>
+      </c>
+      <c r="B178" s="4">
+        <v>4615658</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>420</v>
+        <v>204</v>
       </c>
       <c r="H178" s="5" t="s">
-        <v>307</v>
+        <v>69</v>
       </c>
       <c r="I178" s="3">
-        <v>59</v>
-      </c>
-      <c r="J178" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K178" s="5"/>
-    </row>
-    <row r="179" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="J178" s="5"/>
+      <c r="K178" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="B179" s="5"/>
+        <v>411</v>
+      </c>
+      <c r="B179" s="4">
+        <v>4615655</v>
+      </c>
       <c r="C179" s="5" t="s">
-        <v>384</v>
+        <v>199</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>417</v>
+        <v>200</v>
       </c>
       <c r="H179" s="5" t="s">
-        <v>307</v>
+        <v>69</v>
       </c>
       <c r="I179" s="3">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="J179" s="5"/>
-      <c r="K179" s="5"/>
-    </row>
-    <row r="180" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K179" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>18</v>
+        <v>411</v>
+      </c>
+      <c r="B180" s="4">
+        <v>4615644</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>188</v>
+        <v>38</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>440</v>
+        <v>142</v>
       </c>
       <c r="H180" s="5" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="I180" s="3">
-        <v>48</v>
-      </c>
-      <c r="J180" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K180" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="181" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="J180" s="5"/>
+      <c r="K180" s="5"/>
+    </row>
+    <row r="181" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="B181" s="5"/>
+        <v>411</v>
+      </c>
+      <c r="B181" s="4">
+        <v>4615622</v>
+      </c>
       <c r="C181" s="5" t="s">
-        <v>396</v>
+        <v>158</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>288</v>
+        <v>104</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>441</v>
+        <v>159</v>
       </c>
       <c r="H181" s="5" t="s">
-        <v>307</v>
+        <v>33</v>
       </c>
       <c r="I181" s="3">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="J181" s="5"/>
       <c r="K181" s="5"/>
     </row>
-    <row r="182" spans="1:11" ht="116.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="B182" s="5"/>
+        <v>412</v>
+      </c>
+      <c r="B182" s="4">
+        <v>4615615</v>
+      </c>
       <c r="C182" s="5" t="s">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>443</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G182" s="5"/>
       <c r="H182" s="5" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="I182" s="3">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J182" s="5"/>
-      <c r="K182" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="183" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K182" s="5"/>
+    </row>
+    <row r="183" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="B183" s="5"/>
+        <v>412</v>
+      </c>
+      <c r="B183" s="4">
+        <v>4615609</v>
+      </c>
       <c r="C183" s="5" t="s">
-        <v>239</v>
+        <v>97</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G183" s="5" t="s">
-        <v>445</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G183" s="5"/>
       <c r="H183" s="5" t="s">
-        <v>307</v>
+        <v>33</v>
       </c>
       <c r="I183" s="3">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="J183" s="5"/>
-      <c r="K183" s="4" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K183" s="5"/>
+    </row>
+    <row r="184" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="B184" s="5"/>
+        <v>412</v>
+      </c>
+      <c r="B184" s="4">
+        <v>4615585</v>
+      </c>
       <c r="C184" s="5" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>447</v>
+        <v>306</v>
       </c>
       <c r="H184" s="5" t="s">
-        <v>307</v>
+        <v>33</v>
       </c>
       <c r="I184" s="3">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J184" s="5"/>
       <c r="K184" s="5"/>
     </row>
-    <row r="185" spans="1:11" ht="90.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="B185" s="5"/>
+        <v>412</v>
+      </c>
+      <c r="B185" s="4">
+        <v>4615505</v>
+      </c>
       <c r="C185" s="5" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="G185" s="5" t="s">
-        <v>449</v>
+        <v>305</v>
       </c>
       <c r="H185" s="5" t="s">
-        <v>307</v>
+        <v>17</v>
       </c>
       <c r="I185" s="3">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="J185" s="5"/>
       <c r="K185" s="5"/>
     </row>
-    <row r="186" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="B186" s="5"/>
+        <v>412</v>
+      </c>
+      <c r="B186" s="4">
+        <v>4615316</v>
+      </c>
       <c r="C186" s="5" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G186" s="5" t="s">
-        <v>451</v>
+        <v>91</v>
       </c>
       <c r="H186" s="5" t="s">
-        <v>307</v>
+        <v>69</v>
       </c>
       <c r="I186" s="3">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="J186" s="5"/>
       <c r="K186" s="5"/>
     </row>
-    <row r="187" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="B187" s="5"/>
+        <v>412</v>
+      </c>
+      <c r="B187" s="4">
+        <v>4615297</v>
+      </c>
       <c r="C187" s="5" t="s">
-        <v>41</v>
+        <v>120</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>453</v>
+        <v>386</v>
       </c>
       <c r="H187" s="5" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="I187" s="3">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="J187" s="5"/>
-      <c r="K187" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="188" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K187" s="5"/>
+    </row>
+    <row r="188" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="B188" s="5"/>
+        <v>412</v>
+      </c>
+      <c r="B188" s="4">
+        <v>4615167</v>
+      </c>
       <c r="C188" s="5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G188" s="5" t="s">
-        <v>454</v>
+        <v>307</v>
       </c>
       <c r="H188" s="5" t="s">
         <v>14</v>
       </c>
       <c r="I188" s="3">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="J188" s="5"/>
       <c r="K188" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="189" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="B189" s="5" t="s">
-        <v>18</v>
+        <v>412</v>
+      </c>
+      <c r="B189" s="4">
+        <v>4615145</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>313</v>
+        <v>124</v>
       </c>
       <c r="H189" s="5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I189" s="3">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="J189" s="5"/>
       <c r="K189" s="5"/>
     </row>
-    <row r="190" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="B190" s="5" t="s">
-        <v>18</v>
+        <v>412</v>
+      </c>
+      <c r="B190" s="4">
+        <v>4615039</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G190" s="5" t="s">
-        <v>403</v>
+        <v>316</v>
       </c>
       <c r="H190" s="5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I190" s="3">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="J190" s="5"/>
       <c r="K190" s="5"/>
     </row>
-    <row r="191" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="B191" s="5"/>
+        <v>412</v>
+      </c>
+      <c r="B191" s="4">
+        <v>4614938</v>
+      </c>
       <c r="C191" s="5" t="s">
-        <v>457</v>
+        <v>196</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G191" s="5" t="s">
-        <v>458</v>
+        <v>248</v>
       </c>
       <c r="H191" s="5" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="I191" s="3">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="J191" s="5"/>
       <c r="K191" s="5"/>
     </row>
-    <row r="192" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="B192" s="5"/>
+        <v>413</v>
+      </c>
+      <c r="B192" s="4">
+        <v>4614836</v>
+      </c>
       <c r="C192" s="5" t="s">
-        <v>239</v>
+        <v>129</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G192" s="5" t="s">
-        <v>460</v>
+        <v>387</v>
       </c>
       <c r="H192" s="5" t="s">
-        <v>307</v>
+        <v>33</v>
       </c>
       <c r="I192" s="3">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="J192" s="5"/>
-      <c r="K192" s="4" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="193" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K192" s="5"/>
+    </row>
+    <row r="193" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="B193" s="5"/>
+        <v>413</v>
+      </c>
+      <c r="B193" s="4">
+        <v>4614164</v>
+      </c>
       <c r="C193" s="5" t="s">
-        <v>461</v>
+        <v>161</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F193" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>462</v>
+        <v>226</v>
       </c>
       <c r="H193" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I193" s="3">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="J193" s="5"/>
       <c r="K193" s="5"/>
     </row>
-    <row r="194" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="B194" s="5"/>
+        <v>413</v>
+      </c>
+      <c r="B194" s="4">
+        <v>4615774</v>
+      </c>
       <c r="C194" s="5" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>169</v>
+        <v>257</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G194" s="5" t="s">
-        <v>460</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G194" s="5"/>
       <c r="H194" s="5" t="s">
-        <v>307</v>
+        <v>14</v>
       </c>
       <c r="I194" s="3">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="J194" s="5"/>
-      <c r="K194" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="195" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K194" s="5"/>
+    </row>
+    <row r="195" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="B195" s="5"/>
+        <v>413</v>
+      </c>
+      <c r="B195" s="4">
+        <v>4613034</v>
+      </c>
       <c r="C195" s="5" t="s">
-        <v>465</v>
+        <v>72</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>276</v>
+        <v>73</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G195" s="5" t="s">
-        <v>466</v>
+        <v>74</v>
       </c>
       <c r="H195" s="5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I195" s="3">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="J195" s="5"/>
       <c r="K195" s="5"/>
     </row>
-    <row r="196" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="B196" s="5"/>
+        <v>413</v>
+      </c>
+      <c r="B196" s="4">
+        <v>4615771</v>
+      </c>
       <c r="C196" s="5" t="s">
-        <v>468</v>
+        <v>294</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>393</v>
+        <v>90</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="G196" s="5" t="s">
-        <v>469</v>
+        <v>318</v>
       </c>
       <c r="H196" s="5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I196" s="3">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="J196" s="5"/>
       <c r="K196" s="5"/>
     </row>
-    <row r="197" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>18</v>
+        <v>413</v>
+      </c>
+      <c r="B197" s="4">
+        <v>4615770</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>187</v>
+        <v>319</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>188</v>
+        <v>257</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>471</v>
+        <v>320</v>
       </c>
       <c r="H197" s="5" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="I197" s="3">
-        <v>48</v>
-      </c>
-      <c r="J197" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K197" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="198" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+      <c r="J197" s="5"/>
+      <c r="K197" s="5"/>
+    </row>
+    <row r="198" spans="1:11" ht="141.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
-        <v>472</v>
+        <v>413</v>
       </c>
       <c r="B198" s="5"/>
       <c r="C198" s="5" t="s">
-        <v>473</v>
+        <v>220</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="F198" s="5" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="G198" s="5" t="s">
-        <v>474</v>
+        <v>414</v>
       </c>
       <c r="H198" s="5" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="I198" s="3">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="J198" s="5"/>
-      <c r="K198" s="5"/>
-    </row>
-    <row r="199" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K198" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="B199" s="5"/>
+        <v>413</v>
+      </c>
+      <c r="B199" s="4">
+        <v>4615762</v>
+      </c>
       <c r="C199" s="5" t="s">
-        <v>476</v>
+        <v>321</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>136</v>
+        <v>257</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F199" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>477</v>
+        <v>322</v>
       </c>
       <c r="H199" s="5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I199" s="3">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="J199" s="5"/>
       <c r="K199" s="5"/>
     </row>
-    <row r="200" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="B200" s="5"/>
+        <v>413</v>
+      </c>
+      <c r="B200" s="4">
+        <v>4615757</v>
+      </c>
       <c r="C200" s="5" t="s">
-        <v>479</v>
+        <v>323</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G200" s="5" t="s">
-        <v>480</v>
+        <v>324</v>
       </c>
       <c r="H200" s="5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I200" s="3">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="J200" s="5"/>
       <c r="K200" s="5"/>
     </row>
-    <row r="201" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="B201" s="5"/>
+        <v>413</v>
+      </c>
+      <c r="B201" s="4">
+        <v>4615755</v>
+      </c>
       <c r="C201" s="5" t="s">
-        <v>126</v>
+        <v>275</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>73</v>
+        <v>276</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F201" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G201" s="5" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="H201" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="I201" s="3">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="J201" s="5"/>
       <c r="K201" s="5"/>
     </row>
-    <row r="202" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="B202" s="5"/>
+        <v>415</v>
+      </c>
+      <c r="B202" s="4">
+        <v>4615751</v>
+      </c>
       <c r="C202" s="5" t="s">
-        <v>76</v>
+        <v>263</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="G202" s="5" t="s">
-        <v>483</v>
+        <v>326</v>
       </c>
       <c r="H202" s="5" t="s">
         <v>69</v>
       </c>
       <c r="I202" s="3">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="J202" s="5"/>
       <c r="K202" s="5"/>
     </row>
-    <row r="203" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="B203" s="5"/>
+        <v>415</v>
+      </c>
+      <c r="B203" s="4">
+        <v>4615741</v>
+      </c>
       <c r="C203" s="5" t="s">
-        <v>117</v>
+        <v>266</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>485</v>
+        <v>267</v>
       </c>
       <c r="H203" s="5" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="I203" s="3">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="J203" s="5"/>
-      <c r="K203" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="204" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K203" s="5"/>
+    </row>
+    <row r="204" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="B204" s="5" t="s">
-        <v>18</v>
+        <v>415</v>
+      </c>
+      <c r="B204" s="4">
+        <v>4615740</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>165</v>
+        <v>49</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G204" s="5" t="s">
-        <v>487</v>
+        <v>329</v>
       </c>
       <c r="H204" s="5" t="s">
-        <v>307</v>
+        <v>14</v>
       </c>
       <c r="I204" s="3">
-        <v>59</v>
-      </c>
-      <c r="J204" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="J204" s="5"/>
       <c r="K204" s="5"/>
     </row>
-    <row r="205" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="B205" s="5"/>
+        <v>415</v>
+      </c>
+      <c r="B205" s="4">
+        <v>4615738</v>
+      </c>
       <c r="C205" s="5" t="s">
-        <v>333</v>
+        <v>259</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>229</v>
+        <v>136</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F205" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G205" s="5" t="s">
-        <v>489</v>
+        <v>260</v>
       </c>
       <c r="H205" s="5" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="I205" s="3">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="J205" s="5"/>
       <c r="K205" s="5"/>
     </row>
-    <row r="206" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="B206" s="5"/>
+        <v>415</v>
+      </c>
+      <c r="B206" s="4">
+        <v>4615737</v>
+      </c>
       <c r="C206" s="5" t="s">
-        <v>120</v>
+        <v>253</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G206" s="5" t="s">
-        <v>491</v>
+        <v>254</v>
       </c>
       <c r="H206" s="5" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="I206" s="3">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="J206" s="5"/>
       <c r="K206" s="5"/>
     </row>
-    <row r="207" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="B207" s="5"/>
+        <v>415</v>
+      </c>
+      <c r="B207" s="4">
+        <v>4615728</v>
+      </c>
       <c r="C207" s="5" t="s">
-        <v>129</v>
+        <v>297</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G207" s="5" t="s">
-        <v>493</v>
+        <v>328</v>
       </c>
       <c r="H207" s="5" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="I207" s="3">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="J207" s="5"/>
       <c r="K207" s="5"/>
     </row>
-    <row r="208" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="B208" s="5"/>
+        <v>415</v>
+      </c>
+      <c r="B208" s="4">
+        <v>4615569</v>
+      </c>
       <c r="C208" s="5" t="s">
-        <v>171</v>
+        <v>291</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G208" s="5" t="s">
-        <v>494</v>
+        <v>329</v>
       </c>
       <c r="H208" s="5" t="s">
-        <v>307</v>
+        <v>14</v>
       </c>
       <c r="I208" s="3">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="J208" s="5"/>
       <c r="K208" s="5"/>
     </row>
-    <row r="209" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="B209" s="5"/>
+        <v>415</v>
+      </c>
+      <c r="B209" s="4">
+        <v>4615782</v>
+      </c>
       <c r="C209" s="5" t="s">
-        <v>24</v>
+        <v>373</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>25</v>
+        <v>345</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G209" s="5" t="s">
-        <v>496</v>
+        <v>374</v>
       </c>
       <c r="H209" s="5" t="s">
         <v>17</v>
       </c>
       <c r="I209" s="3">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="J209" s="5"/>
       <c r="K209" s="5"/>
     </row>
-    <row r="210" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="B210" s="5"/>
+        <v>415</v>
+      </c>
+      <c r="B210" s="4">
+        <v>4615780</v>
+      </c>
       <c r="C210" s="5" t="s">
-        <v>396</v>
+        <v>331</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>288</v>
+        <v>104</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F210" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G210" s="5" t="s">
-        <v>498</v>
+        <v>332</v>
       </c>
       <c r="H210" s="5" t="s">
-        <v>307</v>
+        <v>14</v>
       </c>
       <c r="I210" s="3">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J210" s="5"/>
       <c r="K210" s="5"/>
     </row>
-    <row r="211" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="B211" s="5"/>
+        <v>416</v>
+      </c>
+      <c r="B211" s="4">
+        <v>4615779</v>
+      </c>
       <c r="C211" s="5" t="s">
-        <v>64</v>
+        <v>365</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>500</v>
+        <v>366</v>
       </c>
       <c r="H211" s="5" t="s">
-        <v>307</v>
+        <v>17</v>
       </c>
       <c r="I211" s="3">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="J211" s="5"/>
-      <c r="K211" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="212" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K211" s="5"/>
+    </row>
+    <row r="212" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="B212" s="5"/>
+        <v>416</v>
+      </c>
+      <c r="B212" s="4">
+        <v>4615776</v>
+      </c>
       <c r="C212" s="5" t="s">
-        <v>384</v>
+        <v>333</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F212" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G212" s="5" t="s">
-        <v>502</v>
+        <v>334</v>
       </c>
       <c r="H212" s="5" t="s">
-        <v>307</v>
+        <v>14</v>
       </c>
       <c r="I212" s="3">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="J212" s="5"/>
       <c r="K212" s="5"/>
     </row>
-    <row r="213" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="B213" s="5"/>
+        <v>416</v>
+      </c>
+      <c r="B213" s="4">
+        <v>4615768</v>
+      </c>
       <c r="C213" s="5" t="s">
-        <v>176</v>
+        <v>380</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F213" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>504</v>
+        <v>381</v>
       </c>
       <c r="H213" s="5" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="I213" s="3">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="J213" s="5"/>
       <c r="K213" s="5"/>
     </row>
-    <row r="214" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="B214" s="5" t="s">
-        <v>18</v>
+        <v>416</v>
+      </c>
+      <c r="B214" s="4">
+        <v>4615767</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>187</v>
+        <v>336</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>188</v>
+        <v>49</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G214" s="5" t="s">
-        <v>471</v>
+        <v>337</v>
       </c>
       <c r="H214" s="5" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="I214" s="3">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="J214" s="5"/>
-      <c r="K214" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="215" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K214" s="5"/>
+    </row>
+    <row r="215" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="B215" s="5"/>
+        <v>416</v>
+      </c>
+      <c r="B215" s="4">
+        <v>4615763</v>
+      </c>
       <c r="C215" s="5" t="s">
-        <v>155</v>
+        <v>376</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="H215" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I215" s="3">
+        <v>97</v>
+      </c>
+      <c r="J215" s="5"/>
+      <c r="K215" s="5"/>
+    </row>
+    <row r="216" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B216" s="4">
+        <v>4615800</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="D216" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E216" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F216" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G216" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="H216" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I215" s="3">
-        <v>60</v>
-      </c>
-      <c r="J215" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K215" s="5"/>
-    </row>
-    <row r="216" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="B216" s="5"/>
-      <c r="C216" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D216" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E216" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="F216" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G216" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="H216" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="I216" s="3">
-        <v>57</v>
-      </c>
-      <c r="J216" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="J216" s="5"/>
       <c r="K216" s="5"/>
     </row>
-    <row r="217" spans="1:11" ht="90.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="B217" s="5"/>
+        <v>416</v>
+      </c>
+      <c r="B217" s="4">
+        <v>4615794</v>
+      </c>
       <c r="C217" s="5" t="s">
-        <v>246</v>
+        <v>378</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F217" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G217" s="5" t="s">
-        <v>508</v>
+        <v>379</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="I217" s="3">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="J217" s="5"/>
       <c r="K217" s="5"/>
     </row>
-    <row r="218" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="B218" s="5"/>
+        <v>416</v>
+      </c>
+      <c r="B218" s="4">
+        <v>4615792</v>
+      </c>
       <c r="C218" s="5" t="s">
-        <v>239</v>
+        <v>344</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>169</v>
+        <v>345</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F218" s="5" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>460</v>
+        <v>346</v>
       </c>
       <c r="H218" s="5" t="s">
-        <v>307</v>
+        <v>14</v>
       </c>
       <c r="I218" s="3">
+        <v>100</v>
+      </c>
+      <c r="J218" s="5"/>
+      <c r="K218" s="5"/>
+    </row>
+    <row r="219" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B219" s="4">
+        <v>4615786</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D219" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E219" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F219" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J218" s="5"/>
-      <c r="K218" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="219" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="B219" s="5"/>
-      <c r="C219" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="D219" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E219" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F219" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="G219" s="5" t="s">
-        <v>460</v>
+        <v>369</v>
       </c>
       <c r="H219" s="5" t="s">
-        <v>307</v>
+        <v>17</v>
       </c>
       <c r="I219" s="3">
+        <v>102</v>
+      </c>
+      <c r="J219" s="5"/>
+      <c r="K219" s="5"/>
+    </row>
+    <row r="220" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B220" s="4">
+        <v>4615785</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="D220" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="E220" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F220" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="J219" s="5"/>
-      <c r="K219" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="220" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="B220" s="5"/>
-      <c r="C220" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D220" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E220" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F220" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="G220" s="5" t="s">
-        <v>183</v>
+        <v>372</v>
       </c>
       <c r="H220" s="5" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="I220" s="3">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="J220" s="5"/>
-      <c r="K220" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="221" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K220" s="5"/>
+    </row>
+    <row r="221" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="B221" s="5"/>
+        <v>417</v>
+      </c>
+      <c r="B221" s="4">
+        <v>4615836</v>
+      </c>
       <c r="C221" s="5" t="s">
-        <v>168</v>
+        <v>418</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F221" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G221" s="5" t="s">
-        <v>405</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G221" s="5"/>
       <c r="H221" s="5" t="s">
-        <v>307</v>
+        <v>17</v>
       </c>
       <c r="I221" s="3">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="J221" s="5"/>
       <c r="K221" s="5"/>
     </row>
-    <row r="222" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="B222" s="5"/>
+        <v>417</v>
+      </c>
+      <c r="B222" s="4">
+        <v>4615832</v>
+      </c>
       <c r="C222" s="5" t="s">
-        <v>176</v>
+        <v>419</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>177</v>
+        <v>73</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F222" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G222" s="5" t="s">
-        <v>504</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G222" s="5"/>
       <c r="H222" s="5" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="I222" s="3">
-        <v>7</v>
+        <v>106</v>
       </c>
       <c r="J222" s="5"/>
       <c r="K222" s="5"/>
     </row>
-    <row r="223" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="B223" s="5"/>
+        <v>417</v>
+      </c>
+      <c r="B223" s="4">
+        <v>4615831</v>
+      </c>
       <c r="C223" s="5" t="s">
-        <v>228</v>
+        <v>420</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>229</v>
+        <v>25</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F223" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G223" s="5" t="s">
-        <v>230</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G223" s="5"/>
       <c r="H223" s="5" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="I223" s="3">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="J223" s="5"/>
       <c r="K223" s="5"/>
     </row>
-    <row r="224" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="B224" s="5"/>
+        <v>417</v>
+      </c>
+      <c r="B224" s="4">
+        <v>4615814</v>
+      </c>
       <c r="C224" s="5" t="s">
-        <v>223</v>
+        <v>421</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>177</v>
+        <v>136</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G224" s="5" t="s">
-        <v>224</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G224" s="5"/>
       <c r="H224" s="5" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="I224" s="3">
-        <v>12</v>
+        <v>110</v>
       </c>
       <c r="J224" s="5"/>
       <c r="K224" s="5"/>
     </row>
-    <row r="225" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>512</v>
+        <v>422</v>
       </c>
       <c r="B225" s="5"/>
       <c r="C225" s="5" t="s">
-        <v>41</v>
+        <v>396</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G225" s="5" t="s">
-        <v>454</v>
+        <v>423</v>
       </c>
       <c r="H225" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I225" s="3">
+        <v>112</v>
+      </c>
+      <c r="J225" s="5"/>
+      <c r="K225" s="5"/>
+    </row>
+    <row r="226" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B226" s="4">
+        <v>4615692</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D226" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E226" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F226" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G226" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="H226" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I226" s="3">
         <v>14</v>
       </c>
-      <c r="I225" s="3">
-        <v>15</v>
-      </c>
-      <c r="J225" s="5"/>
-      <c r="K225" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="226" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="B226" s="5"/>
-      <c r="C226" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D226" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E226" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F226" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G226" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="H226" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I226" s="3">
-        <v>15</v>
-      </c>
       <c r="J226" s="5"/>
-      <c r="K226" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="227" spans="1:11" ht="116.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K226" s="5"/>
+    </row>
+    <row r="227" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="B227" s="5"/>
+        <v>428</v>
+      </c>
+      <c r="B227" s="4">
+        <v>4615642</v>
+      </c>
       <c r="C227" s="5" t="s">
-        <v>220</v>
+        <v>64</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>177</v>
+        <v>13</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="H227" s="5" t="s">
-        <v>69</v>
+        <v>302</v>
       </c>
       <c r="I227" s="3">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J227" s="5"/>
       <c r="K227" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="228" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="B228" s="5"/>
+        <v>428</v>
+      </c>
+      <c r="B228" s="4">
+        <v>4615525</v>
+      </c>
       <c r="C228" s="5" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F228" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G228" s="5" t="s">
-        <v>94</v>
+        <v>427</v>
       </c>
       <c r="H228" s="5" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="I228" s="3">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J228" s="5"/>
-      <c r="K228" s="5"/>
-    </row>
-    <row r="229" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K228" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="B229" s="5"/>
+        <v>429</v>
+      </c>
+      <c r="B229" s="4">
+        <v>4615801</v>
+      </c>
       <c r="C229" s="5" t="s">
-        <v>76</v>
+        <v>396</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>77</v>
+        <v>13</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F229" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="G229" s="5" t="s">
-        <v>483</v>
+        <v>423</v>
       </c>
       <c r="H229" s="5" t="s">
-        <v>69</v>
+        <v>302</v>
       </c>
       <c r="I229" s="3">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="J229" s="5"/>
       <c r="K229" s="5"/>
     </row>
-    <row r="230" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="B230" s="5"/>
+        <v>429</v>
+      </c>
+      <c r="B230" s="4">
+        <v>4615758</v>
+      </c>
       <c r="C230" s="5" t="s">
-        <v>181</v>
+        <v>339</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F230" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G230" s="5" t="s">
-        <v>183</v>
+        <v>430</v>
       </c>
       <c r="H230" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I230" s="3">
         <v>69</v>
       </c>
-      <c r="I230" s="3">
-        <v>29</v>
-      </c>
       <c r="J230" s="5"/>
-      <c r="K230" s="4" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="231" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="B231" s="5"/>
-      <c r="C231" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D231" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E231" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F231" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G231" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="H231" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I231" s="3">
-        <v>31</v>
-      </c>
-      <c r="J231" s="5"/>
-      <c r="K231" s="5"/>
-    </row>
-    <row r="232" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="B232" s="5"/>
-      <c r="C232" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D232" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E232" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F232" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G232" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="H232" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I232" s="3">
-        <v>33</v>
-      </c>
-      <c r="J232" s="5"/>
-      <c r="K232" s="5"/>
-    </row>
-    <row r="233" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="B233" s="5"/>
-      <c r="C233" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D233" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E233" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F233" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G233" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="H233" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I233" s="3">
-        <v>35</v>
-      </c>
-      <c r="J233" s="5"/>
-      <c r="K233" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="234" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="B234" s="5"/>
-      <c r="C234" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D234" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E234" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F234" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G234" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="H234" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I234" s="3">
-        <v>36</v>
-      </c>
-      <c r="J234" s="5"/>
-      <c r="K234" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="235" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="B235" s="5"/>
-      <c r="C235" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D235" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E235" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F235" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G235" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="H235" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I235" s="3">
-        <v>37</v>
-      </c>
-      <c r="J235" s="5"/>
-      <c r="K235" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="236" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="B236" s="5"/>
-      <c r="C236" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="D236" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="E236" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F236" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G236" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="H236" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I236" s="3">
-        <v>38</v>
-      </c>
-      <c r="J236" s="5"/>
-      <c r="K236" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="237" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="B237" s="5"/>
-      <c r="C237" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D237" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E237" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F237" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G237" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="H237" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I237" s="3">
-        <v>40</v>
-      </c>
-      <c r="J237" s="5"/>
-      <c r="K237" s="5"/>
-    </row>
-    <row r="238" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="B238" s="5"/>
-      <c r="C238" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D238" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E238" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F238" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G238" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="H238" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I238" s="3">
-        <v>41</v>
-      </c>
-      <c r="J238" s="5"/>
-      <c r="K238" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="239" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B239" s="5"/>
-      <c r="C239" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D239" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E239" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F239" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G239" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="H239" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I239" s="3">
-        <v>41</v>
-      </c>
-      <c r="J239" s="5"/>
-      <c r="K239" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="240" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B240" s="5"/>
-      <c r="C240" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D240" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E240" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F240" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G240" s="5" t="s">
-        <v>485</v>
-      </c>
-      <c r="H240" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="I240" s="3">
-        <v>42</v>
-      </c>
-      <c r="J240" s="5"/>
-      <c r="K240" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="241" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B241" s="5"/>
-      <c r="C241" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D241" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="E241" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F241" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G241" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="H241" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I241" s="3">
-        <v>43</v>
-      </c>
-      <c r="J241" s="5"/>
-      <c r="K241" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="242" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B242" s="5"/>
-      <c r="C242" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D242" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E242" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F242" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G242" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="H242" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I242" s="3">
-        <v>44</v>
-      </c>
-      <c r="J242" s="5"/>
-      <c r="K242" s="5"/>
-    </row>
-    <row r="243" spans="1:11" ht="103.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B243" s="5"/>
-      <c r="C243" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="D243" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="E243" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F243" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G243" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="H243" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I243" s="3">
-        <v>48</v>
-      </c>
-      <c r="J243" s="5"/>
-      <c r="K243" s="4" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="244" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B244" s="5"/>
-      <c r="C244" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="D244" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E244" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F244" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G244" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="H244" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I244" s="3">
-        <v>56</v>
-      </c>
-      <c r="J244" s="5"/>
-      <c r="K244" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="245" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B245" s="5"/>
-      <c r="C245" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="D245" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E245" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F245" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G245" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="H245" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I245" s="3">
-        <v>63</v>
-      </c>
-      <c r="J245" s="5"/>
-      <c r="K245" s="5"/>
-    </row>
-    <row r="246" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B246" s="5"/>
-      <c r="C246" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="D246" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="E246" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F246" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G246" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="H246" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I246" s="3">
-        <v>64</v>
-      </c>
-      <c r="J246" s="5"/>
-      <c r="K246" s="5"/>
-    </row>
-    <row r="247" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B247" s="5"/>
-      <c r="C247" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="D247" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E247" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F247" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G247" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="H247" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I247" s="3">
-        <v>71</v>
-      </c>
-      <c r="J247" s="5"/>
-      <c r="K247" s="5"/>
-    </row>
-    <row r="248" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="B248" s="5"/>
-      <c r="C248" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D248" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E248" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F248" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G248" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="H248" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I248" s="3">
-        <v>73</v>
-      </c>
-      <c r="J248" s="5"/>
-      <c r="K248" s="5"/>
-    </row>
-    <row r="249" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B249" s="5"/>
-      <c r="C249" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="D249" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E249" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F249" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G249" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="H249" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I249" s="3">
-        <v>75</v>
-      </c>
-      <c r="J249" s="5"/>
-      <c r="K249" s="5"/>
-    </row>
-    <row r="250" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B250" s="5"/>
-      <c r="C250" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="D250" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E250" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F250" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G250" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="H250" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I250" s="3">
-        <v>76</v>
-      </c>
-      <c r="J250" s="5"/>
-      <c r="K250" s="5"/>
-    </row>
-    <row r="251" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B251" s="5"/>
-      <c r="C251" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="D251" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E251" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F251" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G251" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="H251" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I251" s="3">
-        <v>79</v>
-      </c>
-      <c r="J251" s="5"/>
-      <c r="K251" s="5"/>
-    </row>
-    <row r="252" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B252" s="5"/>
-      <c r="C252" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="D252" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E252" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F252" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G252" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="H252" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I252" s="3">
-        <v>85</v>
-      </c>
-      <c r="J252" s="5"/>
-      <c r="K252" s="5"/>
-    </row>
-    <row r="253" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B253" s="5"/>
-      <c r="C253" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="D253" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E253" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F253" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G253" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="H253" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I253" s="3">
-        <v>101</v>
-      </c>
-      <c r="J253" s="5"/>
-      <c r="K253" s="5"/>
-    </row>
-    <row r="254" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B254" s="5"/>
-      <c r="C254" s="5" t="s">
-        <v>516</v>
-      </c>
-      <c r="D254" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E254" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F254" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G254" s="5"/>
-      <c r="H254" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I254" s="3">
-        <v>108</v>
-      </c>
-      <c r="J254" s="5"/>
-      <c r="K254" s="5"/>
-    </row>
-    <row r="255" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B255" s="5"/>
-      <c r="C255" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="D255" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E255" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F255" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G255" s="5"/>
-      <c r="H255" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I255" s="3">
-        <v>109</v>
-      </c>
-      <c r="J255" s="5"/>
-      <c r="K255" s="5"/>
-    </row>
-    <row r="256" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B256" s="5"/>
-      <c r="C256" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="D256" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E256" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="F256" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G256" s="5"/>
-      <c r="H256" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I256" s="3">
-        <v>111</v>
-      </c>
-      <c r="J256" s="5"/>
-      <c r="K256" s="5"/>
-    </row>
-    <row r="257" spans="1:11" ht="78" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B257" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C257" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D257" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E257" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F257" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G257" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="H257" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I257" s="3">
-        <v>59</v>
-      </c>
-      <c r="J257" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K257" s="5"/>
-    </row>
-    <row r="258" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="B258" s="5"/>
-      <c r="C258" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D258" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E258" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F258" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G258" s="5"/>
-      <c r="H258" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I258" s="3">
-        <v>2</v>
-      </c>
-      <c r="J258" s="5"/>
-      <c r="K258" s="5"/>
-    </row>
-    <row r="259" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="B259" s="5"/>
-      <c r="C259" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D259" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E259" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F259" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G259" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="H259" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I259" s="3">
-        <v>21</v>
-      </c>
-      <c r="J259" s="5"/>
-      <c r="K259" s="5"/>
-    </row>
-    <row r="260" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="B260" s="5"/>
-      <c r="C260" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D260" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E260" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F260" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G260" s="5" t="s">
-        <v>500</v>
-      </c>
-      <c r="H260" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I260" s="3">
-        <v>25</v>
-      </c>
-      <c r="J260" s="5"/>
-      <c r="K260" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="261" spans="1:11" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="B261" s="5"/>
-      <c r="C261" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D261" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E261" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F261" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G261" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="H261" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I261" s="3">
-        <v>28</v>
-      </c>
-      <c r="J261" s="5"/>
-      <c r="K261" s="5"/>
-    </row>
-    <row r="262" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="B262" s="5"/>
-      <c r="C262" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="D262" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E262" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F262" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G262" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="H262" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I262" s="3">
-        <v>47</v>
-      </c>
-      <c r="J262" s="5"/>
-      <c r="K262" s="5"/>
-    </row>
-    <row r="263" spans="1:11" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="B263" s="5"/>
-      <c r="C263" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D263" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="E263" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F263" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G263" s="5" t="s">
-        <v>494</v>
-      </c>
-      <c r="H263" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I263" s="3">
-        <v>61</v>
-      </c>
-      <c r="J263" s="5"/>
-      <c r="K263" s="5"/>
-    </row>
-    <row r="264" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A264" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="B264" s="5"/>
-      <c r="C264" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="D264" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E264" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F264" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G264" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="H264" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I264" s="3">
-        <v>68</v>
-      </c>
-      <c r="J264" s="5"/>
-      <c r="K264" s="5"/>
-    </row>
-    <row r="265" spans="1:11" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="B265" s="5"/>
-      <c r="C265" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="D265" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E265" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F265" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G265" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="H265" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I265" s="3">
-        <v>69</v>
-      </c>
-      <c r="J265" s="5"/>
-      <c r="K265" s="5"/>
-    </row>
-    <row r="266" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="B266" s="5"/>
-      <c r="C266" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="D266" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="E266" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F266" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G266" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="H266" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I266" s="3">
-        <v>83</v>
-      </c>
-      <c r="J266" s="5"/>
-      <c r="K266" s="5"/>
-    </row>
-    <row r="267" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="B267" s="5"/>
-      <c r="C267" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="D267" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="E267" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F267" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G267" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="H267" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I267" s="3">
-        <v>83</v>
-      </c>
-      <c r="J267" s="5"/>
-      <c r="K267" s="5"/>
-    </row>
-    <row r="268" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="B268" s="5"/>
-      <c r="C268" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="D268" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="E268" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F268" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G268" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="H268" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I268" s="3">
-        <v>86</v>
-      </c>
-      <c r="J268" s="5"/>
-      <c r="K268" s="5"/>
-    </row>
-    <row r="269" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="B269" s="5"/>
-      <c r="C269" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="D269" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E269" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F269" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G269" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="H269" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I269" s="3">
-        <v>87</v>
-      </c>
-      <c r="J269" s="5"/>
-      <c r="K269" s="5"/>
-    </row>
-    <row r="270" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A270" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="B270" s="5"/>
-      <c r="C270" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="D270" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="E270" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F270" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G270" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="H270" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I270" s="3">
-        <v>88</v>
-      </c>
-      <c r="J270" s="5"/>
-      <c r="K270" s="5"/>
-    </row>
-    <row r="271" spans="1:11" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="B271" s="5"/>
-      <c r="C271" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="D271" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="E271" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F271" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G271" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="H271" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I271" s="3">
-        <v>93</v>
-      </c>
-      <c r="J271" s="5"/>
-      <c r="K271" s="5"/>
-    </row>
-    <row r="272" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="B272" s="5"/>
-      <c r="C272" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="D272" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E272" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F272" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G272" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="H272" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I272" s="3">
-        <v>96</v>
-      </c>
-      <c r="J272" s="5"/>
-      <c r="K272" s="5"/>
-    </row>
-    <row r="273" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="B273" s="5"/>
-      <c r="C273" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="D273" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E273" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F273" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G273" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="H273" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I273" s="3">
-        <v>112</v>
-      </c>
-      <c r="J273" s="5"/>
-      <c r="K273" s="5"/>
-    </row>
-    <row r="274" spans="1:11" ht="16.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="B274" s="5"/>
-      <c r="C274" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="D274" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E274" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="F274" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G274" s="5"/>
-      <c r="H274" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="I274" s="3">
-        <v>112</v>
-      </c>
-      <c r="J274" s="5"/>
-      <c r="K274" s="5"/>
+      <c r="K230" s="5"/>
+    </row>
+    <row r="231" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="2"/>
+      <c r="B231" s="2"/>
+      <c r="C231" s="2"/>
+      <c r="D231" s="2"/>
+      <c r="E231" s="2"/>
+      <c r="F231" s="2"/>
+      <c r="G231" s="2"/>
+      <c r="H231" s="2"/>
+      <c r="I231" s="2"/>
+      <c r="J231" s="2"/>
+      <c r="K231" s="2"/>
+    </row>
+    <row r="232" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="2"/>
+      <c r="B232" s="2"/>
+      <c r="C232" s="2"/>
+      <c r="D232" s="2"/>
+      <c r="E232" s="2"/>
+      <c r="F232" s="2"/>
+      <c r="G232" s="2"/>
+      <c r="H232" s="2"/>
+      <c r="I232" s="2"/>
+      <c r="J232" s="2"/>
+      <c r="K232" s="2"/>
+    </row>
+    <row r="233" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="2"/>
+      <c r="B233" s="2"/>
+      <c r="C233" s="2"/>
+      <c r="D233" s="2"/>
+      <c r="E233" s="2"/>
+      <c r="F233" s="2"/>
+      <c r="G233" s="2"/>
+      <c r="H233" s="2"/>
+      <c r="I233" s="2"/>
+      <c r="J233" s="2"/>
+      <c r="K233" s="2"/>
+    </row>
+    <row r="234" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="2"/>
+      <c r="B234" s="2"/>
+      <c r="C234" s="2"/>
+      <c r="D234" s="2"/>
+      <c r="E234" s="2"/>
+      <c r="F234" s="2"/>
+      <c r="G234" s="2"/>
+      <c r="H234" s="2"/>
+      <c r="I234" s="2"/>
+      <c r="J234" s="2"/>
+      <c r="K234" s="2"/>
+    </row>
+    <row r="235" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="2"/>
+      <c r="B235" s="2"/>
+      <c r="C235" s="2"/>
+      <c r="D235" s="2"/>
+      <c r="E235" s="2"/>
+      <c r="F235" s="2"/>
+      <c r="G235" s="2"/>
+      <c r="H235" s="2"/>
+      <c r="I235" s="2"/>
+      <c r="J235" s="2"/>
+      <c r="K235" s="2"/>
+    </row>
+    <row r="236" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="2"/>
+      <c r="B236" s="2"/>
+      <c r="C236" s="2"/>
+      <c r="D236" s="2"/>
+      <c r="E236" s="2"/>
+      <c r="F236" s="2"/>
+      <c r="G236" s="2"/>
+      <c r="H236" s="2"/>
+      <c r="I236" s="2"/>
+      <c r="J236" s="2"/>
+      <c r="K236" s="2"/>
+    </row>
+    <row r="237" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="2"/>
+      <c r="B237" s="2"/>
+      <c r="C237" s="2"/>
+      <c r="D237" s="2"/>
+      <c r="E237" s="2"/>
+      <c r="F237" s="2"/>
+      <c r="G237" s="2"/>
+      <c r="H237" s="2"/>
+      <c r="I237" s="2"/>
+      <c r="J237" s="2"/>
+      <c r="K237" s="2"/>
+    </row>
+    <row r="238" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A238" s="2"/>
+      <c r="B238" s="2"/>
+      <c r="C238" s="2"/>
+      <c r="D238" s="2"/>
+      <c r="E238" s="2"/>
+      <c r="F238" s="2"/>
+      <c r="G238" s="2"/>
+      <c r="H238" s="2"/>
+      <c r="I238" s="2"/>
+      <c r="J238" s="2"/>
+      <c r="K238" s="2"/>
+    </row>
+    <row r="239" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="2"/>
+      <c r="B239" s="2"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
+      <c r="E239" s="2"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="2"/>
+      <c r="H239" s="2"/>
+      <c r="I239" s="2"/>
+      <c r="J239" s="2"/>
+      <c r="K239" s="2"/>
+    </row>
+    <row r="240" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="2"/>
+      <c r="B240" s="2"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
+      <c r="E240" s="2"/>
+      <c r="F240" s="2"/>
+      <c r="G240" s="2"/>
+      <c r="H240" s="2"/>
+      <c r="I240" s="2"/>
+      <c r="J240" s="2"/>
+      <c r="K240" s="2"/>
+    </row>
+    <row r="241" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A241" s="2"/>
+      <c r="B241" s="2"/>
+      <c r="C241" s="2"/>
+      <c r="D241" s="2"/>
+      <c r="E241" s="2"/>
+      <c r="F241" s="2"/>
+      <c r="G241" s="2"/>
+      <c r="H241" s="2"/>
+      <c r="I241" s="2"/>
+      <c r="J241" s="2"/>
+      <c r="K241" s="2"/>
+    </row>
+    <row r="242" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="2"/>
+      <c r="B242" s="2"/>
+      <c r="C242" s="2"/>
+      <c r="D242" s="2"/>
+      <c r="E242" s="2"/>
+      <c r="F242" s="2"/>
+      <c r="G242" s="2"/>
+      <c r="H242" s="2"/>
+      <c r="I242" s="2"/>
+      <c r="J242" s="2"/>
+      <c r="K242" s="2"/>
+    </row>
+    <row r="243" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="2"/>
+      <c r="B243" s="2"/>
+      <c r="C243" s="2"/>
+      <c r="D243" s="2"/>
+      <c r="E243" s="2"/>
+      <c r="F243" s="2"/>
+      <c r="G243" s="2"/>
+      <c r="H243" s="2"/>
+      <c r="I243" s="2"/>
+      <c r="J243" s="2"/>
+      <c r="K243" s="2"/>
+    </row>
+    <row r="244" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="2"/>
+      <c r="B244" s="2"/>
+      <c r="C244" s="2"/>
+      <c r="D244" s="2"/>
+      <c r="E244" s="2"/>
+      <c r="F244" s="2"/>
+      <c r="G244" s="2"/>
+      <c r="H244" s="2"/>
+      <c r="I244" s="2"/>
+      <c r="J244" s="2"/>
+      <c r="K244" s="2"/>
+    </row>
+    <row r="245" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="2"/>
+      <c r="B245" s="2"/>
+      <c r="C245" s="2"/>
+      <c r="D245" s="2"/>
+      <c r="E245" s="2"/>
+      <c r="F245" s="2"/>
+      <c r="G245" s="2"/>
+      <c r="H245" s="2"/>
+      <c r="I245" s="2"/>
+      <c r="J245" s="2"/>
+      <c r="K245" s="2"/>
+    </row>
+    <row r="246" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="2"/>
+      <c r="B246" s="2"/>
+      <c r="C246" s="2"/>
+      <c r="D246" s="2"/>
+      <c r="E246" s="2"/>
+      <c r="F246" s="2"/>
+      <c r="G246" s="2"/>
+      <c r="H246" s="2"/>
+      <c r="I246" s="2"/>
+      <c r="J246" s="2"/>
+      <c r="K246" s="2"/>
+    </row>
+    <row r="247" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="2"/>
+      <c r="B247" s="2"/>
+      <c r="C247" s="2"/>
+      <c r="D247" s="2"/>
+      <c r="E247" s="2"/>
+      <c r="F247" s="2"/>
+      <c r="G247" s="2"/>
+      <c r="H247" s="2"/>
+      <c r="I247" s="2"/>
+      <c r="J247" s="2"/>
+      <c r="K247" s="2"/>
+    </row>
+    <row r="248" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A248" s="2"/>
+      <c r="B248" s="2"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
+      <c r="E248" s="2"/>
+      <c r="F248" s="2"/>
+      <c r="G248" s="2"/>
+      <c r="H248" s="2"/>
+      <c r="I248" s="2"/>
+      <c r="J248" s="2"/>
+      <c r="K248" s="2"/>
+    </row>
+    <row r="249" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A249" s="2"/>
+      <c r="B249" s="2"/>
+      <c r="C249" s="2"/>
+      <c r="D249" s="2"/>
+      <c r="E249" s="2"/>
+      <c r="F249" s="2"/>
+      <c r="G249" s="2"/>
+      <c r="H249" s="2"/>
+      <c r="I249" s="2"/>
+      <c r="J249" s="2"/>
+      <c r="K249" s="2"/>
+    </row>
+    <row r="250" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="2"/>
+      <c r="B250" s="2"/>
+      <c r="C250" s="2"/>
+      <c r="D250" s="2"/>
+      <c r="E250" s="2"/>
+      <c r="F250" s="2"/>
+      <c r="G250" s="2"/>
+      <c r="H250" s="2"/>
+      <c r="I250" s="2"/>
+      <c r="J250" s="2"/>
+      <c r="K250" s="2"/>
+    </row>
+    <row r="251" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="2"/>
+      <c r="B251" s="2"/>
+      <c r="C251" s="2"/>
+      <c r="D251" s="2"/>
+      <c r="E251" s="2"/>
+      <c r="F251" s="2"/>
+      <c r="G251" s="2"/>
+      <c r="H251" s="2"/>
+      <c r="I251" s="2"/>
+      <c r="J251" s="2"/>
+      <c r="K251" s="2"/>
+    </row>
+    <row r="252" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A252" s="2"/>
+      <c r="B252" s="2"/>
+      <c r="C252" s="2"/>
+      <c r="D252" s="2"/>
+      <c r="E252" s="2"/>
+      <c r="F252" s="2"/>
+      <c r="G252" s="2"/>
+      <c r="H252" s="2"/>
+      <c r="I252" s="2"/>
+      <c r="J252" s="2"/>
+      <c r="K252" s="2"/>
+    </row>
+    <row r="253" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="2"/>
+      <c r="B253" s="2"/>
+      <c r="C253" s="2"/>
+      <c r="D253" s="2"/>
+      <c r="E253" s="2"/>
+      <c r="F253" s="2"/>
+      <c r="G253" s="2"/>
+      <c r="H253" s="2"/>
+      <c r="I253" s="2"/>
+      <c r="J253" s="2"/>
+      <c r="K253" s="2"/>
+    </row>
+    <row r="254" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="2"/>
+      <c r="B254" s="2"/>
+      <c r="C254" s="2"/>
+      <c r="D254" s="2"/>
+      <c r="E254" s="2"/>
+      <c r="F254" s="2"/>
+      <c r="G254" s="2"/>
+      <c r="H254" s="2"/>
+      <c r="I254" s="2"/>
+      <c r="J254" s="2"/>
+      <c r="K254" s="2"/>
+    </row>
+    <row r="255" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="2"/>
+      <c r="B255" s="2"/>
+      <c r="C255" s="2"/>
+      <c r="D255" s="2"/>
+      <c r="E255" s="2"/>
+      <c r="F255" s="2"/>
+      <c r="G255" s="2"/>
+      <c r="H255" s="2"/>
+      <c r="I255" s="2"/>
+      <c r="J255" s="2"/>
+      <c r="K255" s="2"/>
+    </row>
+    <row r="256" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="2"/>
+      <c r="B256" s="2"/>
+      <c r="C256" s="2"/>
+      <c r="D256" s="2"/>
+      <c r="E256" s="2"/>
+      <c r="F256" s="2"/>
+      <c r="G256" s="2"/>
+      <c r="H256" s="2"/>
+      <c r="I256" s="2"/>
+      <c r="J256" s="2"/>
+      <c r="K256" s="2"/>
+    </row>
+    <row r="257" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="2"/>
+      <c r="B257" s="2"/>
+      <c r="C257" s="2"/>
+      <c r="D257" s="2"/>
+      <c r="E257" s="2"/>
+      <c r="F257" s="2"/>
+      <c r="G257" s="2"/>
+      <c r="H257" s="2"/>
+      <c r="I257" s="2"/>
+      <c r="J257" s="2"/>
+      <c r="K257" s="2"/>
+    </row>
+    <row r="258" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="2"/>
+      <c r="B258" s="2"/>
+      <c r="C258" s="2"/>
+      <c r="D258" s="2"/>
+      <c r="E258" s="2"/>
+      <c r="F258" s="2"/>
+      <c r="G258" s="2"/>
+      <c r="H258" s="2"/>
+      <c r="I258" s="2"/>
+      <c r="J258" s="2"/>
+      <c r="K258" s="2"/>
+    </row>
+    <row r="259" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="2"/>
+      <c r="B259" s="2"/>
+      <c r="C259" s="2"/>
+      <c r="D259" s="2"/>
+      <c r="E259" s="2"/>
+      <c r="F259" s="2"/>
+      <c r="G259" s="2"/>
+      <c r="H259" s="2"/>
+      <c r="I259" s="2"/>
+      <c r="J259" s="2"/>
+      <c r="K259" s="2"/>
+    </row>
+    <row r="260" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="2"/>
+      <c r="B260" s="2"/>
+      <c r="C260" s="2"/>
+      <c r="D260" s="2"/>
+      <c r="E260" s="2"/>
+      <c r="F260" s="2"/>
+      <c r="G260" s="2"/>
+      <c r="H260" s="2"/>
+      <c r="I260" s="2"/>
+      <c r="J260" s="2"/>
+      <c r="K260" s="2"/>
+    </row>
+    <row r="261" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="2"/>
+      <c r="B261" s="2"/>
+      <c r="C261" s="2"/>
+      <c r="D261" s="2"/>
+      <c r="E261" s="2"/>
+      <c r="F261" s="2"/>
+      <c r="G261" s="2"/>
+      <c r="H261" s="2"/>
+      <c r="I261" s="2"/>
+      <c r="J261" s="2"/>
+      <c r="K261" s="2"/>
+    </row>
+    <row r="262" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A262" s="2"/>
+      <c r="B262" s="2"/>
+      <c r="C262" s="2"/>
+      <c r="D262" s="2"/>
+      <c r="E262" s="2"/>
+      <c r="F262" s="2"/>
+      <c r="G262" s="2"/>
+      <c r="H262" s="2"/>
+      <c r="I262" s="2"/>
+      <c r="J262" s="2"/>
+      <c r="K262" s="2"/>
+    </row>
+    <row r="263" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A263" s="2"/>
+      <c r="B263" s="2"/>
+      <c r="C263" s="2"/>
+      <c r="D263" s="2"/>
+      <c r="E263" s="2"/>
+      <c r="F263" s="2"/>
+      <c r="G263" s="2"/>
+      <c r="H263" s="2"/>
+      <c r="I263" s="2"/>
+      <c r="J263" s="2"/>
+      <c r="K263" s="2"/>
+    </row>
+    <row r="264" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A264" s="2"/>
+      <c r="B264" s="2"/>
+      <c r="C264" s="2"/>
+      <c r="D264" s="2"/>
+      <c r="E264" s="2"/>
+      <c r="F264" s="2"/>
+      <c r="G264" s="2"/>
+      <c r="H264" s="2"/>
+      <c r="I264" s="2"/>
+      <c r="J264" s="2"/>
+      <c r="K264" s="2"/>
+    </row>
+    <row r="265" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A265" s="2"/>
+      <c r="B265" s="2"/>
+      <c r="C265" s="2"/>
+      <c r="D265" s="2"/>
+      <c r="E265" s="2"/>
+      <c r="F265" s="2"/>
+      <c r="G265" s="2"/>
+      <c r="H265" s="2"/>
+      <c r="I265" s="2"/>
+      <c r="J265" s="2"/>
+      <c r="K265" s="2"/>
+    </row>
+    <row r="266" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A266" s="2"/>
+      <c r="B266" s="2"/>
+      <c r="C266" s="2"/>
+      <c r="D266" s="2"/>
+      <c r="E266" s="2"/>
+      <c r="F266" s="2"/>
+      <c r="G266" s="2"/>
+      <c r="H266" s="2"/>
+      <c r="I266" s="2"/>
+      <c r="J266" s="2"/>
+      <c r="K266" s="2"/>
+    </row>
+    <row r="267" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A267" s="2"/>
+      <c r="B267" s="2"/>
+      <c r="C267" s="2"/>
+      <c r="D267" s="2"/>
+      <c r="E267" s="2"/>
+      <c r="F267" s="2"/>
+      <c r="G267" s="2"/>
+      <c r="H267" s="2"/>
+      <c r="I267" s="2"/>
+      <c r="J267" s="2"/>
+      <c r="K267" s="2"/>
+    </row>
+    <row r="268" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A268" s="2"/>
+      <c r="B268" s="2"/>
+      <c r="C268" s="2"/>
+      <c r="D268" s="2"/>
+      <c r="E268" s="2"/>
+      <c r="F268" s="2"/>
+      <c r="G268" s="2"/>
+      <c r="H268" s="2"/>
+      <c r="I268" s="2"/>
+      <c r="J268" s="2"/>
+      <c r="K268" s="2"/>
+    </row>
+    <row r="269" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A269" s="2"/>
+      <c r="B269" s="2"/>
+      <c r="C269" s="2"/>
+      <c r="D269" s="2"/>
+      <c r="E269" s="2"/>
+      <c r="F269" s="2"/>
+      <c r="G269" s="2"/>
+      <c r="H269" s="2"/>
+      <c r="I269" s="2"/>
+      <c r="J269" s="2"/>
+      <c r="K269" s="2"/>
+    </row>
+    <row r="270" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A270" s="2"/>
+      <c r="B270" s="2"/>
+      <c r="C270" s="2"/>
+      <c r="D270" s="2"/>
+      <c r="E270" s="2"/>
+      <c r="F270" s="2"/>
+      <c r="G270" s="2"/>
+      <c r="H270" s="2"/>
+      <c r="I270" s="2"/>
+      <c r="J270" s="2"/>
+      <c r="K270" s="2"/>
+    </row>
+    <row r="271" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A271" s="2"/>
+      <c r="B271" s="2"/>
+      <c r="C271" s="2"/>
+      <c r="D271" s="2"/>
+      <c r="E271" s="2"/>
+      <c r="F271" s="2"/>
+      <c r="G271" s="2"/>
+      <c r="H271" s="2"/>
+      <c r="I271" s="2"/>
+      <c r="J271" s="2"/>
+      <c r="K271" s="2"/>
+    </row>
+    <row r="272" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A272" s="2"/>
+      <c r="B272" s="2"/>
+      <c r="C272" s="2"/>
+      <c r="D272" s="2"/>
+      <c r="E272" s="2"/>
+      <c r="F272" s="2"/>
+      <c r="G272" s="2"/>
+      <c r="H272" s="2"/>
+      <c r="I272" s="2"/>
+      <c r="J272" s="2"/>
+      <c r="K272" s="2"/>
+    </row>
+    <row r="273" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A273" s="2"/>
+      <c r="B273" s="2"/>
+      <c r="C273" s="2"/>
+      <c r="D273" s="2"/>
+      <c r="E273" s="2"/>
+      <c r="F273" s="2"/>
+      <c r="G273" s="2"/>
+      <c r="H273" s="2"/>
+      <c r="I273" s="2"/>
+      <c r="J273" s="2"/>
+      <c r="K273" s="2"/>
+    </row>
+    <row r="274" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A274" s="2"/>
+      <c r="B274" s="2"/>
+      <c r="C274" s="2"/>
+      <c r="D274" s="2"/>
+      <c r="E274" s="2"/>
+      <c r="F274" s="2"/>
+      <c r="G274" s="2"/>
+      <c r="H274" s="2"/>
+      <c r="I274" s="2"/>
+      <c r="J274" s="2"/>
+      <c r="K274" s="2"/>
     </row>
     <row r="275" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="2"/>
@@ -19215,638 +18362,8 @@
       <c r="J951" s="2"/>
       <c r="K951" s="2"/>
     </row>
-    <row r="952" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A952" s="2"/>
-      <c r="B952" s="2"/>
-      <c r="C952" s="2"/>
-      <c r="D952" s="2"/>
-      <c r="E952" s="2"/>
-      <c r="F952" s="2"/>
-      <c r="G952" s="2"/>
-      <c r="H952" s="2"/>
-      <c r="I952" s="2"/>
-      <c r="J952" s="2"/>
-      <c r="K952" s="2"/>
-    </row>
-    <row r="953" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A953" s="2"/>
-      <c r="B953" s="2"/>
-      <c r="C953" s="2"/>
-      <c r="D953" s="2"/>
-      <c r="E953" s="2"/>
-      <c r="F953" s="2"/>
-      <c r="G953" s="2"/>
-      <c r="H953" s="2"/>
-      <c r="I953" s="2"/>
-      <c r="J953" s="2"/>
-      <c r="K953" s="2"/>
-    </row>
-    <row r="954" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A954" s="2"/>
-      <c r="B954" s="2"/>
-      <c r="C954" s="2"/>
-      <c r="D954" s="2"/>
-      <c r="E954" s="2"/>
-      <c r="F954" s="2"/>
-      <c r="G954" s="2"/>
-      <c r="H954" s="2"/>
-      <c r="I954" s="2"/>
-      <c r="J954" s="2"/>
-      <c r="K954" s="2"/>
-    </row>
-    <row r="955" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A955" s="2"/>
-      <c r="B955" s="2"/>
-      <c r="C955" s="2"/>
-      <c r="D955" s="2"/>
-      <c r="E955" s="2"/>
-      <c r="F955" s="2"/>
-      <c r="G955" s="2"/>
-      <c r="H955" s="2"/>
-      <c r="I955" s="2"/>
-      <c r="J955" s="2"/>
-      <c r="K955" s="2"/>
-    </row>
-    <row r="956" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A956" s="2"/>
-      <c r="B956" s="2"/>
-      <c r="C956" s="2"/>
-      <c r="D956" s="2"/>
-      <c r="E956" s="2"/>
-      <c r="F956" s="2"/>
-      <c r="G956" s="2"/>
-      <c r="H956" s="2"/>
-      <c r="I956" s="2"/>
-      <c r="J956" s="2"/>
-      <c r="K956" s="2"/>
-    </row>
-    <row r="957" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A957" s="2"/>
-      <c r="B957" s="2"/>
-      <c r="C957" s="2"/>
-      <c r="D957" s="2"/>
-      <c r="E957" s="2"/>
-      <c r="F957" s="2"/>
-      <c r="G957" s="2"/>
-      <c r="H957" s="2"/>
-      <c r="I957" s="2"/>
-      <c r="J957" s="2"/>
-      <c r="K957" s="2"/>
-    </row>
-    <row r="958" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A958" s="2"/>
-      <c r="B958" s="2"/>
-      <c r="C958" s="2"/>
-      <c r="D958" s="2"/>
-      <c r="E958" s="2"/>
-      <c r="F958" s="2"/>
-      <c r="G958" s="2"/>
-      <c r="H958" s="2"/>
-      <c r="I958" s="2"/>
-      <c r="J958" s="2"/>
-      <c r="K958" s="2"/>
-    </row>
-    <row r="959" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A959" s="2"/>
-      <c r="B959" s="2"/>
-      <c r="C959" s="2"/>
-      <c r="D959" s="2"/>
-      <c r="E959" s="2"/>
-      <c r="F959" s="2"/>
-      <c r="G959" s="2"/>
-      <c r="H959" s="2"/>
-      <c r="I959" s="2"/>
-      <c r="J959" s="2"/>
-      <c r="K959" s="2"/>
-    </row>
-    <row r="960" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A960" s="2"/>
-      <c r="B960" s="2"/>
-      <c r="C960" s="2"/>
-      <c r="D960" s="2"/>
-      <c r="E960" s="2"/>
-      <c r="F960" s="2"/>
-      <c r="G960" s="2"/>
-      <c r="H960" s="2"/>
-      <c r="I960" s="2"/>
-      <c r="J960" s="2"/>
-      <c r="K960" s="2"/>
-    </row>
-    <row r="961" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A961" s="2"/>
-      <c r="B961" s="2"/>
-      <c r="C961" s="2"/>
-      <c r="D961" s="2"/>
-      <c r="E961" s="2"/>
-      <c r="F961" s="2"/>
-      <c r="G961" s="2"/>
-      <c r="H961" s="2"/>
-      <c r="I961" s="2"/>
-      <c r="J961" s="2"/>
-      <c r="K961" s="2"/>
-    </row>
-    <row r="962" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A962" s="2"/>
-      <c r="B962" s="2"/>
-      <c r="C962" s="2"/>
-      <c r="D962" s="2"/>
-      <c r="E962" s="2"/>
-      <c r="F962" s="2"/>
-      <c r="G962" s="2"/>
-      <c r="H962" s="2"/>
-      <c r="I962" s="2"/>
-      <c r="J962" s="2"/>
-      <c r="K962" s="2"/>
-    </row>
-    <row r="963" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A963" s="2"/>
-      <c r="B963" s="2"/>
-      <c r="C963" s="2"/>
-      <c r="D963" s="2"/>
-      <c r="E963" s="2"/>
-      <c r="F963" s="2"/>
-      <c r="G963" s="2"/>
-      <c r="H963" s="2"/>
-      <c r="I963" s="2"/>
-      <c r="J963" s="2"/>
-      <c r="K963" s="2"/>
-    </row>
-    <row r="964" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A964" s="2"/>
-      <c r="B964" s="2"/>
-      <c r="C964" s="2"/>
-      <c r="D964" s="2"/>
-      <c r="E964" s="2"/>
-      <c r="F964" s="2"/>
-      <c r="G964" s="2"/>
-      <c r="H964" s="2"/>
-      <c r="I964" s="2"/>
-      <c r="J964" s="2"/>
-      <c r="K964" s="2"/>
-    </row>
-    <row r="965" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A965" s="2"/>
-      <c r="B965" s="2"/>
-      <c r="C965" s="2"/>
-      <c r="D965" s="2"/>
-      <c r="E965" s="2"/>
-      <c r="F965" s="2"/>
-      <c r="G965" s="2"/>
-      <c r="H965" s="2"/>
-      <c r="I965" s="2"/>
-      <c r="J965" s="2"/>
-      <c r="K965" s="2"/>
-    </row>
-    <row r="966" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A966" s="2"/>
-      <c r="B966" s="2"/>
-      <c r="C966" s="2"/>
-      <c r="D966" s="2"/>
-      <c r="E966" s="2"/>
-      <c r="F966" s="2"/>
-      <c r="G966" s="2"/>
-      <c r="H966" s="2"/>
-      <c r="I966" s="2"/>
-      <c r="J966" s="2"/>
-      <c r="K966" s="2"/>
-    </row>
-    <row r="967" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A967" s="2"/>
-      <c r="B967" s="2"/>
-      <c r="C967" s="2"/>
-      <c r="D967" s="2"/>
-      <c r="E967" s="2"/>
-      <c r="F967" s="2"/>
-      <c r="G967" s="2"/>
-      <c r="H967" s="2"/>
-      <c r="I967" s="2"/>
-      <c r="J967" s="2"/>
-      <c r="K967" s="2"/>
-    </row>
-    <row r="968" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A968" s="2"/>
-      <c r="B968" s="2"/>
-      <c r="C968" s="2"/>
-      <c r="D968" s="2"/>
-      <c r="E968" s="2"/>
-      <c r="F968" s="2"/>
-      <c r="G968" s="2"/>
-      <c r="H968" s="2"/>
-      <c r="I968" s="2"/>
-      <c r="J968" s="2"/>
-      <c r="K968" s="2"/>
-    </row>
-    <row r="969" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A969" s="2"/>
-      <c r="B969" s="2"/>
-      <c r="C969" s="2"/>
-      <c r="D969" s="2"/>
-      <c r="E969" s="2"/>
-      <c r="F969" s="2"/>
-      <c r="G969" s="2"/>
-      <c r="H969" s="2"/>
-      <c r="I969" s="2"/>
-      <c r="J969" s="2"/>
-      <c r="K969" s="2"/>
-    </row>
-    <row r="970" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A970" s="2"/>
-      <c r="B970" s="2"/>
-      <c r="C970" s="2"/>
-      <c r="D970" s="2"/>
-      <c r="E970" s="2"/>
-      <c r="F970" s="2"/>
-      <c r="G970" s="2"/>
-      <c r="H970" s="2"/>
-      <c r="I970" s="2"/>
-      <c r="J970" s="2"/>
-      <c r="K970" s="2"/>
-    </row>
-    <row r="971" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A971" s="2"/>
-      <c r="B971" s="2"/>
-      <c r="C971" s="2"/>
-      <c r="D971" s="2"/>
-      <c r="E971" s="2"/>
-      <c r="F971" s="2"/>
-      <c r="G971" s="2"/>
-      <c r="H971" s="2"/>
-      <c r="I971" s="2"/>
-      <c r="J971" s="2"/>
-      <c r="K971" s="2"/>
-    </row>
-    <row r="972" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A972" s="2"/>
-      <c r="B972" s="2"/>
-      <c r="C972" s="2"/>
-      <c r="D972" s="2"/>
-      <c r="E972" s="2"/>
-      <c r="F972" s="2"/>
-      <c r="G972" s="2"/>
-      <c r="H972" s="2"/>
-      <c r="I972" s="2"/>
-      <c r="J972" s="2"/>
-      <c r="K972" s="2"/>
-    </row>
-    <row r="973" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A973" s="2"/>
-      <c r="B973" s="2"/>
-      <c r="C973" s="2"/>
-      <c r="D973" s="2"/>
-      <c r="E973" s="2"/>
-      <c r="F973" s="2"/>
-      <c r="G973" s="2"/>
-      <c r="H973" s="2"/>
-      <c r="I973" s="2"/>
-      <c r="J973" s="2"/>
-      <c r="K973" s="2"/>
-    </row>
-    <row r="974" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A974" s="2"/>
-      <c r="B974" s="2"/>
-      <c r="C974" s="2"/>
-      <c r="D974" s="2"/>
-      <c r="E974" s="2"/>
-      <c r="F974" s="2"/>
-      <c r="G974" s="2"/>
-      <c r="H974" s="2"/>
-      <c r="I974" s="2"/>
-      <c r="J974" s="2"/>
-      <c r="K974" s="2"/>
-    </row>
-    <row r="975" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A975" s="2"/>
-      <c r="B975" s="2"/>
-      <c r="C975" s="2"/>
-      <c r="D975" s="2"/>
-      <c r="E975" s="2"/>
-      <c r="F975" s="2"/>
-      <c r="G975" s="2"/>
-      <c r="H975" s="2"/>
-      <c r="I975" s="2"/>
-      <c r="J975" s="2"/>
-      <c r="K975" s="2"/>
-    </row>
-    <row r="976" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A976" s="2"/>
-      <c r="B976" s="2"/>
-      <c r="C976" s="2"/>
-      <c r="D976" s="2"/>
-      <c r="E976" s="2"/>
-      <c r="F976" s="2"/>
-      <c r="G976" s="2"/>
-      <c r="H976" s="2"/>
-      <c r="I976" s="2"/>
-      <c r="J976" s="2"/>
-      <c r="K976" s="2"/>
-    </row>
-    <row r="977" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A977" s="2"/>
-      <c r="B977" s="2"/>
-      <c r="C977" s="2"/>
-      <c r="D977" s="2"/>
-      <c r="E977" s="2"/>
-      <c r="F977" s="2"/>
-      <c r="G977" s="2"/>
-      <c r="H977" s="2"/>
-      <c r="I977" s="2"/>
-      <c r="J977" s="2"/>
-      <c r="K977" s="2"/>
-    </row>
-    <row r="978" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A978" s="2"/>
-      <c r="B978" s="2"/>
-      <c r="C978" s="2"/>
-      <c r="D978" s="2"/>
-      <c r="E978" s="2"/>
-      <c r="F978" s="2"/>
-      <c r="G978" s="2"/>
-      <c r="H978" s="2"/>
-      <c r="I978" s="2"/>
-      <c r="J978" s="2"/>
-      <c r="K978" s="2"/>
-    </row>
-    <row r="979" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A979" s="2"/>
-      <c r="B979" s="2"/>
-      <c r="C979" s="2"/>
-      <c r="D979" s="2"/>
-      <c r="E979" s="2"/>
-      <c r="F979" s="2"/>
-      <c r="G979" s="2"/>
-      <c r="H979" s="2"/>
-      <c r="I979" s="2"/>
-      <c r="J979" s="2"/>
-      <c r="K979" s="2"/>
-    </row>
-    <row r="980" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A980" s="2"/>
-      <c r="B980" s="2"/>
-      <c r="C980" s="2"/>
-      <c r="D980" s="2"/>
-      <c r="E980" s="2"/>
-      <c r="F980" s="2"/>
-      <c r="G980" s="2"/>
-      <c r="H980" s="2"/>
-      <c r="I980" s="2"/>
-      <c r="J980" s="2"/>
-      <c r="K980" s="2"/>
-    </row>
-    <row r="981" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A981" s="2"/>
-      <c r="B981" s="2"/>
-      <c r="C981" s="2"/>
-      <c r="D981" s="2"/>
-      <c r="E981" s="2"/>
-      <c r="F981" s="2"/>
-      <c r="G981" s="2"/>
-      <c r="H981" s="2"/>
-      <c r="I981" s="2"/>
-      <c r="J981" s="2"/>
-      <c r="K981" s="2"/>
-    </row>
-    <row r="982" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A982" s="2"/>
-      <c r="B982" s="2"/>
-      <c r="C982" s="2"/>
-      <c r="D982" s="2"/>
-      <c r="E982" s="2"/>
-      <c r="F982" s="2"/>
-      <c r="G982" s="2"/>
-      <c r="H982" s="2"/>
-      <c r="I982" s="2"/>
-      <c r="J982" s="2"/>
-      <c r="K982" s="2"/>
-    </row>
-    <row r="983" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A983" s="2"/>
-      <c r="B983" s="2"/>
-      <c r="C983" s="2"/>
-      <c r="D983" s="2"/>
-      <c r="E983" s="2"/>
-      <c r="F983" s="2"/>
-      <c r="G983" s="2"/>
-      <c r="H983" s="2"/>
-      <c r="I983" s="2"/>
-      <c r="J983" s="2"/>
-      <c r="K983" s="2"/>
-    </row>
-    <row r="984" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A984" s="2"/>
-      <c r="B984" s="2"/>
-      <c r="C984" s="2"/>
-      <c r="D984" s="2"/>
-      <c r="E984" s="2"/>
-      <c r="F984" s="2"/>
-      <c r="G984" s="2"/>
-      <c r="H984" s="2"/>
-      <c r="I984" s="2"/>
-      <c r="J984" s="2"/>
-      <c r="K984" s="2"/>
-    </row>
-    <row r="985" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A985" s="2"/>
-      <c r="B985" s="2"/>
-      <c r="C985" s="2"/>
-      <c r="D985" s="2"/>
-      <c r="E985" s="2"/>
-      <c r="F985" s="2"/>
-      <c r="G985" s="2"/>
-      <c r="H985" s="2"/>
-      <c r="I985" s="2"/>
-      <c r="J985" s="2"/>
-      <c r="K985" s="2"/>
-    </row>
-    <row r="986" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A986" s="2"/>
-      <c r="B986" s="2"/>
-      <c r="C986" s="2"/>
-      <c r="D986" s="2"/>
-      <c r="E986" s="2"/>
-      <c r="F986" s="2"/>
-      <c r="G986" s="2"/>
-      <c r="H986" s="2"/>
-      <c r="I986" s="2"/>
-      <c r="J986" s="2"/>
-      <c r="K986" s="2"/>
-    </row>
-    <row r="987" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A987" s="2"/>
-      <c r="B987" s="2"/>
-      <c r="C987" s="2"/>
-      <c r="D987" s="2"/>
-      <c r="E987" s="2"/>
-      <c r="F987" s="2"/>
-      <c r="G987" s="2"/>
-      <c r="H987" s="2"/>
-      <c r="I987" s="2"/>
-      <c r="J987" s="2"/>
-      <c r="K987" s="2"/>
-    </row>
-    <row r="988" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A988" s="2"/>
-      <c r="B988" s="2"/>
-      <c r="C988" s="2"/>
-      <c r="D988" s="2"/>
-      <c r="E988" s="2"/>
-      <c r="F988" s="2"/>
-      <c r="G988" s="2"/>
-      <c r="H988" s="2"/>
-      <c r="I988" s="2"/>
-      <c r="J988" s="2"/>
-      <c r="K988" s="2"/>
-    </row>
-    <row r="989" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A989" s="2"/>
-      <c r="B989" s="2"/>
-      <c r="C989" s="2"/>
-      <c r="D989" s="2"/>
-      <c r="E989" s="2"/>
-      <c r="F989" s="2"/>
-      <c r="G989" s="2"/>
-      <c r="H989" s="2"/>
-      <c r="I989" s="2"/>
-      <c r="J989" s="2"/>
-      <c r="K989" s="2"/>
-    </row>
-    <row r="990" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A990" s="2"/>
-      <c r="B990" s="2"/>
-      <c r="C990" s="2"/>
-      <c r="D990" s="2"/>
-      <c r="E990" s="2"/>
-      <c r="F990" s="2"/>
-      <c r="G990" s="2"/>
-      <c r="H990" s="2"/>
-      <c r="I990" s="2"/>
-      <c r="J990" s="2"/>
-      <c r="K990" s="2"/>
-    </row>
-    <row r="991" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A991" s="2"/>
-      <c r="B991" s="2"/>
-      <c r="C991" s="2"/>
-      <c r="D991" s="2"/>
-      <c r="E991" s="2"/>
-      <c r="F991" s="2"/>
-      <c r="G991" s="2"/>
-      <c r="H991" s="2"/>
-      <c r="I991" s="2"/>
-      <c r="J991" s="2"/>
-      <c r="K991" s="2"/>
-    </row>
-    <row r="992" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A992" s="2"/>
-      <c r="B992" s="2"/>
-      <c r="C992" s="2"/>
-      <c r="D992" s="2"/>
-      <c r="E992" s="2"/>
-      <c r="F992" s="2"/>
-      <c r="G992" s="2"/>
-      <c r="H992" s="2"/>
-      <c r="I992" s="2"/>
-      <c r="J992" s="2"/>
-      <c r="K992" s="2"/>
-    </row>
-    <row r="993" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A993" s="2"/>
-      <c r="B993" s="2"/>
-      <c r="C993" s="2"/>
-      <c r="D993" s="2"/>
-      <c r="E993" s="2"/>
-      <c r="F993" s="2"/>
-      <c r="G993" s="2"/>
-      <c r="H993" s="2"/>
-      <c r="I993" s="2"/>
-      <c r="J993" s="2"/>
-      <c r="K993" s="2"/>
-    </row>
-    <row r="994" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A994" s="2"/>
-      <c r="B994" s="2"/>
-      <c r="C994" s="2"/>
-      <c r="D994" s="2"/>
-      <c r="E994" s="2"/>
-      <c r="F994" s="2"/>
-      <c r="G994" s="2"/>
-      <c r="H994" s="2"/>
-      <c r="I994" s="2"/>
-      <c r="J994" s="2"/>
-      <c r="K994" s="2"/>
-    </row>
-    <row r="995" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A995" s="2"/>
-      <c r="B995" s="2"/>
-      <c r="C995" s="2"/>
-      <c r="D995" s="2"/>
-      <c r="E995" s="2"/>
-      <c r="F995" s="2"/>
-      <c r="G995" s="2"/>
-      <c r="H995" s="2"/>
-      <c r="I995" s="2"/>
-      <c r="J995" s="2"/>
-      <c r="K995" s="2"/>
-    </row>
-    <row r="996" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A996" s="2"/>
-      <c r="B996" s="2"/>
-      <c r="C996" s="2"/>
-      <c r="D996" s="2"/>
-      <c r="E996" s="2"/>
-      <c r="F996" s="2"/>
-      <c r="G996" s="2"/>
-      <c r="H996" s="2"/>
-      <c r="I996" s="2"/>
-      <c r="J996" s="2"/>
-      <c r="K996" s="2"/>
-    </row>
-    <row r="997" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A997" s="2"/>
-      <c r="B997" s="2"/>
-      <c r="C997" s="2"/>
-      <c r="D997" s="2"/>
-      <c r="E997" s="2"/>
-      <c r="F997" s="2"/>
-      <c r="G997" s="2"/>
-      <c r="H997" s="2"/>
-      <c r="I997" s="2"/>
-      <c r="J997" s="2"/>
-      <c r="K997" s="2"/>
-    </row>
-    <row r="998" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A998" s="2"/>
-      <c r="B998" s="2"/>
-      <c r="C998" s="2"/>
-      <c r="D998" s="2"/>
-      <c r="E998" s="2"/>
-      <c r="F998" s="2"/>
-      <c r="G998" s="2"/>
-      <c r="H998" s="2"/>
-      <c r="I998" s="2"/>
-      <c r="J998" s="2"/>
-      <c r="K998" s="2"/>
-    </row>
-    <row r="999" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A999" s="2"/>
-      <c r="B999" s="2"/>
-      <c r="C999" s="2"/>
-      <c r="D999" s="2"/>
-      <c r="E999" s="2"/>
-      <c r="F999" s="2"/>
-      <c r="G999" s="2"/>
-      <c r="H999" s="2"/>
-      <c r="I999" s="2"/>
-      <c r="J999" s="2"/>
-      <c r="K999" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K274" xr:uid="{271A8CFB-3293-473B-894F-86B249B2B19B}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Huỳnh Chí Băng"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K226" xr:uid="{271A8CFB-3293-473B-894F-86B249B2B19B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_PAKH\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C636266F-0223-44AD-89EC-B23C54E52B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD29FEAB-AAFD-4240-9E4C-F48D10715953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2130" yWindow="1890" windowWidth="21600" windowHeight="11295" xr2:uid="{15FDD92A-6CAD-44EB-866F-DB764FC19082}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{15FDD92A-6CAD-44EB-866F-DB764FC19082}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="455">
   <si>
     <t>Thời gian update</t>
   </si>
@@ -1375,9 +1375,6 @@
     <t>Phạm Đình Phương</t>
   </si>
   <si>
-    <t>25/08/2026 10:03</t>
-  </si>
-  <si>
     <t>Hệ thống lỗi, Đã khắc phục cho KH</t>
   </si>
   <si>
@@ -1406,6 +1403,85 @@
     <t>Điều phối lại cho FT kienpv6
 Đang ở nhà KH xử lý sự cố, đã xin gia hạn đến 12:25:00 25/08/2026
 test</t>
+  </si>
+  <si>
+    <t>25/08/2026 10:31</t>
+  </si>
+  <si>
+    <t>25/08/2026 10:32</t>
+  </si>
+  <si>
+    <t>Khách hàng đang đi công tác, Thứ 7 khách về sẽ trao đổi với khách và ký biên bản xác nhận bảo hành hoặc thay thế khách tự bỏ chi phí. Pin Canadian 450 do chi nhánh cung cấp, hiện pin đang vỡ do ngoại lực.
+Đã làm việc thống nhất với KH. BH 1 tấm pin. Chờ thủ tục xuất hàng ra thay cho KH
+Ngày 25/8 Đã tạo BH</t>
+  </si>
+  <si>
+    <t>25/08/2026 11:36</t>
+  </si>
+  <si>
+    <t>P/h hãng báo lỗi fw, đã xin gia hạn đến 11:00 27/08/2026</t>
+  </si>
+  <si>
+    <t>25/08/2026 11:48</t>
+  </si>
+  <si>
+    <t>Giang Văn Nam</t>
+  </si>
+  <si>
+    <t>Trời mưa nên chưa xử lý được.</t>
+  </si>
+  <si>
+    <t>25/08/2026 11:54</t>
+  </si>
+  <si>
+    <t>Nguyễn Mai Nguyệt</t>
+  </si>
+  <si>
+    <t>DBN</t>
+  </si>
+  <si>
+    <t>Pin lưu lỗi</t>
+  </si>
+  <si>
+    <t>25/08/2026 12:01</t>
+  </si>
+  <si>
+    <t>Nguyễn Mạnh Hùng</t>
+  </si>
+  <si>
+    <t>Chờ xử lý</t>
+  </si>
+  <si>
+    <t>25/08/2026 13:33</t>
+  </si>
+  <si>
+    <t>- dự kiến ngày 26/8 hàng về, 27/8 thay cho khách
+hỏng metter, hiện đã chuyển về bảo hành cho hãng powrtech từ 18/08, thiết bị metter không tạo được bảo hành. Đang chờ hàng bảo hành về để lắp cho KH, dự kiến 29/8</t>
+  </si>
+  <si>
+    <t>25/08/2026 13:41</t>
+  </si>
+  <si>
+    <t>Huỳnh Văn Lập</t>
+  </si>
+  <si>
+    <t>- FT đã qua kiểm tra, IVT lỗi đã tháo về kho để gửi bảo hành (Tạo mới YCBH YCBH_VLG_1787635453789 từ B2C lúc 12:24 25/08/2026)</t>
+  </si>
+  <si>
+    <t>09/09/2026</t>
+  </si>
+  <si>
+    <t>25/08/2026 13:43</t>
+  </si>
+  <si>
+    <t>25/08/2026 13:44</t>
+  </si>
+  <si>
+    <t>25/08/2026 13:47</t>
+  </si>
+  <si>
+    <t>- Đã cài đặt cho khách xong và đóng Ticket
+-Đã hẹn lại KH ngày 26/8 xử lý xong cho khách</t>
   </si>
 </sst>
 </file>
@@ -8801,81 +8877,85 @@
       <c r="J224" s="5"/>
       <c r="K224" s="5"/>
     </row>
-    <row r="225" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="B225" s="5"/>
+        <v>423</v>
+      </c>
+      <c r="B225" s="4">
+        <v>4615692</v>
+      </c>
       <c r="C225" s="5" t="s">
-        <v>396</v>
+        <v>138</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G225" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H225" s="5" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="I225" s="3">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="J225" s="5"/>
       <c r="K225" s="5"/>
     </row>
-    <row r="226" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B226" s="4">
-        <v>4615692</v>
+        <v>4615642</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>138</v>
+        <v>64</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="G226" s="5" t="s">
         <v>425</v>
       </c>
       <c r="H226" s="5" t="s">
-        <v>33</v>
+        <v>302</v>
       </c>
       <c r="I226" s="3">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="J226" s="5"/>
-      <c r="K226" s="5"/>
-    </row>
-    <row r="227" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K226" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B227" s="4">
-        <v>4615642</v>
+        <v>4615525</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F227" s="5" t="s">
         <v>20</v>
@@ -8884,240 +8964,430 @@
         <v>426</v>
       </c>
       <c r="H227" s="5" t="s">
-        <v>302</v>
+        <v>14</v>
       </c>
       <c r="I227" s="3">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J227" s="5"/>
       <c r="K227" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="228" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
         <v>428</v>
       </c>
       <c r="B228" s="4">
-        <v>4615525</v>
+        <v>4615801</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>57</v>
+        <v>396</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F228" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G228" s="5" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="H228" s="5" t="s">
-        <v>14</v>
+        <v>302</v>
       </c>
       <c r="I228" s="3">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="J228" s="5"/>
-      <c r="K228" s="4" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="229" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K228" s="5"/>
+    </row>
+    <row r="229" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B229" s="4">
-        <v>4615801</v>
+        <v>4615758</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>396</v>
+        <v>339</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>13</v>
+        <v>165</v>
       </c>
       <c r="E229" s="5" t="s">
         <v>302</v>
       </c>
       <c r="F229" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G229" s="5" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="H229" s="5" t="s">
         <v>302</v>
       </c>
       <c r="I229" s="3">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="J229" s="5"/>
       <c r="K229" s="5"/>
     </row>
-    <row r="230" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B230" s="4">
-        <v>4615758</v>
+        <v>4615711</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>339</v>
+        <v>31</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>165</v>
+        <v>32</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F230" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G230" s="5" t="s">
-        <v>430</v>
+        <v>35</v>
       </c>
       <c r="H230" s="5" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="I230" s="3">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="J230" s="5"/>
       <c r="K230" s="5"/>
     </row>
-    <row r="231" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="2"/>
-      <c r="B231" s="2"/>
-      <c r="C231" s="2"/>
-      <c r="D231" s="2"/>
-      <c r="E231" s="2"/>
-      <c r="F231" s="2"/>
-      <c r="G231" s="2"/>
-      <c r="H231" s="2"/>
-      <c r="I231" s="2"/>
-      <c r="J231" s="2"/>
-      <c r="K231" s="2"/>
-    </row>
-    <row r="232" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="2"/>
-      <c r="B232" s="2"/>
-      <c r="C232" s="2"/>
-      <c r="D232" s="2"/>
-      <c r="E232" s="2"/>
-      <c r="F232" s="2"/>
-      <c r="G232" s="2"/>
-      <c r="H232" s="2"/>
-      <c r="I232" s="2"/>
-      <c r="J232" s="2"/>
-      <c r="K232" s="2"/>
+    <row r="231" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B231" s="4">
+        <v>4612554</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E231" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F231" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G231" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="H231" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I231" s="3">
+        <v>60</v>
+      </c>
+      <c r="J231" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K231" s="5"/>
+    </row>
+    <row r="232" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B232" s="4">
+        <v>4615758</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D232" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E232" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F232" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G232" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="H232" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I232" s="3">
+        <v>69</v>
+      </c>
+      <c r="J232" s="5"/>
+      <c r="K232" s="5"/>
     </row>
     <row r="233" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="2"/>
-      <c r="B233" s="2"/>
-      <c r="C233" s="2"/>
-      <c r="D233" s="2"/>
-      <c r="E233" s="2"/>
-      <c r="F233" s="2"/>
-      <c r="G233" s="2"/>
-      <c r="H233" s="2"/>
-      <c r="I233" s="2"/>
-      <c r="J233" s="2"/>
-      <c r="K233" s="2"/>
+      <c r="A233" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B233" s="4">
+        <v>4615837</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="D233" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E233" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F233" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G233" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="H233" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I233" s="3">
+        <v>113</v>
+      </c>
+      <c r="J233" s="5"/>
+      <c r="K233" s="5"/>
     </row>
     <row r="234" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="2"/>
-      <c r="B234" s="2"/>
-      <c r="C234" s="2"/>
-      <c r="D234" s="2"/>
-      <c r="E234" s="2"/>
-      <c r="F234" s="2"/>
-      <c r="G234" s="2"/>
-      <c r="H234" s="2"/>
-      <c r="I234" s="2"/>
-      <c r="J234" s="2"/>
-      <c r="K234" s="2"/>
+      <c r="A234" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B234" s="4">
+        <v>4615835</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="D234" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="E234" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F234" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G234" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="H234" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I234" s="3">
+        <v>114</v>
+      </c>
+      <c r="J234" s="5"/>
+      <c r="K234" s="5"/>
     </row>
     <row r="235" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="2"/>
-      <c r="B235" s="2"/>
-      <c r="C235" s="2"/>
-      <c r="D235" s="2"/>
-      <c r="E235" s="2"/>
-      <c r="F235" s="2"/>
-      <c r="G235" s="2"/>
-      <c r="H235" s="2"/>
-      <c r="I235" s="2"/>
-      <c r="J235" s="2"/>
-      <c r="K235" s="2"/>
-    </row>
-    <row r="236" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="2"/>
-      <c r="B236" s="2"/>
-      <c r="C236" s="2"/>
-      <c r="D236" s="2"/>
-      <c r="E236" s="2"/>
-      <c r="F236" s="2"/>
-      <c r="G236" s="2"/>
-      <c r="H236" s="2"/>
-      <c r="I236" s="2"/>
-      <c r="J236" s="2"/>
-      <c r="K236" s="2"/>
-    </row>
-    <row r="237" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="2"/>
-      <c r="B237" s="2"/>
-      <c r="C237" s="2"/>
-      <c r="D237" s="2"/>
-      <c r="E237" s="2"/>
-      <c r="F237" s="2"/>
-      <c r="G237" s="2"/>
-      <c r="H237" s="2"/>
-      <c r="I237" s="2"/>
-      <c r="J237" s="2"/>
-      <c r="K237" s="2"/>
-    </row>
-    <row r="238" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="2"/>
-      <c r="B238" s="2"/>
-      <c r="C238" s="2"/>
-      <c r="D238" s="2"/>
-      <c r="E238" s="2"/>
-      <c r="F238" s="2"/>
-      <c r="G238" s="2"/>
-      <c r="H238" s="2"/>
-      <c r="I238" s="2"/>
-      <c r="J238" s="2"/>
-      <c r="K238" s="2"/>
-    </row>
-    <row r="239" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="2"/>
-      <c r="B239" s="2"/>
-      <c r="C239" s="2"/>
-      <c r="D239" s="2"/>
-      <c r="E239" s="2"/>
-      <c r="F239" s="2"/>
-      <c r="G239" s="2"/>
-      <c r="H239" s="2"/>
-      <c r="I239" s="2"/>
-      <c r="J239" s="2"/>
-      <c r="K239" s="2"/>
-    </row>
-    <row r="240" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="2"/>
-      <c r="B240" s="2"/>
-      <c r="C240" s="2"/>
-      <c r="D240" s="2"/>
-      <c r="E240" s="2"/>
-      <c r="F240" s="2"/>
-      <c r="G240" s="2"/>
-      <c r="H240" s="2"/>
-      <c r="I240" s="2"/>
-      <c r="J240" s="2"/>
-      <c r="K240" s="2"/>
+      <c r="A235" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B235" s="4">
+        <v>4615820</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D235" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E235" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F235" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G235" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="H235" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I235" s="3">
+        <v>116</v>
+      </c>
+      <c r="J235" s="5"/>
+      <c r="K235" s="5"/>
+    </row>
+    <row r="236" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B236" s="4">
+        <v>4615553</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D236" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E236" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F236" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G236" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="H236" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I236" s="3">
+        <v>35</v>
+      </c>
+      <c r="J236" s="5"/>
+      <c r="K236" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B237" s="4">
+        <v>4615821</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="D237" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="E237" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G237" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="H237" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I237" s="3">
+        <v>115</v>
+      </c>
+      <c r="J237" s="5"/>
+      <c r="K237" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A238" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="B238" s="4">
+        <v>4615579</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D238" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E238" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G238" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="H238" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I238" s="3">
+        <v>34</v>
+      </c>
+      <c r="J238" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K238" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A239" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B239" s="4">
+        <v>4613034</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D239" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E239" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F239" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G239" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H239" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I239" s="3">
+        <v>58</v>
+      </c>
+      <c r="J239" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K239" s="5"/>
+    </row>
+    <row r="240" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B240" s="4">
+        <v>4615790</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="D240" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E240" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F240" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G240" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="H240" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I240" s="3">
+        <v>85</v>
+      </c>
+      <c r="J240" s="5"/>
+      <c r="K240" s="5"/>
     </row>
     <row r="241" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="2"/>

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_PAKH\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD29FEAB-AAFD-4240-9E4C-F48D10715953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABB1DE4-2AD4-4859-B2E4-B738AA6DF689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{15FDD92A-6CAD-44EB-866F-DB764FC19082}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{15FDD92A-6CAD-44EB-866F-DB764FC19082}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="plot_tong" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$226</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="459">
   <si>
     <t>Thời gian update</t>
   </si>
@@ -1482,6 +1483,18 @@
   <si>
     <t>- Đã cài đặt cho khách xong và đóng Ticket
 -Đã hẹn lại KH ngày 26/8 xử lý xong cho khách</t>
+  </si>
+  <si>
+    <t>Ngày</t>
+  </si>
+  <si>
+    <t>Tổng tồn</t>
+  </si>
+  <si>
+    <t>Quá hạn</t>
+  </si>
+  <si>
+    <t>24/08/2026</t>
   </si>
 </sst>
 </file>
@@ -1509,12 +1522,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAD3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1544,7 +1563,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1558,6 +1577,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -18637,4 +18662,47 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35EBF10C-E87B-485F-A937-7F9515EE4DA9}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="B2" s="4">
+        <v>73</v>
+      </c>
+      <c r="C2" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="4">
+        <v>47</v>
+      </c>
+      <c r="C3" s="4">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_PAKH\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABB1DE4-2AD4-4859-B2E4-B738AA6DF689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A7F50A-041C-49AF-8423-22E49CF41B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{15FDD92A-6CAD-44EB-866F-DB764FC19082}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{15FDD92A-6CAD-44EB-866F-DB764FC19082}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1708" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="535">
   <si>
     <t>Thời gian update</t>
   </si>
@@ -1495,6 +1495,263 @@
   </si>
   <si>
     <t>24/08/2026</t>
+  </si>
+  <si>
+    <t>25/08/2026 13:55</t>
+  </si>
+  <si>
+    <t>Lỗi BMS</t>
+  </si>
+  <si>
+    <t>25/08/2026 13:59</t>
+  </si>
+  <si>
+    <t>Hẹn khách chiều 14h qua thực hiện. Đã hoàn thành xử lý cho KH</t>
+  </si>
+  <si>
+    <t>25/08/2026 14:09</t>
+  </si>
+  <si>
+    <t>- Đã hoàn thành bảo hành cho khách, đã đóng Ticket và YCBH
+- Gửi thiết bị đi bảo hành, dự kiến 27/08 về thay cho khách
+Tạo mới YCBH YCBH_CMU_1787372431973 từ B2C lúc 11:20 22/08/2026</t>
+  </si>
+  <si>
+    <t>Trước đó FT đã tới kiểm tra. do điện lưới của KH bị thấp. FT đã hẹn 22/08 qua xử lý và giải thích với KH
+Ngày 22/8 mưa to nên không kiểm tra đc. Chờ mưa tạnh sẽ qua xử lý
+Ngày 25/8 KT kiểm tra hệ thống hoạt động bt</t>
+  </si>
+  <si>
+    <t>25/08/2026 14:19</t>
+  </si>
+  <si>
+    <t>CÔNG TY TNHH VẬN TẢI THƯƠNG MẠI NGỌC GIÀU</t>
+  </si>
+  <si>
+    <t>Vừa tiếp nhận thông tin, chuẩn bị đến kiểm tra</t>
+  </si>
+  <si>
+    <t>25/08/2026 14:21</t>
+  </si>
+  <si>
+    <t>Trời mưa nên chưa thực hiện đc.
+Đã xử lý xong</t>
+  </si>
+  <si>
+    <t>25/08/2026 14:22</t>
+  </si>
+  <si>
+    <t>- Bổ sung cắt sét DC, đã xử lý xong cho khách và đóng Ticket
+- Đ/c Khánh báo đang xử lý cho khách, dự kiến đóng Ticket trước 15h ngày 25/8</t>
+  </si>
+  <si>
+    <t>25/08/2026 14:23</t>
+  </si>
+  <si>
+    <t>- KT không gọi được cho khách nhiều lần, đã gia hạn thêm đến 31/8 để liên lạc lại
+- KT đã liên hệ với KH và hôm nay hỗ trợ KH phần cài kết nối App trc và kiểm tra thêm cho khách</t>
+  </si>
+  <si>
+    <t>25/08/2026 14:24</t>
+  </si>
+  <si>
+    <t>- KT không gọi được cho khách nhiều lần, đã gia hạn thêm đến 31/8 để liên lạc lại
+- KT đã liên hệ với KH và dự kiến hôm nay hỗ trợ KH phần cài kết nối App trc và kiểm tra thêm cho khách</t>
+  </si>
+  <si>
+    <t>25/08/2026 14:25</t>
+  </si>
+  <si>
+    <t>- Dự kiến mai Pin về, lắp cho khách xong trc 28/8
+BAT pin bị lỗi, đã gửi đi để hãng bảo hành
+Hãng chưa phản hồi ngày trả thiết bị, dự kiến 28/8
+Tạo mới YCBH YCBH_AGG_1786617217200 từ B2C lúc 17:33 13/08/2026 Hạn hoàn thành 23:59 28/08/2026</t>
+  </si>
+  <si>
+    <t>25/08/2026 14:26</t>
+  </si>
+  <si>
+    <t>Do điện app nhảy</t>
+  </si>
+  <si>
+    <t>25/08/2026 14:27</t>
+  </si>
+  <si>
+    <t>Chiều 25/8 KT đến xử lý</t>
+  </si>
+  <si>
+    <t>25/08/2026 14:33</t>
+  </si>
+  <si>
+    <t>Đã gửi email xác nhận chính sách bảo hành với hãng
+Hãng đang yêu cầu ảnh chụp nhưng nhà KH cách xa khoảng 60km, hiện tại chỉ có video quay lại, đã gửi để hãng kiểm tra.
+GDKD đang đi ra ngoài, 18h sẽ phản hồi lại</t>
+  </si>
+  <si>
+    <t>25/08/2026 14:34</t>
+  </si>
+  <si>
+    <t>Thời gian hệ dùng 3 năm rồi trường hợp cháy không xác định nguyên nhân.
+Hợp đồng không ghi rõ thời gian bảo hành tủ điện.
+Khi cháy tủ điện khách không chịu chi phí sửa chữa. 
+Hỗ trợ chi nhánh làm tờ trình xin kinh phí bảo hành.</t>
+  </si>
+  <si>
+    <t>25/08/2026 14:56</t>
+  </si>
+  <si>
+    <t>Lỗi thiết bị đang phối hợp với hãng để xử lý, đã xin gia hạn đến 11:00 27/08/2026</t>
+  </si>
+  <si>
+    <t>25/08/2026 15:13</t>
+  </si>
+  <si>
+    <t>Lê Duy Huế</t>
+  </si>
+  <si>
+    <t>- Đã giao đ/c Toản FT3 liên hệ KH, sáng mai qua nhà khách kiểm tra xử lý</t>
+  </si>
+  <si>
+    <t>25/08/2026 15:26</t>
+  </si>
+  <si>
+    <t>Đặng Bá Hiệp</t>
+  </si>
+  <si>
+    <t>- Đã giao GĐKT Thanh liên hệ và qua kiểm tra cho KH</t>
+  </si>
+  <si>
+    <t>25/08/2026 15:36</t>
+  </si>
+  <si>
+    <t>Đã trao đổi giải thích cho KH</t>
+  </si>
+  <si>
+    <t>25/08/2026 16:02</t>
+  </si>
+  <si>
+    <t>Bị cháy ATS, ngày 25/8 đtac qua thay mới cho KH
+Nhà KH đang bị lụt nên ko vào thay được. Bao giờ nước rút sẽ qua thay.</t>
+  </si>
+  <si>
+    <t>25/08/2026 16:06</t>
+  </si>
+  <si>
+    <t>Lỗi thiết bị đang phối hợp với hãng để xử lý
+Hãng báo tháo inverter gửi về bảo hành</t>
+  </si>
+  <si>
+    <t>25/08/2026 16:13</t>
+  </si>
+  <si>
+    <t>lỗi tiếp điểm cầu dao đảo chiều của nhà khách</t>
+  </si>
+  <si>
+    <t>25/08/2026 16:25</t>
+  </si>
+  <si>
+    <t>Đang nghi ngờ hỏng pin lưu, Kiểm tra onl đang nghi ngờ bị vào nước. 
+Hẹn KH ngày 28 vào tháo đi bảo hành</t>
+  </si>
+  <si>
+    <t>25/08/2026 16:26</t>
+  </si>
+  <si>
+    <t>Hỏng ATS, hiện đang chờ KH về, để chụp ảnh ATS hỏng để làm việc với hãng. Dự kiến 25/08 KH mới về để tới làm việc
+Đã tạo BH, chờ hãng gửi TB về thay. Dự kiến ngày 28/8 có hàng</t>
+  </si>
+  <si>
+    <t>25/08/2026 16:32</t>
+  </si>
+  <si>
+    <t>Lỗi thiết bị đang phối hợp với hãng để xử lý
+Hãng báo tháo inverter gửi về bảo hành, nhanh nhất trong 1 ngày sẽ gửi lại</t>
+  </si>
+  <si>
+    <t>25/08/2026 16:34</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Quân</t>
+  </si>
+  <si>
+    <t>- KH bán điện cho điện lực, PP Toàn đã liên hệ KH và báo đã cung cấp hồ sơ liên quan, việc còn lại KH làm việc với điện lực. Đã đóng Ticket</t>
+  </si>
+  <si>
+    <t>25/08/2026 16:37</t>
+  </si>
+  <si>
+    <t>Hệ bị mất giám sát, ngày 26/8 KT qua cài lại Wifi</t>
+  </si>
+  <si>
+    <t>25/08/2026 16:46</t>
+  </si>
+  <si>
+    <t>Lê Hoài Bảo</t>
+  </si>
+  <si>
+    <t>- FT3 đã liên hệ cho KH, dự kiến qua kiểm tra và đóng Ticket trc 15h ngày 26/08</t>
+  </si>
+  <si>
+    <t>25/08/2026 16:47</t>
+  </si>
+  <si>
+    <t>- GĐKD Tùng đã hỗ trợ cho KH xong và đóng Ticket
+- GĐKD Tùng đang hỗ trợ làm thủ tục cho KH dự kiến xong trước 28/8</t>
+  </si>
+  <si>
+    <t>25/08/2026 16:55</t>
+  </si>
+  <si>
+    <t>lỗi mạch pin lưu trữ bị nước vào</t>
+  </si>
+  <si>
+    <t>25/08/2026 17:04</t>
+  </si>
+  <si>
+    <t>Đã xử lý cho KH
+KH di dời wifi phụ nên thiết bị inverter mất kết nối wifi</t>
+  </si>
+  <si>
+    <t>25/08/2026 17:33</t>
+  </si>
+  <si>
+    <t>Thời gian hệ dùng 3 năm rồi trường hợp cháy không xác định nguyên nhân.
+Hợp đồng ghi thời gian bảo hành tủ điện là 01 năm.
+Khi cháy tủ điện khách không chịu chi phí sửa chữa. 
+Hỗ trợ chi nhánh làm tờ trình xin kinh phí bảo hành.
+Dự kiến tủ điện về vào ngày 26/8</t>
+  </si>
+  <si>
+    <t>25/08/2026 17:55</t>
+  </si>
+  <si>
+    <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN HOA SEN NGHỆ AN</t>
+  </si>
+  <si>
+    <t>Ngày mai KT qua xử lý</t>
+  </si>
+  <si>
+    <t>25/08/2026 17:56</t>
+  </si>
+  <si>
+    <t>Ngày mai 26/8 KT qua xử lý</t>
+  </si>
+  <si>
+    <t>25/08/2026 17:57</t>
+  </si>
+  <si>
+    <t>Lê Phi Long</t>
+  </si>
+  <si>
+    <t>Do trời mưa nên chưa lắp đặt được. Hẹn KH trời hết mưa rồi qua xử lý</t>
+  </si>
+  <si>
+    <t>25/08/2026 18:13</t>
+  </si>
+  <si>
+    <t>Đã gửi email xác nhận chính sách bảo hành với hãng
+Hãng đang yêu cầu ảnh chụp nhưng nhà KH cách xa khoảng 60km, hiện tại chỉ có video quay lại, đã gửi để hãng kiểm tra.
+Nhân sự phụ trách đang đi ra ngoài, chưa kiểm tra được mail phản hồi của hãng</t>
   </si>
 </sst>
 </file>
@@ -9415,524 +9672,1258 @@
       <c r="K240" s="5"/>
     </row>
     <row r="241" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="2"/>
-      <c r="B241" s="2"/>
-      <c r="C241" s="2"/>
-      <c r="D241" s="2"/>
-      <c r="E241" s="2"/>
-      <c r="F241" s="2"/>
-      <c r="G241" s="2"/>
-      <c r="H241" s="2"/>
-      <c r="I241" s="2"/>
-      <c r="J241" s="2"/>
-      <c r="K241" s="2"/>
-    </row>
-    <row r="242" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="2"/>
-      <c r="B242" s="2"/>
-      <c r="C242" s="2"/>
-      <c r="D242" s="2"/>
-      <c r="E242" s="2"/>
-      <c r="F242" s="2"/>
-      <c r="G242" s="2"/>
-      <c r="H242" s="2"/>
-      <c r="I242" s="2"/>
-      <c r="J242" s="2"/>
-      <c r="K242" s="2"/>
-    </row>
-    <row r="243" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="2"/>
-      <c r="B243" s="2"/>
-      <c r="C243" s="2"/>
-      <c r="D243" s="2"/>
-      <c r="E243" s="2"/>
-      <c r="F243" s="2"/>
-      <c r="G243" s="2"/>
-      <c r="H243" s="2"/>
-      <c r="I243" s="2"/>
-      <c r="J243" s="2"/>
-      <c r="K243" s="2"/>
-    </row>
-    <row r="244" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="2"/>
-      <c r="B244" s="2"/>
-      <c r="C244" s="2"/>
-      <c r="D244" s="2"/>
-      <c r="E244" s="2"/>
-      <c r="F244" s="2"/>
-      <c r="G244" s="2"/>
-      <c r="H244" s="2"/>
-      <c r="I244" s="2"/>
-      <c r="J244" s="2"/>
-      <c r="K244" s="2"/>
-    </row>
-    <row r="245" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="2"/>
-      <c r="B245" s="2"/>
-      <c r="C245" s="2"/>
-      <c r="D245" s="2"/>
-      <c r="E245" s="2"/>
-      <c r="F245" s="2"/>
-      <c r="G245" s="2"/>
-      <c r="H245" s="2"/>
-      <c r="I245" s="2"/>
-      <c r="J245" s="2"/>
-      <c r="K245" s="2"/>
-    </row>
-    <row r="246" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="2"/>
-      <c r="B246" s="2"/>
-      <c r="C246" s="2"/>
-      <c r="D246" s="2"/>
-      <c r="E246" s="2"/>
-      <c r="F246" s="2"/>
-      <c r="G246" s="2"/>
-      <c r="H246" s="2"/>
-      <c r="I246" s="2"/>
-      <c r="J246" s="2"/>
-      <c r="K246" s="2"/>
-    </row>
-    <row r="247" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="2"/>
-      <c r="B247" s="2"/>
-      <c r="C247" s="2"/>
-      <c r="D247" s="2"/>
-      <c r="E247" s="2"/>
-      <c r="F247" s="2"/>
-      <c r="G247" s="2"/>
-      <c r="H247" s="2"/>
-      <c r="I247" s="2"/>
-      <c r="J247" s="2"/>
-      <c r="K247" s="2"/>
+      <c r="A241" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B241" s="4">
+        <v>4615814</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="D241" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E241" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G241" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="H241" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I241" s="3">
+        <v>110</v>
+      </c>
+      <c r="J241" s="5"/>
+      <c r="K241" s="5"/>
+    </row>
+    <row r="242" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B242" s="4">
+        <v>4615834</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="D242" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E242" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G242" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="H242" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I242" s="3">
+        <v>105</v>
+      </c>
+      <c r="J242" s="5"/>
+      <c r="K242" s="5"/>
+    </row>
+    <row r="243" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A243" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B243" s="4">
+        <v>4615522</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D243" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E243" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F243" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G243" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="H243" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I243" s="3">
+        <v>38</v>
+      </c>
+      <c r="J243" s="5"/>
+      <c r="K243" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A244" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B244" s="4">
+        <v>4615710</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D244" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E244" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F244" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G244" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="H244" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I244" s="3">
+        <v>10</v>
+      </c>
+      <c r="J244" s="5"/>
+      <c r="K244" s="5"/>
+    </row>
+    <row r="245" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A245" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B245" s="4">
+        <v>4615505</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D245" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E245" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G245" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="H245" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I245" s="3">
+        <v>39</v>
+      </c>
+      <c r="J245" s="5"/>
+      <c r="K245" s="5"/>
+    </row>
+    <row r="246" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A246" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B246" s="4">
+        <v>4615822</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="D246" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E246" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F246" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G246" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="H246" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I246" s="3">
+        <v>119</v>
+      </c>
+      <c r="J246" s="5"/>
+      <c r="K246" s="5"/>
+    </row>
+    <row r="247" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B247" s="4">
+        <v>4615757</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D247" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E247" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G247" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="H247" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I247" s="3">
+        <v>70</v>
+      </c>
+      <c r="J247" s="5"/>
+      <c r="K247" s="5"/>
     </row>
     <row r="248" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="2"/>
-      <c r="B248" s="2"/>
-      <c r="C248" s="2"/>
-      <c r="D248" s="2"/>
-      <c r="E248" s="2"/>
-      <c r="F248" s="2"/>
-      <c r="G248" s="2"/>
-      <c r="H248" s="2"/>
-      <c r="I248" s="2"/>
-      <c r="J248" s="2"/>
-      <c r="K248" s="2"/>
+      <c r="A248" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B248" s="4">
+        <v>4615782</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="D248" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="E248" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F248" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G248" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="H248" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I248" s="3">
+        <v>89</v>
+      </c>
+      <c r="J248" s="5"/>
+      <c r="K248" s="5"/>
     </row>
     <row r="249" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="2"/>
-      <c r="B249" s="2"/>
-      <c r="C249" s="2"/>
-      <c r="D249" s="2"/>
-      <c r="E249" s="2"/>
-      <c r="F249" s="2"/>
-      <c r="G249" s="2"/>
-      <c r="H249" s="2"/>
-      <c r="I249" s="2"/>
-      <c r="J249" s="2"/>
-      <c r="K249" s="2"/>
+      <c r="A249" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B249" s="4">
+        <v>4615776</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D249" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E249" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G249" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="H249" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I249" s="3">
+        <v>92</v>
+      </c>
+      <c r="J249" s="5"/>
+      <c r="K249" s="5"/>
     </row>
     <row r="250" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="2"/>
-      <c r="B250" s="2"/>
-      <c r="C250" s="2"/>
-      <c r="D250" s="2"/>
-      <c r="E250" s="2"/>
-      <c r="F250" s="2"/>
-      <c r="G250" s="2"/>
-      <c r="H250" s="2"/>
-      <c r="I250" s="2"/>
-      <c r="J250" s="2"/>
-      <c r="K250" s="2"/>
-    </row>
-    <row r="251" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="2"/>
-      <c r="B251" s="2"/>
-      <c r="C251" s="2"/>
-      <c r="D251" s="2"/>
-      <c r="E251" s="2"/>
-      <c r="F251" s="2"/>
-      <c r="G251" s="2"/>
-      <c r="H251" s="2"/>
-      <c r="I251" s="2"/>
-      <c r="J251" s="2"/>
-      <c r="K251" s="2"/>
-    </row>
-    <row r="252" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="2"/>
-      <c r="B252" s="2"/>
-      <c r="C252" s="2"/>
-      <c r="D252" s="2"/>
-      <c r="E252" s="2"/>
-      <c r="F252" s="2"/>
-      <c r="G252" s="2"/>
-      <c r="H252" s="2"/>
-      <c r="I252" s="2"/>
-      <c r="J252" s="2"/>
-      <c r="K252" s="2"/>
-    </row>
-    <row r="253" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="2"/>
-      <c r="B253" s="2"/>
-      <c r="C253" s="2"/>
-      <c r="D253" s="2"/>
-      <c r="E253" s="2"/>
-      <c r="F253" s="2"/>
-      <c r="G253" s="2"/>
-      <c r="H253" s="2"/>
-      <c r="I253" s="2"/>
-      <c r="J253" s="2"/>
-      <c r="K253" s="2"/>
-    </row>
-    <row r="254" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="2"/>
-      <c r="B254" s="2"/>
-      <c r="C254" s="2"/>
-      <c r="D254" s="2"/>
-      <c r="E254" s="2"/>
-      <c r="F254" s="2"/>
-      <c r="G254" s="2"/>
-      <c r="H254" s="2"/>
-      <c r="I254" s="2"/>
-      <c r="J254" s="2"/>
-      <c r="K254" s="2"/>
+      <c r="A250" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B250" s="4">
+        <v>4615792</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D250" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="E250" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F250" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G250" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H250" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I250" s="3">
+        <v>100</v>
+      </c>
+      <c r="J250" s="5"/>
+      <c r="K250" s="5"/>
+    </row>
+    <row r="251" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A251" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B251" s="4">
+        <v>4615817</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E251" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G251" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="H251" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I251" s="3">
+        <v>108</v>
+      </c>
+      <c r="J251" s="5"/>
+      <c r="K251" s="5"/>
+    </row>
+    <row r="252" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A252" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="B252" s="4">
+        <v>4615816</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D252" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E252" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F252" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G252" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="H252" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I252" s="3">
+        <v>109</v>
+      </c>
+      <c r="J252" s="5"/>
+      <c r="K252" s="5"/>
+    </row>
+    <row r="253" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="B253" s="4">
+        <v>4615816</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D253" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E253" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F253" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G253" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="H253" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I253" s="3">
+        <v>109</v>
+      </c>
+      <c r="J253" s="5"/>
+      <c r="K253" s="5"/>
+    </row>
+    <row r="254" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="B254" s="4">
+        <v>4615536</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D254" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E254" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G254" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="H254" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I254" s="3">
+        <v>36</v>
+      </c>
+      <c r="J254" s="5"/>
+      <c r="K254" s="4" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="255" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="2"/>
-      <c r="B255" s="2"/>
-      <c r="C255" s="2"/>
-      <c r="D255" s="2"/>
-      <c r="E255" s="2"/>
-      <c r="F255" s="2"/>
-      <c r="G255" s="2"/>
-      <c r="H255" s="2"/>
-      <c r="I255" s="2"/>
-      <c r="J255" s="2"/>
-      <c r="K255" s="2"/>
+      <c r="A255" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="B255" s="4">
+        <v>4615835</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="D255" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="E255" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F255" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G255" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="H255" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I255" s="3">
+        <v>114</v>
+      </c>
+      <c r="J255" s="5"/>
+      <c r="K255" s="5"/>
     </row>
     <row r="256" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="2"/>
-      <c r="B256" s="2"/>
-      <c r="C256" s="2"/>
-      <c r="D256" s="2"/>
-      <c r="E256" s="2"/>
-      <c r="F256" s="2"/>
-      <c r="G256" s="2"/>
-      <c r="H256" s="2"/>
-      <c r="I256" s="2"/>
-      <c r="J256" s="2"/>
-      <c r="K256" s="2"/>
-    </row>
-    <row r="257" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="2"/>
-      <c r="B257" s="2"/>
-      <c r="C257" s="2"/>
-      <c r="D257" s="2"/>
-      <c r="E257" s="2"/>
-      <c r="F257" s="2"/>
-      <c r="G257" s="2"/>
-      <c r="H257" s="2"/>
-      <c r="I257" s="2"/>
-      <c r="J257" s="2"/>
-      <c r="K257" s="2"/>
-    </row>
-    <row r="258" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="2"/>
-      <c r="B258" s="2"/>
-      <c r="C258" s="2"/>
-      <c r="D258" s="2"/>
-      <c r="E258" s="2"/>
-      <c r="F258" s="2"/>
-      <c r="G258" s="2"/>
-      <c r="H258" s="2"/>
-      <c r="I258" s="2"/>
-      <c r="J258" s="2"/>
-      <c r="K258" s="2"/>
-    </row>
-    <row r="259" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="2"/>
-      <c r="B259" s="2"/>
-      <c r="C259" s="2"/>
-      <c r="D259" s="2"/>
-      <c r="E259" s="2"/>
-      <c r="F259" s="2"/>
-      <c r="G259" s="2"/>
-      <c r="H259" s="2"/>
-      <c r="I259" s="2"/>
-      <c r="J259" s="2"/>
-      <c r="K259" s="2"/>
-    </row>
-    <row r="260" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="2"/>
-      <c r="B260" s="2"/>
-      <c r="C260" s="2"/>
-      <c r="D260" s="2"/>
-      <c r="E260" s="2"/>
-      <c r="F260" s="2"/>
-      <c r="G260" s="2"/>
-      <c r="H260" s="2"/>
-      <c r="I260" s="2"/>
-      <c r="J260" s="2"/>
-      <c r="K260" s="2"/>
+      <c r="A256" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B256" s="4">
+        <v>4615832</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D256" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E256" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F256" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G256" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="H256" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I256" s="3">
+        <v>106</v>
+      </c>
+      <c r="J256" s="5"/>
+      <c r="K256" s="5"/>
+    </row>
+    <row r="257" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B257" s="4">
+        <v>4612186</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D257" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E257" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F257" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G257" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="H257" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I257" s="3">
+        <v>61</v>
+      </c>
+      <c r="J257" s="5"/>
+      <c r="K257" s="5"/>
+    </row>
+    <row r="258" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="B258" s="4">
+        <v>4615579</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D258" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E258" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F258" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G258" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="H258" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I258" s="3">
+        <v>34</v>
+      </c>
+      <c r="J258" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K258" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="B259" s="4">
+        <v>4615758</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D259" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E259" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F259" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G259" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="H259" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I259" s="3">
+        <v>69</v>
+      </c>
+      <c r="J259" s="5"/>
+      <c r="K259" s="5"/>
+    </row>
+    <row r="260" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="B260" s="4">
+        <v>4615839</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="D260" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E260" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F260" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G260" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="H260" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I260" s="3">
+        <v>117</v>
+      </c>
+      <c r="J260" s="5"/>
+      <c r="K260" s="5"/>
     </row>
     <row r="261" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="2"/>
-      <c r="B261" s="2"/>
-      <c r="C261" s="2"/>
-      <c r="D261" s="2"/>
-      <c r="E261" s="2"/>
-      <c r="F261" s="2"/>
-      <c r="G261" s="2"/>
-      <c r="H261" s="2"/>
-      <c r="I261" s="2"/>
-      <c r="J261" s="2"/>
-      <c r="K261" s="2"/>
+      <c r="A261" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B261" s="4">
+        <v>4615838</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="D261" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E261" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F261" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G261" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="H261" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I261" s="3">
+        <v>118</v>
+      </c>
+      <c r="J261" s="5"/>
+      <c r="K261" s="5"/>
     </row>
     <row r="262" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="2"/>
-      <c r="B262" s="2"/>
-      <c r="C262" s="2"/>
-      <c r="D262" s="2"/>
-      <c r="E262" s="2"/>
-      <c r="F262" s="2"/>
-      <c r="G262" s="2"/>
-      <c r="H262" s="2"/>
-      <c r="I262" s="2"/>
-      <c r="J262" s="2"/>
-      <c r="K262" s="2"/>
-    </row>
-    <row r="263" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="2"/>
-      <c r="B263" s="2"/>
-      <c r="C263" s="2"/>
-      <c r="D263" s="2"/>
-      <c r="E263" s="2"/>
-      <c r="F263" s="2"/>
-      <c r="G263" s="2"/>
-      <c r="H263" s="2"/>
-      <c r="I263" s="2"/>
-      <c r="J263" s="2"/>
-      <c r="K263" s="2"/>
-    </row>
-    <row r="264" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A264" s="2"/>
-      <c r="B264" s="2"/>
-      <c r="C264" s="2"/>
-      <c r="D264" s="2"/>
-      <c r="E264" s="2"/>
-      <c r="F264" s="2"/>
-      <c r="G264" s="2"/>
-      <c r="H264" s="2"/>
-      <c r="I264" s="2"/>
-      <c r="J264" s="2"/>
-      <c r="K264" s="2"/>
+      <c r="A262" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B262" s="4">
+        <v>4615831</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="D262" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E262" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F262" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G262" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="H262" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I262" s="3">
+        <v>107</v>
+      </c>
+      <c r="J262" s="5"/>
+      <c r="K262" s="5"/>
+    </row>
+    <row r="263" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A263" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B263" s="4">
+        <v>4615786</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D263" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E263" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F263" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G263" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="H263" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I263" s="3">
+        <v>102</v>
+      </c>
+      <c r="J263" s="5"/>
+      <c r="K263" s="5"/>
+    </row>
+    <row r="264" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A264" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B264" s="4">
+        <v>4615758</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D264" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E264" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F264" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G264" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="H264" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I264" s="3">
+        <v>69</v>
+      </c>
+      <c r="J264" s="5"/>
+      <c r="K264" s="5"/>
     </row>
     <row r="265" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="2"/>
-      <c r="B265" s="2"/>
-      <c r="C265" s="2"/>
-      <c r="D265" s="2"/>
-      <c r="E265" s="2"/>
-      <c r="F265" s="2"/>
-      <c r="G265" s="2"/>
-      <c r="H265" s="2"/>
-      <c r="I265" s="2"/>
-      <c r="J265" s="2"/>
-      <c r="K265" s="2"/>
-    </row>
-    <row r="266" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="2"/>
-      <c r="B266" s="2"/>
-      <c r="C266" s="2"/>
-      <c r="D266" s="2"/>
-      <c r="E266" s="2"/>
-      <c r="F266" s="2"/>
-      <c r="G266" s="2"/>
-      <c r="H266" s="2"/>
-      <c r="I266" s="2"/>
-      <c r="J266" s="2"/>
-      <c r="K266" s="2"/>
-    </row>
-    <row r="267" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="2"/>
-      <c r="B267" s="2"/>
-      <c r="C267" s="2"/>
-      <c r="D267" s="2"/>
-      <c r="E267" s="2"/>
-      <c r="F267" s="2"/>
-      <c r="G267" s="2"/>
-      <c r="H267" s="2"/>
-      <c r="I267" s="2"/>
-      <c r="J267" s="2"/>
-      <c r="K267" s="2"/>
-    </row>
-    <row r="268" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="2"/>
-      <c r="B268" s="2"/>
-      <c r="C268" s="2"/>
-      <c r="D268" s="2"/>
-      <c r="E268" s="2"/>
-      <c r="F268" s="2"/>
-      <c r="G268" s="2"/>
-      <c r="H268" s="2"/>
-      <c r="I268" s="2"/>
-      <c r="J268" s="2"/>
-      <c r="K268" s="2"/>
-    </row>
-    <row r="269" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="2"/>
-      <c r="B269" s="2"/>
-      <c r="C269" s="2"/>
-      <c r="D269" s="2"/>
-      <c r="E269" s="2"/>
-      <c r="F269" s="2"/>
-      <c r="G269" s="2"/>
-      <c r="H269" s="2"/>
-      <c r="I269" s="2"/>
-      <c r="J269" s="2"/>
-      <c r="K269" s="2"/>
+      <c r="A265" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B265" s="4">
+        <v>4615820</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D265" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E265" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F265" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G265" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="H265" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I265" s="3">
+        <v>116</v>
+      </c>
+      <c r="J265" s="5"/>
+      <c r="K265" s="5"/>
+    </row>
+    <row r="266" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A266" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="B266" s="4">
+        <v>4615644</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D266" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E266" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F266" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G266" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="H266" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I266" s="3">
+        <v>24</v>
+      </c>
+      <c r="J266" s="5"/>
+      <c r="K266" s="5"/>
+    </row>
+    <row r="267" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A267" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B267" s="4">
+        <v>4615145</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D267" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E267" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F267" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G267" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="H267" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I267" s="3">
+        <v>50</v>
+      </c>
+      <c r="J267" s="5"/>
+      <c r="K267" s="5"/>
+    </row>
+    <row r="268" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A268" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B268" s="4">
+        <v>4615758</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D268" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E268" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F268" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G268" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="H268" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I268" s="3">
+        <v>69</v>
+      </c>
+      <c r="J268" s="5"/>
+      <c r="K268" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A269" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="B269" s="4">
+        <v>4615823</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="D269" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E269" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F269" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G269" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="H269" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I269" s="3">
+        <v>123</v>
+      </c>
+      <c r="J269" s="5"/>
+      <c r="K269" s="5"/>
     </row>
     <row r="270" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A270" s="2"/>
-      <c r="B270" s="2"/>
-      <c r="C270" s="2"/>
-      <c r="D270" s="2"/>
-      <c r="E270" s="2"/>
-      <c r="F270" s="2"/>
-      <c r="G270" s="2"/>
-      <c r="H270" s="2"/>
-      <c r="I270" s="2"/>
-      <c r="J270" s="2"/>
-      <c r="K270" s="2"/>
-    </row>
-    <row r="271" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="2"/>
-      <c r="B271" s="2"/>
-      <c r="C271" s="2"/>
-      <c r="D271" s="2"/>
-      <c r="E271" s="2"/>
-      <c r="F271" s="2"/>
-      <c r="G271" s="2"/>
-      <c r="H271" s="2"/>
-      <c r="I271" s="2"/>
-      <c r="J271" s="2"/>
-      <c r="K271" s="2"/>
-    </row>
-    <row r="272" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="2"/>
-      <c r="B272" s="2"/>
-      <c r="C272" s="2"/>
-      <c r="D272" s="2"/>
-      <c r="E272" s="2"/>
-      <c r="F272" s="2"/>
-      <c r="G272" s="2"/>
-      <c r="H272" s="2"/>
-      <c r="I272" s="2"/>
-      <c r="J272" s="2"/>
-      <c r="K272" s="2"/>
+      <c r="A270" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="B270" s="4">
+        <v>4615779</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="D270" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E270" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F270" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G270" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="H270" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I270" s="3">
+        <v>91</v>
+      </c>
+      <c r="J270" s="5"/>
+      <c r="K270" s="5"/>
+    </row>
+    <row r="271" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A271" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B271" s="4">
+        <v>4615824</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="D271" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E271" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F271" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G271" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="H271" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I271" s="3">
+        <v>122</v>
+      </c>
+      <c r="J271" s="5"/>
+      <c r="K271" s="5"/>
+    </row>
+    <row r="272" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A272" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B272" s="4">
+        <v>4615806</v>
+      </c>
+      <c r="C272" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="D272" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E272" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F272" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G272" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="H272" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I272" s="3">
+        <v>111</v>
+      </c>
+      <c r="J272" s="5"/>
+      <c r="K272" s="5"/>
     </row>
     <row r="273" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="2"/>
-      <c r="B273" s="2"/>
-      <c r="C273" s="2"/>
-      <c r="D273" s="2"/>
-      <c r="E273" s="2"/>
-      <c r="F273" s="2"/>
-      <c r="G273" s="2"/>
-      <c r="H273" s="2"/>
-      <c r="I273" s="2"/>
-      <c r="J273" s="2"/>
-      <c r="K273" s="2"/>
-    </row>
-    <row r="274" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="2"/>
-      <c r="B274" s="2"/>
-      <c r="C274" s="2"/>
-      <c r="D274" s="2"/>
-      <c r="E274" s="2"/>
-      <c r="F274" s="2"/>
-      <c r="G274" s="2"/>
-      <c r="H274" s="2"/>
-      <c r="I274" s="2"/>
-      <c r="J274" s="2"/>
-      <c r="K274" s="2"/>
-    </row>
-    <row r="275" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="2"/>
-      <c r="B275" s="2"/>
-      <c r="C275" s="2"/>
-      <c r="D275" s="2"/>
-      <c r="E275" s="2"/>
-      <c r="F275" s="2"/>
-      <c r="G275" s="2"/>
-      <c r="H275" s="2"/>
-      <c r="I275" s="2"/>
-      <c r="J275" s="2"/>
-      <c r="K275" s="2"/>
-    </row>
-    <row r="276" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="2"/>
-      <c r="B276" s="2"/>
-      <c r="C276" s="2"/>
-      <c r="D276" s="2"/>
-      <c r="E276" s="2"/>
-      <c r="F276" s="2"/>
-      <c r="G276" s="2"/>
-      <c r="H276" s="2"/>
-      <c r="I276" s="2"/>
-      <c r="J276" s="2"/>
-      <c r="K276" s="2"/>
-    </row>
-    <row r="277" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="2"/>
-      <c r="B277" s="2"/>
-      <c r="C277" s="2"/>
-      <c r="D277" s="2"/>
-      <c r="E277" s="2"/>
-      <c r="F277" s="2"/>
-      <c r="G277" s="2"/>
-      <c r="H277" s="2"/>
-      <c r="I277" s="2"/>
-      <c r="J277" s="2"/>
-      <c r="K277" s="2"/>
-    </row>
-    <row r="278" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A278" s="2"/>
-      <c r="B278" s="2"/>
-      <c r="C278" s="2"/>
-      <c r="D278" s="2"/>
-      <c r="E278" s="2"/>
-      <c r="F278" s="2"/>
-      <c r="G278" s="2"/>
-      <c r="H278" s="2"/>
-      <c r="I278" s="2"/>
-      <c r="J278" s="2"/>
-      <c r="K278" s="2"/>
-    </row>
-    <row r="279" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A279" s="2"/>
-      <c r="B279" s="2"/>
-      <c r="C279" s="2"/>
-      <c r="D279" s="2"/>
-      <c r="E279" s="2"/>
-      <c r="F279" s="2"/>
-      <c r="G279" s="2"/>
-      <c r="H279" s="2"/>
-      <c r="I279" s="2"/>
-      <c r="J279" s="2"/>
-      <c r="K279" s="2"/>
-    </row>
-    <row r="280" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A280" s="2"/>
-      <c r="B280" s="2"/>
-      <c r="C280" s="2"/>
-      <c r="D280" s="2"/>
-      <c r="E280" s="2"/>
-      <c r="F280" s="2"/>
-      <c r="G280" s="2"/>
-      <c r="H280" s="2"/>
-      <c r="I280" s="2"/>
-      <c r="J280" s="2"/>
-      <c r="K280" s="2"/>
+      <c r="A273" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="B273" s="4">
+        <v>4615832</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D273" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E273" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F273" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G273" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="H273" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I273" s="3">
+        <v>106</v>
+      </c>
+      <c r="J273" s="5"/>
+      <c r="K273" s="5"/>
+    </row>
+    <row r="274" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A274" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B274" s="4">
+        <v>4615822</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="D274" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E274" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F274" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G274" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="H274" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I274" s="3">
+        <v>119</v>
+      </c>
+      <c r="J274" s="5"/>
+      <c r="K274" s="5"/>
+    </row>
+    <row r="275" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A275" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="B275" s="4">
+        <v>4615579</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D275" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E275" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F275" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G275" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="H275" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I275" s="3">
+        <v>34</v>
+      </c>
+      <c r="J275" s="5"/>
+      <c r="K275" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A276" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="B276" s="4">
+        <v>4615579</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D276" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E276" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F276" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G276" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="H276" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I276" s="3">
+        <v>34</v>
+      </c>
+      <c r="J276" s="5"/>
+      <c r="K276" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A277" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="B277" s="4">
+        <v>4615841</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="D277" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E277" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F277" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G277" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="H277" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I277" s="3">
+        <v>120</v>
+      </c>
+      <c r="J277" s="5"/>
+      <c r="K277" s="5"/>
+    </row>
+    <row r="278" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A278" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B278" s="4">
+        <v>4615841</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="D278" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E278" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F278" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G278" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="H278" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I278" s="3">
+        <v>120</v>
+      </c>
+      <c r="J278" s="5"/>
+      <c r="K278" s="5"/>
+    </row>
+    <row r="279" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A279" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B279" s="4">
+        <v>4615840</v>
+      </c>
+      <c r="C279" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="D279" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E279" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F279" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G279" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="H279" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I279" s="3">
+        <v>121</v>
+      </c>
+      <c r="J279" s="5"/>
+      <c r="K279" s="5"/>
+    </row>
+    <row r="280" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A280" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B280" s="4">
+        <v>4612186</v>
+      </c>
+      <c r="C280" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D280" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E280" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F280" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G280" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="H280" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I280" s="3">
+        <v>61</v>
+      </c>
+      <c r="J280" s="5"/>
+      <c r="K280" s="5"/>
     </row>
     <row r="281" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="2"/>
@@ -18666,7 +19657,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35EBF10C-E87B-485F-A937-7F9515EE4DA9}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -18702,6 +19693,17 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="B4" s="4">
+        <v>44</v>
+      </c>
+      <c r="C4" s="4">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_PAKH\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A7F50A-041C-49AF-8423-22E49CF41B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822327FE-E49D-4F0D-9AF9-149439502F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{15FDD92A-6CAD-44EB-866F-DB764FC19082}"/>
+    <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{15FDD92A-6CAD-44EB-866F-DB764FC19082}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1996" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="586">
   <si>
     <t>Thời gian update</t>
   </si>
@@ -1752,6 +1752,183 @@
     <t>Đã gửi email xác nhận chính sách bảo hành với hãng
 Hãng đang yêu cầu ảnh chụp nhưng nhà KH cách xa khoảng 60km, hiện tại chỉ có video quay lại, đã gửi để hãng kiểm tra.
 Nhân sự phụ trách đang đi ra ngoài, chưa kiểm tra được mail phản hồi của hãng</t>
+  </si>
+  <si>
+    <t>26/08/2026 08:25</t>
+  </si>
+  <si>
+    <t>Đã gửi email xác nhận chính sách bảo hành với hãng
+Hãng đang yêu cầu ảnh chụp nhưng nhà KH cách xa khoảng 60km, hiện tại chỉ có video quay lại, đã gửi để hãng kiểm tra.
+Hãng chưa phản hồi</t>
+  </si>
+  <si>
+    <t>26/08/2026 09:02</t>
+  </si>
+  <si>
+    <t>Lỗi thiết bị đang phối hợp với hãng để xử lý: Inverter Deye, hỏng DC
+Hãng báo tháo inverter gửi về bảo hành, nhanh nhất trong 1 ngày sẽ gửi lại</t>
+  </si>
+  <si>
+    <t>26/08/2026 09:09</t>
+  </si>
+  <si>
+    <t>Đã gửi email xác nhận chính sách bảo hành với hãng
+Pin JA620 bị nứt
+Hãng đang yêu cầu ảnh chụp nhưng nhà KH cách xa khoảng 60km, hiện tại chỉ có video quay lại, đã gửi để hãng kiểm tra.
+Hãng chưa phản hồi</t>
+  </si>
+  <si>
+    <t>26/08/2026 09:24</t>
+  </si>
+  <si>
+    <t>Thời gian hệ dùng 3 năm rồi trường hợp cháy không xác định nguyên nhân.
+Tủ điện kỹ thuật tự mua ngoài để lắp.
+Khi cháy tủ điện khách không chịu chi phí sửa chữa. 
+Hỗ trợ chi nhánh làm tờ trình xin kinh phí bảo hành.
+Dự kiến tủ điện về vào ngày 27/8. Ngày 26/8 đã chuẩn bị để chuyển đi</t>
+  </si>
+  <si>
+    <t>26/08/2026 09:27</t>
+  </si>
+  <si>
+    <t>Thời gian hệ dùng 3 năm rồi trường hợp cháy không xác định nguyên nhân.
+Tủ điện kỹ thuật tự mua ngoài để lắp.
+Khi cháy tủ điện khách không chịu chi phí sửa chữa. 
+Hỗ trợ chi nhánh làm tờ trình xin kinh phí bảo hành.
+Dự kiến tủ điện về vào ngày 27/8. Ngày 26/8 anh Tâm TPGP DLK đã liên hệ và phản hồi hãng đã chuẩn bị hàng để chuyển đi</t>
+  </si>
+  <si>
+    <t>26/08/2026 09:28</t>
+  </si>
+  <si>
+    <t>Lỗi thiết bị đang phối hợp với hãng để xử lý: Inverter Deye, hỏng DC
+Hãng báo tháo inverter gửi về bảo hành, nhanh nhất trong 1 ngày sẽ gửi lại
+Đầu mối xử lý với hãng: Đặng Hải Quan và Trần Quốc Du</t>
+  </si>
+  <si>
+    <t>26/08/2026 09:29</t>
+  </si>
+  <si>
+    <t>26/08/2026 09:42</t>
+  </si>
+  <si>
+    <t>KT đang xin user để vào check hệ thống
+Bị lỗi app, đã xử lý xong</t>
+  </si>
+  <si>
+    <t>26/08/2026 09:53</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Anh</t>
+  </si>
+  <si>
+    <t>Do mất kết nối Wifi</t>
+  </si>
+  <si>
+    <t>26/08/2026 09:57</t>
+  </si>
+  <si>
+    <t>26/08/2026 09:58</t>
+  </si>
+  <si>
+    <t>Vũ Cao Đạt</t>
+  </si>
+  <si>
+    <t>- Đã tư vấn cho KH</t>
+  </si>
+  <si>
+    <t>26/08/2026 10:08</t>
+  </si>
+  <si>
+    <t>- Đã qua kiểm tra cho khách: acquy vẫn nạp xả, đang phối hợp hãng theo dõi thêm, do đấu nối củ của 2 acquy k dùng cầu nối nên khả năng trở kháng chênh lệch, đồng thời phát sinh hỏng 1 CB DC đang yêu cầu KD cấp bổ sung thay cho KH =&gt; Dự kiến 28/8 xong
+- Đã giao GĐKT Thanh liên hệ và qua kiểm tra cho KH</t>
+  </si>
+  <si>
+    <t>26/08/2026 10:17</t>
+  </si>
+  <si>
+    <t>Lê Thị Dung</t>
+  </si>
+  <si>
+    <t>- Ngày 27/8 qua kiểm tra cho khách</t>
+  </si>
+  <si>
+    <t>26/08/2026 10:29</t>
+  </si>
+  <si>
+    <t>Công Thắng Lê</t>
+  </si>
+  <si>
+    <t>Đơn hỗ trợ, xử lý báo giá cho KH</t>
+  </si>
+  <si>
+    <t>26/08/2026 10:30</t>
+  </si>
+  <si>
+    <t>Lê Văn Học</t>
+  </si>
+  <si>
+    <t>Lỗi đường truyền, đã xử lý</t>
+  </si>
+  <si>
+    <t>26/08/2026 10:42</t>
+  </si>
+  <si>
+    <t>Không liên hệ được với KH để xử lý</t>
+  </si>
+  <si>
+    <t>26/08/2026 10:46</t>
+  </si>
+  <si>
+    <t>26/08/2026 10:53</t>
+  </si>
+  <si>
+    <t>Bảo hành xong và lắp lại cho khách
+Bảo hành IVT và đã tạo bảo hành, dự kiến 29/8 xong
+Tạo mới YCBH YCBH_DTP_1786585633759 từ B2C lúc 08:47 13/08/2026 Hạn hoàn thành 23:59 28/08/2026</t>
+  </si>
+  <si>
+    <t>26/08/2026 10:59</t>
+  </si>
+  <si>
+    <t>Lê Văn Mong</t>
+  </si>
+  <si>
+    <t>- GĐKD Hào đang làm việc với KH, KH muốn nâng cấp tấm thêm tấm pin nhưng k muốn trả tiền.</t>
+  </si>
+  <si>
+    <t>Hanh Test TT Cntt</t>
+  </si>
+  <si>
+    <t>TK test</t>
+  </si>
+  <si>
+    <t>26/08/2026 11:01</t>
+  </si>
+  <si>
+    <t>Do trời mưa nên chưa lắp đặt được. Hẹn KH trời hết mưa rồi qua xử lý
+KT đang đặt vật tư phụ. Dự kiến nagfy 28/8 triển khai</t>
+  </si>
+  <si>
+    <t>26/08/2026 11:02</t>
+  </si>
+  <si>
+    <t>Đơn hỗ trợ, xử lý báo giá cho KH, Ngày 26/8 thợ đang qua xử lý</t>
+  </si>
+  <si>
+    <t>26/08/2026 11:07</t>
+  </si>
+  <si>
+    <t>- Đã thay CB cho khách xong và đóng Ticket
+- Đã qua kiểm tra cho khách: acquy vẫn nạp xả, đang phối hợp hãng theo dõi thêm, do đấu nối củ của 2 acquy k dùng cầu nối nên khả năng trở kháng chênh lệch, đồng thời phát sinh hỏng 1 CB DC đang yêu cầu KD cấp bổ sung thay cho KH =&gt; Dự kiến 28/8 xong
+- Đã giao GĐKT Thanh liên hệ và qua kiểm tra cho KH</t>
+  </si>
+  <si>
+    <t>26/08/2026 11:09</t>
+  </si>
+  <si>
+    <t>- Đã qua kiểm tra cho khách, hiện đang mất 1 lai =&gt; Gia hạn
+- Đã giao đ/c Toản FT3 liên hệ KH, sáng mai qua nhà khách kiểm tra xử lý</t>
   </si>
 </sst>
 </file>
@@ -10925,317 +11102,763 @@
       <c r="J280" s="5"/>
       <c r="K280" s="5"/>
     </row>
-    <row r="281" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A281" s="2"/>
-      <c r="B281" s="2"/>
-      <c r="C281" s="2"/>
-      <c r="D281" s="2"/>
-      <c r="E281" s="2"/>
-      <c r="F281" s="2"/>
-      <c r="G281" s="2"/>
-      <c r="H281" s="2"/>
-      <c r="I281" s="2"/>
-      <c r="J281" s="2"/>
-      <c r="K281" s="2"/>
-    </row>
-    <row r="282" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A282" s="2"/>
-      <c r="B282" s="2"/>
-      <c r="C282" s="2"/>
-      <c r="D282" s="2"/>
-      <c r="E282" s="2"/>
-      <c r="F282" s="2"/>
-      <c r="G282" s="2"/>
-      <c r="H282" s="2"/>
-      <c r="I282" s="2"/>
-      <c r="J282" s="2"/>
-      <c r="K282" s="2"/>
-    </row>
-    <row r="283" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A283" s="2"/>
-      <c r="B283" s="2"/>
-      <c r="C283" s="2"/>
-      <c r="D283" s="2"/>
-      <c r="E283" s="2"/>
-      <c r="F283" s="2"/>
-      <c r="G283" s="2"/>
-      <c r="H283" s="2"/>
-      <c r="I283" s="2"/>
-      <c r="J283" s="2"/>
-      <c r="K283" s="2"/>
-    </row>
-    <row r="284" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="2"/>
-      <c r="B284" s="2"/>
-      <c r="C284" s="2"/>
-      <c r="D284" s="2"/>
-      <c r="E284" s="2"/>
-      <c r="F284" s="2"/>
-      <c r="G284" s="2"/>
-      <c r="H284" s="2"/>
-      <c r="I284" s="2"/>
-      <c r="J284" s="2"/>
-      <c r="K284" s="2"/>
-    </row>
-    <row r="285" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A285" s="2"/>
-      <c r="B285" s="2"/>
-      <c r="C285" s="2"/>
-      <c r="D285" s="2"/>
-      <c r="E285" s="2"/>
-      <c r="F285" s="2"/>
-      <c r="G285" s="2"/>
-      <c r="H285" s="2"/>
-      <c r="I285" s="2"/>
-      <c r="J285" s="2"/>
-      <c r="K285" s="2"/>
-    </row>
-    <row r="286" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A286" s="2"/>
-      <c r="B286" s="2"/>
-      <c r="C286" s="2"/>
-      <c r="D286" s="2"/>
-      <c r="E286" s="2"/>
-      <c r="F286" s="2"/>
-      <c r="G286" s="2"/>
-      <c r="H286" s="2"/>
-      <c r="I286" s="2"/>
-      <c r="J286" s="2"/>
-      <c r="K286" s="2"/>
-    </row>
-    <row r="287" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A287" s="2"/>
-      <c r="B287" s="2"/>
-      <c r="C287" s="2"/>
-      <c r="D287" s="2"/>
-      <c r="E287" s="2"/>
-      <c r="F287" s="2"/>
-      <c r="G287" s="2"/>
-      <c r="H287" s="2"/>
-      <c r="I287" s="2"/>
-      <c r="J287" s="2"/>
-      <c r="K287" s="2"/>
-    </row>
-    <row r="288" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A288" s="2"/>
-      <c r="B288" s="2"/>
-      <c r="C288" s="2"/>
-      <c r="D288" s="2"/>
-      <c r="E288" s="2"/>
-      <c r="F288" s="2"/>
-      <c r="G288" s="2"/>
-      <c r="H288" s="2"/>
-      <c r="I288" s="2"/>
-      <c r="J288" s="2"/>
-      <c r="K288" s="2"/>
+    <row r="281" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A281" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B281" s="4">
+        <v>4612186</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D281" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E281" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F281" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G281" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="H281" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I281" s="3">
+        <v>61</v>
+      </c>
+      <c r="J281" s="5"/>
+      <c r="K281" s="5"/>
+    </row>
+    <row r="282" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A282" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="B282" s="4">
+        <v>4615758</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D282" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E282" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F282" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G282" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="H282" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I282" s="3">
+        <v>69</v>
+      </c>
+      <c r="J282" s="5"/>
+      <c r="K282" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="283" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A283" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="B283" s="4">
+        <v>4612186</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="D283" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E283" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F283" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G283" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="H283" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I283" s="3">
+        <v>61</v>
+      </c>
+      <c r="J283" s="5"/>
+      <c r="K283" s="5"/>
+    </row>
+    <row r="284" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A284" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B284" s="4">
+        <v>4615579</v>
+      </c>
+      <c r="C284" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D284" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E284" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F284" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G284" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="H284" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I284" s="3">
+        <v>34</v>
+      </c>
+      <c r="J284" s="5"/>
+      <c r="K284" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="285" spans="1:11" ht="103.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A285" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B285" s="4">
+        <v>4615579</v>
+      </c>
+      <c r="C285" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D285" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E285" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F285" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G285" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="H285" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I285" s="3">
+        <v>34</v>
+      </c>
+      <c r="J285" s="5"/>
+      <c r="K285" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A286" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="B286" s="4">
+        <v>4615758</v>
+      </c>
+      <c r="C286" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D286" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E286" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F286" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G286" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="H286" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I286" s="3">
+        <v>69</v>
+      </c>
+      <c r="J286" s="5"/>
+      <c r="K286" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="287" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A287" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B287" s="4">
+        <v>4615758</v>
+      </c>
+      <c r="C287" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="D287" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="E287" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F287" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G287" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="H287" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I287" s="3">
+        <v>69</v>
+      </c>
+      <c r="J287" s="5"/>
+      <c r="K287" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A288" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="B288" s="4">
+        <v>4615728</v>
+      </c>
+      <c r="C288" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="D288" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E288" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F288" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G288" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="H288" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I288" s="3">
+        <v>82</v>
+      </c>
+      <c r="J288" s="5"/>
+      <c r="K288" s="5"/>
     </row>
     <row r="289" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A289" s="2"/>
-      <c r="B289" s="2"/>
-      <c r="C289" s="2"/>
-      <c r="D289" s="2"/>
-      <c r="E289" s="2"/>
-      <c r="F289" s="2"/>
-      <c r="G289" s="2"/>
-      <c r="H289" s="2"/>
-      <c r="I289" s="2"/>
-      <c r="J289" s="2"/>
-      <c r="K289" s="2"/>
-    </row>
-    <row r="290" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A290" s="2"/>
-      <c r="B290" s="2"/>
-      <c r="C290" s="2"/>
-      <c r="D290" s="2"/>
-      <c r="E290" s="2"/>
-      <c r="F290" s="2"/>
-      <c r="G290" s="2"/>
-      <c r="H290" s="2"/>
-      <c r="I290" s="2"/>
-      <c r="J290" s="2"/>
-      <c r="K290" s="2"/>
+      <c r="A289" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B289" s="4">
+        <v>4615825</v>
+      </c>
+      <c r="C289" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="D289" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E289" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F289" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G289" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="H289" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I289" s="3">
+        <v>126</v>
+      </c>
+      <c r="J289" s="5"/>
+      <c r="K289" s="5"/>
+    </row>
+    <row r="290" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A290" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="B290" s="4">
+        <v>4615824</v>
+      </c>
+      <c r="C290" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="D290" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E290" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F290" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G290" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="H290" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I290" s="3">
+        <v>122</v>
+      </c>
+      <c r="J290" s="5"/>
+      <c r="K290" s="5"/>
     </row>
     <row r="291" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A291" s="2"/>
-      <c r="B291" s="2"/>
-      <c r="C291" s="2"/>
-      <c r="D291" s="2"/>
-      <c r="E291" s="2"/>
-      <c r="F291" s="2"/>
-      <c r="G291" s="2"/>
-      <c r="H291" s="2"/>
-      <c r="I291" s="2"/>
-      <c r="J291" s="2"/>
-      <c r="K291" s="2"/>
-    </row>
-    <row r="292" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A292" s="2"/>
-      <c r="B292" s="2"/>
-      <c r="C292" s="2"/>
-      <c r="D292" s="2"/>
-      <c r="E292" s="2"/>
-      <c r="F292" s="2"/>
-      <c r="G292" s="2"/>
-      <c r="H292" s="2"/>
-      <c r="I292" s="2"/>
-      <c r="J292" s="2"/>
-      <c r="K292" s="2"/>
+      <c r="A291" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B291" s="4">
+        <v>4615827</v>
+      </c>
+      <c r="C291" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="D291" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E291" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F291" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G291" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="H291" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I291" s="3">
+        <v>130</v>
+      </c>
+      <c r="J291" s="5"/>
+      <c r="K291" s="5"/>
+    </row>
+    <row r="292" spans="1:11" ht="78" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A292" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="B292" s="4">
+        <v>4615838</v>
+      </c>
+      <c r="C292" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="D292" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E292" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F292" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G292" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="H292" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I292" s="3">
+        <v>118</v>
+      </c>
+      <c r="J292" s="5"/>
+      <c r="K292" s="5"/>
     </row>
     <row r="293" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A293" s="2"/>
-      <c r="B293" s="2"/>
-      <c r="C293" s="2"/>
-      <c r="D293" s="2"/>
-      <c r="E293" s="2"/>
-      <c r="F293" s="2"/>
-      <c r="G293" s="2"/>
-      <c r="H293" s="2"/>
-      <c r="I293" s="2"/>
-      <c r="J293" s="2"/>
-      <c r="K293" s="2"/>
+      <c r="A293" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B293" s="4">
+        <v>4615826</v>
+      </c>
+      <c r="C293" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="D293" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E293" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F293" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G293" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="H293" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I293" s="3">
+        <v>131</v>
+      </c>
+      <c r="J293" s="5"/>
+      <c r="K293" s="5"/>
     </row>
     <row r="294" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A294" s="2"/>
-      <c r="B294" s="2"/>
-      <c r="C294" s="2"/>
-      <c r="D294" s="2"/>
-      <c r="E294" s="2"/>
-      <c r="F294" s="2"/>
-      <c r="G294" s="2"/>
-      <c r="H294" s="2"/>
-      <c r="I294" s="2"/>
-      <c r="J294" s="2"/>
-      <c r="K294" s="2"/>
+      <c r="A294" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B294" s="4">
+        <v>4615828</v>
+      </c>
+      <c r="C294" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="D294" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E294" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F294" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G294" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="H294" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I294" s="3">
+        <v>129</v>
+      </c>
+      <c r="J294" s="5"/>
+      <c r="K294" s="5"/>
     </row>
     <row r="295" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A295" s="2"/>
-      <c r="B295" s="2"/>
-      <c r="C295" s="2"/>
-      <c r="D295" s="2"/>
-      <c r="E295" s="2"/>
-      <c r="F295" s="2"/>
-      <c r="G295" s="2"/>
-      <c r="H295" s="2"/>
-      <c r="I295" s="2"/>
-      <c r="J295" s="2"/>
-      <c r="K295" s="2"/>
+      <c r="A295" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="B295" s="4">
+        <v>4615846</v>
+      </c>
+      <c r="C295" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D295" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E295" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F295" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G295" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="H295" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I295" s="3">
+        <v>134</v>
+      </c>
+      <c r="J295" s="5"/>
+      <c r="K295" s="5"/>
     </row>
     <row r="296" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A296" s="2"/>
-      <c r="B296" s="2"/>
-      <c r="C296" s="2"/>
-      <c r="D296" s="2"/>
-      <c r="E296" s="2"/>
-      <c r="F296" s="2"/>
-      <c r="G296" s="2"/>
-      <c r="H296" s="2"/>
-      <c r="I296" s="2"/>
-      <c r="J296" s="2"/>
-      <c r="K296" s="2"/>
-    </row>
-    <row r="297" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A297" s="2"/>
-      <c r="B297" s="2"/>
-      <c r="C297" s="2"/>
-      <c r="D297" s="2"/>
-      <c r="E297" s="2"/>
-      <c r="F297" s="2"/>
-      <c r="G297" s="2"/>
-      <c r="H297" s="2"/>
-      <c r="I297" s="2"/>
-      <c r="J297" s="2"/>
-      <c r="K297" s="2"/>
-    </row>
-    <row r="298" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A298" s="2"/>
-      <c r="B298" s="2"/>
-      <c r="C298" s="2"/>
-      <c r="D298" s="2"/>
-      <c r="E298" s="2"/>
-      <c r="F298" s="2"/>
-      <c r="G298" s="2"/>
-      <c r="H298" s="2"/>
-      <c r="I298" s="2"/>
-      <c r="J298" s="2"/>
-      <c r="K298" s="2"/>
-    </row>
-    <row r="299" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A299" s="2"/>
-      <c r="B299" s="2"/>
-      <c r="C299" s="2"/>
-      <c r="D299" s="2"/>
-      <c r="E299" s="2"/>
-      <c r="F299" s="2"/>
-      <c r="G299" s="2"/>
-      <c r="H299" s="2"/>
-      <c r="I299" s="2"/>
-      <c r="J299" s="2"/>
-      <c r="K299" s="2"/>
+      <c r="A296" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="B296" s="4">
+        <v>4615836</v>
+      </c>
+      <c r="C296" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="D296" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E296" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F296" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G296" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="H296" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I296" s="3">
+        <v>104</v>
+      </c>
+      <c r="J296" s="5"/>
+      <c r="K296" s="5"/>
+    </row>
+    <row r="297" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A297" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="B297" s="4">
+        <v>4615536</v>
+      </c>
+      <c r="C297" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D297" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E297" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F297" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G297" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="H297" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I297" s="3">
+        <v>36</v>
+      </c>
+      <c r="J297" s="5"/>
+      <c r="K297" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="298" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A298" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="B298" s="4">
+        <v>4615476</v>
+      </c>
+      <c r="C298" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D298" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E298" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F298" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G298" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="H298" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I298" s="3">
+        <v>41</v>
+      </c>
+      <c r="J298" s="5"/>
+      <c r="K298" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A299" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="B299" s="4">
+        <v>4615842</v>
+      </c>
+      <c r="C299" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="D299" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E299" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F299" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G299" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="H299" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I299" s="3">
+        <v>125</v>
+      </c>
+      <c r="J299" s="5"/>
+      <c r="K299" s="5"/>
     </row>
     <row r="300" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A300" s="2"/>
-      <c r="B300" s="2"/>
-      <c r="C300" s="2"/>
-      <c r="D300" s="2"/>
-      <c r="E300" s="2"/>
-      <c r="F300" s="2"/>
-      <c r="G300" s="2"/>
-      <c r="H300" s="2"/>
-      <c r="I300" s="2"/>
-      <c r="J300" s="2"/>
-      <c r="K300" s="2"/>
-    </row>
-    <row r="301" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A301" s="2"/>
-      <c r="B301" s="2"/>
-      <c r="C301" s="2"/>
-      <c r="D301" s="2"/>
-      <c r="E301" s="2"/>
-      <c r="F301" s="2"/>
-      <c r="G301" s="2"/>
-      <c r="H301" s="2"/>
-      <c r="I301" s="2"/>
-      <c r="J301" s="2"/>
-      <c r="K301" s="2"/>
-    </row>
-    <row r="302" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A302" s="2"/>
-      <c r="B302" s="2"/>
-      <c r="C302" s="2"/>
-      <c r="D302" s="2"/>
-      <c r="E302" s="2"/>
-      <c r="F302" s="2"/>
-      <c r="G302" s="2"/>
-      <c r="H302" s="2"/>
-      <c r="I302" s="2"/>
-      <c r="J302" s="2"/>
-      <c r="K302" s="2"/>
-    </row>
-    <row r="303" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A303" s="2"/>
-      <c r="B303" s="2"/>
-      <c r="C303" s="2"/>
-      <c r="D303" s="2"/>
-      <c r="E303" s="2"/>
-      <c r="F303" s="2"/>
-      <c r="G303" s="2"/>
-      <c r="H303" s="2"/>
-      <c r="I303" s="2"/>
-      <c r="J303" s="2"/>
-      <c r="K303" s="2"/>
-    </row>
-    <row r="304" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A304" s="2"/>
-      <c r="B304" s="2"/>
-      <c r="C304" s="2"/>
-      <c r="D304" s="2"/>
-      <c r="E304" s="2"/>
-      <c r="F304" s="2"/>
-      <c r="G304" s="2"/>
-      <c r="H304" s="2"/>
-      <c r="I304" s="2"/>
-      <c r="J304" s="2"/>
-      <c r="K304" s="2"/>
+      <c r="A300" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="B300" s="4">
+        <v>4615844</v>
+      </c>
+      <c r="C300" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="D300" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E300" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F300" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G300" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="H300" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I300" s="3">
+        <v>128</v>
+      </c>
+      <c r="J300" s="5"/>
+      <c r="K300" s="5"/>
+    </row>
+    <row r="301" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A301" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="B301" s="4">
+        <v>4615840</v>
+      </c>
+      <c r="C301" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="D301" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E301" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F301" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G301" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="H301" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I301" s="3">
+        <v>121</v>
+      </c>
+      <c r="J301" s="5"/>
+      <c r="K301" s="5"/>
+    </row>
+    <row r="302" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A302" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="B302" s="4">
+        <v>4615828</v>
+      </c>
+      <c r="C302" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="D302" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="E302" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F302" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G302" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="H302" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I302" s="3">
+        <v>129</v>
+      </c>
+      <c r="J302" s="5"/>
+      <c r="K302" s="5"/>
+    </row>
+    <row r="303" spans="1:11" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A303" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="B303" s="4">
+        <v>4615838</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="D303" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E303" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F303" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G303" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="H303" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I303" s="3">
+        <v>118</v>
+      </c>
+      <c r="J303" s="5"/>
+      <c r="K303" s="5"/>
+    </row>
+    <row r="304" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A304" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="B304" s="4">
+        <v>4615839</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="D304" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E304" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F304" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G304" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="H304" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I304" s="3">
+        <v>117</v>
+      </c>
+      <c r="J304" s="5"/>
+      <c r="K304" s="5"/>
     </row>
     <row r="305" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="2"/>
@@ -19698,7 +20321,7 @@
         <v>370</v>
       </c>
       <c r="B4" s="4">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C4" s="4">
         <v>4</v>

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nhungnt27\Desktop\3. Hàng hóa P.TK\Code_Dashboard_PAKH\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822327FE-E49D-4F0D-9AF9-149439502F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DA4BA9-1A02-4FD1-94A5-F4A727C63601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-60" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{15FDD92A-6CAD-44EB-866F-DB764FC19082}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="609">
   <si>
     <t>Thời gian update</t>
   </si>
@@ -1929,6 +1929,79 @@
   <si>
     <t>- Đã qua kiểm tra cho khách, hiện đang mất 1 lai =&gt; Gia hạn
 - Đã giao đ/c Toản FT3 liên hệ KH, sáng mai qua nhà khách kiểm tra xử lý</t>
+  </si>
+  <si>
+    <t>26/08/2026 11:39</t>
+  </si>
+  <si>
+    <t>Nguyen Trong Thuan</t>
+  </si>
+  <si>
+    <t>OFT đa liên hệ KH và đóng Ticket</t>
+  </si>
+  <si>
+    <t>26/08/2026 11:45</t>
+  </si>
+  <si>
+    <t>Mrs Thảo</t>
+  </si>
+  <si>
+    <t>- FT3 đang triển khai cho khách, dự kiến đóng ticket trước 8h ngày 27/8</t>
+  </si>
+  <si>
+    <t>26/08/2026 12:13</t>
+  </si>
+  <si>
+    <t>- Đã qua kiểm tra cho khách, hiện đang mất 1 lai =&gt; Đã đề xuất gia hạn đến 17h30 ngày 27/8
+- Đã giao đ/c Toản FT3 liên hệ KH, sáng mai qua nhà khách kiểm tra xử lý</t>
+  </si>
+  <si>
+    <t>26/08/2026 13:30</t>
+  </si>
+  <si>
+    <t>26/08/2026 13:32</t>
+  </si>
+  <si>
+    <t>- Đã làm biên bản với khách hàng và đóng Ticket
+- GĐKD Hào đang làm việc với KH, KH muốn nâng cấp tấm thêm tấm pin nhưng k muốn trả tiền.</t>
+  </si>
+  <si>
+    <t>26/08/2026 13:46</t>
+  </si>
+  <si>
+    <t>Vũ Duy Thành</t>
+  </si>
+  <si>
+    <t>Lỗi dây tín hiệu. KT hẹn ngày 27/8 qua xử lý</t>
+  </si>
+  <si>
+    <t>26/08/2026 13:57</t>
+  </si>
+  <si>
+    <t>- Đã xử lý xong cho khách và đóng Ticket
+- Đã qua kiểm tra cho khách, hiện đang mất 1 lai =&gt; Đã đề xuất gia hạn đến 17h30 ngày 27/8
+- Đã giao đ/c Toản FT3 liên hệ KH, sáng mai qua nhà khách kiểm tra xử lý</t>
+  </si>
+  <si>
+    <t>26/08/2026 14:02</t>
+  </si>
+  <si>
+    <t>Lâm Văn Nhẫn</t>
+  </si>
+  <si>
+    <t>GLI</t>
+  </si>
+  <si>
+    <t>Đã nhận được thông tin và sắp xếp nhân sự thực hiện</t>
+  </si>
+  <si>
+    <t>26/08/2026 14:18</t>
+  </si>
+  <si>
+    <t>Trịnh Văn Bình</t>
+  </si>
+  <si>
+    <t>Thay tủ điện mới cho KH</t>
   </si>
 </sst>
 </file>
@@ -3482,7 +3555,7 @@
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
     </row>
-    <row r="37" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>125</v>
       </c>
@@ -11861,121 +11934,283 @@
       <c r="K304" s="5"/>
     </row>
     <row r="305" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A305" s="2"/>
-      <c r="B305" s="2"/>
-      <c r="C305" s="2"/>
-      <c r="D305" s="2"/>
-      <c r="E305" s="2"/>
-      <c r="F305" s="2"/>
-      <c r="G305" s="2"/>
-      <c r="H305" s="2"/>
-      <c r="I305" s="2"/>
-      <c r="J305" s="2"/>
-      <c r="K305" s="2"/>
-    </row>
-    <row r="306" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A306" s="2"/>
-      <c r="B306" s="2"/>
-      <c r="C306" s="2"/>
-      <c r="D306" s="2"/>
-      <c r="E306" s="2"/>
-      <c r="F306" s="2"/>
-      <c r="G306" s="2"/>
-      <c r="H306" s="2"/>
-      <c r="I306" s="2"/>
-      <c r="J306" s="2"/>
-      <c r="K306" s="2"/>
-    </row>
-    <row r="307" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A307" s="2"/>
-      <c r="B307" s="2"/>
-      <c r="C307" s="2"/>
-      <c r="D307" s="2"/>
-      <c r="E307" s="2"/>
-      <c r="F307" s="2"/>
-      <c r="G307" s="2"/>
-      <c r="H307" s="2"/>
-      <c r="I307" s="2"/>
-      <c r="J307" s="2"/>
-      <c r="K307" s="2"/>
-    </row>
-    <row r="308" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A308" s="2"/>
-      <c r="B308" s="2"/>
-      <c r="C308" s="2"/>
-      <c r="D308" s="2"/>
-      <c r="E308" s="2"/>
-      <c r="F308" s="2"/>
-      <c r="G308" s="2"/>
-      <c r="H308" s="2"/>
-      <c r="I308" s="2"/>
-      <c r="J308" s="2"/>
-      <c r="K308" s="2"/>
-    </row>
-    <row r="309" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A309" s="2"/>
-      <c r="B309" s="2"/>
-      <c r="C309" s="2"/>
-      <c r="D309" s="2"/>
-      <c r="E309" s="2"/>
-      <c r="F309" s="2"/>
-      <c r="G309" s="2"/>
-      <c r="H309" s="2"/>
-      <c r="I309" s="2"/>
-      <c r="J309" s="2"/>
-      <c r="K309" s="2"/>
+      <c r="A305" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B305" s="4">
+        <v>4615851</v>
+      </c>
+      <c r="C305" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="D305" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E305" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F305" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G305" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="H305" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I305" s="3">
+        <v>132</v>
+      </c>
+      <c r="J305" s="5"/>
+      <c r="K305" s="5"/>
+    </row>
+    <row r="306" spans="1:11" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A306" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B306" s="4">
+        <v>4615850</v>
+      </c>
+      <c r="C306" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="D306" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="E306" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F306" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G306" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="H306" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I306" s="3">
+        <v>133</v>
+      </c>
+      <c r="J306" s="5"/>
+      <c r="K306" s="5"/>
+    </row>
+    <row r="307" spans="1:11" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A307" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="B307" s="4">
+        <v>4615839</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="D307" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E307" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F307" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G307" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="H307" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I307" s="3">
+        <v>117</v>
+      </c>
+      <c r="J307" s="5"/>
+      <c r="K307" s="5"/>
+    </row>
+    <row r="308" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A308" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="B308" s="4">
+        <v>4615823</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="D308" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E308" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F308" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G308" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="H308" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I308" s="3">
+        <v>123</v>
+      </c>
+      <c r="J308" s="5"/>
+      <c r="K308" s="5"/>
+    </row>
+    <row r="309" spans="1:11" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A309" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="B309" s="4">
+        <v>4615842</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="D309" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E309" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F309" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G309" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="H309" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I309" s="3">
+        <v>125</v>
+      </c>
+      <c r="J309" s="5"/>
+      <c r="K309" s="5"/>
     </row>
     <row r="310" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A310" s="2"/>
-      <c r="B310" s="2"/>
-      <c r="C310" s="2"/>
-      <c r="D310" s="2"/>
-      <c r="E310" s="2"/>
-      <c r="F310" s="2"/>
-      <c r="G310" s="2"/>
-      <c r="H310" s="2"/>
-      <c r="I310" s="2"/>
-      <c r="J310" s="2"/>
-      <c r="K310" s="2"/>
-    </row>
-    <row r="311" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A311" s="2"/>
-      <c r="B311" s="2"/>
-      <c r="C311" s="2"/>
-      <c r="D311" s="2"/>
-      <c r="E311" s="2"/>
-      <c r="F311" s="2"/>
-      <c r="G311" s="2"/>
-      <c r="H311" s="2"/>
-      <c r="I311" s="2"/>
-      <c r="J311" s="2"/>
-      <c r="K311" s="2"/>
+      <c r="A310" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="B310" s="4">
+        <v>4615845</v>
+      </c>
+      <c r="C310" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="D310" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E310" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F310" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G310" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="H310" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I310" s="3">
+        <v>135</v>
+      </c>
+      <c r="J310" s="5"/>
+      <c r="K310" s="5"/>
+    </row>
+    <row r="311" spans="1:11" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A311" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="B311" s="4">
+        <v>4615839</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="D311" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E311" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F311" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G311" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="H311" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I311" s="3">
+        <v>117</v>
+      </c>
+      <c r="J311" s="5"/>
+      <c r="K311" s="5"/>
     </row>
     <row r="312" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A312" s="2"/>
-      <c r="B312" s="2"/>
-      <c r="C312" s="2"/>
-      <c r="D312" s="2"/>
-      <c r="E312" s="2"/>
-      <c r="F312" s="2"/>
-      <c r="G312" s="2"/>
-      <c r="H312" s="2"/>
-      <c r="I312" s="2"/>
-      <c r="J312" s="2"/>
-      <c r="K312" s="2"/>
+      <c r="A312" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B312" s="4">
+        <v>4615856</v>
+      </c>
+      <c r="C312" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="D312" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="E312" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F312" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G312" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="H312" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I312" s="3">
+        <v>143</v>
+      </c>
+      <c r="J312" s="5"/>
+      <c r="K312" s="5"/>
     </row>
     <row r="313" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A313" s="2"/>
-      <c r="B313" s="2"/>
-      <c r="C313" s="2"/>
-      <c r="D313" s="2"/>
-      <c r="E313" s="2"/>
-      <c r="F313" s="2"/>
-      <c r="G313" s="2"/>
-      <c r="H313" s="2"/>
-      <c r="I313" s="2"/>
-      <c r="J313" s="2"/>
-      <c r="K313" s="2"/>
+      <c r="A313" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="B313" s="4">
+        <v>4615843</v>
+      </c>
+      <c r="C313" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="D313" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E313" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F313" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G313" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="H313" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="I313" s="3">
+        <v>124</v>
+      </c>
+      <c r="J313" s="5"/>
+      <c r="K313" s="5"/>
     </row>
     <row r="314" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="2"/>
@@ -20321,10 +20556,10 @@
         <v>370</v>
       </c>
       <c r="B4" s="4">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C4" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="461">
   <si>
     <t xml:space="preserve">Thời gian update</t>
   </si>
@@ -1535,6 +1535,13 @@
   </si>
   <si>
     <t xml:space="preserve">Hãng Sigenergy báo lại hệ thống giám sát đang được hãng nâng cấp và khôi phục dữ liệu, dự kiến lịch hoàn tất khắc phục sẽ báo cáo lại trong hôm nay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Ngọc Hiếu Nhi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Do nhu cầu sử dụng của KH nhiều hơn, thời tiết HCM đang mùa mưa nên hiệu suất giảm.
+- KH muốn thay đổi làm dàn khung nên khiếu nại lên tổng đài =&gt; GĐ Phụng sẽ làm việc lại với KH phần thay đổi này.</t>
   </si>
   <si>
     <t xml:space="preserve">Ngày</t>
@@ -1599,8 +1606,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K355" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K355"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K356" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K356"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Thời gian update"/>
     <tableColumn id="2" name="ID"/>
@@ -12997,6 +13004,37 @@
       <c r="J355"/>
       <c r="K355" s="1"/>
     </row>
+    <row r="356">
+      <c r="A356" s="1" t="n">
+        <v>46261.3784722222</v>
+      </c>
+      <c r="B356" t="n">
+        <v>4615857</v>
+      </c>
+      <c r="C356" t="s">
+        <v>456</v>
+      </c>
+      <c r="D356" t="s">
+        <v>152</v>
+      </c>
+      <c r="E356" t="s">
+        <v>219</v>
+      </c>
+      <c r="F356" t="s">
+        <v>27</v>
+      </c>
+      <c r="G356" t="s">
+        <v>457</v>
+      </c>
+      <c r="H356" t="s">
+        <v>50</v>
+      </c>
+      <c r="I356" t="n">
+        <v>148</v>
+      </c>
+      <c r="J356"/>
+      <c r="K356" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -13013,13 +13051,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="2">

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="496">
   <si>
     <t xml:space="preserve">Thời gian update</t>
   </si>
@@ -1542,6 +1542,146 @@
   <si>
     <t xml:space="preserve">- Do nhu cầu sử dụng của KH nhiều hơn, thời tiết HCM đang mùa mưa nên hiệu suất giảm.
 - KH muốn thay đổi làm dàn khung nên khiếu nại lên tổng đài =&gt; GĐ Phụng sẽ làm việc lại với KH phần thay đổi này.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Thị Vĩnh Quyên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã tiếp nhận thông tin và tiến hành xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trời mưa nên chưa xử lý được.
+Dự kiến 28/8 mang tiếp địa đến lắp nốt cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Đình Trung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KT đang tính toán vật tư và chi phí để xử lý cho KH
+Dự kiến 30/8 có vật tư để triển khai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Hồng Thái</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- GĐKD Thiện đang trao đổi lại với KH để đóng Ticket 
+- Ban đầu KH không cần xuất hóa đơn, mới báo lại xuất hóa đơn nên CN hỗ trợ nhưng phải chờ có Kh nào trùng thông tin thì mới hỗ trợ xong đc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhà KH mất wifi. Đã xử lý cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhà KH mất wifi dẫn tới mất giám sát. Đã xử lý cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Võ Châu Phi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đ/c Phát đang xử lý cho khách, hỏng CB đang báo ncc bảo hành =&gt; Chờ NCC phản hồi rồi Đề xuất gia hạn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã gửi email xác nhận chính sách bảo hành với hãng
+Pin JA620 bị nứt
+Hãng đã gửi hướng dẫn chụp lại hư hại để xác nhận bảo hành</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thời gian hệ dùng 3 năm rồi trường hợp cháy không xác định nguyên nhân.
+Tủ điện kỹ thuật tự mua ngoài để lắp.
+Khi cháy tủ điện khách không chịu chi phí sửa chữa. 
+Hỗ trợ chi nhánh làm tờ trình xin kinh phí bảo hành.
+Anh Tâm TPGP DLK đang kiểm tra lại tiến độ gửi hàng đi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Thị Quý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Hỏng Cb, đã thay cho khách xong, đóng Ticket trc 16h ngày 27/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Minh Thành</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã YC GĐKT liên hệ KH và qua kiểm tra cho khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Công Ty TNHH Hoa Sen Hoàn Mỹ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhà Kh bị mất điện lưới nên biến tần bị mât điẹn theo đã bật biến tiền hoạt động bt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hệ thống đang dùng bình thường. Ban đầu lắp xong 30kw, giờ hiệu suất chỉ còn 26kw. KH muốn hiệu suất lên lại như ban đầu. CNCT đã cho người đo nhiệt, cân tải nhưng chưa tìm được phương án giải quyết cho KH nên KH không đồng ý cho đóng ticket. Đã tạo nhóm điều hành để trao đổi phương án xử lý.
+Ngày nghiệm thu: 30/07/2025
+ID/Pass: phonggpdvkt@gmail.com / Hanoi@0209#
+Đầu mối đang làm việc: Đặng Hải Quan – Quandh28
+Số điện thoại: 0971725775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hệ thống đang dùng bình thường. Ban đầu lắp xong 30kw, giờ hiệu suất chỉ còn 26kw. KH muốn hiệu suất lên lại như ban đầu. CNCT đã cho người đo nhiệt, cân tải nhưng chưa tìm được phương án giải quyết cho KH nên KH không đồng ý cho đóng ticket. Đã tạo nhóm điều hành để trao đổi phương án xử lý.
+Thông tin KH:
+- Ngày nghiệm thu: 30/07/2025
+- ID/Pass: phonggpdvkt@gmail.com / Hanoi@0209#
+- Đầu mối đang làm việc: Đặng Hải Quan – Quandh28
+- Số điện thoại đầu mối: 0971725775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hệ thống đang dùng bình thường. Ban đầu lắp xong 30kw, giờ hiệu suất chỉ còn 26kw. KH muốn hiệu suất lên lại như ban đầu. CNCT đã cho người đo nhiệt, cân tải nhưng chưa tìm được phương án giải quyết cho KH nên KH không đồng ý cho đóng ticket. Đã tạo nhóm điều hành để trao đổi phương án xử lý.
+Thông tin bổ sung:
+- Ngày nghiệm thu: 30/07/2025
+- ID/Pass: phonggpdvkt@gmail.com / Hanoi@0209#
+- Đầu mối đang làm việc: Đặng Hải Quan – Quandh28
+- Số điện thoại đầu mối: 0971725775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Minh Trường</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biến tần bị lỗi, đã hết hạn bảo hành. Chờ báo giá xử lý cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trần Thị Nghĩa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mất kết nối wifi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Hỏng ATS, không tạo được bảo hành =&gt; Tháo đi bảo hành (Đã đề xuất gia hạn đến 6/9, KH sạc quá tải dẫn đến cháy ATS)
+- Đang ở nhà xử lý cho KH, xử lý Ticket trc 9h
+- GĐKD Hải 27/8 kiểm tra cho khách trước 9h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã xử lý xong và đóng ticket
+- Hỏng Cb, đã thay cho khách xong, đóng Ticket trc 16h ngày 27/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hệ thống đang dùng bình thường. Ban đầu lắp xong 30kw, giờ hiệu suất chỉ còn 26kw. KH muốn hiệu suất lên lại như ban đầu. CNCT đã cho người đo nhiệt, cân tải nhưng chưa tìm được phương án giải quyết cho KH nên KH không đồng ý cho đóng ticket. Đã tạo nhóm điều hành để trao đổi phương án xử lý.
+Thông tin bổ sung:
+- Ngày ký hợp đồng: 29/11/2024 (lần đầu ký hợp đồng trong số 4 lần ký)
+- Ngày nghiệm thu: 29/11/2024
+- Ngày lắp bổ sung tấm pin: 24/05/2025
+- ID/Pass: phonggpdvkt@gmail.com / Hanoi@0209#
+- Đầu mối đang làm việc: Đặng Hải Quan – Quandh28
+- Số điện thoại đầu mối: 0971725775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Thanh Ba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KH nhờ hỗ trợ cài sạc xả acquy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lỗi thiết bị đang phối hợp với hãng để xử lý: Inverter Deye, hỏng DC
+Hãng báo tháo inverter gửi về bảo hành, chưa có thông tin ngày dự kiến gửi lại
+Đầu mối xử lý với hãng: Đặng Hải Quan và Trần Quốc Du</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KH hẹn 28/8 vào xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- FT đã qua kiểm tra, IVT lỗi đã tháo về kho để gửi bảo hành dự kiến 9/9 có hàng (Tạo mới YCBH YCBH_VLG_1787635453789 từ B2C lúc 12:24 25/08/2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lỗi dây tín hiệu.</t>
   </si>
   <si>
     <t xml:space="preserve">Ngày</t>
@@ -1606,8 +1746,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K356" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K356"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K382" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K382"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Thời gian update"/>
     <tableColumn id="2" name="ID"/>
@@ -13035,6 +13175,824 @@
       <c r="J356"/>
       <c r="K356" s="1"/>
     </row>
+    <row r="357">
+      <c r="A357" s="1" t="n">
+        <v>46261.3923611111</v>
+      </c>
+      <c r="B357" t="n">
+        <v>4615865</v>
+      </c>
+      <c r="C357" t="s">
+        <v>458</v>
+      </c>
+      <c r="D357" t="s">
+        <v>12</v>
+      </c>
+      <c r="E357" t="s">
+        <v>195</v>
+      </c>
+      <c r="F357" t="s">
+        <v>23</v>
+      </c>
+      <c r="G357" t="s">
+        <v>459</v>
+      </c>
+      <c r="H357" t="s">
+        <v>195</v>
+      </c>
+      <c r="I357" t="n">
+        <v>164</v>
+      </c>
+      <c r="J357"/>
+      <c r="K357" s="1"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="n">
+        <v>46261.3993055556</v>
+      </c>
+      <c r="B358" t="n">
+        <v>4615837</v>
+      </c>
+      <c r="C358" t="s">
+        <v>310</v>
+      </c>
+      <c r="D358" t="s">
+        <v>65</v>
+      </c>
+      <c r="E358" t="s">
+        <v>251</v>
+      </c>
+      <c r="F358" t="s">
+        <v>23</v>
+      </c>
+      <c r="G358" t="s">
+        <v>460</v>
+      </c>
+      <c r="H358" t="s">
+        <v>13</v>
+      </c>
+      <c r="I358" t="n">
+        <v>113</v>
+      </c>
+      <c r="J358"/>
+      <c r="K358" s="1"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="n">
+        <v>46261.4069444444</v>
+      </c>
+      <c r="B359" t="n">
+        <v>4615876</v>
+      </c>
+      <c r="C359" t="s">
+        <v>461</v>
+      </c>
+      <c r="D359" t="s">
+        <v>75</v>
+      </c>
+      <c r="E359" t="s">
+        <v>251</v>
+      </c>
+      <c r="F359" t="s">
+        <v>23</v>
+      </c>
+      <c r="G359" t="s">
+        <v>462</v>
+      </c>
+      <c r="H359" t="s">
+        <v>13</v>
+      </c>
+      <c r="I359" t="n">
+        <v>152</v>
+      </c>
+      <c r="J359"/>
+      <c r="K359" s="1"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="n">
+        <v>46261.4083333333</v>
+      </c>
+      <c r="B360" t="n">
+        <v>4615877</v>
+      </c>
+      <c r="C360" t="s">
+        <v>463</v>
+      </c>
+      <c r="D360" t="s">
+        <v>33</v>
+      </c>
+      <c r="E360" t="s">
+        <v>219</v>
+      </c>
+      <c r="F360" t="s">
+        <v>27</v>
+      </c>
+      <c r="G360" t="s">
+        <v>464</v>
+      </c>
+      <c r="H360" t="s">
+        <v>50</v>
+      </c>
+      <c r="I360" t="n">
+        <v>160</v>
+      </c>
+      <c r="J360"/>
+      <c r="K360" s="1"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="n">
+        <v>46261.4090277778</v>
+      </c>
+      <c r="B361" t="n">
+        <v>4615865</v>
+      </c>
+      <c r="C361" t="s">
+        <v>458</v>
+      </c>
+      <c r="D361" t="s">
+        <v>12</v>
+      </c>
+      <c r="E361" t="s">
+        <v>195</v>
+      </c>
+      <c r="F361" t="s">
+        <v>18</v>
+      </c>
+      <c r="G361" t="s">
+        <v>465</v>
+      </c>
+      <c r="H361" t="s">
+        <v>195</v>
+      </c>
+      <c r="I361" t="n">
+        <v>164</v>
+      </c>
+      <c r="J361"/>
+      <c r="K361" s="1"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="n">
+        <v>46261.4090277778</v>
+      </c>
+      <c r="B362" t="n">
+        <v>4615865</v>
+      </c>
+      <c r="C362" t="s">
+        <v>458</v>
+      </c>
+      <c r="D362" t="s">
+        <v>12</v>
+      </c>
+      <c r="E362" t="s">
+        <v>195</v>
+      </c>
+      <c r="F362" t="s">
+        <v>18</v>
+      </c>
+      <c r="G362" t="s">
+        <v>466</v>
+      </c>
+      <c r="H362" t="s">
+        <v>195</v>
+      </c>
+      <c r="I362" t="n">
+        <v>164</v>
+      </c>
+      <c r="J362"/>
+      <c r="K362" s="1"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="n">
+        <v>46261.4125</v>
+      </c>
+      <c r="B363" t="n">
+        <v>4615863</v>
+      </c>
+      <c r="C363" t="s">
+        <v>467</v>
+      </c>
+      <c r="D363" t="s">
+        <v>72</v>
+      </c>
+      <c r="E363" t="s">
+        <v>219</v>
+      </c>
+      <c r="F363" t="s">
+        <v>19</v>
+      </c>
+      <c r="G363" t="s">
+        <v>468</v>
+      </c>
+      <c r="H363" t="s">
+        <v>50</v>
+      </c>
+      <c r="I363" t="n">
+        <v>162</v>
+      </c>
+      <c r="J363"/>
+      <c r="K363" s="1"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="n">
+        <v>46261.4166666667</v>
+      </c>
+      <c r="B364" t="n">
+        <v>4612186</v>
+      </c>
+      <c r="C364" t="s">
+        <v>119</v>
+      </c>
+      <c r="D364" t="s">
+        <v>118</v>
+      </c>
+      <c r="E364" t="s">
+        <v>195</v>
+      </c>
+      <c r="F364" t="s">
+        <v>34</v>
+      </c>
+      <c r="G364" t="s">
+        <v>469</v>
+      </c>
+      <c r="H364" t="s">
+        <v>195</v>
+      </c>
+      <c r="I364" t="n">
+        <v>61</v>
+      </c>
+      <c r="J364"/>
+      <c r="K364" s="1"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="n">
+        <v>46261.4166666667</v>
+      </c>
+      <c r="B365" t="n">
+        <v>4615579</v>
+      </c>
+      <c r="C365" t="s">
+        <v>156</v>
+      </c>
+      <c r="D365" t="s">
+        <v>118</v>
+      </c>
+      <c r="E365" t="s">
+        <v>195</v>
+      </c>
+      <c r="F365" t="s">
+        <v>34</v>
+      </c>
+      <c r="G365" t="s">
+        <v>470</v>
+      </c>
+      <c r="H365" t="s">
+        <v>195</v>
+      </c>
+      <c r="I365" t="n">
+        <v>34</v>
+      </c>
+      <c r="J365"/>
+      <c r="K365" s="1" t="n">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="n">
+        <v>46261.4180555556</v>
+      </c>
+      <c r="B366" t="n">
+        <v>4615862</v>
+      </c>
+      <c r="C366" t="s">
+        <v>471</v>
+      </c>
+      <c r="D366" t="s">
+        <v>238</v>
+      </c>
+      <c r="E366" t="s">
+        <v>219</v>
+      </c>
+      <c r="F366" t="s">
+        <v>19</v>
+      </c>
+      <c r="G366" t="s">
+        <v>472</v>
+      </c>
+      <c r="H366" t="s">
+        <v>50</v>
+      </c>
+      <c r="I366" t="n">
+        <v>153</v>
+      </c>
+      <c r="J366"/>
+      <c r="K366" s="1"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="1" t="n">
+        <v>46261.41875</v>
+      </c>
+      <c r="B367" t="n">
+        <v>4615880</v>
+      </c>
+      <c r="C367" t="s">
+        <v>473</v>
+      </c>
+      <c r="D367" t="s">
+        <v>49</v>
+      </c>
+      <c r="E367" t="s">
+        <v>219</v>
+      </c>
+      <c r="F367" t="s">
+        <v>23</v>
+      </c>
+      <c r="G367" t="s">
+        <v>474</v>
+      </c>
+      <c r="H367" t="s">
+        <v>50</v>
+      </c>
+      <c r="I367" t="n">
+        <v>157</v>
+      </c>
+      <c r="J367"/>
+      <c r="K367" s="1"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="n">
+        <v>46261.425</v>
+      </c>
+      <c r="B368" t="n">
+        <v>4615879</v>
+      </c>
+      <c r="C368" t="s">
+        <v>475</v>
+      </c>
+      <c r="D368" t="s">
+        <v>75</v>
+      </c>
+      <c r="E368" t="s">
+        <v>251</v>
+      </c>
+      <c r="F368" t="s">
+        <v>18</v>
+      </c>
+      <c r="G368" t="s">
+        <v>476</v>
+      </c>
+      <c r="H368" t="s">
+        <v>13</v>
+      </c>
+      <c r="I368" t="n">
+        <v>158</v>
+      </c>
+      <c r="J368"/>
+      <c r="K368" s="1"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="n">
+        <v>46261.4486111111</v>
+      </c>
+      <c r="B369" t="n">
+        <v>4612987</v>
+      </c>
+      <c r="C369" t="s">
+        <v>114</v>
+      </c>
+      <c r="D369" t="s">
+        <v>115</v>
+      </c>
+      <c r="E369" t="s">
+        <v>195</v>
+      </c>
+      <c r="F369" t="s">
+        <v>14</v>
+      </c>
+      <c r="G369" t="s">
+        <v>477</v>
+      </c>
+      <c r="H369" t="s">
+        <v>195</v>
+      </c>
+      <c r="I369" t="n">
+        <v>59</v>
+      </c>
+      <c r="J369" t="s">
+        <v>17</v>
+      </c>
+      <c r="K369" s="1"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="n">
+        <v>46261.4541666667</v>
+      </c>
+      <c r="B370" t="n">
+        <v>4612987</v>
+      </c>
+      <c r="C370" t="s">
+        <v>114</v>
+      </c>
+      <c r="D370" t="s">
+        <v>115</v>
+      </c>
+      <c r="E370" t="s">
+        <v>195</v>
+      </c>
+      <c r="F370" t="s">
+        <v>14</v>
+      </c>
+      <c r="G370" t="s">
+        <v>478</v>
+      </c>
+      <c r="H370" t="s">
+        <v>195</v>
+      </c>
+      <c r="I370" t="n">
+        <v>59</v>
+      </c>
+      <c r="J370" t="s">
+        <v>17</v>
+      </c>
+      <c r="K370" s="1"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="n">
+        <v>46261.4541666667</v>
+      </c>
+      <c r="B371" t="n">
+        <v>4612987</v>
+      </c>
+      <c r="C371" t="s">
+        <v>114</v>
+      </c>
+      <c r="D371" t="s">
+        <v>115</v>
+      </c>
+      <c r="E371" t="s">
+        <v>195</v>
+      </c>
+      <c r="F371" t="s">
+        <v>14</v>
+      </c>
+      <c r="G371" t="s">
+        <v>479</v>
+      </c>
+      <c r="H371" t="s">
+        <v>195</v>
+      </c>
+      <c r="I371" t="n">
+        <v>59</v>
+      </c>
+      <c r="J371" t="s">
+        <v>17</v>
+      </c>
+      <c r="K371" s="1"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="n">
+        <v>46261.4618055556</v>
+      </c>
+      <c r="B372" t="n">
+        <v>4615859</v>
+      </c>
+      <c r="C372" t="s">
+        <v>480</v>
+      </c>
+      <c r="D372" t="s">
+        <v>275</v>
+      </c>
+      <c r="E372" t="s">
+        <v>251</v>
+      </c>
+      <c r="F372" t="s">
+        <v>19</v>
+      </c>
+      <c r="G372" t="s">
+        <v>481</v>
+      </c>
+      <c r="H372" t="s">
+        <v>13</v>
+      </c>
+      <c r="I372" t="n">
+        <v>150</v>
+      </c>
+      <c r="J372"/>
+      <c r="K372" s="1"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="n">
+        <v>46261.4652777778</v>
+      </c>
+      <c r="B373" t="n">
+        <v>4615858</v>
+      </c>
+      <c r="C373" t="s">
+        <v>482</v>
+      </c>
+      <c r="D373" t="s">
+        <v>30</v>
+      </c>
+      <c r="E373" t="s">
+        <v>251</v>
+      </c>
+      <c r="F373" t="s">
+        <v>18</v>
+      </c>
+      <c r="G373" t="s">
+        <v>483</v>
+      </c>
+      <c r="H373" t="s">
+        <v>13</v>
+      </c>
+      <c r="I373" t="n">
+        <v>151</v>
+      </c>
+      <c r="J373"/>
+      <c r="K373" s="1"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="n">
+        <v>46261.4659722222</v>
+      </c>
+      <c r="B374" t="n">
+        <v>4615853</v>
+      </c>
+      <c r="C374" t="s">
+        <v>160</v>
+      </c>
+      <c r="D374" t="s">
+        <v>56</v>
+      </c>
+      <c r="E374" t="s">
+        <v>219</v>
+      </c>
+      <c r="F374" t="s">
+        <v>19</v>
+      </c>
+      <c r="G374" t="s">
+        <v>484</v>
+      </c>
+      <c r="H374" t="s">
+        <v>50</v>
+      </c>
+      <c r="I374" t="n">
+        <v>139</v>
+      </c>
+      <c r="J374"/>
+      <c r="K374" s="1"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="n">
+        <v>46261.46875</v>
+      </c>
+      <c r="B375" t="n">
+        <v>4615862</v>
+      </c>
+      <c r="C375" t="s">
+        <v>471</v>
+      </c>
+      <c r="D375" t="s">
+        <v>238</v>
+      </c>
+      <c r="E375" t="s">
+        <v>219</v>
+      </c>
+      <c r="F375" t="s">
+        <v>18</v>
+      </c>
+      <c r="G375" t="s">
+        <v>485</v>
+      </c>
+      <c r="H375" t="s">
+        <v>50</v>
+      </c>
+      <c r="I375" t="n">
+        <v>153</v>
+      </c>
+      <c r="J375"/>
+      <c r="K375" s="1"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="n">
+        <v>46261.475</v>
+      </c>
+      <c r="B376" t="n">
+        <v>4612987</v>
+      </c>
+      <c r="C376" t="s">
+        <v>114</v>
+      </c>
+      <c r="D376" t="s">
+        <v>115</v>
+      </c>
+      <c r="E376" t="s">
+        <v>195</v>
+      </c>
+      <c r="F376" t="s">
+        <v>14</v>
+      </c>
+      <c r="G376" t="s">
+        <v>486</v>
+      </c>
+      <c r="H376" t="s">
+        <v>195</v>
+      </c>
+      <c r="I376" t="n">
+        <v>59</v>
+      </c>
+      <c r="J376" t="s">
+        <v>17</v>
+      </c>
+      <c r="K376" s="1"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="n">
+        <v>46261.48125</v>
+      </c>
+      <c r="B377" t="n">
+        <v>4615881</v>
+      </c>
+      <c r="C377" t="s">
+        <v>487</v>
+      </c>
+      <c r="D377" t="s">
+        <v>25</v>
+      </c>
+      <c r="E377" t="s">
+        <v>251</v>
+      </c>
+      <c r="F377" t="s">
+        <v>27</v>
+      </c>
+      <c r="G377" t="s">
+        <v>488</v>
+      </c>
+      <c r="H377" t="s">
+        <v>13</v>
+      </c>
+      <c r="I377" t="n">
+        <v>156</v>
+      </c>
+      <c r="J377"/>
+      <c r="K377" s="1"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="n">
+        <v>46261.4840277778</v>
+      </c>
+      <c r="B378" t="n">
+        <v>4615758</v>
+      </c>
+      <c r="C378" t="s">
+        <v>204</v>
+      </c>
+      <c r="D378" t="s">
+        <v>115</v>
+      </c>
+      <c r="E378" t="s">
+        <v>195</v>
+      </c>
+      <c r="F378" t="s">
+        <v>34</v>
+      </c>
+      <c r="G378" t="s">
+        <v>489</v>
+      </c>
+      <c r="H378" t="s">
+        <v>195</v>
+      </c>
+      <c r="I378" t="n">
+        <v>69</v>
+      </c>
+      <c r="J378"/>
+      <c r="K378" s="1"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="n">
+        <v>46261.4895833333</v>
+      </c>
+      <c r="B379" t="n">
+        <v>4615841</v>
+      </c>
+      <c r="C379" t="s">
+        <v>357</v>
+      </c>
+      <c r="D379" t="s">
+        <v>96</v>
+      </c>
+      <c r="E379" t="s">
+        <v>251</v>
+      </c>
+      <c r="F379" t="s">
+        <v>19</v>
+      </c>
+      <c r="G379" t="s">
+        <v>490</v>
+      </c>
+      <c r="H379" t="s">
+        <v>16</v>
+      </c>
+      <c r="I379" t="n">
+        <v>120</v>
+      </c>
+      <c r="J379"/>
+      <c r="K379" s="1"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="n">
+        <v>46261.4895833333</v>
+      </c>
+      <c r="B380" t="n">
+        <v>4615841</v>
+      </c>
+      <c r="C380" t="s">
+        <v>357</v>
+      </c>
+      <c r="D380" t="s">
+        <v>96</v>
+      </c>
+      <c r="E380" t="s">
+        <v>251</v>
+      </c>
+      <c r="F380" t="s">
+        <v>27</v>
+      </c>
+      <c r="G380" t="s">
+        <v>490</v>
+      </c>
+      <c r="H380" t="s">
+        <v>16</v>
+      </c>
+      <c r="I380" t="n">
+        <v>120</v>
+      </c>
+      <c r="J380"/>
+      <c r="K380" s="1"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="n">
+        <v>46261.4909722222</v>
+      </c>
+      <c r="B381" t="n">
+        <v>4615821</v>
+      </c>
+      <c r="C381" t="s">
+        <v>318</v>
+      </c>
+      <c r="D381" t="s">
+        <v>238</v>
+      </c>
+      <c r="E381" t="s">
+        <v>219</v>
+      </c>
+      <c r="F381" t="s">
+        <v>34</v>
+      </c>
+      <c r="G381" t="s">
+        <v>491</v>
+      </c>
+      <c r="H381" t="s">
+        <v>26</v>
+      </c>
+      <c r="I381" t="n">
+        <v>115</v>
+      </c>
+      <c r="J381"/>
+      <c r="K381" s="1" t="n">
+        <v>46274</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="n">
+        <v>46261.49375</v>
+      </c>
+      <c r="B382" t="n">
+        <v>4615845</v>
+      </c>
+      <c r="C382" t="s">
+        <v>397</v>
+      </c>
+      <c r="D382" t="s">
+        <v>21</v>
+      </c>
+      <c r="E382" t="s">
+        <v>251</v>
+      </c>
+      <c r="F382" t="s">
+        <v>18</v>
+      </c>
+      <c r="G382" t="s">
+        <v>492</v>
+      </c>
+      <c r="H382" t="s">
+        <v>50</v>
+      </c>
+      <c r="I382" t="n">
+        <v>135</v>
+      </c>
+      <c r="J382"/>
+      <c r="K382" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -13051,13 +14009,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>458</v>
+        <v>493</v>
       </c>
       <c r="B1" t="s">
-        <v>459</v>
+        <v>494</v>
       </c>
       <c r="C1" t="s">
-        <v>460</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2">

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="508">
   <si>
     <t xml:space="preserve">Thời gian update</t>
   </si>
@@ -1682,6 +1682,49 @@
   </si>
   <si>
     <t xml:space="preserve">Lỗi dây tín hiệu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do trời mưa nên chưa lắp đặt được. Hẹn KH trời hết mưa rồi qua xử lý
+Hoàn thành</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Đình Vỹ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lỗi app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phạm Thanh Bình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QTI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã tiếp nhận và phân nhân sự kiểm tra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Võ Ưu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã nhận thông tin và đang phân nhân sự kiểm tra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Hỏng CB AC =&gt; Đã thay CB AC cho khách
+- Đã gia hạn đến 17h ngày 27/8 để xử lý cho KH
+- FT3 đã liên hệ KH hẹn sáng 27/8 kiểm tra cho khách, xử lý trc 9h42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket CN tạo CSKH chưa duyệt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã thay xong cho khách
+- dự kiến ngày 26/8 hàng về, 27/8 thay cho khách
+hỏng metter, hiện đã chuyển về bảo hành cho hãng powrtech từ 18/08, thiết bị metter không tạo được bảo hành.  Đang chờ hàng bảo hành về để lắp cho KH, dự kiến 29/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Thời tiết đang mưa, GĐKD Phụng hẹn lại lịch với Kh về đề xuất gia hạn đến 10/9
+- Do nhu cầu sử dụng của KH nhiều hơn, thời tiết HCM đang mùa mưa nên hiệu suất giảm.
+- KH muốn thay đổi làm dàn khung nên khiếu nại lên tổng đài =&gt; GĐ Phụng sẽ làm việc lại với KH phần thay đổi này.</t>
   </si>
   <si>
     <t xml:space="preserve">Ngày</t>
@@ -1746,8 +1789,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K382" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K382"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K395" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K395"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Thời gian update"/>
     <tableColumn id="2" name="ID"/>
@@ -13993,6 +14036,413 @@
       <c r="J382"/>
       <c r="K382" s="1"/>
     </row>
+    <row r="383">
+      <c r="A383" s="1" t="n">
+        <v>46261.5666666667</v>
+      </c>
+      <c r="B383" t="n">
+        <v>4615579</v>
+      </c>
+      <c r="C383" t="s">
+        <v>156</v>
+      </c>
+      <c r="D383" t="s">
+        <v>118</v>
+      </c>
+      <c r="E383" t="s">
+        <v>195</v>
+      </c>
+      <c r="F383" t="s">
+        <v>34</v>
+      </c>
+      <c r="G383" t="s">
+        <v>470</v>
+      </c>
+      <c r="H383" t="s">
+        <v>195</v>
+      </c>
+      <c r="I383" t="n">
+        <v>34</v>
+      </c>
+      <c r="J383"/>
+      <c r="K383" s="1" t="n">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="n">
+        <v>46261.5680555556</v>
+      </c>
+      <c r="B384" t="n">
+        <v>4615840</v>
+      </c>
+      <c r="C384" t="s">
+        <v>360</v>
+      </c>
+      <c r="D384" t="s">
+        <v>75</v>
+      </c>
+      <c r="E384" t="s">
+        <v>251</v>
+      </c>
+      <c r="F384" t="s">
+        <v>18</v>
+      </c>
+      <c r="G384" t="s">
+        <v>493</v>
+      </c>
+      <c r="H384" t="s">
+        <v>16</v>
+      </c>
+      <c r="I384" t="n">
+        <v>121</v>
+      </c>
+      <c r="J384"/>
+      <c r="K384" s="1"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="n">
+        <v>46261.5694444444</v>
+      </c>
+      <c r="B385" t="n">
+        <v>4615887</v>
+      </c>
+      <c r="C385" t="s">
+        <v>494</v>
+      </c>
+      <c r="D385" t="s">
+        <v>96</v>
+      </c>
+      <c r="E385" t="s">
+        <v>251</v>
+      </c>
+      <c r="F385" t="s">
+        <v>23</v>
+      </c>
+      <c r="G385" t="s">
+        <v>495</v>
+      </c>
+      <c r="H385" t="s">
+        <v>16</v>
+      </c>
+      <c r="I385" t="n">
+        <v>169</v>
+      </c>
+      <c r="J385"/>
+      <c r="K385" s="1"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="n">
+        <v>46261.5694444444</v>
+      </c>
+      <c r="B386" t="n">
+        <v>4615909</v>
+      </c>
+      <c r="C386" t="s">
+        <v>496</v>
+      </c>
+      <c r="D386" t="s">
+        <v>497</v>
+      </c>
+      <c r="E386" t="s">
+        <v>195</v>
+      </c>
+      <c r="F386" t="s">
+        <v>23</v>
+      </c>
+      <c r="G386" t="s">
+        <v>498</v>
+      </c>
+      <c r="H386" t="s">
+        <v>195</v>
+      </c>
+      <c r="I386" t="n">
+        <v>166</v>
+      </c>
+      <c r="J386"/>
+      <c r="K386" s="1"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="n">
+        <v>46261.5694444444</v>
+      </c>
+      <c r="B387" t="n">
+        <v>4615909</v>
+      </c>
+      <c r="C387" t="s">
+        <v>496</v>
+      </c>
+      <c r="D387" t="s">
+        <v>497</v>
+      </c>
+      <c r="E387" t="s">
+        <v>195</v>
+      </c>
+      <c r="F387" t="s">
+        <v>23</v>
+      </c>
+      <c r="G387" t="s">
+        <v>498</v>
+      </c>
+      <c r="H387" t="s">
+        <v>195</v>
+      </c>
+      <c r="I387" t="n">
+        <v>166</v>
+      </c>
+      <c r="J387"/>
+      <c r="K387" s="1"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="n">
+        <v>46261.5715277778</v>
+      </c>
+      <c r="B388" t="n">
+        <v>4615888</v>
+      </c>
+      <c r="C388" t="s">
+        <v>499</v>
+      </c>
+      <c r="D388" t="s">
+        <v>45</v>
+      </c>
+      <c r="E388" t="s">
+        <v>195</v>
+      </c>
+      <c r="F388" t="s">
+        <v>23</v>
+      </c>
+      <c r="G388" t="s">
+        <v>500</v>
+      </c>
+      <c r="H388" t="s">
+        <v>195</v>
+      </c>
+      <c r="I388" t="n">
+        <v>168</v>
+      </c>
+      <c r="J388"/>
+      <c r="K388" s="1"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="n">
+        <v>46261.5715277778</v>
+      </c>
+      <c r="B389" t="n">
+        <v>4615909</v>
+      </c>
+      <c r="C389" t="s">
+        <v>496</v>
+      </c>
+      <c r="D389" t="s">
+        <v>497</v>
+      </c>
+      <c r="E389" t="s">
+        <v>195</v>
+      </c>
+      <c r="F389" t="s">
+        <v>23</v>
+      </c>
+      <c r="G389" t="s">
+        <v>500</v>
+      </c>
+      <c r="H389" t="s">
+        <v>195</v>
+      </c>
+      <c r="I389" t="n">
+        <v>166</v>
+      </c>
+      <c r="J389"/>
+      <c r="K389" s="1"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="n">
+        <v>46261.5715277778</v>
+      </c>
+      <c r="B390" t="n">
+        <v>4615870</v>
+      </c>
+      <c r="C390" t="s">
+        <v>415</v>
+      </c>
+      <c r="D390" t="s">
+        <v>56</v>
+      </c>
+      <c r="E390" t="s">
+        <v>219</v>
+      </c>
+      <c r="F390" t="s">
+        <v>18</v>
+      </c>
+      <c r="G390" t="s">
+        <v>501</v>
+      </c>
+      <c r="H390" t="s">
+        <v>50</v>
+      </c>
+      <c r="I390" t="n">
+        <v>137</v>
+      </c>
+      <c r="J390"/>
+      <c r="K390" s="1"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="n">
+        <v>46261.5715277778</v>
+      </c>
+      <c r="B391" t="n">
+        <v>4615877</v>
+      </c>
+      <c r="C391" t="s">
+        <v>463</v>
+      </c>
+      <c r="D391" t="s">
+        <v>33</v>
+      </c>
+      <c r="E391" t="s">
+        <v>219</v>
+      </c>
+      <c r="F391" t="s">
+        <v>18</v>
+      </c>
+      <c r="G391" t="s">
+        <v>464</v>
+      </c>
+      <c r="H391" t="s">
+        <v>50</v>
+      </c>
+      <c r="I391" t="n">
+        <v>160</v>
+      </c>
+      <c r="J391"/>
+      <c r="K391" s="1"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="n">
+        <v>46261.5784722222</v>
+      </c>
+      <c r="B392" t="n">
+        <v>4615882</v>
+      </c>
+      <c r="C392" t="s">
+        <v>71</v>
+      </c>
+      <c r="D392" t="s">
+        <v>72</v>
+      </c>
+      <c r="E392" t="s">
+        <v>219</v>
+      </c>
+      <c r="F392" t="s">
+        <v>23</v>
+      </c>
+      <c r="G392" t="s">
+        <v>502</v>
+      </c>
+      <c r="H392" t="s">
+        <v>50</v>
+      </c>
+      <c r="I392" t="n">
+        <v>155</v>
+      </c>
+      <c r="J392"/>
+      <c r="K392" s="1"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="n">
+        <v>46261.58125</v>
+      </c>
+      <c r="B393" t="n">
+        <v>4615855</v>
+      </c>
+      <c r="C393" t="s">
+        <v>428</v>
+      </c>
+      <c r="D393" t="s">
+        <v>128</v>
+      </c>
+      <c r="E393" t="s">
+        <v>219</v>
+      </c>
+      <c r="F393" t="s">
+        <v>18</v>
+      </c>
+      <c r="G393" t="s">
+        <v>429</v>
+      </c>
+      <c r="H393" t="s">
+        <v>50</v>
+      </c>
+      <c r="I393" t="n">
+        <v>144</v>
+      </c>
+      <c r="J393"/>
+      <c r="K393" s="1"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="n">
+        <v>46261.58125</v>
+      </c>
+      <c r="B394" t="n">
+        <v>4615553</v>
+      </c>
+      <c r="C394" t="s">
+        <v>71</v>
+      </c>
+      <c r="D394" t="s">
+        <v>72</v>
+      </c>
+      <c r="E394" t="s">
+        <v>219</v>
+      </c>
+      <c r="F394" t="s">
+        <v>18</v>
+      </c>
+      <c r="G394" t="s">
+        <v>503</v>
+      </c>
+      <c r="H394" t="s">
+        <v>26</v>
+      </c>
+      <c r="I394" t="n">
+        <v>35</v>
+      </c>
+      <c r="J394"/>
+      <c r="K394" s="1" t="n">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="n">
+        <v>46261.5930555556</v>
+      </c>
+      <c r="B395" t="n">
+        <v>4615857</v>
+      </c>
+      <c r="C395" t="s">
+        <v>456</v>
+      </c>
+      <c r="D395" t="s">
+        <v>152</v>
+      </c>
+      <c r="E395" t="s">
+        <v>219</v>
+      </c>
+      <c r="F395" t="s">
+        <v>27</v>
+      </c>
+      <c r="G395" t="s">
+        <v>504</v>
+      </c>
+      <c r="H395" t="s">
+        <v>50</v>
+      </c>
+      <c r="I395" t="n">
+        <v>148</v>
+      </c>
+      <c r="J395"/>
+      <c r="K395" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -14009,13 +14459,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="B1" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C1" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2">

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="528">
   <si>
     <t xml:space="preserve">Thời gian update</t>
   </si>
@@ -1725,6 +1725,82 @@
     <t xml:space="preserve">- Thời tiết đang mưa, GĐKD Phụng hẹn lại lịch với Kh về đề xuất gia hạn đến 10/9
 - Do nhu cầu sử dụng của KH nhiều hơn, thời tiết HCM đang mùa mưa nên hiệu suất giảm.
 - KH muốn thay đổi làm dàn khung nên khiếu nại lên tổng đài =&gt; GĐ Phụng sẽ làm việc lại với KH phần thay đổi này.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-IVT bị lỗi phải thay linh kiện đã hết bảo hành (KH đã báo lỗi với CN lúc còn bảo hành), dự kiến 25/8 xong. 
+- KH đã chuyển tiền cho CNCT, CNCT chưa chuyển đủ 100% tiền cho Hãng để Hãng xử lý. Đ/c Tuần cam kết trong ngày 27/8 nếu Hãng ko xử lý thì Tuần sẽ bỏ chi phí ra khắc phục cho KH
+CN đã nộp đủ tiền cho bên DAT, Dự kiến ngày 29/8 hãng gửi tb về. Ngày 30/8 triển khai lắp đặt lại cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đầu mối trao đổi: Trương Nguyễn Thương Hoài
+Đang trao đổi với anh Bắc và với hãng để đánh giá bảo hành tấm pin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đầu mối trao đổi: Trương Nguyễn Thương Hoài
+Đang trao đổi với anh Bắc và với hãng để đánh giá bảo hành tấm pin
+Dự đoán tấm pin bị nứt do tác động của ngoại lực</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Hàng đã về và thay cho khách =&gt; Đóng Ticket trong hôm nay
+- Đã gửi IVT đi bảo hành dự kiến 03/09 về thay cho khách
+- Tạo mới YCBH YCBH_CMU_1786682703995 từ B2C lúc 11:45 14/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Trường Giang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siết lại hết các đầu at. Lỗi At ngoài điện lực</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- CN Đang đặng hàng mua ngoài nhưng chưa có, dự kiến 1/9 có hàng xử lý cho khách
+- HĐ đang để cọc đồng, thực tế là mạ đồng (KH check HĐ nên yêu cầu thay thế)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trần Văn Cương</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Hệ thống điện lưới nhà KH bị sụt áp còn 180v, ATS đóng ngắt liên tục =&gt; Đã xử lý xong và đóng Ticket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- FT3 đã liên hệ hẹn lại lịch với KH 17h ngày 29/8
+- Đã YC GĐKT liên hệ KH và qua kiểm tra cho khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Đăng Khoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nhảy át chống giật trong nhà khách hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lỗi app,  Chiều 28/8 qua nahf KH hướng dẫn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hãng Sigenergy báo lại hệ thống giám sát đang được hãng nâng cấp và khôi phục dữ liệu. Đã khắc phục xong cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-IVT bị lỗi phải thay linh kiện đã hết bảo hành (KH đã báo lỗi với CN lúc còn bảo hành), dự kiến 25/8 xong. 
+- KH đã chuyển tiền cho CNCT, CNCT chưa chuyển đủ 100% tiền cho Hãng để Hãng xử lý. Đ/c Tuần cam kết trong ngày 27/8 nếu Hãng ko xử lý thì Tuần sẽ bỏ chi phí ra khắc phục cho KH
+CN đã nộp đủ tiền cho bên DAT, Dự kiến ngày 05/9 hãng gửi tb về.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phạm Văn Khuê</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã giao GĐKT liên hệ hỗ trợ KH, đến kiểm tra trước 10h ngày 28/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lương Minh Thuận</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã xử lý xong khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Dự kiến ngày 27/8 về hàng rồi thay cho khách, xử lý xong trước 28/8
+- Hệ thống NLMT bị sét đánh trúng, hỏng 2 SPD DC + 1 ATS.
+- Đã lắp đặt hệ thống để thiết bị hoạt động không bị mất sản lượng.
+- Thiết bị nhập khẩu Trung Quốc, hiện tại không sẵn hàng.
+- Khách hàng không đồng ý đổi sang mã hàng tương đương.
+- Dự kiến 28/8 có hàng thay cho khách</t>
   </si>
   <si>
     <t xml:space="preserve">Ngày</t>
@@ -1789,8 +1865,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K395" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K395"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K412" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K412"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Thời gian update"/>
     <tableColumn id="2" name="ID"/>
@@ -14443,6 +14519,543 @@
       <c r="J395"/>
       <c r="K395" s="1"/>
     </row>
+    <row r="396">
+      <c r="A396" s="1" t="n">
+        <v>46261.6111111111</v>
+      </c>
+      <c r="B396" t="n">
+        <v>4615658</v>
+      </c>
+      <c r="C396" t="s">
+        <v>136</v>
+      </c>
+      <c r="D396" t="s">
+        <v>65</v>
+      </c>
+      <c r="E396" t="s">
+        <v>251</v>
+      </c>
+      <c r="F396" t="s">
+        <v>34</v>
+      </c>
+      <c r="G396" t="s">
+        <v>505</v>
+      </c>
+      <c r="H396" t="s">
+        <v>50</v>
+      </c>
+      <c r="I396" t="n">
+        <v>19</v>
+      </c>
+      <c r="J396"/>
+      <c r="K396" s="1" t="n">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="n">
+        <v>46261.6118055556</v>
+      </c>
+      <c r="B397" t="n">
+        <v>4615888</v>
+      </c>
+      <c r="C397" t="s">
+        <v>499</v>
+      </c>
+      <c r="D397" t="s">
+        <v>45</v>
+      </c>
+      <c r="E397" t="s">
+        <v>195</v>
+      </c>
+      <c r="F397" t="s">
+        <v>27</v>
+      </c>
+      <c r="G397" t="s">
+        <v>506</v>
+      </c>
+      <c r="H397" t="s">
+        <v>195</v>
+      </c>
+      <c r="I397" t="n">
+        <v>168</v>
+      </c>
+      <c r="J397"/>
+      <c r="K397" s="1"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="n">
+        <v>46261.6145833333</v>
+      </c>
+      <c r="B398" t="n">
+        <v>4615888</v>
+      </c>
+      <c r="C398" t="s">
+        <v>499</v>
+      </c>
+      <c r="D398" t="s">
+        <v>45</v>
+      </c>
+      <c r="E398" t="s">
+        <v>195</v>
+      </c>
+      <c r="F398" t="s">
+        <v>27</v>
+      </c>
+      <c r="G398" t="s">
+        <v>507</v>
+      </c>
+      <c r="H398" t="s">
+        <v>195</v>
+      </c>
+      <c r="I398" t="n">
+        <v>168</v>
+      </c>
+      <c r="J398"/>
+      <c r="K398" s="1"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="n">
+        <v>46261.6159722222</v>
+      </c>
+      <c r="B399" t="n">
+        <v>4615434</v>
+      </c>
+      <c r="C399" t="s">
+        <v>138</v>
+      </c>
+      <c r="D399" t="s">
+        <v>128</v>
+      </c>
+      <c r="E399" t="s">
+        <v>219</v>
+      </c>
+      <c r="F399" t="s">
+        <v>34</v>
+      </c>
+      <c r="G399" t="s">
+        <v>508</v>
+      </c>
+      <c r="H399" t="s">
+        <v>50</v>
+      </c>
+      <c r="I399" t="n">
+        <v>43</v>
+      </c>
+      <c r="J399"/>
+      <c r="K399" s="1" t="n">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="n">
+        <v>46261.6208333333</v>
+      </c>
+      <c r="B400" t="n">
+        <v>4615883</v>
+      </c>
+      <c r="C400" t="s">
+        <v>509</v>
+      </c>
+      <c r="D400" t="s">
+        <v>53</v>
+      </c>
+      <c r="E400" t="s">
+        <v>251</v>
+      </c>
+      <c r="F400" t="s">
+        <v>19</v>
+      </c>
+      <c r="G400" t="s">
+        <v>510</v>
+      </c>
+      <c r="H400" t="s">
+        <v>50</v>
+      </c>
+      <c r="I400" t="n">
+        <v>163</v>
+      </c>
+      <c r="J400"/>
+      <c r="K400" s="1"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="n">
+        <v>46261.6284722222</v>
+      </c>
+      <c r="B401" t="n">
+        <v>4615434</v>
+      </c>
+      <c r="C401" t="s">
+        <v>138</v>
+      </c>
+      <c r="D401" t="s">
+        <v>128</v>
+      </c>
+      <c r="E401" t="s">
+        <v>219</v>
+      </c>
+      <c r="F401" t="s">
+        <v>18</v>
+      </c>
+      <c r="G401" t="s">
+        <v>508</v>
+      </c>
+      <c r="H401" t="s">
+        <v>50</v>
+      </c>
+      <c r="I401" t="n">
+        <v>43</v>
+      </c>
+      <c r="J401"/>
+      <c r="K401" s="1" t="n">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="n">
+        <v>46261.6375</v>
+      </c>
+      <c r="B402" t="n">
+        <v>4615883</v>
+      </c>
+      <c r="C402" t="s">
+        <v>509</v>
+      </c>
+      <c r="D402" t="s">
+        <v>53</v>
+      </c>
+      <c r="E402" t="s">
+        <v>251</v>
+      </c>
+      <c r="F402" t="s">
+        <v>18</v>
+      </c>
+      <c r="G402" t="s">
+        <v>510</v>
+      </c>
+      <c r="H402" t="s">
+        <v>50</v>
+      </c>
+      <c r="I402" t="n">
+        <v>163</v>
+      </c>
+      <c r="J402"/>
+      <c r="K402" s="1"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="n">
+        <v>46261.6388888889</v>
+      </c>
+      <c r="B403" t="n">
+        <v>4615646</v>
+      </c>
+      <c r="C403" t="s">
+        <v>55</v>
+      </c>
+      <c r="D403" t="s">
+        <v>56</v>
+      </c>
+      <c r="E403" t="s">
+        <v>219</v>
+      </c>
+      <c r="F403" t="s">
+        <v>27</v>
+      </c>
+      <c r="G403" t="s">
+        <v>511</v>
+      </c>
+      <c r="H403" t="s">
+        <v>50</v>
+      </c>
+      <c r="I403" t="n">
+        <v>23</v>
+      </c>
+      <c r="J403"/>
+      <c r="K403" s="1"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="n">
+        <v>46261.6493055556</v>
+      </c>
+      <c r="B404" t="n">
+        <v>4615910</v>
+      </c>
+      <c r="C404" t="s">
+        <v>512</v>
+      </c>
+      <c r="D404" t="s">
+        <v>42</v>
+      </c>
+      <c r="E404" t="s">
+        <v>219</v>
+      </c>
+      <c r="F404" t="s">
+        <v>18</v>
+      </c>
+      <c r="G404" t="s">
+        <v>513</v>
+      </c>
+      <c r="H404" t="s">
+        <v>50</v>
+      </c>
+      <c r="I404" t="n">
+        <v>165</v>
+      </c>
+      <c r="J404"/>
+      <c r="K404" s="1"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="n">
+        <v>46261.6548611111</v>
+      </c>
+      <c r="B405" t="n">
+        <v>4615880</v>
+      </c>
+      <c r="C405" t="s">
+        <v>473</v>
+      </c>
+      <c r="D405" t="s">
+        <v>49</v>
+      </c>
+      <c r="E405" t="s">
+        <v>219</v>
+      </c>
+      <c r="F405" t="s">
+        <v>27</v>
+      </c>
+      <c r="G405" t="s">
+        <v>514</v>
+      </c>
+      <c r="H405" t="s">
+        <v>50</v>
+      </c>
+      <c r="I405" t="n">
+        <v>157</v>
+      </c>
+      <c r="J405"/>
+      <c r="K405" s="1"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="n">
+        <v>46261.65625</v>
+      </c>
+      <c r="B406" t="n">
+        <v>4615864</v>
+      </c>
+      <c r="C406" t="s">
+        <v>515</v>
+      </c>
+      <c r="D406" t="s">
+        <v>178</v>
+      </c>
+      <c r="E406" t="s">
+        <v>251</v>
+      </c>
+      <c r="F406" t="s">
+        <v>18</v>
+      </c>
+      <c r="G406" t="s">
+        <v>516</v>
+      </c>
+      <c r="H406" t="s">
+        <v>50</v>
+      </c>
+      <c r="I406" t="n">
+        <v>161</v>
+      </c>
+      <c r="J406"/>
+      <c r="K406" s="1"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="n">
+        <v>46261.6638888889</v>
+      </c>
+      <c r="B407" t="n">
+        <v>4615887</v>
+      </c>
+      <c r="C407" t="s">
+        <v>494</v>
+      </c>
+      <c r="D407" t="s">
+        <v>96</v>
+      </c>
+      <c r="E407" t="s">
+        <v>251</v>
+      </c>
+      <c r="F407" t="s">
+        <v>27</v>
+      </c>
+      <c r="G407" t="s">
+        <v>517</v>
+      </c>
+      <c r="H407" t="s">
+        <v>16</v>
+      </c>
+      <c r="I407" t="n">
+        <v>169</v>
+      </c>
+      <c r="J407"/>
+      <c r="K407" s="1"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="n">
+        <v>46261.6659722222</v>
+      </c>
+      <c r="B408" t="n">
+        <v>4615856</v>
+      </c>
+      <c r="C408" t="s">
+        <v>400</v>
+      </c>
+      <c r="D408" t="s">
+        <v>401</v>
+      </c>
+      <c r="E408" t="s">
+        <v>195</v>
+      </c>
+      <c r="F408" t="s">
+        <v>18</v>
+      </c>
+      <c r="G408" t="s">
+        <v>518</v>
+      </c>
+      <c r="H408" t="s">
+        <v>195</v>
+      </c>
+      <c r="I408" t="n">
+        <v>143</v>
+      </c>
+      <c r="J408"/>
+      <c r="K408" s="1"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="n">
+        <v>46261.6743055556</v>
+      </c>
+      <c r="B409" t="n">
+        <v>4615658</v>
+      </c>
+      <c r="C409" t="s">
+        <v>136</v>
+      </c>
+      <c r="D409" t="s">
+        <v>65</v>
+      </c>
+      <c r="E409" t="s">
+        <v>251</v>
+      </c>
+      <c r="F409" t="s">
+        <v>18</v>
+      </c>
+      <c r="G409" t="s">
+        <v>519</v>
+      </c>
+      <c r="H409" t="s">
+        <v>50</v>
+      </c>
+      <c r="I409" t="n">
+        <v>19</v>
+      </c>
+      <c r="J409"/>
+      <c r="K409" s="1" t="n">
+        <v>46259</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="n">
+        <v>46261.6777777778</v>
+      </c>
+      <c r="B410" t="n">
+        <v>4615890</v>
+      </c>
+      <c r="C410" t="s">
+        <v>520</v>
+      </c>
+      <c r="D410" t="s">
+        <v>123</v>
+      </c>
+      <c r="E410" t="s">
+        <v>219</v>
+      </c>
+      <c r="F410" t="s">
+        <v>23</v>
+      </c>
+      <c r="G410" t="s">
+        <v>521</v>
+      </c>
+      <c r="H410" t="s">
+        <v>50</v>
+      </c>
+      <c r="I410" t="n">
+        <v>167</v>
+      </c>
+      <c r="J410"/>
+      <c r="K410" s="1"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="n">
+        <v>46261.68125</v>
+      </c>
+      <c r="B411" t="n">
+        <v>4615886</v>
+      </c>
+      <c r="C411" t="s">
+        <v>522</v>
+      </c>
+      <c r="D411" t="s">
+        <v>56</v>
+      </c>
+      <c r="E411" t="s">
+        <v>219</v>
+      </c>
+      <c r="F411" t="s">
+        <v>18</v>
+      </c>
+      <c r="G411" t="s">
+        <v>523</v>
+      </c>
+      <c r="H411" t="s">
+        <v>50</v>
+      </c>
+      <c r="I411" t="n">
+        <v>170</v>
+      </c>
+      <c r="J411"/>
+      <c r="K411" s="1"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="n">
+        <v>46261.6833333333</v>
+      </c>
+      <c r="B412" t="n">
+        <v>4615669</v>
+      </c>
+      <c r="C412" t="s">
+        <v>146</v>
+      </c>
+      <c r="D412" t="s">
+        <v>123</v>
+      </c>
+      <c r="E412" t="s">
+        <v>219</v>
+      </c>
+      <c r="F412" t="s">
+        <v>34</v>
+      </c>
+      <c r="G412" t="s">
+        <v>524</v>
+      </c>
+      <c r="H412" t="s">
+        <v>50</v>
+      </c>
+      <c r="I412" t="n">
+        <v>18</v>
+      </c>
+      <c r="J412"/>
+      <c r="K412" s="1" t="n">
+        <v>46262</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -14459,13 +15072,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="B1" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="C1" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
     </row>
     <row r="2">
@@ -14506,7 +15119,7 @@
         <v>46261</v>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="549">
   <si>
     <t xml:space="preserve">Thời gian update</t>
   </si>
@@ -1801,6 +1801,80 @@
 - Thiết bị nhập khẩu Trung Quốc, hiện tại không sẵn hàng.
 - Khách hàng không đồng ý đổi sang mã hàng tương đương.
 - Dự kiến 28/8 có hàng thay cho khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Chí Hùng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Thiết bị đã hoạt đồng bình thường</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kỹ thuật đã nhận thông tin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đầu mối trao đổi: Trương Nguyễn Thương Hoài
+Đang trao đổi với anh Bắc và với hãng để đánh giá bảo hành tấm pin
+Dự đoán tấm pin bị nứt do tác động của ngoại lực
+Đầu mối đang thu thập thông tin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lỗi inverter, hãng báo đổi hàng mới, hãng chưa xác định được thời gian sẽ gửi hàng về cho khách.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đầu mối trao đổi: Trương Nguyễn Thương Hoài
+Đang trao đổi với anh Bắc và với hãng để đánh giá bảo hành tấm pin
+Dự đoán tấm pin bị nứt do tác động của ngoại lực
+Đầu mối đang thu thập thông tin hợp đồng để gửi lại anh Bắc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đoàn Thành Nam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cty hẹn sẽ báo đến xử lý sau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Viết Hưng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KH nhờ hỗ trợ di chuyển tấm pin, CN đang làm việc xem tính chi phí phát sinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Khoa Huy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đang theo dõi hoạt động của pin lưu trữ để đánh giá phản ánh của KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Thời tiết đang mưa, GĐKD Phụng hẹn lại lịch với Kh về đề xuất gia hạn đến 10/9 để qua nhà KH để ký BBLV
+- Do nhu cầu sử dụng của KH nhiều hơn, thời tiết HCM đang mùa mưa nên hiệu suất giảm.
+- KH muốn thay đổi làm dàn khung nên khiếu nại lên tổng đài =&gt; GĐ Phụng sẽ làm việc lại với KH phần thay đổi này.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hệ bị mất giám sát, ngày 28/8 KT qua cài lại Wifi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vũ Nguyễn Anh Tú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã xử lý xong cho khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đ/c Phát đang xử lý cho khách, hỏng CB đang báo ncc bảo hành =&gt; Chờ NCC phản hồi rồi Đề xuất gia hạn đến 31/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã giao GĐKT liên hệ hỗ trợ KH, Đã gia hạn đến 18h ngày 29/8 ( Chờ duyệt gia hạn)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- 28/8 hãng mới gửi thiết bị về đã gia hạn Ticket đến 5/9
+- Ticket bảo hành trên 15 ngày, CSKH đã yêu cầu giải trình
+- Tạo mới YCBH YCBH_CMU_1785983741402 từ B2C lúc 09:35 06/08/2026, dự kiến 28/8 thiết bị gửi về
+- Đã gửi pin lưu trữ đi bảo hành và tạo bảo hành, dự kiến 28/8 xong. Chi nhánh CMU phải lấy xe từ chi nhánh lên HCM để gửi thiết bị (không có đơn vị vận chuyển bộ lưu trữ từ CMU=&gt;HCM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lỗi inverter Unitek, phối hợp với hãng đổi hàng mới, hãng chưa xác định được thời gian sẽ gửi hàng về cho khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã liên hệ KH và thống nhất off pin 1 vài ngày theo dõi thực tế tải nhà KH đang sử dụng bao nhiêu để đánh giá lại</t>
   </si>
   <si>
     <t xml:space="preserve">Ngày</t>
@@ -1865,8 +1939,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K412" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K412"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K433" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K433"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Thời gian update"/>
     <tableColumn id="2" name="ID"/>
@@ -1885,8 +1959,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C5" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:C5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C6" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:C6"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Ngày"/>
     <tableColumn id="2" name="Tổng tồn"/>
@@ -15056,6 +15130,659 @@
         <v>46262</v>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" s="1" t="n">
+        <v>46261.7020833333</v>
+      </c>
+      <c r="B413" t="n">
+        <v>4615866</v>
+      </c>
+      <c r="C413" t="s">
+        <v>525</v>
+      </c>
+      <c r="D413" t="s">
+        <v>128</v>
+      </c>
+      <c r="E413" t="s">
+        <v>219</v>
+      </c>
+      <c r="F413" t="s">
+        <v>18</v>
+      </c>
+      <c r="G413" t="s">
+        <v>526</v>
+      </c>
+      <c r="H413" t="s">
+        <v>50</v>
+      </c>
+      <c r="I413" t="n">
+        <v>176</v>
+      </c>
+      <c r="J413"/>
+      <c r="K413" s="1"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="n">
+        <v>46261.7104166667</v>
+      </c>
+      <c r="B414" t="n">
+        <v>4615909</v>
+      </c>
+      <c r="C414" t="s">
+        <v>496</v>
+      </c>
+      <c r="D414" t="s">
+        <v>497</v>
+      </c>
+      <c r="E414" t="s">
+        <v>195</v>
+      </c>
+      <c r="F414" t="s">
+        <v>23</v>
+      </c>
+      <c r="G414" t="s">
+        <v>527</v>
+      </c>
+      <c r="H414" t="s">
+        <v>195</v>
+      </c>
+      <c r="I414" t="n">
+        <v>166</v>
+      </c>
+      <c r="J414"/>
+      <c r="K414" s="1"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="n">
+        <v>46261.7131944444</v>
+      </c>
+      <c r="B415" t="n">
+        <v>4615888</v>
+      </c>
+      <c r="C415" t="s">
+        <v>499</v>
+      </c>
+      <c r="D415" t="s">
+        <v>45</v>
+      </c>
+      <c r="E415" t="s">
+        <v>195</v>
+      </c>
+      <c r="F415" t="s">
+        <v>27</v>
+      </c>
+      <c r="G415" t="s">
+        <v>528</v>
+      </c>
+      <c r="H415" t="s">
+        <v>195</v>
+      </c>
+      <c r="I415" t="n">
+        <v>168</v>
+      </c>
+      <c r="J415"/>
+      <c r="K415" s="1"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="n">
+        <v>46261.7243055556</v>
+      </c>
+      <c r="B416" t="n">
+        <v>4615909</v>
+      </c>
+      <c r="C416" t="s">
+        <v>496</v>
+      </c>
+      <c r="D416" t="s">
+        <v>497</v>
+      </c>
+      <c r="E416" t="s">
+        <v>195</v>
+      </c>
+      <c r="F416" t="s">
+        <v>34</v>
+      </c>
+      <c r="G416" t="s">
+        <v>529</v>
+      </c>
+      <c r="H416" t="s">
+        <v>195</v>
+      </c>
+      <c r="I416" t="n">
+        <v>166</v>
+      </c>
+      <c r="J416"/>
+      <c r="K416" s="1"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="n">
+        <v>46261.7243055556</v>
+      </c>
+      <c r="B417" t="n">
+        <v>4615888</v>
+      </c>
+      <c r="C417" t="s">
+        <v>499</v>
+      </c>
+      <c r="D417" t="s">
+        <v>45</v>
+      </c>
+      <c r="E417" t="s">
+        <v>195</v>
+      </c>
+      <c r="F417" t="s">
+        <v>27</v>
+      </c>
+      <c r="G417" t="s">
+        <v>530</v>
+      </c>
+      <c r="H417" t="s">
+        <v>195</v>
+      </c>
+      <c r="I417" t="n">
+        <v>168</v>
+      </c>
+      <c r="J417"/>
+      <c r="K417" s="1"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="n">
+        <v>46261.73125</v>
+      </c>
+      <c r="B418" t="n">
+        <v>4615891</v>
+      </c>
+      <c r="C418" t="s">
+        <v>531</v>
+      </c>
+      <c r="D418" t="s">
+        <v>75</v>
+      </c>
+      <c r="E418" t="s">
+        <v>251</v>
+      </c>
+      <c r="F418" t="s">
+        <v>27</v>
+      </c>
+      <c r="G418" t="s">
+        <v>532</v>
+      </c>
+      <c r="H418" t="s">
+        <v>50</v>
+      </c>
+      <c r="I418" t="n">
+        <v>174</v>
+      </c>
+      <c r="J418"/>
+      <c r="K418" s="1"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="n">
+        <v>46261.73125</v>
+      </c>
+      <c r="B419" t="n">
+        <v>4615884</v>
+      </c>
+      <c r="C419" t="s">
+        <v>533</v>
+      </c>
+      <c r="D419" t="s">
+        <v>275</v>
+      </c>
+      <c r="E419" t="s">
+        <v>251</v>
+      </c>
+      <c r="F419" t="s">
+        <v>23</v>
+      </c>
+      <c r="G419" t="s">
+        <v>534</v>
+      </c>
+      <c r="H419" t="s">
+        <v>50</v>
+      </c>
+      <c r="I419" t="n">
+        <v>172</v>
+      </c>
+      <c r="J419"/>
+      <c r="K419" s="1"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="n">
+        <v>46261.7347222222</v>
+      </c>
+      <c r="B420" t="n">
+        <v>4615881</v>
+      </c>
+      <c r="C420" t="s">
+        <v>487</v>
+      </c>
+      <c r="D420" t="s">
+        <v>25</v>
+      </c>
+      <c r="E420" t="s">
+        <v>251</v>
+      </c>
+      <c r="F420" t="s">
+        <v>18</v>
+      </c>
+      <c r="G420" t="s">
+        <v>488</v>
+      </c>
+      <c r="H420" t="s">
+        <v>13</v>
+      </c>
+      <c r="I420" t="n">
+        <v>156</v>
+      </c>
+      <c r="J420"/>
+      <c r="K420" s="1"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="n">
+        <v>46261.7479166667</v>
+      </c>
+      <c r="B421" t="n">
+        <v>4615914</v>
+      </c>
+      <c r="C421" t="s">
+        <v>535</v>
+      </c>
+      <c r="D421" t="s">
+        <v>12</v>
+      </c>
+      <c r="E421" t="s">
+        <v>195</v>
+      </c>
+      <c r="F421" t="s">
+        <v>27</v>
+      </c>
+      <c r="G421" t="s">
+        <v>536</v>
+      </c>
+      <c r="H421" t="s">
+        <v>195</v>
+      </c>
+      <c r="I421" t="n">
+        <v>177</v>
+      </c>
+      <c r="J421"/>
+      <c r="K421" s="1"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="n">
+        <v>46261.75</v>
+      </c>
+      <c r="B422" t="n">
+        <v>4615857</v>
+      </c>
+      <c r="C422" t="s">
+        <v>456</v>
+      </c>
+      <c r="D422" t="s">
+        <v>152</v>
+      </c>
+      <c r="E422" t="s">
+        <v>219</v>
+      </c>
+      <c r="F422" t="s">
+        <v>27</v>
+      </c>
+      <c r="G422" t="s">
+        <v>537</v>
+      </c>
+      <c r="H422" t="s">
+        <v>50</v>
+      </c>
+      <c r="I422" t="n">
+        <v>148</v>
+      </c>
+      <c r="J422"/>
+      <c r="K422" s="1"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="n">
+        <v>46261.7513888889</v>
+      </c>
+      <c r="B423" t="n">
+        <v>4615779</v>
+      </c>
+      <c r="C423" t="s">
+        <v>279</v>
+      </c>
+      <c r="D423" t="s">
+        <v>21</v>
+      </c>
+      <c r="E423" t="s">
+        <v>251</v>
+      </c>
+      <c r="F423" t="s">
+        <v>23</v>
+      </c>
+      <c r="G423" t="s">
+        <v>538</v>
+      </c>
+      <c r="H423" t="s">
+        <v>16</v>
+      </c>
+      <c r="I423" t="n">
+        <v>91</v>
+      </c>
+      <c r="J423"/>
+      <c r="K423" s="1"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="n">
+        <v>46261.7527777778</v>
+      </c>
+      <c r="B424" t="n">
+        <v>4615914</v>
+      </c>
+      <c r="C424" t="s">
+        <v>535</v>
+      </c>
+      <c r="D424" t="s">
+        <v>12</v>
+      </c>
+      <c r="E424" t="s">
+        <v>195</v>
+      </c>
+      <c r="F424" t="s">
+        <v>27</v>
+      </c>
+      <c r="G424" t="s">
+        <v>536</v>
+      </c>
+      <c r="H424" t="s">
+        <v>195</v>
+      </c>
+      <c r="I424" t="n">
+        <v>177</v>
+      </c>
+      <c r="J424"/>
+      <c r="K424" s="1"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="n">
+        <v>46261.7534722222</v>
+      </c>
+      <c r="B425" t="n">
+        <v>4615888</v>
+      </c>
+      <c r="C425" t="s">
+        <v>499</v>
+      </c>
+      <c r="D425" t="s">
+        <v>45</v>
+      </c>
+      <c r="E425" t="s">
+        <v>195</v>
+      </c>
+      <c r="F425" t="s">
+        <v>14</v>
+      </c>
+      <c r="G425" t="s">
+        <v>530</v>
+      </c>
+      <c r="H425" t="s">
+        <v>195</v>
+      </c>
+      <c r="I425" t="n">
+        <v>168</v>
+      </c>
+      <c r="J425"/>
+      <c r="K425" s="1"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="n">
+        <v>46261.7541666667</v>
+      </c>
+      <c r="B426" t="n">
+        <v>4615579</v>
+      </c>
+      <c r="C426" t="s">
+        <v>156</v>
+      </c>
+      <c r="D426" t="s">
+        <v>118</v>
+      </c>
+      <c r="E426" t="s">
+        <v>195</v>
+      </c>
+      <c r="F426" t="s">
+        <v>34</v>
+      </c>
+      <c r="G426" t="s">
+        <v>470</v>
+      </c>
+      <c r="H426" t="s">
+        <v>195</v>
+      </c>
+      <c r="I426" t="n">
+        <v>34</v>
+      </c>
+      <c r="J426"/>
+      <c r="K426" s="1"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="n">
+        <v>46261.76875</v>
+      </c>
+      <c r="B427" t="n">
+        <v>4615911</v>
+      </c>
+      <c r="C427" t="s">
+        <v>539</v>
+      </c>
+      <c r="D427" t="s">
+        <v>152</v>
+      </c>
+      <c r="E427" t="s">
+        <v>219</v>
+      </c>
+      <c r="F427" t="s">
+        <v>18</v>
+      </c>
+      <c r="G427" t="s">
+        <v>540</v>
+      </c>
+      <c r="H427" t="s">
+        <v>50</v>
+      </c>
+      <c r="I427" t="n">
+        <v>173</v>
+      </c>
+      <c r="J427"/>
+      <c r="K427" s="1"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="n">
+        <v>46262.3138888889</v>
+      </c>
+      <c r="B428" t="n">
+        <v>4615863</v>
+      </c>
+      <c r="C428" t="s">
+        <v>467</v>
+      </c>
+      <c r="D428" t="s">
+        <v>72</v>
+      </c>
+      <c r="E428" t="s">
+        <v>219</v>
+      </c>
+      <c r="F428" t="s">
+        <v>19</v>
+      </c>
+      <c r="G428" t="s">
+        <v>541</v>
+      </c>
+      <c r="H428" t="s">
+        <v>50</v>
+      </c>
+      <c r="I428" t="n">
+        <v>162</v>
+      </c>
+      <c r="J428"/>
+      <c r="K428" s="1"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="n">
+        <v>46262.3277777778</v>
+      </c>
+      <c r="B429" t="n">
+        <v>4615585</v>
+      </c>
+      <c r="C429" t="s">
+        <v>79</v>
+      </c>
+      <c r="D429" t="s">
+        <v>75</v>
+      </c>
+      <c r="E429" t="s">
+        <v>251</v>
+      </c>
+      <c r="F429" t="s">
+        <v>18</v>
+      </c>
+      <c r="G429" t="s">
+        <v>454</v>
+      </c>
+      <c r="H429" t="s">
+        <v>26</v>
+      </c>
+      <c r="I429" t="n">
+        <v>32</v>
+      </c>
+      <c r="J429"/>
+      <c r="K429" s="1"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="n">
+        <v>46262.3284722222</v>
+      </c>
+      <c r="B430" t="n">
+        <v>4615890</v>
+      </c>
+      <c r="C430" t="s">
+        <v>520</v>
+      </c>
+      <c r="D430" t="s">
+        <v>123</v>
+      </c>
+      <c r="E430" t="s">
+        <v>219</v>
+      </c>
+      <c r="F430" t="s">
+        <v>27</v>
+      </c>
+      <c r="G430" t="s">
+        <v>542</v>
+      </c>
+      <c r="H430" t="s">
+        <v>50</v>
+      </c>
+      <c r="I430" t="n">
+        <v>167</v>
+      </c>
+      <c r="J430"/>
+      <c r="K430" s="1"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46262.3305555556</v>
+      </c>
+      <c r="B431" t="n">
+        <v>4615274</v>
+      </c>
+      <c r="C431" t="s">
+        <v>127</v>
+      </c>
+      <c r="D431" t="s">
+        <v>128</v>
+      </c>
+      <c r="E431" t="s">
+        <v>219</v>
+      </c>
+      <c r="F431" t="s">
+        <v>34</v>
+      </c>
+      <c r="G431" t="s">
+        <v>543</v>
+      </c>
+      <c r="H431" t="s">
+        <v>50</v>
+      </c>
+      <c r="I431" t="n">
+        <v>48</v>
+      </c>
+      <c r="J431"/>
+      <c r="K431" s="1" t="n">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46262.3381944444</v>
+      </c>
+      <c r="B432" t="n">
+        <v>4615909</v>
+      </c>
+      <c r="C432" t="s">
+        <v>496</v>
+      </c>
+      <c r="D432" t="s">
+        <v>497</v>
+      </c>
+      <c r="E432" t="s">
+        <v>195</v>
+      </c>
+      <c r="F432" t="s">
+        <v>34</v>
+      </c>
+      <c r="G432" t="s">
+        <v>544</v>
+      </c>
+      <c r="H432" t="s">
+        <v>195</v>
+      </c>
+      <c r="I432" t="n">
+        <v>166</v>
+      </c>
+      <c r="J432"/>
+      <c r="K432" s="1"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46262.3388888889</v>
+      </c>
+      <c r="B433" t="n">
+        <v>4615914</v>
+      </c>
+      <c r="C433" t="s">
+        <v>535</v>
+      </c>
+      <c r="D433" t="s">
+        <v>12</v>
+      </c>
+      <c r="E433" t="s">
+        <v>195</v>
+      </c>
+      <c r="F433" t="s">
+        <v>19</v>
+      </c>
+      <c r="G433" t="s">
+        <v>545</v>
+      </c>
+      <c r="H433" t="s">
+        <v>195</v>
+      </c>
+      <c r="I433" t="n">
+        <v>177</v>
+      </c>
+      <c r="J433"/>
+      <c r="K433" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -15072,13 +15799,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="B1" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="C1" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
     </row>
     <row r="2">
@@ -15119,10 +15846,21 @@
         <v>46261</v>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B6" t="n">
+        <v>47</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="570">
   <si>
     <t xml:space="preserve">Thời gian update</t>
   </si>
@@ -1875,6 +1875,84 @@
   </si>
   <si>
     <t xml:space="preserve">Đã liên hệ KH và thống nhất off pin 1 vài ngày theo dõi thực tế tải nhà KH đang sử dụng bao nhiêu để đánh giá lại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trần Đình Chất</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cài lại áp cho khách hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CÔNG TY TNHH ThƯƠNG MẠI DỊCH VỤ SU VI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- GĐKT liên hệ KH bận chưa hẹn được thời gian tới xử lý. Đã đóng ticket để khi nào Kh bố trí đc thời gian sẽ hỗ trợ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- đã đóng Ticket
+- Đ/c Phát đang xử lý cho khách, hỏng CB đang báo ncc bảo hành =&gt; Chờ NCC phản hồi rồi Đề xuất gia hạn đến 31/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Không liên hệ được KH =&gt; Đóng Ticket
+- Đã giao GĐKT liên hệ hỗ trợ KH, Đã gia hạn đến 18h ngày 29/8 ( Chờ duyệt gia hạn)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mất wifi thiết bị không bắt được tín hiệu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App cũ , tải mới app cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bị cháy ATS, ngày 25/8 đtac qua thay mới cho KH
+Nhà KH đang bị lụt nên ko vào thay được. Bao giờ nước rút sẽ qua thay.
+Đã xử lý hệ thống hoạt động bt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KT đang tính toán vật tư và chi phí để xử lý cho KH
+bắn và thít lại đường ống, hoàn thành</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã thống nhất với KH hẹn qua lễ xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biến tần bị lỗi, đã hết hạn bảo hành. Đang tìm nhà cung cấp để gửi sửa chữa cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Văn Phương</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cài lại app cho khách hàng. phối hợp theo dõi thêm. kh không phản ánh gì thêm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lê Thị Thanh Tâm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- NCC Bách châu hỗ trợ đổi sản phẩm khác tương đương cho khách, đã đề xuất gia hạn đến 4/9 (Chờ duyệt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Văn Sơn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KT kiểm tra qua app hệ vẫn hoạt động bt, Đã thống nhất hẹn KH qua lễ đến kiểm tra lại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hỏng ATS, hiện đang  chờ KH về, để chụp ảnh  ATS hỏng để làm việc với hãng. Dự kiến 25/08 KH mới về để tới làm việc
+Đã tạo BH, chờ hãng gửi TB về thay. ngày 28/8 Hãng đã gửi hàng.
+Dự kiến ngày 30/8 lắp lại cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thời gian hệ dùng 3 năm rồi trường hợp cháy không xác định nguyên nhân.
+Tủ điện kỹ thuật tự mua ngoài để lắp.
+Khi cháy tủ điện khách không chịu chi phí sửa chữa. 
+Hỗ trợ chi nhánh làm tờ trình xin kinh phí bảo hành.
+Anh Quân - 0363474779 DLK đang kiểm tra lại tiến độ gửi hàng đi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thời gian hệ dùng 3 năm rồi trường hợp cháy không xác định nguyên nhân.
+Tủ điện kỹ thuật tự mua ngoài để lắp.
+Khi cháy tủ điện khách không chịu chi phí sửa chữa. 
+Hỗ trợ chi nhánh làm tờ trình xin kinh phí bảo hành.
+Anh Quân - 0363474779 DLK đã nhận tủ điện, còn chờ thêm CT để lắp đặt</t>
   </si>
   <si>
     <t xml:space="preserve">Ngày</t>
@@ -1939,8 +2017,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K433" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K433"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K450" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K450"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Thời gian update"/>
     <tableColumn id="2" name="ID"/>
@@ -15783,6 +15861,533 @@
       <c r="J433"/>
       <c r="K433" s="1"/>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46262.3569444444</v>
+      </c>
+      <c r="B434" t="n">
+        <v>4615867</v>
+      </c>
+      <c r="C434" t="s">
+        <v>546</v>
+      </c>
+      <c r="D434" t="s">
+        <v>96</v>
+      </c>
+      <c r="E434" t="s">
+        <v>251</v>
+      </c>
+      <c r="F434" t="s">
+        <v>18</v>
+      </c>
+      <c r="G434" t="s">
+        <v>547</v>
+      </c>
+      <c r="H434" t="s">
+        <v>26</v>
+      </c>
+      <c r="I434" t="n">
+        <v>175</v>
+      </c>
+      <c r="J434"/>
+      <c r="K434" s="1"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46262.3708333333</v>
+      </c>
+      <c r="B435" t="n">
+        <v>4612186</v>
+      </c>
+      <c r="C435" t="s">
+        <v>119</v>
+      </c>
+      <c r="D435" t="s">
+        <v>118</v>
+      </c>
+      <c r="E435" t="s">
+        <v>195</v>
+      </c>
+      <c r="F435" t="s">
+        <v>14</v>
+      </c>
+      <c r="G435" t="s">
+        <v>469</v>
+      </c>
+      <c r="H435" t="s">
+        <v>195</v>
+      </c>
+      <c r="I435" t="n">
+        <v>61</v>
+      </c>
+      <c r="J435"/>
+      <c r="K435" s="1"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46262.3993055556</v>
+      </c>
+      <c r="B436" t="n">
+        <v>4615885</v>
+      </c>
+      <c r="C436" t="s">
+        <v>548</v>
+      </c>
+      <c r="D436" t="s">
+        <v>152</v>
+      </c>
+      <c r="E436" t="s">
+        <v>219</v>
+      </c>
+      <c r="F436" t="s">
+        <v>18</v>
+      </c>
+      <c r="G436" t="s">
+        <v>549</v>
+      </c>
+      <c r="H436" t="s">
+        <v>50</v>
+      </c>
+      <c r="I436" t="n">
+        <v>171</v>
+      </c>
+      <c r="J436"/>
+      <c r="K436" s="1"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46262.4034722222</v>
+      </c>
+      <c r="B437" t="n">
+        <v>4615863</v>
+      </c>
+      <c r="C437" t="s">
+        <v>467</v>
+      </c>
+      <c r="D437" t="s">
+        <v>72</v>
+      </c>
+      <c r="E437" t="s">
+        <v>219</v>
+      </c>
+      <c r="F437" t="s">
+        <v>18</v>
+      </c>
+      <c r="G437" t="s">
+        <v>550</v>
+      </c>
+      <c r="H437" t="s">
+        <v>50</v>
+      </c>
+      <c r="I437" t="n">
+        <v>162</v>
+      </c>
+      <c r="J437"/>
+      <c r="K437" s="1"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46262.4041666667</v>
+      </c>
+      <c r="B438" t="n">
+        <v>4615890</v>
+      </c>
+      <c r="C438" t="s">
+        <v>520</v>
+      </c>
+      <c r="D438" t="s">
+        <v>123</v>
+      </c>
+      <c r="E438" t="s">
+        <v>219</v>
+      </c>
+      <c r="F438" t="s">
+        <v>18</v>
+      </c>
+      <c r="G438" t="s">
+        <v>551</v>
+      </c>
+      <c r="H438" t="s">
+        <v>50</v>
+      </c>
+      <c r="I438" t="n">
+        <v>167</v>
+      </c>
+      <c r="J438"/>
+      <c r="K438" s="1"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46262.4173611111</v>
+      </c>
+      <c r="B439" t="n">
+        <v>4615785</v>
+      </c>
+      <c r="C439" t="s">
+        <v>297</v>
+      </c>
+      <c r="D439" t="s">
+        <v>178</v>
+      </c>
+      <c r="E439" t="s">
+        <v>251</v>
+      </c>
+      <c r="F439" t="s">
+        <v>18</v>
+      </c>
+      <c r="G439" t="s">
+        <v>552</v>
+      </c>
+      <c r="H439" t="s">
+        <v>16</v>
+      </c>
+      <c r="I439" t="n">
+        <v>103</v>
+      </c>
+      <c r="J439"/>
+      <c r="K439" s="1"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46262.4222222222</v>
+      </c>
+      <c r="B440" t="n">
+        <v>4615887</v>
+      </c>
+      <c r="C440" t="s">
+        <v>494</v>
+      </c>
+      <c r="D440" t="s">
+        <v>96</v>
+      </c>
+      <c r="E440" t="s">
+        <v>251</v>
+      </c>
+      <c r="F440" t="s">
+        <v>18</v>
+      </c>
+      <c r="G440" t="s">
+        <v>553</v>
+      </c>
+      <c r="H440" t="s">
+        <v>16</v>
+      </c>
+      <c r="I440" t="n">
+        <v>169</v>
+      </c>
+      <c r="J440"/>
+      <c r="K440" s="1"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46262.4388888889</v>
+      </c>
+      <c r="B441" t="n">
+        <v>4615786</v>
+      </c>
+      <c r="C441" t="s">
+        <v>295</v>
+      </c>
+      <c r="D441" t="s">
+        <v>65</v>
+      </c>
+      <c r="E441" t="s">
+        <v>251</v>
+      </c>
+      <c r="F441" t="s">
+        <v>18</v>
+      </c>
+      <c r="G441" t="s">
+        <v>554</v>
+      </c>
+      <c r="H441" t="s">
+        <v>16</v>
+      </c>
+      <c r="I441" t="n">
+        <v>102</v>
+      </c>
+      <c r="J441"/>
+      <c r="K441" s="1"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46262.4722222222</v>
+      </c>
+      <c r="B442" t="n">
+        <v>4615876</v>
+      </c>
+      <c r="C442" t="s">
+        <v>461</v>
+      </c>
+      <c r="D442" t="s">
+        <v>75</v>
+      </c>
+      <c r="E442" t="s">
+        <v>251</v>
+      </c>
+      <c r="F442" t="s">
+        <v>18</v>
+      </c>
+      <c r="G442" t="s">
+        <v>555</v>
+      </c>
+      <c r="H442" t="s">
+        <v>13</v>
+      </c>
+      <c r="I442" t="n">
+        <v>152</v>
+      </c>
+      <c r="J442"/>
+      <c r="K442" s="1"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46262.4826388889</v>
+      </c>
+      <c r="B443" t="n">
+        <v>4615884</v>
+      </c>
+      <c r="C443" t="s">
+        <v>533</v>
+      </c>
+      <c r="D443" t="s">
+        <v>275</v>
+      </c>
+      <c r="E443" t="s">
+        <v>251</v>
+      </c>
+      <c r="F443" t="s">
+        <v>18</v>
+      </c>
+      <c r="G443" t="s">
+        <v>556</v>
+      </c>
+      <c r="H443" t="s">
+        <v>50</v>
+      </c>
+      <c r="I443" t="n">
+        <v>172</v>
+      </c>
+      <c r="J443"/>
+      <c r="K443" s="1"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46262.4833333333</v>
+      </c>
+      <c r="B444" t="n">
+        <v>4615859</v>
+      </c>
+      <c r="C444" t="s">
+        <v>480</v>
+      </c>
+      <c r="D444" t="s">
+        <v>275</v>
+      </c>
+      <c r="E444" t="s">
+        <v>251</v>
+      </c>
+      <c r="F444" t="s">
+        <v>18</v>
+      </c>
+      <c r="G444" t="s">
+        <v>557</v>
+      </c>
+      <c r="H444" t="s">
+        <v>13</v>
+      </c>
+      <c r="I444" t="n">
+        <v>150</v>
+      </c>
+      <c r="J444"/>
+      <c r="K444" s="1"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46262.4875</v>
+      </c>
+      <c r="B445" t="n">
+        <v>4615893</v>
+      </c>
+      <c r="C445" t="s">
+        <v>558</v>
+      </c>
+      <c r="D445" t="s">
+        <v>65</v>
+      </c>
+      <c r="E445" t="s">
+        <v>251</v>
+      </c>
+      <c r="F445" t="s">
+        <v>18</v>
+      </c>
+      <c r="G445" t="s">
+        <v>559</v>
+      </c>
+      <c r="H445" t="s">
+        <v>13</v>
+      </c>
+      <c r="I445" t="n">
+        <v>179</v>
+      </c>
+      <c r="J445"/>
+      <c r="K445" s="1"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="n">
+        <v>46262.56875</v>
+      </c>
+      <c r="B446" t="n">
+        <v>4615915</v>
+      </c>
+      <c r="C446" t="s">
+        <v>560</v>
+      </c>
+      <c r="D446" t="s">
+        <v>56</v>
+      </c>
+      <c r="E446" t="s">
+        <v>219</v>
+      </c>
+      <c r="F446" t="s">
+        <v>34</v>
+      </c>
+      <c r="G446" t="s">
+        <v>561</v>
+      </c>
+      <c r="H446" t="s">
+        <v>50</v>
+      </c>
+      <c r="I446" t="n">
+        <v>181</v>
+      </c>
+      <c r="J446"/>
+      <c r="K446" s="1"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="n">
+        <v>46262.5743055556</v>
+      </c>
+      <c r="B447" t="n">
+        <v>4615913</v>
+      </c>
+      <c r="C447" t="s">
+        <v>562</v>
+      </c>
+      <c r="D447" t="s">
+        <v>53</v>
+      </c>
+      <c r="E447" t="s">
+        <v>251</v>
+      </c>
+      <c r="F447" t="s">
+        <v>27</v>
+      </c>
+      <c r="G447" t="s">
+        <v>563</v>
+      </c>
+      <c r="H447" t="s">
+        <v>13</v>
+      </c>
+      <c r="I447" t="n">
+        <v>178</v>
+      </c>
+      <c r="J447"/>
+      <c r="K447" s="1"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="n">
+        <v>46262.5791666667</v>
+      </c>
+      <c r="B448" t="n">
+        <v>4615145</v>
+      </c>
+      <c r="C448" t="s">
+        <v>87</v>
+      </c>
+      <c r="D448" t="s">
+        <v>30</v>
+      </c>
+      <c r="E448" t="s">
+        <v>251</v>
+      </c>
+      <c r="F448" t="s">
+        <v>27</v>
+      </c>
+      <c r="G448" t="s">
+        <v>564</v>
+      </c>
+      <c r="H448" t="s">
+        <v>26</v>
+      </c>
+      <c r="I448" t="n">
+        <v>50</v>
+      </c>
+      <c r="J448"/>
+      <c r="K448" s="1"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="n">
+        <v>46262.5979166667</v>
+      </c>
+      <c r="B449" t="n">
+        <v>4615579</v>
+      </c>
+      <c r="C449" t="s">
+        <v>156</v>
+      </c>
+      <c r="D449" t="s">
+        <v>118</v>
+      </c>
+      <c r="E449" t="s">
+        <v>195</v>
+      </c>
+      <c r="F449" t="s">
+        <v>34</v>
+      </c>
+      <c r="G449" t="s">
+        <v>565</v>
+      </c>
+      <c r="H449" t="s">
+        <v>195</v>
+      </c>
+      <c r="I449" t="n">
+        <v>34</v>
+      </c>
+      <c r="J449"/>
+      <c r="K449" s="1"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="n">
+        <v>46262.6076388889</v>
+      </c>
+      <c r="B450" t="n">
+        <v>4615579</v>
+      </c>
+      <c r="C450" t="s">
+        <v>156</v>
+      </c>
+      <c r="D450" t="s">
+        <v>118</v>
+      </c>
+      <c r="E450" t="s">
+        <v>195</v>
+      </c>
+      <c r="F450" t="s">
+        <v>34</v>
+      </c>
+      <c r="G450" t="s">
+        <v>566</v>
+      </c>
+      <c r="H450" t="s">
+        <v>195</v>
+      </c>
+      <c r="I450" t="n">
+        <v>34</v>
+      </c>
+      <c r="J450"/>
+      <c r="K450" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -15799,13 +16404,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="B1" t="s">
-        <v>547</v>
+        <v>568</v>
       </c>
       <c r="C1" t="s">
-        <v>548</v>
+        <v>569</v>
       </c>
     </row>
     <row r="2">
@@ -15857,7 +16462,7 @@
         <v>46262</v>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="622">
   <si>
     <t xml:space="preserve">Thời gian update</t>
   </si>
@@ -1953,6 +1953,190 @@
 Khi cháy tủ điện khách không chịu chi phí sửa chữa. 
 Hỗ trợ chi nhánh làm tờ trình xin kinh phí bảo hành.
 Anh Quân - 0363474779 DLK đã nhận tủ điện, còn chờ thêm CT để lắp đặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHI NHÁNH III - CÔNG TY TNHH VƯƠNG THUẬN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã có tấm pin bảo hành thay thế, đang yêu cầu kỹ thuật nhận pin xử lý ngay cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mai Tiến Phước</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã nhận thông tin và giao kỹ thuật xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã xử lý xong cho khách
+- FT3 đã liên hệ hẹn lại lịch với KH 17h ngày 29/8
+- Đã YC GĐKT liên hệ KH và qua kiểm tra cho khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- FT3 qua kiểm tra xử lý cho khách trước 3/9
+Ticket CN tạo CSKH chưa duyệt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- 28/8 hàng đã về, dự kiến 29/8 thay cho khách
+- Dự kiến ngày 27/8 về hàng rồi thay cho khách, xử lý xong trước 28/8
+- Hệ thống NLMT bị sét đánh trúng, hỏng 2 SPD DC + 1 ATS.
+- Đã lắp đặt hệ thống để thiết bị hoạt động không bị mất sản lượng.
+- Thiết bị nhập khẩu Trung Quốc, hiện tại không sẵn hàng.
+- Khách hàng không đồng ý đổi sang mã hàng tương đương.
+- Dự kiến 28/8 có hàng thay cho khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Tiến Ngọc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cập nhật phần mềm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CÔNG TY TNHH CHINH YẾN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lỗi app bị mất giám sát</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Công Ty Tnhh Thanh Bình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khi mất điện hoặc điện lưới yếu ATS nhảy để chuyển sang đường Backup xảy ra nháy điện. Đã giải thích với KH.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cao Văn Bình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hỏng tủ điện, đang gửi hãng BH
+Dự kiến 05/9 có hàng lắp lại cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CÔNG TY TNHH SẢN XUẤT THƯƠNG MẠI DỊCH VỤ CMF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã Giao FT3 liên hệ kiểm tra cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã gửi email xác nhận chính sách bảo hành với hãng
+Pin JA620 bị nứt
+Hãng đã gửi hướng dẫn chụp lại hư hại để xác nhận bảo hành
+Kỹ thuật hẹn sau lễ có flycam để chụp do vị trí hãng yêu cầu khó tiếp cận</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoàng Văn Công</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hỗ trợ KH cài lại app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hồ Sỹ Đệ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trần Văn Long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-đã giao Ft3 liên hệ qua kiểm tra cho khách, dự kiến mai qua kiểm tra xử lý cho khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đinh Văn Hưng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KH cần qua kiểm tra xem tiền điện bị tăng lên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trần Văn Đức</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã giao FT liên hệ đẻ qua kiểm tra cho khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lê Thế Nam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KT đang kiểm tra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Hải Thúy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã giao Ft3 dự kiến ngày mai qua hỗ trợ KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- CT mất kết nối =&gt; Đã xử lý xong và đóng Ticket
+- Đã đề xuất gia hạn đến 17h30 ngày 29/8 ( Chờ duyệt)
+- Ngày 27/8 qua kiểm tra cho khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Văn Ngon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Chuyển FT3 liên hệ qua kiểm tra cho khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- NCC Bách châu hỗ trợ đổi sản phẩm khác tương đương cho khách, đã đề xuất gia hạn đến 4/9 (Đã duyệt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã có tấm pin bảo hành thay thế ở HNI nhưng chưa chuyển về. Anh Huyhm đang yêu cầu kỹ thuật ghép xe chuyển về. Dự kiến 1/9 có hàng để lắp đặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- 28/8 KH phản ánh thêm đi dây loằng ngoằng nên CSKH trả lại Ticket =&gt; FT3 xử lý lại cho khách  
+- Đã thay xong cho khách 27/8
+- dự kiến ngày 26/8 hàng về, 27/8 thay cho khách
+hỏng metter, hiện đã chuyển về bảo hành cho hãng powrtech từ 18/08, thiết bị metter không tạo được bảo hành.  Đang chờ hàng bảo hành về để lắp cho KH, dự kiến 29/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hỗ trợ KH cài lại app
+Ngày 29/8 KT qua hỗ trợ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lỗi app bị mất giám sát
+Ngày 29/8 KT qua hỗ trợ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Đình Nguyên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thiết bị pin bị mất kết nối, pin đã kết nối trở lại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cháy ATS, đã thay cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã đóg Ticket
+- CN Đang đặng hàng mua ngoài nhưng chưa có, dự kiến 1/9 có hàng xử lý cho khách
+- HĐ đang để cọc đồng, thực tế là mạ đồng (KH check HĐ nên yêu cầu thay thế)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã đề xuất gia hạn đến 15h ngày 04/09
+- 28/8 KH phản ánh thêm đi dây loằng ngoằng nên CSKH trả lại Ticket =&gt; FT3 xử lý lại cho khách  
+- Đã thay xong cho khách 27/8
+- dự kiến ngày 26/8 hàng về, 27/8 thay cho khách
+hỏng metter, hiện đã chuyển về bảo hành cho hãng powrtech từ 18/08, thiết bị metter không tạo được bảo hành.  Đang chờ hàng bảo hành về để lắp cho KH, dự kiến 29/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã hỗ trợ xong cho KH
+- Đã giao Ft3 dự kiến ngày mai qua hỗ trợ KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cài đặt lại phần mềm cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hỗ trợ KH cài lại app
+Ngày 29/8 KT qua hỗ trợ cài lại App cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trà Văn Nhàn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tải của nhà KH cao (nhà KH kinh doanh quán cơm), KT đã đến ktra và điều chỉnh cho KH ngày 2/9. AM đã liên hệ KT đóng ticket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Thị Hoà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã xử lý cho KH ngày 31/08 (chị vợ đứng tên HĐ, đi vắng nên chưa lấy OTP đóng ticket), 03/09 KT liên hệ lấy OTP để đóng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thiết bị ATS bị hỏng, đã thay mới cho KH xong ngày 1/9</t>
   </si>
   <si>
     <t xml:space="preserve">Ngày</t>
@@ -2017,8 +2201,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K450" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K450"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K489" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K489"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Thời gian update"/>
     <tableColumn id="2" name="ID"/>
@@ -2037,8 +2221,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C6" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:C6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C7" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:C7"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Ngày"/>
     <tableColumn id="2" name="Tổng tồn"/>
@@ -16388,6 +16572,1225 @@
       <c r="J450"/>
       <c r="K450" s="1"/>
     </row>
+    <row r="451">
+      <c r="A451" s="1" t="n">
+        <v>46262.6305555556</v>
+      </c>
+      <c r="B451" t="n">
+        <v>4615925</v>
+      </c>
+      <c r="C451" t="s">
+        <v>567</v>
+      </c>
+      <c r="D451" t="s">
+        <v>497</v>
+      </c>
+      <c r="E451" t="s">
+        <v>195</v>
+      </c>
+      <c r="F451" t="s">
+        <v>39</v>
+      </c>
+      <c r="G451" t="s">
+        <v>568</v>
+      </c>
+      <c r="H451" t="s">
+        <v>195</v>
+      </c>
+      <c r="I451" t="n">
+        <v>194</v>
+      </c>
+      <c r="J451"/>
+      <c r="K451" s="1"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="n">
+        <v>46262.63125</v>
+      </c>
+      <c r="B452" t="n">
+        <v>4615927</v>
+      </c>
+      <c r="C452" t="s">
+        <v>569</v>
+      </c>
+      <c r="D452" t="s">
+        <v>12</v>
+      </c>
+      <c r="E452" t="s">
+        <v>195</v>
+      </c>
+      <c r="F452" t="s">
+        <v>23</v>
+      </c>
+      <c r="G452" t="s">
+        <v>570</v>
+      </c>
+      <c r="H452" t="s">
+        <v>195</v>
+      </c>
+      <c r="I452" t="n">
+        <v>193</v>
+      </c>
+      <c r="J452"/>
+      <c r="K452" s="1"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="n">
+        <v>46262.6326388889</v>
+      </c>
+      <c r="B453" t="n">
+        <v>4615880</v>
+      </c>
+      <c r="C453" t="s">
+        <v>473</v>
+      </c>
+      <c r="D453" t="s">
+        <v>49</v>
+      </c>
+      <c r="E453" t="s">
+        <v>219</v>
+      </c>
+      <c r="F453" t="s">
+        <v>18</v>
+      </c>
+      <c r="G453" t="s">
+        <v>571</v>
+      </c>
+      <c r="H453" t="s">
+        <v>50</v>
+      </c>
+      <c r="I453" t="n">
+        <v>157</v>
+      </c>
+      <c r="J453"/>
+      <c r="K453" s="1"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="n">
+        <v>46262.6354166667</v>
+      </c>
+      <c r="B454" t="n">
+        <v>4615882</v>
+      </c>
+      <c r="C454" t="s">
+        <v>71</v>
+      </c>
+      <c r="D454" t="s">
+        <v>72</v>
+      </c>
+      <c r="E454" t="s">
+        <v>219</v>
+      </c>
+      <c r="F454" t="s">
+        <v>27</v>
+      </c>
+      <c r="G454" t="s">
+        <v>572</v>
+      </c>
+      <c r="H454" t="s">
+        <v>50</v>
+      </c>
+      <c r="I454" t="n">
+        <v>155</v>
+      </c>
+      <c r="J454"/>
+      <c r="K454" s="1"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="n">
+        <v>46262.6375</v>
+      </c>
+      <c r="B455" t="n">
+        <v>4615669</v>
+      </c>
+      <c r="C455" t="s">
+        <v>146</v>
+      </c>
+      <c r="D455" t="s">
+        <v>123</v>
+      </c>
+      <c r="E455" t="s">
+        <v>219</v>
+      </c>
+      <c r="F455" t="s">
+        <v>34</v>
+      </c>
+      <c r="G455" t="s">
+        <v>573</v>
+      </c>
+      <c r="H455" t="s">
+        <v>50</v>
+      </c>
+      <c r="I455" t="n">
+        <v>18</v>
+      </c>
+      <c r="J455"/>
+      <c r="K455" s="1" t="n">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="n">
+        <v>46262.6597222222</v>
+      </c>
+      <c r="B456" t="n">
+        <v>4615916</v>
+      </c>
+      <c r="C456" t="s">
+        <v>574</v>
+      </c>
+      <c r="D456" t="s">
+        <v>96</v>
+      </c>
+      <c r="E456" t="s">
+        <v>251</v>
+      </c>
+      <c r="F456" t="s">
+        <v>18</v>
+      </c>
+      <c r="G456" t="s">
+        <v>575</v>
+      </c>
+      <c r="H456" t="s">
+        <v>26</v>
+      </c>
+      <c r="I456" t="n">
+        <v>180</v>
+      </c>
+      <c r="J456"/>
+      <c r="K456" s="1"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="n">
+        <v>46262.6597222222</v>
+      </c>
+      <c r="B457" t="n">
+        <v>4615898</v>
+      </c>
+      <c r="C457" t="s">
+        <v>576</v>
+      </c>
+      <c r="D457" t="s">
+        <v>96</v>
+      </c>
+      <c r="E457" t="s">
+        <v>251</v>
+      </c>
+      <c r="F457" t="s">
+        <v>27</v>
+      </c>
+      <c r="G457" t="s">
+        <v>577</v>
+      </c>
+      <c r="H457" t="s">
+        <v>26</v>
+      </c>
+      <c r="I457" t="n">
+        <v>186</v>
+      </c>
+      <c r="J457"/>
+      <c r="K457" s="1"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="n">
+        <v>46262.7131944444</v>
+      </c>
+      <c r="B458" t="n">
+        <v>4615919</v>
+      </c>
+      <c r="C458" t="s">
+        <v>578</v>
+      </c>
+      <c r="D458" t="s">
+        <v>167</v>
+      </c>
+      <c r="E458" t="s">
+        <v>251</v>
+      </c>
+      <c r="F458" t="s">
+        <v>18</v>
+      </c>
+      <c r="G458" t="s">
+        <v>579</v>
+      </c>
+      <c r="H458" t="s">
+        <v>26</v>
+      </c>
+      <c r="I458" t="n">
+        <v>189</v>
+      </c>
+      <c r="J458"/>
+      <c r="K458" s="1"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="n">
+        <v>46262.7138888889</v>
+      </c>
+      <c r="B459" t="n">
+        <v>4615922</v>
+      </c>
+      <c r="C459" t="s">
+        <v>580</v>
+      </c>
+      <c r="D459" t="s">
+        <v>96</v>
+      </c>
+      <c r="E459" t="s">
+        <v>251</v>
+      </c>
+      <c r="F459" t="s">
+        <v>19</v>
+      </c>
+      <c r="G459" t="s">
+        <v>581</v>
+      </c>
+      <c r="H459" t="s">
+        <v>26</v>
+      </c>
+      <c r="I459" t="n">
+        <v>192</v>
+      </c>
+      <c r="J459"/>
+      <c r="K459" s="1"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="n">
+        <v>46262.7229166667</v>
+      </c>
+      <c r="B460" t="n">
+        <v>4615918</v>
+      </c>
+      <c r="C460" t="s">
+        <v>582</v>
+      </c>
+      <c r="D460" t="s">
+        <v>128</v>
+      </c>
+      <c r="E460" t="s">
+        <v>219</v>
+      </c>
+      <c r="F460" t="s">
+        <v>23</v>
+      </c>
+      <c r="G460" t="s">
+        <v>583</v>
+      </c>
+      <c r="H460" t="s">
+        <v>50</v>
+      </c>
+      <c r="I460" t="n">
+        <v>183</v>
+      </c>
+      <c r="J460"/>
+      <c r="K460" s="1"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="n">
+        <v>46262.7243055556</v>
+      </c>
+      <c r="B461" t="n">
+        <v>4612186</v>
+      </c>
+      <c r="C461" t="s">
+        <v>119</v>
+      </c>
+      <c r="D461" t="s">
+        <v>118</v>
+      </c>
+      <c r="E461" t="s">
+        <v>195</v>
+      </c>
+      <c r="F461" t="s">
+        <v>14</v>
+      </c>
+      <c r="G461" t="s">
+        <v>584</v>
+      </c>
+      <c r="H461" t="s">
+        <v>195</v>
+      </c>
+      <c r="I461" t="n">
+        <v>61</v>
+      </c>
+      <c r="J461"/>
+      <c r="K461" s="1"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="n">
+        <v>46262.7243055556</v>
+      </c>
+      <c r="B462" t="n">
+        <v>4615912</v>
+      </c>
+      <c r="C462" t="s">
+        <v>585</v>
+      </c>
+      <c r="D462" t="s">
+        <v>96</v>
+      </c>
+      <c r="E462" t="s">
+        <v>251</v>
+      </c>
+      <c r="F462" t="s">
+        <v>23</v>
+      </c>
+      <c r="G462" t="s">
+        <v>586</v>
+      </c>
+      <c r="H462" t="s">
+        <v>26</v>
+      </c>
+      <c r="I462" t="n">
+        <v>195</v>
+      </c>
+      <c r="J462"/>
+      <c r="K462" s="1"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="n">
+        <v>46262.7243055556</v>
+      </c>
+      <c r="B463" t="n">
+        <v>4615892</v>
+      </c>
+      <c r="C463" t="s">
+        <v>587</v>
+      </c>
+      <c r="D463" t="s">
+        <v>96</v>
+      </c>
+      <c r="E463" t="s">
+        <v>251</v>
+      </c>
+      <c r="F463" t="s">
+        <v>23</v>
+      </c>
+      <c r="G463" t="s">
+        <v>586</v>
+      </c>
+      <c r="H463" t="s">
+        <v>26</v>
+      </c>
+      <c r="I463" t="n">
+        <v>196</v>
+      </c>
+      <c r="J463"/>
+      <c r="K463" s="1"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="n">
+        <v>46262.725</v>
+      </c>
+      <c r="B464" t="n">
+        <v>4615896</v>
+      </c>
+      <c r="C464" t="s">
+        <v>588</v>
+      </c>
+      <c r="D464" t="s">
+        <v>238</v>
+      </c>
+      <c r="E464" t="s">
+        <v>219</v>
+      </c>
+      <c r="F464" t="s">
+        <v>23</v>
+      </c>
+      <c r="G464" t="s">
+        <v>589</v>
+      </c>
+      <c r="H464" t="s">
+        <v>50</v>
+      </c>
+      <c r="I464" t="n">
+        <v>185</v>
+      </c>
+      <c r="J464"/>
+      <c r="K464" s="1"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="n">
+        <v>46262.7256944444</v>
+      </c>
+      <c r="B465" t="n">
+        <v>4615924</v>
+      </c>
+      <c r="C465" t="s">
+        <v>590</v>
+      </c>
+      <c r="D465" t="s">
+        <v>53</v>
+      </c>
+      <c r="E465" t="s">
+        <v>251</v>
+      </c>
+      <c r="F465" t="s">
+        <v>23</v>
+      </c>
+      <c r="G465" t="s">
+        <v>591</v>
+      </c>
+      <c r="H465" t="s">
+        <v>26</v>
+      </c>
+      <c r="I465" t="n">
+        <v>190</v>
+      </c>
+      <c r="J465"/>
+      <c r="K465" s="1"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="n">
+        <v>46262.7263888889</v>
+      </c>
+      <c r="B466" t="n">
+        <v>4615920</v>
+      </c>
+      <c r="C466" t="s">
+        <v>592</v>
+      </c>
+      <c r="D466" t="s">
+        <v>152</v>
+      </c>
+      <c r="E466" t="s">
+        <v>219</v>
+      </c>
+      <c r="F466" t="s">
+        <v>27</v>
+      </c>
+      <c r="G466" t="s">
+        <v>593</v>
+      </c>
+      <c r="H466" t="s">
+        <v>50</v>
+      </c>
+      <c r="I466" t="n">
+        <v>188</v>
+      </c>
+      <c r="J466"/>
+      <c r="K466" s="1"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="n">
+        <v>46262.7270833333</v>
+      </c>
+      <c r="B467" t="n">
+        <v>4615897</v>
+      </c>
+      <c r="C467" t="s">
+        <v>594</v>
+      </c>
+      <c r="D467" t="s">
+        <v>75</v>
+      </c>
+      <c r="E467" t="s">
+        <v>251</v>
+      </c>
+      <c r="F467" t="s">
+        <v>19</v>
+      </c>
+      <c r="G467" t="s">
+        <v>595</v>
+      </c>
+      <c r="H467" t="s">
+        <v>26</v>
+      </c>
+      <c r="I467" t="n">
+        <v>187</v>
+      </c>
+      <c r="J467"/>
+      <c r="K467" s="1"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="n">
+        <v>46262.7340277778</v>
+      </c>
+      <c r="B468" t="n">
+        <v>4615923</v>
+      </c>
+      <c r="C468" t="s">
+        <v>596</v>
+      </c>
+      <c r="D468" t="s">
+        <v>152</v>
+      </c>
+      <c r="E468" t="s">
+        <v>219</v>
+      </c>
+      <c r="F468" t="s">
+        <v>23</v>
+      </c>
+      <c r="G468" t="s">
+        <v>597</v>
+      </c>
+      <c r="H468" t="s">
+        <v>50</v>
+      </c>
+      <c r="I468" t="n">
+        <v>191</v>
+      </c>
+      <c r="J468"/>
+      <c r="K468" s="1"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="n">
+        <v>46262.7381944444</v>
+      </c>
+      <c r="B469" t="n">
+        <v>4615826</v>
+      </c>
+      <c r="C469" t="s">
+        <v>375</v>
+      </c>
+      <c r="D469" t="s">
+        <v>72</v>
+      </c>
+      <c r="E469" t="s">
+        <v>219</v>
+      </c>
+      <c r="F469" t="s">
+        <v>18</v>
+      </c>
+      <c r="G469" t="s">
+        <v>598</v>
+      </c>
+      <c r="H469" t="s">
+        <v>50</v>
+      </c>
+      <c r="I469" t="n">
+        <v>131</v>
+      </c>
+      <c r="J469"/>
+      <c r="K469" s="1"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="n">
+        <v>46262.7381944444</v>
+      </c>
+      <c r="B470" t="n">
+        <v>4615926</v>
+      </c>
+      <c r="C470" t="s">
+        <v>599</v>
+      </c>
+      <c r="D470" t="s">
+        <v>128</v>
+      </c>
+      <c r="E470" t="s">
+        <v>219</v>
+      </c>
+      <c r="F470" t="s">
+        <v>23</v>
+      </c>
+      <c r="G470" t="s">
+        <v>600</v>
+      </c>
+      <c r="H470" t="s">
+        <v>50</v>
+      </c>
+      <c r="I470" t="n">
+        <v>197</v>
+      </c>
+      <c r="J470"/>
+      <c r="K470" s="1"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="n">
+        <v>46262.7395833333</v>
+      </c>
+      <c r="B471" t="n">
+        <v>4615915</v>
+      </c>
+      <c r="C471" t="s">
+        <v>560</v>
+      </c>
+      <c r="D471" t="s">
+        <v>56</v>
+      </c>
+      <c r="E471" t="s">
+        <v>219</v>
+      </c>
+      <c r="F471" t="s">
+        <v>34</v>
+      </c>
+      <c r="G471" t="s">
+        <v>601</v>
+      </c>
+      <c r="H471" t="s">
+        <v>50</v>
+      </c>
+      <c r="I471" t="n">
+        <v>181</v>
+      </c>
+      <c r="J471"/>
+      <c r="K471" s="1"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="n">
+        <v>46262.7451388889</v>
+      </c>
+      <c r="B472" t="n">
+        <v>4615925</v>
+      </c>
+      <c r="C472" t="s">
+        <v>567</v>
+      </c>
+      <c r="D472" t="s">
+        <v>497</v>
+      </c>
+      <c r="E472" t="s">
+        <v>195</v>
+      </c>
+      <c r="F472" t="s">
+        <v>39</v>
+      </c>
+      <c r="G472" t="s">
+        <v>602</v>
+      </c>
+      <c r="H472" t="s">
+        <v>195</v>
+      </c>
+      <c r="I472" t="n">
+        <v>194</v>
+      </c>
+      <c r="J472"/>
+      <c r="K472" s="1" t="n">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="n">
+        <v>46262.7472222222</v>
+      </c>
+      <c r="B473" t="n">
+        <v>4615553</v>
+      </c>
+      <c r="C473" t="s">
+        <v>71</v>
+      </c>
+      <c r="D473" t="s">
+        <v>72</v>
+      </c>
+      <c r="E473" t="s">
+        <v>219</v>
+      </c>
+      <c r="F473" t="s">
+        <v>19</v>
+      </c>
+      <c r="G473" t="s">
+        <v>603</v>
+      </c>
+      <c r="H473" t="s">
+        <v>26</v>
+      </c>
+      <c r="I473" t="n">
+        <v>35</v>
+      </c>
+      <c r="J473"/>
+      <c r="K473" s="1" t="n">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="n">
+        <v>46262.7770833333</v>
+      </c>
+      <c r="B474" t="n">
+        <v>4615912</v>
+      </c>
+      <c r="C474" t="s">
+        <v>585</v>
+      </c>
+      <c r="D474" t="s">
+        <v>96</v>
+      </c>
+      <c r="E474" t="s">
+        <v>251</v>
+      </c>
+      <c r="F474" t="s">
+        <v>23</v>
+      </c>
+      <c r="G474" t="s">
+        <v>604</v>
+      </c>
+      <c r="H474" t="s">
+        <v>26</v>
+      </c>
+      <c r="I474" t="n">
+        <v>195</v>
+      </c>
+      <c r="J474"/>
+      <c r="K474" s="1"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="n">
+        <v>46262.7770833333</v>
+      </c>
+      <c r="B475" t="n">
+        <v>4615892</v>
+      </c>
+      <c r="C475" t="s">
+        <v>587</v>
+      </c>
+      <c r="D475" t="s">
+        <v>96</v>
+      </c>
+      <c r="E475" t="s">
+        <v>251</v>
+      </c>
+      <c r="F475" t="s">
+        <v>23</v>
+      </c>
+      <c r="G475" t="s">
+        <v>604</v>
+      </c>
+      <c r="H475" t="s">
+        <v>26</v>
+      </c>
+      <c r="I475" t="n">
+        <v>196</v>
+      </c>
+      <c r="J475"/>
+      <c r="K475" s="1"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="n">
+        <v>46262.7770833333</v>
+      </c>
+      <c r="B476" t="n">
+        <v>4615898</v>
+      </c>
+      <c r="C476" t="s">
+        <v>576</v>
+      </c>
+      <c r="D476" t="s">
+        <v>96</v>
+      </c>
+      <c r="E476" t="s">
+        <v>251</v>
+      </c>
+      <c r="F476" t="s">
+        <v>27</v>
+      </c>
+      <c r="G476" t="s">
+        <v>605</v>
+      </c>
+      <c r="H476" t="s">
+        <v>26</v>
+      </c>
+      <c r="I476" t="n">
+        <v>186</v>
+      </c>
+      <c r="J476"/>
+      <c r="K476" s="1"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="n">
+        <v>46262.7791666667</v>
+      </c>
+      <c r="B477" t="n">
+        <v>4615917</v>
+      </c>
+      <c r="C477" t="s">
+        <v>606</v>
+      </c>
+      <c r="D477" t="s">
+        <v>65</v>
+      </c>
+      <c r="E477" t="s">
+        <v>251</v>
+      </c>
+      <c r="F477" t="s">
+        <v>18</v>
+      </c>
+      <c r="G477" t="s">
+        <v>607</v>
+      </c>
+      <c r="H477" t="s">
+        <v>26</v>
+      </c>
+      <c r="I477" t="n">
+        <v>184</v>
+      </c>
+      <c r="J477"/>
+      <c r="K477" s="1"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="n">
+        <v>46263.4513888889</v>
+      </c>
+      <c r="B478" t="n">
+        <v>4615897</v>
+      </c>
+      <c r="C478" t="s">
+        <v>594</v>
+      </c>
+      <c r="D478" t="s">
+        <v>75</v>
+      </c>
+      <c r="E478" t="s">
+        <v>251</v>
+      </c>
+      <c r="F478" t="s">
+        <v>18</v>
+      </c>
+      <c r="G478" t="s">
+        <v>608</v>
+      </c>
+      <c r="H478" t="s">
+        <v>26</v>
+      </c>
+      <c r="I478" t="n">
+        <v>187</v>
+      </c>
+      <c r="J478"/>
+      <c r="K478" s="1"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="n">
+        <v>46263.6645833333</v>
+      </c>
+      <c r="B479" t="n">
+        <v>4615669</v>
+      </c>
+      <c r="C479" t="s">
+        <v>146</v>
+      </c>
+      <c r="D479" t="s">
+        <v>123</v>
+      </c>
+      <c r="E479" t="s">
+        <v>219</v>
+      </c>
+      <c r="F479" t="s">
+        <v>18</v>
+      </c>
+      <c r="G479" t="s">
+        <v>573</v>
+      </c>
+      <c r="H479" t="s">
+        <v>50</v>
+      </c>
+      <c r="I479" t="n">
+        <v>18</v>
+      </c>
+      <c r="J479"/>
+      <c r="K479" s="1" t="n">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="n">
+        <v>46263.6652777778</v>
+      </c>
+      <c r="B480" t="n">
+        <v>4615646</v>
+      </c>
+      <c r="C480" t="s">
+        <v>55</v>
+      </c>
+      <c r="D480" t="s">
+        <v>56</v>
+      </c>
+      <c r="E480" t="s">
+        <v>219</v>
+      </c>
+      <c r="F480" t="s">
+        <v>18</v>
+      </c>
+      <c r="G480" t="s">
+        <v>609</v>
+      </c>
+      <c r="H480" t="s">
+        <v>50</v>
+      </c>
+      <c r="I480" t="n">
+        <v>23</v>
+      </c>
+      <c r="J480"/>
+      <c r="K480" s="1"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="n">
+        <v>46263.6659722222</v>
+      </c>
+      <c r="B481" t="n">
+        <v>4615553</v>
+      </c>
+      <c r="C481" t="s">
+        <v>71</v>
+      </c>
+      <c r="D481" t="s">
+        <v>72</v>
+      </c>
+      <c r="E481" t="s">
+        <v>219</v>
+      </c>
+      <c r="F481" t="s">
+        <v>19</v>
+      </c>
+      <c r="G481" t="s">
+        <v>610</v>
+      </c>
+      <c r="H481" t="s">
+        <v>26</v>
+      </c>
+      <c r="I481" t="n">
+        <v>35</v>
+      </c>
+      <c r="J481"/>
+      <c r="K481" s="1" t="n">
+        <v>46263</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="n">
+        <v>46263.6666666667</v>
+      </c>
+      <c r="B482" t="n">
+        <v>4615923</v>
+      </c>
+      <c r="C482" t="s">
+        <v>596</v>
+      </c>
+      <c r="D482" t="s">
+        <v>152</v>
+      </c>
+      <c r="E482" t="s">
+        <v>219</v>
+      </c>
+      <c r="F482" t="s">
+        <v>18</v>
+      </c>
+      <c r="G482" t="s">
+        <v>611</v>
+      </c>
+      <c r="H482" t="s">
+        <v>50</v>
+      </c>
+      <c r="I482" t="n">
+        <v>191</v>
+      </c>
+      <c r="J482"/>
+      <c r="K482" s="1"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="n">
+        <v>46267.7034722222</v>
+      </c>
+      <c r="B483" t="n">
+        <v>4615927</v>
+      </c>
+      <c r="C483" t="s">
+        <v>569</v>
+      </c>
+      <c r="D483" t="s">
+        <v>12</v>
+      </c>
+      <c r="E483" t="s">
+        <v>195</v>
+      </c>
+      <c r="F483" t="s">
+        <v>18</v>
+      </c>
+      <c r="G483" t="s">
+        <v>612</v>
+      </c>
+      <c r="H483" t="s">
+        <v>195</v>
+      </c>
+      <c r="I483" t="n">
+        <v>193</v>
+      </c>
+      <c r="J483"/>
+      <c r="K483" s="1"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="n">
+        <v>46268.3451388889</v>
+      </c>
+      <c r="B484" t="n">
+        <v>4615892</v>
+      </c>
+      <c r="C484" t="s">
+        <v>587</v>
+      </c>
+      <c r="D484" t="s">
+        <v>96</v>
+      </c>
+      <c r="E484" t="s">
+        <v>251</v>
+      </c>
+      <c r="F484" t="s">
+        <v>18</v>
+      </c>
+      <c r="G484" t="s">
+        <v>613</v>
+      </c>
+      <c r="H484" t="s">
+        <v>26</v>
+      </c>
+      <c r="I484" t="n">
+        <v>196</v>
+      </c>
+      <c r="J484"/>
+      <c r="K484" s="1"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="n">
+        <v>46268.3458333333</v>
+      </c>
+      <c r="B485" t="n">
+        <v>4615912</v>
+      </c>
+      <c r="C485" t="s">
+        <v>585</v>
+      </c>
+      <c r="D485" t="s">
+        <v>96</v>
+      </c>
+      <c r="E485" t="s">
+        <v>251</v>
+      </c>
+      <c r="F485" t="s">
+        <v>27</v>
+      </c>
+      <c r="G485" t="s">
+        <v>604</v>
+      </c>
+      <c r="H485" t="s">
+        <v>26</v>
+      </c>
+      <c r="I485" t="n">
+        <v>195</v>
+      </c>
+      <c r="J485"/>
+      <c r="K485" s="1"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="n">
+        <v>46268.3555555556</v>
+      </c>
+      <c r="B486" t="n">
+        <v>4615995</v>
+      </c>
+      <c r="C486" t="s">
+        <v>614</v>
+      </c>
+      <c r="D486" t="s">
+        <v>42</v>
+      </c>
+      <c r="E486" t="s">
+        <v>219</v>
+      </c>
+      <c r="F486" t="s">
+        <v>18</v>
+      </c>
+      <c r="G486" t="s">
+        <v>615</v>
+      </c>
+      <c r="H486" t="s">
+        <v>50</v>
+      </c>
+      <c r="I486" t="n">
+        <v>209</v>
+      </c>
+      <c r="J486"/>
+      <c r="K486" s="1"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="n">
+        <v>46268.3597222222</v>
+      </c>
+      <c r="B487" t="n">
+        <v>4615954</v>
+      </c>
+      <c r="C487" t="s">
+        <v>616</v>
+      </c>
+      <c r="D487" t="s">
+        <v>178</v>
+      </c>
+      <c r="E487" t="s">
+        <v>251</v>
+      </c>
+      <c r="F487" t="s">
+        <v>18</v>
+      </c>
+      <c r="G487" t="s">
+        <v>617</v>
+      </c>
+      <c r="H487" t="s">
+        <v>50</v>
+      </c>
+      <c r="I487" t="n">
+        <v>232</v>
+      </c>
+      <c r="J487"/>
+      <c r="K487" s="1"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="n">
+        <v>46268.3618055556</v>
+      </c>
+      <c r="B488" t="n">
+        <v>4615912</v>
+      </c>
+      <c r="C488" t="s">
+        <v>585</v>
+      </c>
+      <c r="D488" t="s">
+        <v>96</v>
+      </c>
+      <c r="E488" t="s">
+        <v>251</v>
+      </c>
+      <c r="F488" t="s">
+        <v>18</v>
+      </c>
+      <c r="G488" t="s">
+        <v>613</v>
+      </c>
+      <c r="H488" t="s">
+        <v>26</v>
+      </c>
+      <c r="I488" t="n">
+        <v>195</v>
+      </c>
+      <c r="J488"/>
+      <c r="K488" s="1"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="n">
+        <v>46268.3652777778</v>
+      </c>
+      <c r="B489" t="n">
+        <v>4615853</v>
+      </c>
+      <c r="C489" t="s">
+        <v>160</v>
+      </c>
+      <c r="D489" t="s">
+        <v>56</v>
+      </c>
+      <c r="E489" t="s">
+        <v>219</v>
+      </c>
+      <c r="F489" t="s">
+        <v>18</v>
+      </c>
+      <c r="G489" t="s">
+        <v>618</v>
+      </c>
+      <c r="H489" t="s">
+        <v>195</v>
+      </c>
+      <c r="I489" t="n">
+        <v>139</v>
+      </c>
+      <c r="J489"/>
+      <c r="K489" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -16404,13 +17807,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>567</v>
+        <v>619</v>
       </c>
       <c r="B1" t="s">
-        <v>568</v>
+        <v>620</v>
       </c>
       <c r="C1" t="s">
-        <v>569</v>
+        <v>621</v>
       </c>
     </row>
     <row r="2">
@@ -16466,6 +17869,17 @@
       </c>
       <c r="C6" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B7" t="n">
+        <v>84</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="632">
   <si>
     <t xml:space="preserve">Thời gian update</t>
   </si>
@@ -2137,6 +2137,40 @@
   </si>
   <si>
     <t xml:space="preserve">Thiết bị ATS bị hỏng, đã thay mới cho KH xong ngày 1/9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CÔNG TY TNHH MỘT THÀNH VIÊN PHƯƠNG MAI ĐẮK NÔNG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qua kiểm tra báo rồi, hệ lớn. Kiểm tra phức tạp, muốn kiểm tra thì cần 2-3 người, CNCT không đủ người. Thuê ngoài tốn chi phí, KH không muốn. 
+KH lắp thêm 1 hệ bên khác, xong nhờ bên đó kiểm tra rồi bảo bên mình về. Nhưng bên khác không bảo hành nên KH quay sang nhờ bên mình kiểm tra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã Giao FT3 liên hệ kiểm tra cho KH. Trời mưa nên xin gia hạn thời gian thực hiện PAKH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Toàn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã hoàn thành YCTX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thời gian hệ dùng 3 năm rồi trường hợp cháy không xác định nguyên nhân.
+Tủ điện kỹ thuật tự mua ngoài để lắp.
+Khi cháy tủ điện khách không chịu chi phí sửa chữa. 
+Anh Quân - 0363474779 DLK đã nhận tủ điện, bàn giao cho anh Bộ lắp đặt cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lê Đức Trung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tủ điện dùng CB 32. KH dùng quá tải khiến nhảy CB hỏng --&gt; Mua CB về thay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đỗ Thanh Hiền</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đang ở nhà KH xử lý</t>
   </si>
   <si>
     <t xml:space="preserve">Ngày</t>
@@ -2201,8 +2235,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K489" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K489"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K495" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K495"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Thời gian update"/>
     <tableColumn id="2" name="ID"/>
@@ -17791,6 +17825,192 @@
       <c r="J489"/>
       <c r="K489" s="1"/>
     </row>
+    <row r="490">
+      <c r="A490" s="1" t="n">
+        <v>46268.3784722222</v>
+      </c>
+      <c r="B490" t="n">
+        <v>4615958</v>
+      </c>
+      <c r="C490" t="s">
+        <v>619</v>
+      </c>
+      <c r="D490" t="s">
+        <v>49</v>
+      </c>
+      <c r="E490" t="s">
+        <v>219</v>
+      </c>
+      <c r="F490" t="s">
+        <v>27</v>
+      </c>
+      <c r="G490" t="s">
+        <v>620</v>
+      </c>
+      <c r="H490" t="s">
+        <v>195</v>
+      </c>
+      <c r="I490" t="n">
+        <v>230</v>
+      </c>
+      <c r="J490"/>
+      <c r="K490" s="1"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="n">
+        <v>46268.3895833333</v>
+      </c>
+      <c r="B491" t="n">
+        <v>4615918</v>
+      </c>
+      <c r="C491" t="s">
+        <v>582</v>
+      </c>
+      <c r="D491" t="s">
+        <v>128</v>
+      </c>
+      <c r="E491" t="s">
+        <v>219</v>
+      </c>
+      <c r="F491" t="s">
+        <v>27</v>
+      </c>
+      <c r="G491" t="s">
+        <v>621</v>
+      </c>
+      <c r="H491" t="s">
+        <v>195</v>
+      </c>
+      <c r="I491" t="n">
+        <v>183</v>
+      </c>
+      <c r="J491"/>
+      <c r="K491" s="1"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="n">
+        <v>46268.3902777778</v>
+      </c>
+      <c r="B492" t="n">
+        <v>4615900</v>
+      </c>
+      <c r="C492" t="s">
+        <v>622</v>
+      </c>
+      <c r="D492" t="s">
+        <v>128</v>
+      </c>
+      <c r="E492" t="s">
+        <v>219</v>
+      </c>
+      <c r="F492" t="s">
+        <v>18</v>
+      </c>
+      <c r="G492" t="s">
+        <v>623</v>
+      </c>
+      <c r="H492" t="s">
+        <v>195</v>
+      </c>
+      <c r="I492" t="n">
+        <v>199</v>
+      </c>
+      <c r="J492"/>
+      <c r="K492" s="1"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="n">
+        <v>46268.3951388889</v>
+      </c>
+      <c r="B493" t="n">
+        <v>4615579</v>
+      </c>
+      <c r="C493" t="s">
+        <v>156</v>
+      </c>
+      <c r="D493" t="s">
+        <v>118</v>
+      </c>
+      <c r="E493" t="s">
+        <v>195</v>
+      </c>
+      <c r="F493" t="s">
+        <v>39</v>
+      </c>
+      <c r="G493" t="s">
+        <v>624</v>
+      </c>
+      <c r="H493" t="s">
+        <v>195</v>
+      </c>
+      <c r="I493" t="n">
+        <v>34</v>
+      </c>
+      <c r="J493"/>
+      <c r="K493" s="1"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="n">
+        <v>46268.4048611111</v>
+      </c>
+      <c r="B494" t="n">
+        <v>4615957</v>
+      </c>
+      <c r="C494" t="s">
+        <v>625</v>
+      </c>
+      <c r="D494" t="s">
+        <v>49</v>
+      </c>
+      <c r="E494" t="s">
+        <v>219</v>
+      </c>
+      <c r="F494" t="s">
+        <v>23</v>
+      </c>
+      <c r="G494" t="s">
+        <v>626</v>
+      </c>
+      <c r="H494" t="s">
+        <v>195</v>
+      </c>
+      <c r="I494" t="n">
+        <v>231</v>
+      </c>
+      <c r="J494"/>
+      <c r="K494" s="1"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="n">
+        <v>46268.4048611111</v>
+      </c>
+      <c r="B495" t="n">
+        <v>4615932</v>
+      </c>
+      <c r="C495" t="s">
+        <v>627</v>
+      </c>
+      <c r="D495" t="s">
+        <v>49</v>
+      </c>
+      <c r="E495" t="s">
+        <v>219</v>
+      </c>
+      <c r="F495" t="s">
+        <v>19</v>
+      </c>
+      <c r="G495" t="s">
+        <v>628</v>
+      </c>
+      <c r="H495" t="s">
+        <v>195</v>
+      </c>
+      <c r="I495" t="n">
+        <v>246</v>
+      </c>
+      <c r="J495"/>
+      <c r="K495" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -17807,13 +18027,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="B1" t="s">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="C1" t="s">
-        <v>621</v>
+        <v>631</v>
       </c>
     </row>
     <row r="2">

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="652">
   <si>
     <t xml:space="preserve">Thời gian update</t>
   </si>
@@ -2171,6 +2171,70 @@
   </si>
   <si>
     <t xml:space="preserve">Đang ở nhà KH xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dangph11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Mạnh Đằng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thaoltt16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cầu dao điện nhà KH bị lỗi, FT đã xử lý xong. Ticket giao về TP nên FT chưa đóng được, AM đã báo chuyển ticket về FT để đóng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huỳnh Văn Lạc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chungdd2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã liên hệ tư vấn cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Datnt547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thiết bị chưa về, gia hạn Ticket đến 17h55 ngày 06/09
+GĐKT gửi IVT về CN, nhưng hôm nay Cn mới gửi hàng về cho đối tác DAT =&gt; chờ bên DAT nhận hàng kiểm tra để báo lại thời gian gia hạn với khách
+- Đã gửi thiết bị bảo hành ngày 10/08, dự kiến ngày 28/08 có thiết bị bảo hành. (Tạo mới YCBH YCBH_DNI_1786939964679 từ B2C lúc 11:12 17/08/2026)
+- Ngày 01/09 hoàn thành công tác lắp đặt và chạy thử cho khách hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trần Văn Trung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã giao cho FT xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Quốc Anh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trần Văn Thanh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Võ Hồng Nam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thái Thanh Sơn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã giao FT xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã giao FT xử lý. KH mới xây nhà xong có thay đổi thiết kế so với ban đầu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đặng Quốc Bảo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đang đến nhà KH kiểm tra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hệ lớn, kiểm tra phức tạp, muốn kiểm tra thì cần 2-3 người, CNCT không đủ người. Thuê ngoài tốn chi phí, KH không muốn. 
+KH lắp thêm 1 hệ bên khác, xong nhờ bên đó kiểm tra rồi bảo bên mình về. Nhưng bên khác không bảo hành nên KH quay sang nhờ bên mình kiểm tra</t>
   </si>
   <si>
     <t xml:space="preserve">Ngày</t>
@@ -2235,8 +2299,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K495" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K495"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K509" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K509"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Thời gian update"/>
     <tableColumn id="2" name="ID"/>
@@ -18011,6 +18075,436 @@
       <c r="J495"/>
       <c r="K495" s="1"/>
     </row>
+    <row r="496">
+      <c r="A496" s="1" t="n">
+        <v>46268.4111111111</v>
+      </c>
+      <c r="B496" t="n">
+        <v>4615957</v>
+      </c>
+      <c r="C496" t="s">
+        <v>625</v>
+      </c>
+      <c r="D496" t="s">
+        <v>49</v>
+      </c>
+      <c r="E496" t="s">
+        <v>629</v>
+      </c>
+      <c r="F496" t="s">
+        <v>27</v>
+      </c>
+      <c r="G496" t="s">
+        <v>626</v>
+      </c>
+      <c r="H496" t="s">
+        <v>195</v>
+      </c>
+      <c r="I496" t="n">
+        <v>55</v>
+      </c>
+      <c r="J496"/>
+      <c r="K496" s="1"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="n">
+        <v>46268.4145833333</v>
+      </c>
+      <c r="B497" t="n">
+        <v>4615988</v>
+      </c>
+      <c r="C497" t="s">
+        <v>630</v>
+      </c>
+      <c r="D497" t="s">
+        <v>178</v>
+      </c>
+      <c r="E497" t="s">
+        <v>631</v>
+      </c>
+      <c r="F497" t="s">
+        <v>18</v>
+      </c>
+      <c r="G497" t="s">
+        <v>632</v>
+      </c>
+      <c r="H497" t="s">
+        <v>50</v>
+      </c>
+      <c r="I497" t="n">
+        <v>41</v>
+      </c>
+      <c r="J497"/>
+      <c r="K497" s="1"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="n">
+        <v>46268.4145833333</v>
+      </c>
+      <c r="B498" t="n">
+        <v>4615907</v>
+      </c>
+      <c r="C498" t="s">
+        <v>633</v>
+      </c>
+      <c r="D498" t="s">
+        <v>45</v>
+      </c>
+      <c r="E498" t="s">
+        <v>634</v>
+      </c>
+      <c r="F498" t="s">
+        <v>27</v>
+      </c>
+      <c r="G498" t="s">
+        <v>635</v>
+      </c>
+      <c r="H498" t="s">
+        <v>26</v>
+      </c>
+      <c r="I498" t="n">
+        <v>72</v>
+      </c>
+      <c r="J498"/>
+      <c r="K498" s="1"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="n">
+        <v>46268.4215277778</v>
+      </c>
+      <c r="B499" t="n">
+        <v>4614161</v>
+      </c>
+      <c r="C499" t="s">
+        <v>144</v>
+      </c>
+      <c r="D499" t="s">
+        <v>123</v>
+      </c>
+      <c r="E499" t="s">
+        <v>636</v>
+      </c>
+      <c r="F499" t="s">
+        <v>14</v>
+      </c>
+      <c r="G499" t="s">
+        <v>637</v>
+      </c>
+      <c r="H499" t="s">
+        <v>50</v>
+      </c>
+      <c r="I499" t="n">
+        <v>10</v>
+      </c>
+      <c r="J499"/>
+      <c r="K499" s="1" t="n">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="n">
+        <v>46268.4243055556</v>
+      </c>
+      <c r="B500" t="n">
+        <v>4616004</v>
+      </c>
+      <c r="C500" t="s">
+        <v>638</v>
+      </c>
+      <c r="D500" t="s">
+        <v>96</v>
+      </c>
+      <c r="E500" t="s">
+        <v>634</v>
+      </c>
+      <c r="F500" t="s">
+        <v>23</v>
+      </c>
+      <c r="G500" t="s">
+        <v>639</v>
+      </c>
+      <c r="H500" t="s">
+        <v>26</v>
+      </c>
+      <c r="I500" t="n">
+        <v>76</v>
+      </c>
+      <c r="J500"/>
+      <c r="K500" s="1"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="n">
+        <v>46268.4243055556</v>
+      </c>
+      <c r="B501" t="n">
+        <v>4616004</v>
+      </c>
+      <c r="C501" t="s">
+        <v>638</v>
+      </c>
+      <c r="D501" t="s">
+        <v>96</v>
+      </c>
+      <c r="E501" t="s">
+        <v>634</v>
+      </c>
+      <c r="F501" t="s">
+        <v>23</v>
+      </c>
+      <c r="G501" t="s">
+        <v>639</v>
+      </c>
+      <c r="H501" t="s">
+        <v>26</v>
+      </c>
+      <c r="I501" t="n">
+        <v>76</v>
+      </c>
+      <c r="J501"/>
+      <c r="K501" s="1"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="n">
+        <v>46268.425</v>
+      </c>
+      <c r="B502" t="n">
+        <v>4615960</v>
+      </c>
+      <c r="C502" t="s">
+        <v>640</v>
+      </c>
+      <c r="D502" t="s">
+        <v>96</v>
+      </c>
+      <c r="E502" t="s">
+        <v>634</v>
+      </c>
+      <c r="F502" t="s">
+        <v>27</v>
+      </c>
+      <c r="G502"/>
+      <c r="H502" t="s">
+        <v>26</v>
+      </c>
+      <c r="I502" t="n">
+        <v>53</v>
+      </c>
+      <c r="J502"/>
+      <c r="K502" s="1"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="n">
+        <v>46268.425</v>
+      </c>
+      <c r="B503" t="n">
+        <v>4615952</v>
+      </c>
+      <c r="C503" t="s">
+        <v>641</v>
+      </c>
+      <c r="D503" t="s">
+        <v>96</v>
+      </c>
+      <c r="E503" t="s">
+        <v>634</v>
+      </c>
+      <c r="F503" t="s">
+        <v>19</v>
+      </c>
+      <c r="G503"/>
+      <c r="H503" t="s">
+        <v>26</v>
+      </c>
+      <c r="I503" t="n">
+        <v>58</v>
+      </c>
+      <c r="J503"/>
+      <c r="K503" s="1"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="n">
+        <v>46268.425</v>
+      </c>
+      <c r="B504" t="n">
+        <v>4615907</v>
+      </c>
+      <c r="C504" t="s">
+        <v>633</v>
+      </c>
+      <c r="D504" t="s">
+        <v>45</v>
+      </c>
+      <c r="E504" t="s">
+        <v>634</v>
+      </c>
+      <c r="F504" t="s">
+        <v>18</v>
+      </c>
+      <c r="G504" t="s">
+        <v>635</v>
+      </c>
+      <c r="H504" t="s">
+        <v>26</v>
+      </c>
+      <c r="I504" t="n">
+        <v>72</v>
+      </c>
+      <c r="J504"/>
+      <c r="K504" s="1"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="n">
+        <v>46268.4256944444</v>
+      </c>
+      <c r="B505" t="n">
+        <v>4615902</v>
+      </c>
+      <c r="C505" t="s">
+        <v>642</v>
+      </c>
+      <c r="D505" t="s">
+        <v>96</v>
+      </c>
+      <c r="E505" t="s">
+        <v>634</v>
+      </c>
+      <c r="F505" t="s">
+        <v>27</v>
+      </c>
+      <c r="G505"/>
+      <c r="H505" t="s">
+        <v>26</v>
+      </c>
+      <c r="I505" t="n">
+        <v>75</v>
+      </c>
+      <c r="J505"/>
+      <c r="K505" s="1"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="n">
+        <v>46268.4263888889</v>
+      </c>
+      <c r="B506" t="n">
+        <v>4615949</v>
+      </c>
+      <c r="C506" t="s">
+        <v>643</v>
+      </c>
+      <c r="D506" t="s">
+        <v>96</v>
+      </c>
+      <c r="E506" t="s">
+        <v>634</v>
+      </c>
+      <c r="F506" t="s">
+        <v>23</v>
+      </c>
+      <c r="G506" t="s">
+        <v>644</v>
+      </c>
+      <c r="H506" t="s">
+        <v>26</v>
+      </c>
+      <c r="I506" t="n">
+        <v>60</v>
+      </c>
+      <c r="J506"/>
+      <c r="K506" s="1"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="n">
+        <v>46268.4284722222</v>
+      </c>
+      <c r="B507" t="n">
+        <v>4615949</v>
+      </c>
+      <c r="C507" t="s">
+        <v>643</v>
+      </c>
+      <c r="D507" t="s">
+        <v>96</v>
+      </c>
+      <c r="E507" t="s">
+        <v>634</v>
+      </c>
+      <c r="F507" t="s">
+        <v>23</v>
+      </c>
+      <c r="G507" t="s">
+        <v>645</v>
+      </c>
+      <c r="H507" t="s">
+        <v>26</v>
+      </c>
+      <c r="I507" t="n">
+        <v>60</v>
+      </c>
+      <c r="J507"/>
+      <c r="K507" s="1"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="n">
+        <v>46268.4305555556</v>
+      </c>
+      <c r="B508" t="n">
+        <v>4616003</v>
+      </c>
+      <c r="C508" t="s">
+        <v>646</v>
+      </c>
+      <c r="D508" t="s">
+        <v>128</v>
+      </c>
+      <c r="E508" t="s">
+        <v>629</v>
+      </c>
+      <c r="F508" t="s">
+        <v>19</v>
+      </c>
+      <c r="G508" t="s">
+        <v>647</v>
+      </c>
+      <c r="H508" t="s">
+        <v>195</v>
+      </c>
+      <c r="I508" t="n">
+        <v>77</v>
+      </c>
+      <c r="J508"/>
+      <c r="K508" s="1"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="n">
+        <v>46268.4368055556</v>
+      </c>
+      <c r="B509" t="n">
+        <v>4615958</v>
+      </c>
+      <c r="C509" t="s">
+        <v>619</v>
+      </c>
+      <c r="D509" t="s">
+        <v>49</v>
+      </c>
+      <c r="E509" t="s">
+        <v>629</v>
+      </c>
+      <c r="F509" t="s">
+        <v>27</v>
+      </c>
+      <c r="G509" t="s">
+        <v>648</v>
+      </c>
+      <c r="H509" t="s">
+        <v>195</v>
+      </c>
+      <c r="I509" t="n">
+        <v>54</v>
+      </c>
+      <c r="J509"/>
+      <c r="K509" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -18027,13 +18521,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="B1" t="s">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="C1" t="s">
-        <v>631</v>
+        <v>651</v>
       </c>
     </row>
     <row r="2">

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="672">
   <si>
     <t xml:space="preserve">Thời gian update</t>
   </si>
@@ -2235,6 +2235,71 @@
   <si>
     <t xml:space="preserve">Hệ lớn, kiểm tra phức tạp, muốn kiểm tra thì cần 2-3 người, CNCT không đủ người. Thuê ngoài tốn chi phí, KH không muốn. 
 KH lắp thêm 1 hệ bên khác, xong nhờ bên đó kiểm tra rồi bảo bên mình về. Nhưng bên khác không bảo hành nên KH quay sang nhờ bên mình kiểm tra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bơm 3 pha bị chạm. Đã xử lý xong cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trần Minh Phương</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSKH điều ticket về TP nên FT chưa nhận được, AM đã điều ticket về FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hieutv4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hỏng mạch Pin, chờ hãng gửi thiết bị về
+Dự kiến ngày 05/9 có hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trần Quốc Vượng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đặng Phượng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hẹn lịch triển khai đơn cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Thắm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hỏng ATS. Ngày 03/9 vào thay cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Hải</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Quang Hải</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KH nhờ hỗ trợ kiểm tra tb Wifi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Văn Hoà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 tấm pin bị vỡ. 03/9 KT qua kiểm tra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đỗ Thuyên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YCTX chuyển bên P.KD xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- 28/8 hãng mới gửi thiết bị về đã gia hạn Ticket đến 5/9
+- Ticket bảo hành trên 15 ngày, CSKH đã yêu cầu giải trình
+- Tạo mới YCBH YCBH_CMU_1785983741402 từ B2C lúc 09:35 06/08/2026, dự kiến 28/8 thiết bị gửi về
+- Đã gửi pin lưu trữ đi bảo hành và tạo bảo hành, dự kiến 28/8 xong. Chi nhánh CMU phải lấy xe từ chi nhánh lên HCM để gửi thiết bị (không có đơn vị vận chuyển bộ lưu trữ từ CMU=&gt;HCM)
+Chưa pin lấy về được.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phạm Thị Ngà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KH ko theo dõi đc hiệu suất qua app. Ngày 03/9 KT qua kiểm tra</t>
   </si>
   <si>
     <t xml:space="preserve">Ngày</t>
@@ -2299,8 +2364,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K509" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K509"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K525" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K525"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Thời gian update"/>
     <tableColumn id="2" name="ID"/>
@@ -18505,6 +18570,496 @@
       <c r="J509"/>
       <c r="K509" s="1"/>
     </row>
+    <row r="510">
+      <c r="A510" s="1" t="n">
+        <v>46268.4465277778</v>
+      </c>
+      <c r="B510" t="n">
+        <v>4615932</v>
+      </c>
+      <c r="C510" t="s">
+        <v>627</v>
+      </c>
+      <c r="D510" t="s">
+        <v>49</v>
+      </c>
+      <c r="E510" t="s">
+        <v>629</v>
+      </c>
+      <c r="F510" t="s">
+        <v>18</v>
+      </c>
+      <c r="G510" t="s">
+        <v>649</v>
+      </c>
+      <c r="H510" t="s">
+        <v>195</v>
+      </c>
+      <c r="I510" t="n">
+        <v>70</v>
+      </c>
+      <c r="J510"/>
+      <c r="K510" s="1"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="n">
+        <v>46268.4479166667</v>
+      </c>
+      <c r="B511" t="n">
+        <v>4615841</v>
+      </c>
+      <c r="C511" t="s">
+        <v>357</v>
+      </c>
+      <c r="D511" t="s">
+        <v>96</v>
+      </c>
+      <c r="E511" t="s">
+        <v>634</v>
+      </c>
+      <c r="F511" t="s">
+        <v>18</v>
+      </c>
+      <c r="G511" t="s">
+        <v>490</v>
+      </c>
+      <c r="H511" t="s">
+        <v>16</v>
+      </c>
+      <c r="I511" t="n">
+        <v>16</v>
+      </c>
+      <c r="J511"/>
+      <c r="K511" s="1"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="n">
+        <v>46268.4618055556</v>
+      </c>
+      <c r="B512" t="n">
+        <v>4615951</v>
+      </c>
+      <c r="C512" t="s">
+        <v>650</v>
+      </c>
+      <c r="D512" t="s">
+        <v>178</v>
+      </c>
+      <c r="E512" t="s">
+        <v>631</v>
+      </c>
+      <c r="F512" t="s">
+        <v>23</v>
+      </c>
+      <c r="G512" t="s">
+        <v>651</v>
+      </c>
+      <c r="H512" t="s">
+        <v>50</v>
+      </c>
+      <c r="I512" t="n">
+        <v>59</v>
+      </c>
+      <c r="J512"/>
+      <c r="K512" s="1"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="n">
+        <v>46268.4666666667</v>
+      </c>
+      <c r="B513" t="n">
+        <v>4616009</v>
+      </c>
+      <c r="C513" t="s">
+        <v>300</v>
+      </c>
+      <c r="D513" t="s">
+        <v>53</v>
+      </c>
+      <c r="E513" t="s">
+        <v>652</v>
+      </c>
+      <c r="F513" t="s">
+        <v>27</v>
+      </c>
+      <c r="G513" t="s">
+        <v>653</v>
+      </c>
+      <c r="H513" t="s">
+        <v>26</v>
+      </c>
+      <c r="I513" t="n">
+        <v>37</v>
+      </c>
+      <c r="J513"/>
+      <c r="K513" s="1"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="n">
+        <v>46268.46875</v>
+      </c>
+      <c r="B514" t="n">
+        <v>4615973</v>
+      </c>
+      <c r="C514" t="s">
+        <v>654</v>
+      </c>
+      <c r="D514" t="s">
+        <v>65</v>
+      </c>
+      <c r="E514" t="s">
+        <v>652</v>
+      </c>
+      <c r="F514" t="s">
+        <v>18</v>
+      </c>
+      <c r="G514"/>
+      <c r="H514" t="s">
+        <v>26</v>
+      </c>
+      <c r="I514" t="n">
+        <v>45</v>
+      </c>
+      <c r="J514"/>
+      <c r="K514" s="1"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="n">
+        <v>46268.4694444444</v>
+      </c>
+      <c r="B515" t="n">
+        <v>4615971</v>
+      </c>
+      <c r="C515" t="s">
+        <v>655</v>
+      </c>
+      <c r="D515" t="s">
+        <v>53</v>
+      </c>
+      <c r="E515" t="s">
+        <v>652</v>
+      </c>
+      <c r="F515" t="s">
+        <v>27</v>
+      </c>
+      <c r="G515" t="s">
+        <v>656</v>
+      </c>
+      <c r="H515" t="s">
+        <v>26</v>
+      </c>
+      <c r="I515" t="n">
+        <v>46</v>
+      </c>
+      <c r="J515"/>
+      <c r="K515" s="1"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="n">
+        <v>46268.4694444444</v>
+      </c>
+      <c r="B516" t="n">
+        <v>4615970</v>
+      </c>
+      <c r="C516" t="s">
+        <v>657</v>
+      </c>
+      <c r="D516" t="s">
+        <v>30</v>
+      </c>
+      <c r="E516" t="s">
+        <v>652</v>
+      </c>
+      <c r="F516" t="s">
+        <v>18</v>
+      </c>
+      <c r="G516"/>
+      <c r="H516" t="s">
+        <v>26</v>
+      </c>
+      <c r="I516" t="n">
+        <v>47</v>
+      </c>
+      <c r="J516"/>
+      <c r="K516" s="1"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="n">
+        <v>46268.4701388889</v>
+      </c>
+      <c r="B517" t="n">
+        <v>4615963</v>
+      </c>
+      <c r="C517" t="s">
+        <v>437</v>
+      </c>
+      <c r="D517" t="s">
+        <v>53</v>
+      </c>
+      <c r="E517" t="s">
+        <v>652</v>
+      </c>
+      <c r="F517" t="s">
+        <v>19</v>
+      </c>
+      <c r="G517" t="s">
+        <v>658</v>
+      </c>
+      <c r="H517" t="s">
+        <v>26</v>
+      </c>
+      <c r="I517" t="n">
+        <v>50</v>
+      </c>
+      <c r="J517"/>
+      <c r="K517" s="1"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="n">
+        <v>46268.4805555556</v>
+      </c>
+      <c r="B518" t="n">
+        <v>4615962</v>
+      </c>
+      <c r="C518" t="s">
+        <v>659</v>
+      </c>
+      <c r="D518" t="s">
+        <v>30</v>
+      </c>
+      <c r="E518" t="s">
+        <v>652</v>
+      </c>
+      <c r="F518" t="s">
+        <v>18</v>
+      </c>
+      <c r="G518"/>
+      <c r="H518" t="s">
+        <v>26</v>
+      </c>
+      <c r="I518" t="n">
+        <v>51</v>
+      </c>
+      <c r="J518"/>
+      <c r="K518" s="1"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="n">
+        <v>46268.4819444444</v>
+      </c>
+      <c r="B519" t="n">
+        <v>4615948</v>
+      </c>
+      <c r="C519" t="s">
+        <v>660</v>
+      </c>
+      <c r="D519" t="s">
+        <v>53</v>
+      </c>
+      <c r="E519" t="s">
+        <v>652</v>
+      </c>
+      <c r="F519" t="s">
+        <v>23</v>
+      </c>
+      <c r="G519" t="s">
+        <v>661</v>
+      </c>
+      <c r="H519" t="s">
+        <v>26</v>
+      </c>
+      <c r="I519" t="n">
+        <v>61</v>
+      </c>
+      <c r="J519"/>
+      <c r="K519" s="1"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="n">
+        <v>46268.4944444444</v>
+      </c>
+      <c r="B520" t="n">
+        <v>4615943</v>
+      </c>
+      <c r="C520" t="s">
+        <v>662</v>
+      </c>
+      <c r="D520" t="s">
+        <v>30</v>
+      </c>
+      <c r="E520" t="s">
+        <v>652</v>
+      </c>
+      <c r="F520" t="s">
+        <v>27</v>
+      </c>
+      <c r="G520" t="s">
+        <v>663</v>
+      </c>
+      <c r="H520" t="s">
+        <v>26</v>
+      </c>
+      <c r="I520" t="n">
+        <v>63</v>
+      </c>
+      <c r="J520"/>
+      <c r="K520" s="1"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="n">
+        <v>46268.4951388889</v>
+      </c>
+      <c r="B521" t="n">
+        <v>4615941</v>
+      </c>
+      <c r="C521" t="s">
+        <v>664</v>
+      </c>
+      <c r="D521" t="s">
+        <v>53</v>
+      </c>
+      <c r="E521" t="s">
+        <v>652</v>
+      </c>
+      <c r="F521" t="s">
+        <v>23</v>
+      </c>
+      <c r="G521" t="s">
+        <v>665</v>
+      </c>
+      <c r="H521" t="s">
+        <v>26</v>
+      </c>
+      <c r="I521" t="n">
+        <v>64</v>
+      </c>
+      <c r="J521"/>
+      <c r="K521" s="1"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="n">
+        <v>46268.4958333333</v>
+      </c>
+      <c r="B522" t="n">
+        <v>4615274</v>
+      </c>
+      <c r="C522" t="s">
+        <v>127</v>
+      </c>
+      <c r="D522" t="s">
+        <v>128</v>
+      </c>
+      <c r="E522" t="s">
+        <v>629</v>
+      </c>
+      <c r="F522" t="s">
+        <v>34</v>
+      </c>
+      <c r="G522" t="s">
+        <v>666</v>
+      </c>
+      <c r="H522" t="s">
+        <v>50</v>
+      </c>
+      <c r="I522" t="n">
+        <v>7</v>
+      </c>
+      <c r="J522"/>
+      <c r="K522" s="1" t="n">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="n">
+        <v>46268.4965277778</v>
+      </c>
+      <c r="B523" t="n">
+        <v>4615903</v>
+      </c>
+      <c r="C523" t="s">
+        <v>667</v>
+      </c>
+      <c r="D523" t="s">
+        <v>21</v>
+      </c>
+      <c r="E523" t="s">
+        <v>652</v>
+      </c>
+      <c r="F523" t="s">
+        <v>23</v>
+      </c>
+      <c r="G523" t="s">
+        <v>668</v>
+      </c>
+      <c r="H523" t="s">
+        <v>26</v>
+      </c>
+      <c r="I523" t="n">
+        <v>74</v>
+      </c>
+      <c r="J523"/>
+      <c r="K523" s="1"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="n">
+        <v>46268.5222222222</v>
+      </c>
+      <c r="B524" t="n">
+        <v>4615914</v>
+      </c>
+      <c r="C524" t="s">
+        <v>535</v>
+      </c>
+      <c r="D524" t="s">
+        <v>12</v>
+      </c>
+      <c r="E524" t="s">
+        <v>634</v>
+      </c>
+      <c r="F524" t="s">
+        <v>18</v>
+      </c>
+      <c r="G524" t="s">
+        <v>545</v>
+      </c>
+      <c r="H524" t="s">
+        <v>195</v>
+      </c>
+      <c r="I524" t="n">
+        <v>24</v>
+      </c>
+      <c r="J524"/>
+      <c r="K524" s="1"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="n">
+        <v>46268.5222222222</v>
+      </c>
+      <c r="B525" t="n">
+        <v>4615952</v>
+      </c>
+      <c r="C525" t="s">
+        <v>641</v>
+      </c>
+      <c r="D525" t="s">
+        <v>96</v>
+      </c>
+      <c r="E525" t="s">
+        <v>634</v>
+      </c>
+      <c r="F525" t="s">
+        <v>18</v>
+      </c>
+      <c r="G525"/>
+      <c r="H525" t="s">
+        <v>26</v>
+      </c>
+      <c r="I525" t="n">
+        <v>58</v>
+      </c>
+      <c r="J525"/>
+      <c r="K525" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -18521,13 +19076,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="B1" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="C1" t="s">
-        <v>651</v>
+        <v>671</v>
       </c>
     </row>
     <row r="2">

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="709">
   <si>
     <t xml:space="preserve">Thời gian update</t>
   </si>
@@ -2300,6 +2300,121 @@
   </si>
   <si>
     <t xml:space="preserve">KH ko theo dõi đc hiệu suất qua app. Ngày 03/9 KT qua kiểm tra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã gửi pin lưu trữ đi bảo hành và tạo bảo hành, chưa lấy pin về được</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Trọng Hiền</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã nhận thông tin và điều phối cho nhân sự thực hiện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/09 CSKH điều ticket về TP nên FT chưa nhận được, AM đã điều ticket về FT
+03/09 FT đã sang nhà KH xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mất wifi giám sát thiết bị, đã xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truongdv17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hỏng biến tần Ehuatech, hệ lắp từ 2022, hiện đang tìm lại dữ liệu hãng để liên hệ bảo hành.
+Ngày 25/8 tháo IVT để gửi hãng BH. hiện đã đề xuất gia hạn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoàng Công Quốc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cài lại app cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đinh Thị Ngát</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đang xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 tấm pin bị cháy bảo hành cho KH. HĐ chưa đóng không tạo BH được</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGUYỄN THỊ MAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã liên hệ giải thích cho KH đóng Ticket trước 9h ngày 04/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoàng Ngọc Khoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã giao FT3 liên hệ kiểm tra cho khách trước 9h ngày 04/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Quốc Trí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- KT đã liên hệ KH hẹn lại và gia hạn đến 11h ngày 04/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đặng Khắc Quang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT3 đã liên hệ KH để qua kiểm tra xử lý ngày 04/9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Đức Cường</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- GĐKD đã liên hệ KH và xử lý Ticket trước 9h ngày 04/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hồ Xuân Hiếu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-GĐKD Phấn đã giải thích cho Kh và đóng Ticket trước 9h ngày 04/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phạm Vinh Hiển</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã giao FT3 qua kiểm tra cho khách, xử lý ticket trc 9h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Đức Tuấn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lỗi Pin lưu trữ, đang phối hợp với hãng xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trần Ngọc Phương</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treo biến tần, KT đang xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hỏng biến tần Ehuatech, hệ lắp từ 2022, hiện đang tìm lại dữ liệu hãng để liên hệ bảo hành. Hãng đang hỗ trợ  khắc phục sự cố
+Ngày 25/8 tháo IVT để gửi hãng BH. Ngày 03/09: hãng đang báo lắp lại IVT để kỹ thuật hãng  check metter (chứ không hỏng IVT). Hiện CN đang sắp xếp để lắp lại tại nhà KH để xử lý
+ hiện đã đề xuất gia hạn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Việt Tiến</t>
+  </si>
+  <si>
+    <t xml:space="preserve">đã đóng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CÔNG TY CỔ PHẦN QUỐC TẾ SAO VIỆT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ĐOÀN ĐỨC TÂN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cháy tủ điện</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGUYỄN MẠNH CƯỜNG</t>
   </si>
   <si>
     <t xml:space="preserve">Ngày</t>
@@ -2364,8 +2479,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K525" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K525"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K550" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K550"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Thời gian update"/>
     <tableColumn id="2" name="ID"/>
@@ -19060,6 +19175,781 @@
       <c r="J525"/>
       <c r="K525" s="1"/>
     </row>
+    <row r="526">
+      <c r="A526" s="1" t="n">
+        <v>46268.5826388889</v>
+      </c>
+      <c r="B526" t="n">
+        <v>4615274</v>
+      </c>
+      <c r="C526" t="s">
+        <v>127</v>
+      </c>
+      <c r="D526" t="s">
+        <v>128</v>
+      </c>
+      <c r="E526" t="s">
+        <v>629</v>
+      </c>
+      <c r="F526" t="s">
+        <v>34</v>
+      </c>
+      <c r="G526" t="s">
+        <v>666</v>
+      </c>
+      <c r="H526" t="s">
+        <v>629</v>
+      </c>
+      <c r="I526" t="n">
+        <v>7</v>
+      </c>
+      <c r="J526"/>
+      <c r="K526" s="1"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="n">
+        <v>46268.5826388889</v>
+      </c>
+      <c r="B527" t="n">
+        <v>4615932</v>
+      </c>
+      <c r="C527" t="s">
+        <v>627</v>
+      </c>
+      <c r="D527" t="s">
+        <v>49</v>
+      </c>
+      <c r="E527" t="s">
+        <v>629</v>
+      </c>
+      <c r="F527" t="s">
+        <v>18</v>
+      </c>
+      <c r="G527" t="s">
+        <v>649</v>
+      </c>
+      <c r="H527" t="s">
+        <v>629</v>
+      </c>
+      <c r="I527" t="n">
+        <v>70</v>
+      </c>
+      <c r="J527"/>
+      <c r="K527" s="1"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="n">
+        <v>46268.5840277778</v>
+      </c>
+      <c r="B528" t="n">
+        <v>4615274</v>
+      </c>
+      <c r="C528" t="s">
+        <v>127</v>
+      </c>
+      <c r="D528" t="s">
+        <v>128</v>
+      </c>
+      <c r="E528" t="s">
+        <v>629</v>
+      </c>
+      <c r="F528" t="s">
+        <v>34</v>
+      </c>
+      <c r="G528" t="s">
+        <v>669</v>
+      </c>
+      <c r="H528" t="s">
+        <v>629</v>
+      </c>
+      <c r="I528" t="n">
+        <v>7</v>
+      </c>
+      <c r="J528"/>
+      <c r="K528" s="1"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="n">
+        <v>46268.5902777778</v>
+      </c>
+      <c r="B529" t="n">
+        <v>4616049</v>
+      </c>
+      <c r="C529" t="s">
+        <v>670</v>
+      </c>
+      <c r="D529" t="s">
+        <v>56</v>
+      </c>
+      <c r="E529" t="s">
+        <v>629</v>
+      </c>
+      <c r="F529" t="s">
+        <v>23</v>
+      </c>
+      <c r="G529" t="s">
+        <v>671</v>
+      </c>
+      <c r="H529" t="s">
+        <v>629</v>
+      </c>
+      <c r="I529" t="n">
+        <v>84</v>
+      </c>
+      <c r="J529"/>
+      <c r="K529" s="1"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="n">
+        <v>46268.6076388889</v>
+      </c>
+      <c r="B530" t="n">
+        <v>4615951</v>
+      </c>
+      <c r="C530" t="s">
+        <v>650</v>
+      </c>
+      <c r="D530" t="s">
+        <v>178</v>
+      </c>
+      <c r="E530" t="s">
+        <v>631</v>
+      </c>
+      <c r="F530" t="s">
+        <v>18</v>
+      </c>
+      <c r="G530" t="s">
+        <v>672</v>
+      </c>
+      <c r="H530" t="s">
+        <v>50</v>
+      </c>
+      <c r="I530" t="n">
+        <v>59</v>
+      </c>
+      <c r="J530"/>
+      <c r="K530" s="1"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="n">
+        <v>46268.6145833333</v>
+      </c>
+      <c r="B531" t="n">
+        <v>4615960</v>
+      </c>
+      <c r="C531" t="s">
+        <v>640</v>
+      </c>
+      <c r="D531" t="s">
+        <v>96</v>
+      </c>
+      <c r="E531" t="s">
+        <v>634</v>
+      </c>
+      <c r="F531" t="s">
+        <v>18</v>
+      </c>
+      <c r="G531" t="s">
+        <v>673</v>
+      </c>
+      <c r="H531" t="s">
+        <v>26</v>
+      </c>
+      <c r="I531" t="n">
+        <v>52</v>
+      </c>
+      <c r="J531"/>
+      <c r="K531" s="1"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="n">
+        <v>46268.6159722222</v>
+      </c>
+      <c r="B532" t="n">
+        <v>4616004</v>
+      </c>
+      <c r="C532" t="s">
+        <v>638</v>
+      </c>
+      <c r="D532" t="s">
+        <v>96</v>
+      </c>
+      <c r="E532" t="s">
+        <v>634</v>
+      </c>
+      <c r="F532" t="s">
+        <v>18</v>
+      </c>
+      <c r="G532" t="s">
+        <v>639</v>
+      </c>
+      <c r="H532" t="s">
+        <v>26</v>
+      </c>
+      <c r="I532" t="n">
+        <v>75</v>
+      </c>
+      <c r="J532"/>
+      <c r="K532" s="1"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="n">
+        <v>46268.6229166667</v>
+      </c>
+      <c r="B533" t="n">
+        <v>4615692</v>
+      </c>
+      <c r="C533" t="s">
+        <v>97</v>
+      </c>
+      <c r="D533" t="s">
+        <v>25</v>
+      </c>
+      <c r="E533" t="s">
+        <v>674</v>
+      </c>
+      <c r="F533" t="s">
+        <v>27</v>
+      </c>
+      <c r="G533" t="s">
+        <v>675</v>
+      </c>
+      <c r="H533" t="s">
+        <v>26</v>
+      </c>
+      <c r="I533" t="n">
+        <v>2</v>
+      </c>
+      <c r="J533"/>
+      <c r="K533" s="1"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="n">
+        <v>46268.625</v>
+      </c>
+      <c r="B534" t="n">
+        <v>4616005</v>
+      </c>
+      <c r="C534" t="s">
+        <v>676</v>
+      </c>
+      <c r="D534" t="s">
+        <v>12</v>
+      </c>
+      <c r="E534" t="s">
+        <v>634</v>
+      </c>
+      <c r="F534" t="s">
+        <v>18</v>
+      </c>
+      <c r="G534" t="s">
+        <v>677</v>
+      </c>
+      <c r="H534" t="s">
+        <v>26</v>
+      </c>
+      <c r="I534" t="n">
+        <v>77</v>
+      </c>
+      <c r="J534"/>
+      <c r="K534" s="1"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="n">
+        <v>46268.6277777778</v>
+      </c>
+      <c r="B535" t="n">
+        <v>4616028</v>
+      </c>
+      <c r="C535" t="s">
+        <v>678</v>
+      </c>
+      <c r="D535" t="s">
+        <v>12</v>
+      </c>
+      <c r="E535" t="s">
+        <v>634</v>
+      </c>
+      <c r="F535" t="s">
+        <v>19</v>
+      </c>
+      <c r="G535" t="s">
+        <v>679</v>
+      </c>
+      <c r="H535" t="s">
+        <v>26</v>
+      </c>
+      <c r="I535" t="n">
+        <v>85</v>
+      </c>
+      <c r="J535"/>
+      <c r="K535" s="1"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="n">
+        <v>46268.6298611111</v>
+      </c>
+      <c r="B536" t="n">
+        <v>4616028</v>
+      </c>
+      <c r="C536" t="s">
+        <v>678</v>
+      </c>
+      <c r="D536" t="s">
+        <v>12</v>
+      </c>
+      <c r="E536" t="s">
+        <v>634</v>
+      </c>
+      <c r="F536" t="s">
+        <v>19</v>
+      </c>
+      <c r="G536" t="s">
+        <v>680</v>
+      </c>
+      <c r="H536" t="s">
+        <v>26</v>
+      </c>
+      <c r="I536" t="n">
+        <v>85</v>
+      </c>
+      <c r="J536"/>
+      <c r="K536" s="1"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="n">
+        <v>46268.6305555556</v>
+      </c>
+      <c r="B537" t="n">
+        <v>4616015</v>
+      </c>
+      <c r="C537" t="s">
+        <v>681</v>
+      </c>
+      <c r="D537" t="s">
+        <v>123</v>
+      </c>
+      <c r="E537" t="s">
+        <v>636</v>
+      </c>
+      <c r="F537" t="s">
+        <v>27</v>
+      </c>
+      <c r="G537" t="s">
+        <v>682</v>
+      </c>
+      <c r="H537" t="s">
+        <v>50</v>
+      </c>
+      <c r="I537" t="n">
+        <v>33</v>
+      </c>
+      <c r="J537"/>
+      <c r="K537" s="1"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="n">
+        <v>46268.6319444444</v>
+      </c>
+      <c r="B538" t="n">
+        <v>4615985</v>
+      </c>
+      <c r="C538" t="s">
+        <v>683</v>
+      </c>
+      <c r="D538" t="s">
+        <v>275</v>
+      </c>
+      <c r="E538" t="s">
+        <v>636</v>
+      </c>
+      <c r="F538" t="s">
+        <v>23</v>
+      </c>
+      <c r="G538" t="s">
+        <v>684</v>
+      </c>
+      <c r="H538" t="s">
+        <v>50</v>
+      </c>
+      <c r="I538" t="n">
+        <v>41</v>
+      </c>
+      <c r="J538"/>
+      <c r="K538" s="1"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="n">
+        <v>46268.6340277778</v>
+      </c>
+      <c r="B539" t="n">
+        <v>4615967</v>
+      </c>
+      <c r="C539" t="s">
+        <v>685</v>
+      </c>
+      <c r="D539" t="s">
+        <v>123</v>
+      </c>
+      <c r="E539" t="s">
+        <v>636</v>
+      </c>
+      <c r="F539" t="s">
+        <v>27</v>
+      </c>
+      <c r="G539" t="s">
+        <v>686</v>
+      </c>
+      <c r="H539" t="s">
+        <v>50</v>
+      </c>
+      <c r="I539" t="n">
+        <v>47</v>
+      </c>
+      <c r="J539"/>
+      <c r="K539" s="1"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="n">
+        <v>46268.6402777778</v>
+      </c>
+      <c r="B540" t="n">
+        <v>4615966</v>
+      </c>
+      <c r="C540" t="s">
+        <v>687</v>
+      </c>
+      <c r="D540" t="s">
+        <v>275</v>
+      </c>
+      <c r="E540" t="s">
+        <v>636</v>
+      </c>
+      <c r="F540" t="s">
+        <v>27</v>
+      </c>
+      <c r="G540" t="s">
+        <v>688</v>
+      </c>
+      <c r="H540" t="s">
+        <v>50</v>
+      </c>
+      <c r="I540" t="n">
+        <v>48</v>
+      </c>
+      <c r="J540"/>
+      <c r="K540" s="1"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="n">
+        <v>46268.6423611111</v>
+      </c>
+      <c r="B541" t="n">
+        <v>4615934</v>
+      </c>
+      <c r="C541" t="s">
+        <v>689</v>
+      </c>
+      <c r="D541" t="s">
+        <v>152</v>
+      </c>
+      <c r="E541" t="s">
+        <v>636</v>
+      </c>
+      <c r="F541" t="s">
+        <v>27</v>
+      </c>
+      <c r="G541" t="s">
+        <v>690</v>
+      </c>
+      <c r="H541" t="s">
+        <v>50</v>
+      </c>
+      <c r="I541" t="n">
+        <v>67</v>
+      </c>
+      <c r="J541"/>
+      <c r="K541" s="1"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="n">
+        <v>46268.64375</v>
+      </c>
+      <c r="B542" t="n">
+        <v>4615937</v>
+      </c>
+      <c r="C542" t="s">
+        <v>691</v>
+      </c>
+      <c r="D542" t="s">
+        <v>497</v>
+      </c>
+      <c r="E542" t="s">
+        <v>636</v>
+      </c>
+      <c r="F542" t="s">
+        <v>19</v>
+      </c>
+      <c r="G542" t="s">
+        <v>692</v>
+      </c>
+      <c r="H542" t="s">
+        <v>50</v>
+      </c>
+      <c r="I542" t="n">
+        <v>66</v>
+      </c>
+      <c r="J542"/>
+      <c r="K542" s="1"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="n">
+        <v>46268.6479166667</v>
+      </c>
+      <c r="B543" t="n">
+        <v>4615933</v>
+      </c>
+      <c r="C543" t="s">
+        <v>693</v>
+      </c>
+      <c r="D543" t="s">
+        <v>275</v>
+      </c>
+      <c r="E543" t="s">
+        <v>636</v>
+      </c>
+      <c r="F543" t="s">
+        <v>27</v>
+      </c>
+      <c r="G543" t="s">
+        <v>694</v>
+      </c>
+      <c r="H543" t="s">
+        <v>50</v>
+      </c>
+      <c r="I543" t="n">
+        <v>68</v>
+      </c>
+      <c r="J543"/>
+      <c r="K543" s="1"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="n">
+        <v>46268.6486111111</v>
+      </c>
+      <c r="B544" t="n">
+        <v>4615945</v>
+      </c>
+      <c r="C544" t="s">
+        <v>695</v>
+      </c>
+      <c r="D544" t="s">
+        <v>30</v>
+      </c>
+      <c r="E544" t="s">
+        <v>652</v>
+      </c>
+      <c r="F544" t="s">
+        <v>19</v>
+      </c>
+      <c r="G544" t="s">
+        <v>696</v>
+      </c>
+      <c r="H544" t="s">
+        <v>26</v>
+      </c>
+      <c r="I544" t="n">
+        <v>62</v>
+      </c>
+      <c r="J544"/>
+      <c r="K544" s="1"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="n">
+        <v>46268.6506944444</v>
+      </c>
+      <c r="B545" t="n">
+        <v>4616025</v>
+      </c>
+      <c r="C545" t="s">
+        <v>697</v>
+      </c>
+      <c r="D545" t="s">
+        <v>30</v>
+      </c>
+      <c r="E545" t="s">
+        <v>652</v>
+      </c>
+      <c r="F545" t="s">
+        <v>19</v>
+      </c>
+      <c r="G545" t="s">
+        <v>698</v>
+      </c>
+      <c r="H545" t="s">
+        <v>26</v>
+      </c>
+      <c r="I545" t="n">
+        <v>79</v>
+      </c>
+      <c r="J545"/>
+      <c r="K545" s="1"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="n">
+        <v>46268.6527777778</v>
+      </c>
+      <c r="B546" t="n">
+        <v>4615692</v>
+      </c>
+      <c r="C546" t="s">
+        <v>97</v>
+      </c>
+      <c r="D546" t="s">
+        <v>25</v>
+      </c>
+      <c r="E546" t="s">
+        <v>674</v>
+      </c>
+      <c r="F546" t="s">
+        <v>27</v>
+      </c>
+      <c r="G546" t="s">
+        <v>699</v>
+      </c>
+      <c r="H546" t="s">
+        <v>26</v>
+      </c>
+      <c r="I546" t="n">
+        <v>2</v>
+      </c>
+      <c r="J546"/>
+      <c r="K546" s="1"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="n">
+        <v>46268.6548611111</v>
+      </c>
+      <c r="B547" t="n">
+        <v>4616017</v>
+      </c>
+      <c r="C547" t="s">
+        <v>700</v>
+      </c>
+      <c r="D547" t="s">
+        <v>75</v>
+      </c>
+      <c r="E547" t="s">
+        <v>674</v>
+      </c>
+      <c r="F547" t="s">
+        <v>23</v>
+      </c>
+      <c r="G547" t="s">
+        <v>701</v>
+      </c>
+      <c r="H547" t="s">
+        <v>26</v>
+      </c>
+      <c r="I547" t="n">
+        <v>33</v>
+      </c>
+      <c r="J547"/>
+      <c r="K547" s="1"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="n">
+        <v>46268.6548611111</v>
+      </c>
+      <c r="B548" t="n">
+        <v>4615996</v>
+      </c>
+      <c r="C548" t="s">
+        <v>702</v>
+      </c>
+      <c r="D548" t="s">
+        <v>75</v>
+      </c>
+      <c r="E548" t="s">
+        <v>674</v>
+      </c>
+      <c r="F548" t="s">
+        <v>23</v>
+      </c>
+      <c r="G548" t="s">
+        <v>701</v>
+      </c>
+      <c r="H548" t="s">
+        <v>26</v>
+      </c>
+      <c r="I548" t="n">
+        <v>38</v>
+      </c>
+      <c r="J548"/>
+      <c r="K548" s="1"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="n">
+        <v>46268.6548611111</v>
+      </c>
+      <c r="B549" t="n">
+        <v>4616008</v>
+      </c>
+      <c r="C549" t="s">
+        <v>703</v>
+      </c>
+      <c r="D549" t="s">
+        <v>30</v>
+      </c>
+      <c r="E549" t="s">
+        <v>652</v>
+      </c>
+      <c r="F549" t="s">
+        <v>27</v>
+      </c>
+      <c r="G549" t="s">
+        <v>704</v>
+      </c>
+      <c r="H549" t="s">
+        <v>26</v>
+      </c>
+      <c r="I549" t="n">
+        <v>81</v>
+      </c>
+      <c r="J549"/>
+      <c r="K549" s="1"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="n">
+        <v>46268.6555555556</v>
+      </c>
+      <c r="B550" t="n">
+        <v>4615992</v>
+      </c>
+      <c r="C550" t="s">
+        <v>705</v>
+      </c>
+      <c r="D550" t="s">
+        <v>75</v>
+      </c>
+      <c r="E550" t="s">
+        <v>674</v>
+      </c>
+      <c r="F550" t="s">
+        <v>23</v>
+      </c>
+      <c r="G550" t="s">
+        <v>701</v>
+      </c>
+      <c r="H550" t="s">
+        <v>26</v>
+      </c>
+      <c r="I550" t="n">
+        <v>40</v>
+      </c>
+      <c r="J550"/>
+      <c r="K550" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -19076,13 +19966,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>669</v>
+        <v>706</v>
       </c>
       <c r="B1" t="s">
-        <v>670</v>
+        <v>707</v>
       </c>
       <c r="C1" t="s">
-        <v>671</v>
+        <v>708</v>
       </c>
     </row>
     <row r="2">
@@ -19145,10 +20035,10 @@
         <v>46268</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/AM_update.xlsx
+++ b/data/AM_update.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="784">
   <si>
     <t xml:space="preserve">Thời gian update</t>
   </si>
@@ -2415,6 +2415,252 @@
   </si>
   <si>
     <t xml:space="preserve">NGUYỄN MẠNH CƯỜNG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoàng Quốc Tế</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TQG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binhtt6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KH phản ánh: nhảy rơ le xong tắt hẳn cả điện nlmt lẫn điện lưới. Đã cho nhân sự FT1 đến nhà KH kiểm tra, chỉ lúc cao tải thì hệ thống bị lỗi nhưng chưa xác định được chính xác nguyên nhân. Dự kiến sáng mai 04/9, FT3 Chí sẽ trực tiếp đến nhà KH để kiểm tra, xử lý.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đỗ Văn Hùng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Hỏng mettor, hết hạn bảo hành, đang hỗ trợ KH đặt về thay cho khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lê Xuân Hùng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã giao FT liên hệ qua kiểm tra cho khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phạm Văn Ngơi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khu vực không có nhân sự FT3, chi nhánh đang sắp xếp nhân sự qua kiểm tra cho KHách. Đã yêu cầu kiểm tra cho khach trước 17h ngya 05/09. mai sẽ kiểm tra tiến độ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Văn Thức</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân sự được giao đang vướng đi xử lý sự cố. đã yêu cầu nhân sự Huế, hện khách ngày 04/09 qua xử lý cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phạm Trọng Hoà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đội thợ chưa xếp được thời gian. CN hẹn báo lại tiến độ xử lý ngày 04/09.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CÔNG TY TNHH VĂN XUÂN AC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhân sự đang qua kiểm tra cho KH. sẽ  sử lý trước 18h ngày 03/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Văn Chung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSKH điều ticket về sai FT nên chưa nhận được, AM đã điều ticket về đúng FT, FT đang liên hệ KH
+Đến 17h 03/09 ko xử lý kịp sẽ xin gia hạn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đào Đức Huy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã giao Ft3 liên hệ qua hỗ trợ KH. Xử lý ticket trc 10h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã giao Ft3 liên hệ qua hỗ trợ KH. Xử lý ticket trc 10h ngày 04/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Duy Tân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã kiểm tra, cháy ATS, hiện NCC đang chuyển lại ATS mới, dự kiến 05/09 có hàng. sẽ lắp cho KH ngay khi có hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- FT3 qua kiểm tra xử lý cho khách trước 3/9
+Ticket CN tạo CSKH chưa duyệt
+- Đã qua dựng giàn giáo, sáng mai hãng qua kiểm tra xử lý cho khách hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Tiến Anh Đức</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Khách hàng hẹn 17h30 qua xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSKH điều ticket về sai FT nên chưa nhận được, AM đã điều ticket về đúng FT, FT đang liên hệ KH hướng dẫn để fix lại app
+Đến 17h 03/09 ko xử lý kịp sẽ xin gia hạn để đến hướng dẫn trực tiếp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phan Vĩnh Hoàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã đóng Ticket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Thanh Phố</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã Đóng ticket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lê Thị Thu Hương</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KH bị cháy ATS, NCC hẹn 04/09 sẽ giao hàng cho CN, CN sẽ thực hiện cho KH trong ngày 04/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">đã đóng Ticket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Kh báo đã HĐ Bỉnh thường =&gt; Đóng Ticket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bùi Tá Thanh Bình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- KH hỏng dongle, đã hết hạn bảo hành =&gt; tư vấn cho Kh và xử lý Tickey trc 9h ngày 04/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hẹn 4/9 xử lý cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do thợ điện khu vực đến sửa điện cho khách hàng và đã đấu nối nhầm dây điện AC của nlmt dẫn đến hệ thống lỗi không hoat động. Đã xử lý cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gió thổi đứt đoạn cáp. Sáng 4/9 qua khắc phục cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lôi Pin lưu trữ, đang phối hợp hãng xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoàng Đăng Lợi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KH cần hỗ trợ xuất HĐ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hỏng 1 tấm Pin, KT đang xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã gửi IVT, pin lưu trữ đi bảo hành và tạo bảo hành, dự kiến 03/09 hàng về
+Ngày 07/9 Pin lưu trữ về</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hỏng ATS, hiện đang  chờ KH về, để chụp ảnh  ATS hỏng để làm việc với hãng. Dự kiến 25/08 KH mới về để tới làm việc
+Đã tạo BH, chờ hãng gửi TB về thay. 
+Dự kiến ngày 04/9 lắp lại cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- CN sẽ thuê xe ngoài, dự kiến có pin thay cho khách trc 10/09
+Đã có tấm pin bảo hành thay thế ở HNI nhưng chưa chuyển về. Anh Huyhm đang yêu cầu kỹ thuật ghép xe chuyển về. Dự kiến 1/9 có hàng để lắp đặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSKH điều ticket về sai FT nên chưa nhận được, AM đã điều ticket về đúng FT, FT đang liên hệ KH hướng dẫn để fix lại app
+Đến 17h 03/09 ko xử lý kịp sẽ xin gia hạn để đến hướng dẫn trực tiếp
+FT đã hướng dẫn KH cài lại app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hỏng ATS. Ngày 03/9 vào thay cho KH
+Đã thay xong nhưng chưa chạy, đang phối hợp hãng xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phạm Văn Lưu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nghi vấn hỏng ATS, Ngày 04/9 CN cho người qua xử lý</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Bị tuột logger, đã lắp lại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAN ĐẠI DIỆN CHA MẸ HỌC SINH TRƯỜNG THPT AN PHÚ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket lên muộn, 4/9 xử lý cho KH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lê Thế Anh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không gọi được cho NV để trao đổi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tủ điện dùng CB 32. KH dùng quá tải khiến nhảy CB hỏng --&gt; Mua CB về thay
+Đã hoàn thành cho Kh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP Vũ Thái Sơn bị cắt quyền điều phối. Ticket chuyển về cho Giám đốc trung tâm. Hỗ trợ điều phối về user 472143 - Nguyễn Trung Hiếu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xác định nguyên nhân do hỏng ATS, nguồn AC vượt áp 250V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã gửi hồ sơ về bưu điện cho khách và hoàn thành Ticket
+- GĐKD đã liên hệ KH và xử lý Ticket trước 9h ngày 04/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- atomat bị cháy =&gt; thay cho khách. Đã đóng Ticket
+- Đã giao FT3 liên hệ kiểm tra cho khách trước 9h ngày 04/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã gia hạn Ticket đến 17h45 để xử lý
+- KH hỏng dongle, đã hết hạn bảo hành =&gt; tư vấn cho Kh và xử lý Tickey trc 9h ngày 04/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã giải thích cho Kh và đóng Ticket
+-GĐKD Phấn đã giải thích cho Kh và đóng Ticket trước 9h ngày 04/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Bếp từ hỏng, đã liên hệ hãng gửi thiết bị về thay, dự kiến xong trước 19/9
+- Đã giao FT3 qua kiểm tra cho khách, xử lý ticket trc 9h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Hỏng mettor, hết hạn bảo hành, đang hỗ trợ KH đặt về thay cho khách =&gt; Đã đóng Ticket, chờ đặt mua để hỗ trợ thay cho khách</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vũ Văn Hiếu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/9 FT đã thay ATS cho KH nhưng đường nguồn có vấn đề
+4/9 FT đến ktra lại sau để đóng ticket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lỗi AC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Đã phối hợp hãng up FW cho khách xong
+- Đã giao Ft3 liên hệ qua hỗ trợ KH. Xử lý ticket trc 10h ngày 04/09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguyễn Viết Chín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lỗi nhảy CB, Đã đến kiểm tra cần theo dõi thêm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KH nhờ hỗ trợ kiểm tra app</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Ticket của HCM, đã giao về nhân sự HCM hẹn lại khách 16h ngày 04/09
+Khu vực không có nhân sự FT3, chi nhánh đang sắp xếp nhân sự qua kiểm tra cho 
+KHách. Đã yêu cầu kiểm tra cho khach trước 17h ngya 05/09. mai sẽ kiểm tra tiến độ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phạm Khuyên</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anh Quân - 0363474779 DLK đã nhận tủ điện, bàn giao cho anh Bộ lắp đặt cho KH. Anh Bộ báo lại thời tiết mưa to khiến việc lắp tủ điện khó khăn, xin gia hạn để lắp đặt hoàn thành cho KH</t>
   </si>
   <si>
     <t xml:space="preserve">Ngày</t>
@@ -2479,8 +2725,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K550" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K550"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K614" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K614"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Thời gian update"/>
     <tableColumn id="2" name="ID"/>
@@ -2499,8 +2745,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C7" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:C7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:C8" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:C8"/>
   <tableColumns count="3">
     <tableColumn id="1" name="Ngày"/>
     <tableColumn id="2" name="Tổng tồn"/>
@@ -19950,6 +20196,1996 @@
       <c r="J550"/>
       <c r="K550" s="1"/>
     </row>
+    <row r="551">
+      <c r="A551" s="1" t="n">
+        <v>46268.675</v>
+      </c>
+      <c r="B551" t="n">
+        <v>4615951</v>
+      </c>
+      <c r="C551" t="s">
+        <v>650</v>
+      </c>
+      <c r="D551" t="s">
+        <v>178</v>
+      </c>
+      <c r="E551" t="s">
+        <v>631</v>
+      </c>
+      <c r="F551" t="s">
+        <v>18</v>
+      </c>
+      <c r="G551" t="s">
+        <v>651</v>
+      </c>
+      <c r="H551" t="s">
+        <v>50</v>
+      </c>
+      <c r="I551" t="n">
+        <v>58</v>
+      </c>
+      <c r="J551"/>
+      <c r="K551" s="1"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="n">
+        <v>46268.6763888889</v>
+      </c>
+      <c r="B552" t="n">
+        <v>4615894</v>
+      </c>
+      <c r="C552" t="s">
+        <v>706</v>
+      </c>
+      <c r="D552" t="s">
+        <v>707</v>
+      </c>
+      <c r="E552" t="s">
+        <v>708</v>
+      </c>
+      <c r="F552" t="s">
+        <v>27</v>
+      </c>
+      <c r="G552" t="s">
+        <v>709</v>
+      </c>
+      <c r="H552" t="s">
+        <v>708</v>
+      </c>
+      <c r="I552" t="n">
+        <v>24</v>
+      </c>
+      <c r="J552"/>
+      <c r="K552" s="1"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="n">
+        <v>46268.68125</v>
+      </c>
+      <c r="B553" t="n">
+        <v>4615933</v>
+      </c>
+      <c r="C553" t="s">
+        <v>693</v>
+      </c>
+      <c r="D553" t="s">
+        <v>275</v>
+      </c>
+      <c r="E553" t="s">
+        <v>636</v>
+      </c>
+      <c r="F553" t="s">
+        <v>27</v>
+      </c>
+      <c r="G553" t="s">
+        <v>694</v>
+      </c>
+      <c r="H553" t="s">
+        <v>50</v>
+      </c>
+      <c r="I553" t="n">
+        <v>68</v>
+      </c>
+      <c r="J553"/>
+      <c r="K553" s="1"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="n">
+        <v>46268.6819444444</v>
+      </c>
+      <c r="B554" t="n">
+        <v>4615930</v>
+      </c>
+      <c r="C554" t="s">
+        <v>710</v>
+      </c>
+      <c r="D554" t="s">
+        <v>275</v>
+      </c>
+      <c r="E554" t="s">
+        <v>636</v>
+      </c>
+      <c r="F554" t="s">
+        <v>19</v>
+      </c>
+      <c r="G554" t="s">
+        <v>711</v>
+      </c>
+      <c r="H554" t="s">
+        <v>50</v>
+      </c>
+      <c r="I554" t="n">
+        <v>70</v>
+      </c>
+      <c r="J554"/>
+      <c r="K554" s="1"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="n">
+        <v>46268.6875</v>
+      </c>
+      <c r="B555" t="n">
+        <v>4616030</v>
+      </c>
+      <c r="C555" t="s">
+        <v>712</v>
+      </c>
+      <c r="D555" t="s">
+        <v>275</v>
+      </c>
+      <c r="E555" t="s">
+        <v>636</v>
+      </c>
+      <c r="F555" t="s">
+        <v>23</v>
+      </c>
+      <c r="G555" t="s">
+        <v>713</v>
+      </c>
+      <c r="H555" t="s">
+        <v>50</v>
+      </c>
+      <c r="I555" t="n">
+        <v>84</v>
+      </c>
+      <c r="J555"/>
+      <c r="K555" s="1"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="n">
+        <v>46268.6881944444</v>
+      </c>
+      <c r="B556" t="n">
+        <v>4615906</v>
+      </c>
+      <c r="C556" t="s">
+        <v>714</v>
+      </c>
+      <c r="D556" t="s">
+        <v>75</v>
+      </c>
+      <c r="E556" t="s">
+        <v>674</v>
+      </c>
+      <c r="F556" t="s">
+        <v>23</v>
+      </c>
+      <c r="G556" t="s">
+        <v>715</v>
+      </c>
+      <c r="H556" t="s">
+        <v>26</v>
+      </c>
+      <c r="I556" t="n">
+        <v>73</v>
+      </c>
+      <c r="J556"/>
+      <c r="K556" s="1"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="n">
+        <v>46268.6888888889</v>
+      </c>
+      <c r="B557" t="n">
+        <v>4615940</v>
+      </c>
+      <c r="C557" t="s">
+        <v>716</v>
+      </c>
+      <c r="D557" t="s">
+        <v>75</v>
+      </c>
+      <c r="E557" t="s">
+        <v>674</v>
+      </c>
+      <c r="F557" t="s">
+        <v>23</v>
+      </c>
+      <c r="G557" t="s">
+        <v>717</v>
+      </c>
+      <c r="H557" t="s">
+        <v>26</v>
+      </c>
+      <c r="I557" t="n">
+        <v>65</v>
+      </c>
+      <c r="J557"/>
+      <c r="K557" s="1"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="n">
+        <v>46268.6895833333</v>
+      </c>
+      <c r="B558" t="n">
+        <v>4616022</v>
+      </c>
+      <c r="C558" t="s">
+        <v>718</v>
+      </c>
+      <c r="D558" t="s">
+        <v>75</v>
+      </c>
+      <c r="E558" t="s">
+        <v>674</v>
+      </c>
+      <c r="F558" t="s">
+        <v>23</v>
+      </c>
+      <c r="G558" t="s">
+        <v>719</v>
+      </c>
+      <c r="H558" t="s">
+        <v>26</v>
+      </c>
+      <c r="I558" t="n">
+        <v>30</v>
+      </c>
+      <c r="J558"/>
+      <c r="K558" s="1"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="n">
+        <v>46268.6930555556</v>
+      </c>
+      <c r="B559" t="n">
+        <v>4616019</v>
+      </c>
+      <c r="C559" t="s">
+        <v>720</v>
+      </c>
+      <c r="D559" t="s">
+        <v>25</v>
+      </c>
+      <c r="E559" t="s">
+        <v>674</v>
+      </c>
+      <c r="F559" t="s">
+        <v>27</v>
+      </c>
+      <c r="G559" t="s">
+        <v>721</v>
+      </c>
+      <c r="H559" t="s">
+        <v>26</v>
+      </c>
+      <c r="I559" t="n">
+        <v>31</v>
+      </c>
+      <c r="J559"/>
+      <c r="K559" s="1"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="n">
+        <v>46268.6958333333</v>
+      </c>
+      <c r="B560" t="n">
+        <v>4616029</v>
+      </c>
+      <c r="C560" t="s">
+        <v>722</v>
+      </c>
+      <c r="D560" t="s">
+        <v>178</v>
+      </c>
+      <c r="E560" t="s">
+        <v>631</v>
+      </c>
+      <c r="F560" t="s">
+        <v>23</v>
+      </c>
+      <c r="G560" t="s">
+        <v>723</v>
+      </c>
+      <c r="H560" t="s">
+        <v>50</v>
+      </c>
+      <c r="I560" t="n">
+        <v>78</v>
+      </c>
+      <c r="J560"/>
+      <c r="K560" s="1"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="n">
+        <v>46268.6972222222</v>
+      </c>
+      <c r="B561" t="n">
+        <v>4616024</v>
+      </c>
+      <c r="C561" t="s">
+        <v>724</v>
+      </c>
+      <c r="D561" t="s">
+        <v>152</v>
+      </c>
+      <c r="E561" t="s">
+        <v>636</v>
+      </c>
+      <c r="F561" t="s">
+        <v>23</v>
+      </c>
+      <c r="G561" t="s">
+        <v>725</v>
+      </c>
+      <c r="H561" t="s">
+        <v>50</v>
+      </c>
+      <c r="I561" t="n">
+        <v>80</v>
+      </c>
+      <c r="J561"/>
+      <c r="K561" s="1"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="n">
+        <v>46268.6979166667</v>
+      </c>
+      <c r="B562" t="n">
+        <v>4616024</v>
+      </c>
+      <c r="C562" t="s">
+        <v>724</v>
+      </c>
+      <c r="D562" t="s">
+        <v>152</v>
+      </c>
+      <c r="E562" t="s">
+        <v>636</v>
+      </c>
+      <c r="F562" t="s">
+        <v>23</v>
+      </c>
+      <c r="G562" t="s">
+        <v>726</v>
+      </c>
+      <c r="H562" t="s">
+        <v>50</v>
+      </c>
+      <c r="I562" t="n">
+        <v>80</v>
+      </c>
+      <c r="J562"/>
+      <c r="K562" s="1"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="n">
+        <v>46268.6979166667</v>
+      </c>
+      <c r="B563" t="n">
+        <v>4616018</v>
+      </c>
+      <c r="C563" t="s">
+        <v>727</v>
+      </c>
+      <c r="D563" t="s">
+        <v>25</v>
+      </c>
+      <c r="E563" t="s">
+        <v>674</v>
+      </c>
+      <c r="F563" t="s">
+        <v>27</v>
+      </c>
+      <c r="G563" t="s">
+        <v>728</v>
+      </c>
+      <c r="H563" t="s">
+        <v>26</v>
+      </c>
+      <c r="I563" t="n">
+        <v>32</v>
+      </c>
+      <c r="J563"/>
+      <c r="K563" s="1"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="n">
+        <v>46268.6993055556</v>
+      </c>
+      <c r="B564" t="n">
+        <v>4615882</v>
+      </c>
+      <c r="C564" t="s">
+        <v>71</v>
+      </c>
+      <c r="D564" t="s">
+        <v>72</v>
+      </c>
+      <c r="E564" t="s">
+        <v>219</v>
+      </c>
+      <c r="F564" t="s">
+        <v>27</v>
+      </c>
+      <c r="G564" t="s">
+        <v>729</v>
+      </c>
+      <c r="H564" t="s">
+        <v>13</v>
+      </c>
+      <c r="I564" t="n">
+        <v>155</v>
+      </c>
+      <c r="J564"/>
+      <c r="K564" s="1"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="n">
+        <v>46268.6993055556</v>
+      </c>
+      <c r="B565" t="n">
+        <v>4615874</v>
+      </c>
+      <c r="C565" t="s">
+        <v>447</v>
+      </c>
+      <c r="D565" t="s">
+        <v>72</v>
+      </c>
+      <c r="E565" t="s">
+        <v>219</v>
+      </c>
+      <c r="F565" t="s">
+        <v>18</v>
+      </c>
+      <c r="G565" t="s">
+        <v>448</v>
+      </c>
+      <c r="H565" t="s">
+        <v>13</v>
+      </c>
+      <c r="I565" t="n">
+        <v>147</v>
+      </c>
+      <c r="J565"/>
+      <c r="K565" s="1"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="n">
+        <v>46268.7</v>
+      </c>
+      <c r="B566" t="n">
+        <v>4615994</v>
+      </c>
+      <c r="C566" t="s">
+        <v>730</v>
+      </c>
+      <c r="D566" t="s">
+        <v>38</v>
+      </c>
+      <c r="E566" t="s">
+        <v>251</v>
+      </c>
+      <c r="F566" t="s">
+        <v>27</v>
+      </c>
+      <c r="G566" t="s">
+        <v>731</v>
+      </c>
+      <c r="H566" t="s">
+        <v>13</v>
+      </c>
+      <c r="I566" t="n">
+        <v>210</v>
+      </c>
+      <c r="J566"/>
+      <c r="K566" s="1"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="n">
+        <v>46268.7020833333</v>
+      </c>
+      <c r="B567" t="n">
+        <v>4615988</v>
+      </c>
+      <c r="C567" t="s">
+        <v>630</v>
+      </c>
+      <c r="D567" t="s">
+        <v>178</v>
+      </c>
+      <c r="E567" t="s">
+        <v>631</v>
+      </c>
+      <c r="F567" t="s">
+        <v>18</v>
+      </c>
+      <c r="G567" t="s">
+        <v>701</v>
+      </c>
+      <c r="H567" t="s">
+        <v>631</v>
+      </c>
+      <c r="I567" t="n">
+        <v>40</v>
+      </c>
+      <c r="J567"/>
+      <c r="K567" s="1"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="n">
+        <v>46268.7020833333</v>
+      </c>
+      <c r="B568" t="n">
+        <v>4616029</v>
+      </c>
+      <c r="C568" t="s">
+        <v>722</v>
+      </c>
+      <c r="D568" t="s">
+        <v>178</v>
+      </c>
+      <c r="E568" t="s">
+        <v>631</v>
+      </c>
+      <c r="F568" t="s">
+        <v>23</v>
+      </c>
+      <c r="G568" t="s">
+        <v>732</v>
+      </c>
+      <c r="H568" t="s">
+        <v>50</v>
+      </c>
+      <c r="I568" t="n">
+        <v>78</v>
+      </c>
+      <c r="J568"/>
+      <c r="K568" s="1"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="n">
+        <v>46268.7041666667</v>
+      </c>
+      <c r="B569" t="n">
+        <v>4616033</v>
+      </c>
+      <c r="C569" t="s">
+        <v>733</v>
+      </c>
+      <c r="D569" t="s">
+        <v>497</v>
+      </c>
+      <c r="E569" t="s">
+        <v>636</v>
+      </c>
+      <c r="F569" t="s">
+        <v>18</v>
+      </c>
+      <c r="G569" t="s">
+        <v>734</v>
+      </c>
+      <c r="H569" t="s">
+        <v>50</v>
+      </c>
+      <c r="I569" t="n">
+        <v>93</v>
+      </c>
+      <c r="J569"/>
+      <c r="K569" s="1"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="n">
+        <v>46268.7048611111</v>
+      </c>
+      <c r="B570" t="n">
+        <v>4616012</v>
+      </c>
+      <c r="C570" t="s">
+        <v>735</v>
+      </c>
+      <c r="D570" t="s">
+        <v>497</v>
+      </c>
+      <c r="E570" t="s">
+        <v>636</v>
+      </c>
+      <c r="F570" t="s">
+        <v>18</v>
+      </c>
+      <c r="G570" t="s">
+        <v>736</v>
+      </c>
+      <c r="H570" t="s">
+        <v>50</v>
+      </c>
+      <c r="I570" t="n">
+        <v>34</v>
+      </c>
+      <c r="J570"/>
+      <c r="K570" s="1"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="n">
+        <v>46268.7055555556</v>
+      </c>
+      <c r="B571" t="n">
+        <v>4616011</v>
+      </c>
+      <c r="C571" t="s">
+        <v>737</v>
+      </c>
+      <c r="D571" t="s">
+        <v>25</v>
+      </c>
+      <c r="E571" t="s">
+        <v>674</v>
+      </c>
+      <c r="F571" t="s">
+        <v>19</v>
+      </c>
+      <c r="G571" t="s">
+        <v>738</v>
+      </c>
+      <c r="H571" t="s">
+        <v>26</v>
+      </c>
+      <c r="I571" t="n">
+        <v>36</v>
+      </c>
+      <c r="J571"/>
+      <c r="K571" s="1"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="n">
+        <v>46268.7055555556</v>
+      </c>
+      <c r="B572" t="n">
+        <v>4616015</v>
+      </c>
+      <c r="C572" t="s">
+        <v>681</v>
+      </c>
+      <c r="D572" t="s">
+        <v>123</v>
+      </c>
+      <c r="E572" t="s">
+        <v>636</v>
+      </c>
+      <c r="F572" t="s">
+        <v>18</v>
+      </c>
+      <c r="G572" t="s">
+        <v>739</v>
+      </c>
+      <c r="H572" t="s">
+        <v>26</v>
+      </c>
+      <c r="I572" t="n">
+        <v>33</v>
+      </c>
+      <c r="J572"/>
+      <c r="K572" s="1"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="n">
+        <v>46268.70625</v>
+      </c>
+      <c r="B573" t="n">
+        <v>4615966</v>
+      </c>
+      <c r="C573" t="s">
+        <v>687</v>
+      </c>
+      <c r="D573" t="s">
+        <v>275</v>
+      </c>
+      <c r="E573" t="s">
+        <v>636</v>
+      </c>
+      <c r="F573" t="s">
+        <v>18</v>
+      </c>
+      <c r="G573" t="s">
+        <v>740</v>
+      </c>
+      <c r="H573" t="s">
+        <v>50</v>
+      </c>
+      <c r="I573" t="n">
+        <v>48</v>
+      </c>
+      <c r="J573"/>
+      <c r="K573" s="1"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="n">
+        <v>46268.7090277778</v>
+      </c>
+      <c r="B574" t="n">
+        <v>4615949</v>
+      </c>
+      <c r="C574" t="s">
+        <v>643</v>
+      </c>
+      <c r="D574" t="s">
+        <v>96</v>
+      </c>
+      <c r="E574" t="s">
+        <v>634</v>
+      </c>
+      <c r="F574" t="s">
+        <v>19</v>
+      </c>
+      <c r="G574" t="s">
+        <v>672</v>
+      </c>
+      <c r="H574" t="s">
+        <v>50</v>
+      </c>
+      <c r="I574" t="n">
+        <v>59</v>
+      </c>
+      <c r="J574"/>
+      <c r="K574" s="1"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="n">
+        <v>46268.7104166667</v>
+      </c>
+      <c r="B575" t="n">
+        <v>4615939</v>
+      </c>
+      <c r="C575" t="s">
+        <v>741</v>
+      </c>
+      <c r="D575" t="s">
+        <v>152</v>
+      </c>
+      <c r="E575" t="s">
+        <v>636</v>
+      </c>
+      <c r="F575" t="s">
+        <v>23</v>
+      </c>
+      <c r="G575" t="s">
+        <v>742</v>
+      </c>
+      <c r="H575" t="s">
+        <v>26</v>
+      </c>
+      <c r="I575" t="n">
+        <v>65</v>
+      </c>
+      <c r="J575"/>
+      <c r="K575" s="1"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="n">
+        <v>46268.7180555556</v>
+      </c>
+      <c r="B576" t="n">
+        <v>4615902</v>
+      </c>
+      <c r="C576" t="s">
+        <v>642</v>
+      </c>
+      <c r="D576" t="s">
+        <v>96</v>
+      </c>
+      <c r="E576" t="s">
+        <v>634</v>
+      </c>
+      <c r="F576" t="s">
+        <v>27</v>
+      </c>
+      <c r="G576" t="s">
+        <v>743</v>
+      </c>
+      <c r="H576" t="s">
+        <v>26</v>
+      </c>
+      <c r="I576" t="n">
+        <v>74</v>
+      </c>
+      <c r="J576"/>
+      <c r="K576" s="1"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="n">
+        <v>46268.7208333333</v>
+      </c>
+      <c r="B577" t="n">
+        <v>4616003</v>
+      </c>
+      <c r="C577" t="s">
+        <v>646</v>
+      </c>
+      <c r="D577" t="s">
+        <v>128</v>
+      </c>
+      <c r="E577" t="s">
+        <v>629</v>
+      </c>
+      <c r="F577" t="s">
+        <v>18</v>
+      </c>
+      <c r="G577" t="s">
+        <v>744</v>
+      </c>
+      <c r="H577" t="s">
+        <v>195</v>
+      </c>
+      <c r="I577" t="n">
+        <v>76</v>
+      </c>
+      <c r="J577"/>
+      <c r="K577" s="1"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="n">
+        <v>46268.7215277778</v>
+      </c>
+      <c r="B578" t="n">
+        <v>4616049</v>
+      </c>
+      <c r="C578" t="s">
+        <v>670</v>
+      </c>
+      <c r="D578" t="s">
+        <v>56</v>
+      </c>
+      <c r="E578" t="s">
+        <v>629</v>
+      </c>
+      <c r="F578" t="s">
+        <v>27</v>
+      </c>
+      <c r="G578" t="s">
+        <v>745</v>
+      </c>
+      <c r="H578" t="s">
+        <v>629</v>
+      </c>
+      <c r="I578" t="n">
+        <v>83</v>
+      </c>
+      <c r="J578"/>
+      <c r="K578" s="1"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="n">
+        <v>46268.7215277778</v>
+      </c>
+      <c r="B579" t="n">
+        <v>4615945</v>
+      </c>
+      <c r="C579" t="s">
+        <v>695</v>
+      </c>
+      <c r="D579" t="s">
+        <v>30</v>
+      </c>
+      <c r="E579" t="s">
+        <v>652</v>
+      </c>
+      <c r="F579" t="s">
+        <v>27</v>
+      </c>
+      <c r="G579" t="s">
+        <v>746</v>
+      </c>
+      <c r="H579" t="s">
+        <v>26</v>
+      </c>
+      <c r="I579" t="n">
+        <v>61</v>
+      </c>
+      <c r="J579"/>
+      <c r="K579" s="1"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="n">
+        <v>46268.7215277778</v>
+      </c>
+      <c r="B580" t="n">
+        <v>4616055</v>
+      </c>
+      <c r="C580" t="s">
+        <v>747</v>
+      </c>
+      <c r="D580" t="s">
+        <v>65</v>
+      </c>
+      <c r="E580" t="s">
+        <v>652</v>
+      </c>
+      <c r="F580" t="s">
+        <v>27</v>
+      </c>
+      <c r="G580" t="s">
+        <v>748</v>
+      </c>
+      <c r="H580" t="s">
+        <v>26</v>
+      </c>
+      <c r="I580" t="n">
+        <v>94</v>
+      </c>
+      <c r="J580"/>
+      <c r="K580" s="1"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="n">
+        <v>46268.7222222222</v>
+      </c>
+      <c r="B581" t="n">
+        <v>4615943</v>
+      </c>
+      <c r="C581" t="s">
+        <v>662</v>
+      </c>
+      <c r="D581" t="s">
+        <v>30</v>
+      </c>
+      <c r="E581" t="s">
+        <v>652</v>
+      </c>
+      <c r="F581" t="s">
+        <v>19</v>
+      </c>
+      <c r="G581" t="s">
+        <v>749</v>
+      </c>
+      <c r="H581" t="s">
+        <v>26</v>
+      </c>
+      <c r="I581" t="n">
+        <v>62</v>
+      </c>
+      <c r="J581"/>
+      <c r="K581" s="1"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="n">
+        <v>46268.73125</v>
+      </c>
+      <c r="B582" t="n">
+        <v>4615655</v>
+      </c>
+      <c r="C582" t="s">
+        <v>134</v>
+      </c>
+      <c r="D582" t="s">
+        <v>65</v>
+      </c>
+      <c r="E582" t="s">
+        <v>652</v>
+      </c>
+      <c r="F582" t="s">
+        <v>34</v>
+      </c>
+      <c r="G582" t="s">
+        <v>750</v>
+      </c>
+      <c r="H582" t="s">
+        <v>50</v>
+      </c>
+      <c r="I582" t="n">
+        <v>3</v>
+      </c>
+      <c r="J582"/>
+      <c r="K582" s="1" t="n">
+        <v>46268</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="n">
+        <v>46268.73125</v>
+      </c>
+      <c r="B583" t="n">
+        <v>4615145</v>
+      </c>
+      <c r="C583" t="s">
+        <v>87</v>
+      </c>
+      <c r="D583" t="s">
+        <v>30</v>
+      </c>
+      <c r="E583" t="s">
+        <v>652</v>
+      </c>
+      <c r="F583" t="s">
+        <v>27</v>
+      </c>
+      <c r="G583" t="s">
+        <v>751</v>
+      </c>
+      <c r="H583" t="s">
+        <v>26</v>
+      </c>
+      <c r="I583" t="n">
+        <v>8</v>
+      </c>
+      <c r="J583"/>
+      <c r="K583" s="1"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="n">
+        <v>46268.7319444444</v>
+      </c>
+      <c r="B584" t="n">
+        <v>4615971</v>
+      </c>
+      <c r="C584" t="s">
+        <v>655</v>
+      </c>
+      <c r="D584" t="s">
+        <v>53</v>
+      </c>
+      <c r="E584" t="s">
+        <v>652</v>
+      </c>
+      <c r="F584" t="s">
+        <v>18</v>
+      </c>
+      <c r="G584" t="s">
+        <v>656</v>
+      </c>
+      <c r="H584" t="s">
+        <v>26</v>
+      </c>
+      <c r="I584" t="n">
+        <v>45</v>
+      </c>
+      <c r="J584"/>
+      <c r="K584" s="1"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="n">
+        <v>46268.7493055556</v>
+      </c>
+      <c r="B585" t="n">
+        <v>4614161</v>
+      </c>
+      <c r="C585" t="s">
+        <v>144</v>
+      </c>
+      <c r="D585" t="s">
+        <v>123</v>
+      </c>
+      <c r="E585" t="s">
+        <v>636</v>
+      </c>
+      <c r="F585" t="s">
+        <v>14</v>
+      </c>
+      <c r="G585" t="s">
+        <v>637</v>
+      </c>
+      <c r="H585" t="s">
+        <v>50</v>
+      </c>
+      <c r="I585" t="n">
+        <v>10</v>
+      </c>
+      <c r="J585"/>
+      <c r="K585" s="1" t="n">
+        <v>46271</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="n">
+        <v>46268.75</v>
+      </c>
+      <c r="B586" t="n">
+        <v>4615925</v>
+      </c>
+      <c r="C586" t="s">
+        <v>567</v>
+      </c>
+      <c r="D586" t="s">
+        <v>497</v>
+      </c>
+      <c r="E586" t="s">
+        <v>636</v>
+      </c>
+      <c r="F586" t="s">
+        <v>39</v>
+      </c>
+      <c r="G586" t="s">
+        <v>752</v>
+      </c>
+      <c r="H586" t="s">
+        <v>195</v>
+      </c>
+      <c r="I586" t="n">
+        <v>28</v>
+      </c>
+      <c r="J586"/>
+      <c r="K586" s="1" t="n">
+        <v>46275</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="n">
+        <v>46268.7527777778</v>
+      </c>
+      <c r="B587" t="n">
+        <v>4616029</v>
+      </c>
+      <c r="C587" t="s">
+        <v>722</v>
+      </c>
+      <c r="D587" t="s">
+        <v>178</v>
+      </c>
+      <c r="E587" t="s">
+        <v>631</v>
+      </c>
+      <c r="F587" t="s">
+        <v>18</v>
+      </c>
+      <c r="G587" t="s">
+        <v>753</v>
+      </c>
+      <c r="H587" t="s">
+        <v>50</v>
+      </c>
+      <c r="I587" t="n">
+        <v>78</v>
+      </c>
+      <c r="J587"/>
+      <c r="K587" s="1"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="n">
+        <v>46268.7527777778</v>
+      </c>
+      <c r="B588" t="n">
+        <v>4615963</v>
+      </c>
+      <c r="C588" t="s">
+        <v>437</v>
+      </c>
+      <c r="D588" t="s">
+        <v>53</v>
+      </c>
+      <c r="E588" t="s">
+        <v>652</v>
+      </c>
+      <c r="F588" t="s">
+        <v>19</v>
+      </c>
+      <c r="G588" t="s">
+        <v>754</v>
+      </c>
+      <c r="H588" t="s">
+        <v>26</v>
+      </c>
+      <c r="I588" t="n">
+        <v>49</v>
+      </c>
+      <c r="J588"/>
+      <c r="K588" s="1"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="n">
+        <v>46268.7534722222</v>
+      </c>
+      <c r="B589" t="n">
+        <v>4615981</v>
+      </c>
+      <c r="C589" t="s">
+        <v>755</v>
+      </c>
+      <c r="D589" t="s">
+        <v>53</v>
+      </c>
+      <c r="E589" t="s">
+        <v>652</v>
+      </c>
+      <c r="F589" t="s">
+        <v>23</v>
+      </c>
+      <c r="G589" t="s">
+        <v>756</v>
+      </c>
+      <c r="H589" t="s">
+        <v>26</v>
+      </c>
+      <c r="I589" t="n">
+        <v>43</v>
+      </c>
+      <c r="J589"/>
+      <c r="K589" s="1"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="n">
+        <v>46268.7666666667</v>
+      </c>
+      <c r="B590" t="n">
+        <v>4615994</v>
+      </c>
+      <c r="C590" t="s">
+        <v>730</v>
+      </c>
+      <c r="D590" t="s">
+        <v>38</v>
+      </c>
+      <c r="E590" t="s">
+        <v>251</v>
+      </c>
+      <c r="F590" t="s">
+        <v>18</v>
+      </c>
+      <c r="G590" t="s">
+        <v>757</v>
+      </c>
+      <c r="H590" t="s">
+        <v>13</v>
+      </c>
+      <c r="I590" t="n">
+        <v>210</v>
+      </c>
+      <c r="J590"/>
+      <c r="K590" s="1"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="n">
+        <v>46268.7666666667</v>
+      </c>
+      <c r="B591" t="n">
+        <v>4615994</v>
+      </c>
+      <c r="C591" t="s">
+        <v>730</v>
+      </c>
+      <c r="D591" t="s">
+        <v>38</v>
+      </c>
+      <c r="E591" t="s">
+        <v>251</v>
+      </c>
+      <c r="F591" t="s">
+        <v>18</v>
+      </c>
+      <c r="G591" t="s">
+        <v>757</v>
+      </c>
+      <c r="H591" t="s">
+        <v>13</v>
+      </c>
+      <c r="I591" t="n">
+        <v>210</v>
+      </c>
+      <c r="J591"/>
+      <c r="K591" s="1"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="n">
+        <v>46268.7708333333</v>
+      </c>
+      <c r="B592" t="n">
+        <v>4616038</v>
+      </c>
+      <c r="C592" t="s">
+        <v>758</v>
+      </c>
+      <c r="D592" t="s">
+        <v>56</v>
+      </c>
+      <c r="E592" t="s">
+        <v>629</v>
+      </c>
+      <c r="F592" t="s">
+        <v>23</v>
+      </c>
+      <c r="G592" t="s">
+        <v>759</v>
+      </c>
+      <c r="H592" t="s">
+        <v>629</v>
+      </c>
+      <c r="I592" t="n">
+        <v>97</v>
+      </c>
+      <c r="J592"/>
+      <c r="K592" s="1"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="n">
+        <v>46268.7708333333</v>
+      </c>
+      <c r="B593" t="n">
+        <v>4616031</v>
+      </c>
+      <c r="C593" t="s">
+        <v>760</v>
+      </c>
+      <c r="D593" t="s">
+        <v>128</v>
+      </c>
+      <c r="E593" t="s">
+        <v>629</v>
+      </c>
+      <c r="F593" t="s">
+        <v>23</v>
+      </c>
+      <c r="G593" t="s">
+        <v>761</v>
+      </c>
+      <c r="H593" t="s">
+        <v>629</v>
+      </c>
+      <c r="I593" t="n">
+        <v>90</v>
+      </c>
+      <c r="J593"/>
+      <c r="K593" s="1"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="n">
+        <v>46268.7708333333</v>
+      </c>
+      <c r="B594" t="n">
+        <v>4615957</v>
+      </c>
+      <c r="C594" t="s">
+        <v>625</v>
+      </c>
+      <c r="D594" t="s">
+        <v>49</v>
+      </c>
+      <c r="E594" t="s">
+        <v>629</v>
+      </c>
+      <c r="F594" t="s">
+        <v>18</v>
+      </c>
+      <c r="G594" t="s">
+        <v>762</v>
+      </c>
+      <c r="H594" t="s">
+        <v>629</v>
+      </c>
+      <c r="I594" t="n">
+        <v>54</v>
+      </c>
+      <c r="J594"/>
+      <c r="K594" s="1"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="n">
+        <v>46268.7770833333</v>
+      </c>
+      <c r="B595" t="n">
+        <v>4615958</v>
+      </c>
+      <c r="C595" t="s">
+        <v>619</v>
+      </c>
+      <c r="D595" t="s">
+        <v>49</v>
+      </c>
+      <c r="E595" t="s">
+        <v>629</v>
+      </c>
+      <c r="F595" t="s">
+        <v>14</v>
+      </c>
+      <c r="G595" t="s">
+        <v>648</v>
+      </c>
+      <c r="H595" t="s">
+        <v>195</v>
+      </c>
+      <c r="I595" t="n">
+        <v>53</v>
+      </c>
+      <c r="J595"/>
+      <c r="K595" s="1"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="n">
+        <v>46268.8020833333</v>
+      </c>
+      <c r="B596" t="n">
+        <v>4616031</v>
+      </c>
+      <c r="C596" t="s">
+        <v>760</v>
+      </c>
+      <c r="D596" t="s">
+        <v>128</v>
+      </c>
+      <c r="E596" t="s">
+        <v>629</v>
+      </c>
+      <c r="F596" t="s">
+        <v>23</v>
+      </c>
+      <c r="G596" t="s">
+        <v>763</v>
+      </c>
+      <c r="H596" t="s">
+        <v>629</v>
+      </c>
+      <c r="I596" t="n">
+        <v>90</v>
+      </c>
+      <c r="J596"/>
+      <c r="K596" s="1"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="n">
+        <v>46269.325</v>
+      </c>
+      <c r="B597" t="n">
+        <v>4616031</v>
+      </c>
+      <c r="C597" t="s">
+        <v>760</v>
+      </c>
+      <c r="D597" t="s">
+        <v>128</v>
+      </c>
+      <c r="E597" t="s">
+        <v>629</v>
+      </c>
+      <c r="F597" t="s">
+        <v>19</v>
+      </c>
+      <c r="G597" t="s">
+        <v>764</v>
+      </c>
+      <c r="H597" t="s">
+        <v>629</v>
+      </c>
+      <c r="I597" t="n">
+        <v>90</v>
+      </c>
+      <c r="J597"/>
+      <c r="K597" s="1"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="n">
+        <v>46269.3305555556</v>
+      </c>
+      <c r="B598" t="n">
+        <v>4615934</v>
+      </c>
+      <c r="C598" t="s">
+        <v>689</v>
+      </c>
+      <c r="D598" t="s">
+        <v>152</v>
+      </c>
+      <c r="E598" t="s">
+        <v>636</v>
+      </c>
+      <c r="F598" t="s">
+        <v>18</v>
+      </c>
+      <c r="G598" t="s">
+        <v>765</v>
+      </c>
+      <c r="H598" t="s">
+        <v>50</v>
+      </c>
+      <c r="I598" t="n">
+        <v>67</v>
+      </c>
+      <c r="J598"/>
+      <c r="K598" s="1"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="n">
+        <v>46269.3319444444</v>
+      </c>
+      <c r="B599" t="n">
+        <v>4615985</v>
+      </c>
+      <c r="C599" t="s">
+        <v>683</v>
+      </c>
+      <c r="D599" t="s">
+        <v>275</v>
+      </c>
+      <c r="E599" t="s">
+        <v>636</v>
+      </c>
+      <c r="F599" t="s">
+        <v>18</v>
+      </c>
+      <c r="G599" t="s">
+        <v>766</v>
+      </c>
+      <c r="H599" t="s">
+        <v>50</v>
+      </c>
+      <c r="I599" t="n">
+        <v>41</v>
+      </c>
+      <c r="J599"/>
+      <c r="K599" s="1"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="n">
+        <v>46269.3326388889</v>
+      </c>
+      <c r="B600" t="n">
+        <v>4615939</v>
+      </c>
+      <c r="C600" t="s">
+        <v>741</v>
+      </c>
+      <c r="D600" t="s">
+        <v>152</v>
+      </c>
+      <c r="E600" t="s">
+        <v>636</v>
+      </c>
+      <c r="F600" t="s">
+        <v>27</v>
+      </c>
+      <c r="G600" t="s">
+        <v>767</v>
+      </c>
+      <c r="H600" t="s">
+        <v>26</v>
+      </c>
+      <c r="I600" t="n">
+        <v>65</v>
+      </c>
+      <c r="J600"/>
+      <c r="K600" s="1"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="n">
+        <v>46269.3333333333</v>
+      </c>
+      <c r="B601" t="n">
+        <v>4615937</v>
+      </c>
+      <c r="C601" t="s">
+        <v>691</v>
+      </c>
+      <c r="D601" t="s">
+        <v>497</v>
+      </c>
+      <c r="E601" t="s">
+        <v>636</v>
+      </c>
+      <c r="F601" t="s">
+        <v>18</v>
+      </c>
+      <c r="G601" t="s">
+        <v>768</v>
+      </c>
+      <c r="H601" t="s">
+        <v>50</v>
+      </c>
+      <c r="I601" t="n">
+        <v>66</v>
+      </c>
+      <c r="J601"/>
+      <c r="K601" s="1"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="n">
+        <v>46269.3354166667</v>
+      </c>
+      <c r="B602" t="n">
+        <v>4615933</v>
+      </c>
+      <c r="C602" t="s">
+        <v>693</v>
+      </c>
+      <c r="D602" t="s">
+        <v>275</v>
+      </c>
+      <c r="E602" t="s">
+        <v>636</v>
+      </c>
+      <c r="F602" t="s">
+        <v>27</v>
+      </c>
+      <c r="G602" t="s">
+        <v>769</v>
+      </c>
+      <c r="H602" t="s">
+        <v>50</v>
+      </c>
+      <c r="I602" t="n">
+        <v>68</v>
+      </c>
+      <c r="J602"/>
+      <c r="K602" s="1" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="n">
+        <v>46269.3361111111</v>
+      </c>
+      <c r="B603" t="n">
+        <v>4615933</v>
+      </c>
+      <c r="C603" t="s">
+        <v>693</v>
+      </c>
+      <c r="D603" t="s">
+        <v>275</v>
+      </c>
+      <c r="E603" t="s">
+        <v>636</v>
+      </c>
+      <c r="F603" t="s">
+        <v>34</v>
+      </c>
+      <c r="G603" t="s">
+        <v>769</v>
+      </c>
+      <c r="H603" t="s">
+        <v>50</v>
+      </c>
+      <c r="I603" t="n">
+        <v>68</v>
+      </c>
+      <c r="J603"/>
+      <c r="K603" s="1" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="n">
+        <v>46269.3368055556</v>
+      </c>
+      <c r="B604" t="n">
+        <v>4615930</v>
+      </c>
+      <c r="C604" t="s">
+        <v>710</v>
+      </c>
+      <c r="D604" t="s">
+        <v>275</v>
+      </c>
+      <c r="E604" t="s">
+        <v>636</v>
+      </c>
+      <c r="F604" t="s">
+        <v>18</v>
+      </c>
+      <c r="G604" t="s">
+        <v>770</v>
+      </c>
+      <c r="H604" t="s">
+        <v>50</v>
+      </c>
+      <c r="I604" t="n">
+        <v>70</v>
+      </c>
+      <c r="J604"/>
+      <c r="K604" s="1"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="1" t="n">
+        <v>46269.3381944444</v>
+      </c>
+      <c r="B605" t="n">
+        <v>4616017</v>
+      </c>
+      <c r="C605" t="s">
+        <v>700</v>
+      </c>
+      <c r="D605" t="s">
+        <v>75</v>
+      </c>
+      <c r="E605" t="s">
+        <v>674</v>
+      </c>
+      <c r="F605" t="s">
+        <v>18</v>
+      </c>
+      <c r="G605" t="s">
+        <v>728</v>
+      </c>
+      <c r="H605" t="s">
+        <v>26</v>
+      </c>
+      <c r="I605" t="n">
+        <v>32</v>
+      </c>
+      <c r="J605"/>
+      <c r="K605" s="1"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="n">
+        <v>46269.3388888889</v>
+      </c>
+      <c r="B606" t="n">
+        <v>4616040</v>
+      </c>
+      <c r="C606" t="s">
+        <v>771</v>
+      </c>
+      <c r="D606" t="s">
+        <v>178</v>
+      </c>
+      <c r="E606" t="s">
+        <v>631</v>
+      </c>
+      <c r="F606" t="s">
+        <v>19</v>
+      </c>
+      <c r="G606" t="s">
+        <v>772</v>
+      </c>
+      <c r="H606" t="s">
+        <v>50</v>
+      </c>
+      <c r="I606" t="n">
+        <v>100</v>
+      </c>
+      <c r="J606"/>
+      <c r="K606" s="1"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="n">
+        <v>46269.3409722222</v>
+      </c>
+      <c r="B607" t="n">
+        <v>4616008</v>
+      </c>
+      <c r="C607" t="s">
+        <v>703</v>
+      </c>
+      <c r="D607" t="s">
+        <v>30</v>
+      </c>
+      <c r="E607" t="s">
+        <v>652</v>
+      </c>
+      <c r="F607" t="s">
+        <v>18</v>
+      </c>
+      <c r="G607" t="s">
+        <v>773</v>
+      </c>
+      <c r="H607" t="s">
+        <v>26</v>
+      </c>
+      <c r="I607" t="n">
+        <v>81</v>
+      </c>
+      <c r="J607"/>
+      <c r="K607" s="1"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="n">
+        <v>46269.3416666667</v>
+      </c>
+      <c r="B608" t="n">
+        <v>4615941</v>
+      </c>
+      <c r="C608" t="s">
+        <v>664</v>
+      </c>
+      <c r="D608" t="s">
+        <v>53</v>
+      </c>
+      <c r="E608" t="s">
+        <v>652</v>
+      </c>
+      <c r="F608" t="s">
+        <v>18</v>
+      </c>
+      <c r="G608"/>
+      <c r="H608" t="s">
+        <v>26</v>
+      </c>
+      <c r="I608" t="n">
+        <v>63</v>
+      </c>
+      <c r="J608"/>
+      <c r="K608" s="1"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="n">
+        <v>46269.3444444444</v>
+      </c>
+      <c r="B609" t="n">
+        <v>4616024</v>
+      </c>
+      <c r="C609" t="s">
+        <v>724</v>
+      </c>
+      <c r="D609" t="s">
+        <v>152</v>
+      </c>
+      <c r="E609" t="s">
+        <v>636</v>
+      </c>
+      <c r="F609" t="s">
+        <v>18</v>
+      </c>
+      <c r="G609" t="s">
+        <v>774</v>
+      </c>
+      <c r="H609" t="s">
+        <v>50</v>
+      </c>
+      <c r="I609" t="n">
+        <v>80</v>
+      </c>
+      <c r="J609"/>
+      <c r="K609" s="1"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="n">
+        <v>46269.3479166667</v>
+      </c>
+      <c r="B610" t="n">
+        <v>4616051</v>
+      </c>
+      <c r="C610" t="s">
+        <v>775</v>
+      </c>
+      <c r="D610" t="s">
+        <v>96</v>
+      </c>
+      <c r="E610" t="s">
+        <v>634</v>
+      </c>
+      <c r="F610" t="s">
+        <v>19</v>
+      </c>
+      <c r="G610" t="s">
+        <v>776</v>
+      </c>
+      <c r="H610" t="s">
+        <v>26</v>
+      </c>
+      <c r="I610" t="n">
+        <v>88</v>
+      </c>
+      <c r="J610"/>
+      <c r="K610" s="1"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="n">
+        <v>46269.3479166667</v>
+      </c>
+      <c r="B611" t="n">
+        <v>4615948</v>
+      </c>
+      <c r="C611" t="s">
+        <v>660</v>
+      </c>
+      <c r="D611" t="s">
+        <v>53</v>
+      </c>
+      <c r="E611" t="s">
+        <v>652</v>
+      </c>
+      <c r="F611" t="s">
+        <v>18</v>
+      </c>
+      <c r="G611" t="s">
+        <v>777</v>
+      </c>
+      <c r="H611" t="s">
+        <v>26</v>
+      </c>
+      <c r="I611" t="n">
+        <v>60</v>
+      </c>
+      <c r="J611"/>
+      <c r="K611" s="1"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="n">
+        <v>46269.3506944444</v>
+      </c>
+      <c r="B612" t="n">
+        <v>4615903</v>
+      </c>
+      <c r="C612" t="s">
+        <v>667</v>
+      </c>
+      <c r="D612" t="s">
+        <v>21</v>
+      </c>
+      <c r="E612" t="s">
+        <v>652</v>
+      </c>
+      <c r="F612" t="s">
+        <v>27</v>
+      </c>
+      <c r="G612" t="s">
+        <v>778</v>
+      </c>
+      <c r="H612" t="s">
+        <v>26</v>
+      </c>
+      <c r="I612" t="n">
+        <v>73</v>
+      </c>
+      <c r="J612"/>
+      <c r="K612" s="1"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="n">
+        <v>46269.3527777778</v>
+      </c>
+      <c r="B613" t="n">
+        <v>4616050</v>
+      </c>
+      <c r="C613" t="s">
+        <v>779</v>
+      </c>
+      <c r="D613" t="s">
+        <v>96</v>
+      </c>
+      <c r="E613" t="s">
+        <v>634</v>
+      </c>
+      <c r="F613" t="s">
+        <v>19</v>
+      </c>
+      <c r="G613"/>
+      <c r="H613" t="s">
+        <v>26</v>
+      </c>
+      <c r="I613" t="n">
+        <v>82</v>
+      </c>
+      <c r="J613"/>
+      <c r="K613" s="1"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="n">
+        <v>46269.3548611111</v>
+      </c>
+      <c r="B614" t="n">
+        <v>4615579</v>
+      </c>
+      <c r="C614" t="s">
+        <v>156</v>
+      </c>
+      <c r="D614" t="s">
+        <v>118</v>
+      </c>
+      <c r="E614" t="s">
+        <v>629</v>
+      </c>
+      <c r="F614" t="s">
+        <v>39</v>
+      </c>
+      <c r="G614" t="s">
+        <v>780</v>
+      </c>
+      <c r="H614" t="s">
+        <v>195</v>
+      </c>
+      <c r="I614" t="n">
+        <v>5</v>
+      </c>
+      <c r="J614"/>
+      <c r="K614" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -19966,13 +22202,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>706</v>
+        <v>781</v>
       </c>
       <c r="B1" t="s">
-        <v>707</v>
+        <v>782</v>
       </c>
       <c r="C1" t="s">
-        <v>708</v>
+        <v>783</v>
       </c>
     </row>
     <row r="2">
@@ -20038,6 +22274,17 @@
         <v>68</v>
       </c>
       <c r="C7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B8" t="n">
+        <v>61</v>
+      </c>
+      <c r="C8" t="n">
         <v>2</v>
       </c>
     </row>
